--- a/artfynd/A 61338-2024 artfynd.xlsx
+++ b/artfynd/A 61338-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567315</v>
+        <v>122566981</v>
       </c>
       <c r="B2" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488773</v>
+        <v>488599</v>
       </c>
       <c r="R2" t="n">
-        <v>6786561</v>
+        <v>6786673</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122566996</v>
+        <v>122566958</v>
       </c>
       <c r="B3" t="n">
         <v>78656</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488757</v>
+        <v>488301</v>
       </c>
       <c r="R3" t="n">
-        <v>6786723</v>
+        <v>6786839</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122566997</v>
+        <v>122567004</v>
       </c>
       <c r="B4" t="n">
         <v>78656</v>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488731</v>
+        <v>488475</v>
       </c>
       <c r="R4" t="n">
-        <v>6786733</v>
+        <v>6786864</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567310</v>
+        <v>122566997</v>
       </c>
       <c r="B5" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,43 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488294</v>
+        <v>488731</v>
       </c>
       <c r="R5" t="n">
-        <v>6786825</v>
+        <v>6786733</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566894</v>
+        <v>122566966</v>
       </c>
       <c r="B6" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488182</v>
+        <v>488390</v>
       </c>
       <c r="R6" t="n">
-        <v>6787001</v>
+        <v>6786813</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566984</v>
+        <v>122567022</v>
       </c>
       <c r="B7" t="n">
         <v>78656</v>
@@ -1235,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488699</v>
+        <v>488137</v>
       </c>
       <c r="R7" t="n">
-        <v>6786596</v>
+        <v>6787026</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566990</v>
+        <v>122567320</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,38 +1299,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488840</v>
+        <v>488833</v>
       </c>
       <c r="R8" t="n">
-        <v>6786622</v>
+        <v>6786674</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566909</v>
+        <v>122566974</v>
       </c>
       <c r="B9" t="n">
-        <v>91264</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488882</v>
+        <v>488486</v>
       </c>
       <c r="R9" t="n">
-        <v>6786607</v>
+        <v>6786718</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566972</v>
+        <v>122566969</v>
       </c>
       <c r="B10" t="n">
         <v>78656</v>
@@ -1541,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488465</v>
+        <v>488452</v>
       </c>
       <c r="R10" t="n">
-        <v>6786729</v>
+        <v>6786772</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567313</v>
+        <v>122566985</v>
       </c>
       <c r="B11" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,43 +1610,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488616</v>
+        <v>488698</v>
       </c>
       <c r="R11" t="n">
-        <v>6786649</v>
+        <v>6786584</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566987</v>
+        <v>122566903</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>90859</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488735</v>
+        <v>488770</v>
       </c>
       <c r="R12" t="n">
-        <v>6786569</v>
+        <v>6786732</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566991</v>
+        <v>122566952</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>80613</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488918</v>
+        <v>488363</v>
       </c>
       <c r="R13" t="n">
-        <v>6786607</v>
+        <v>6786907</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566954</v>
+        <v>122567324</v>
       </c>
       <c r="B14" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1926,38 +1916,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488416</v>
+        <v>488638</v>
       </c>
       <c r="R14" t="n">
-        <v>6786896</v>
+        <v>6786764</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567009</v>
+        <v>122567291</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,38 +2023,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488465</v>
+        <v>488440</v>
       </c>
       <c r="R15" t="n">
-        <v>6786880</v>
+        <v>6786759</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567025</v>
+        <v>122567006</v>
       </c>
       <c r="B16" t="n">
-        <v>78301</v>
+        <v>78656</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2134,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488378</v>
+        <v>488556</v>
       </c>
       <c r="R16" t="n">
-        <v>6786805</v>
+        <v>6786835</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,7 +2220,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566961</v>
+        <v>122567015</v>
       </c>
       <c r="B17" t="n">
         <v>78656</v>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488327</v>
+        <v>488366</v>
       </c>
       <c r="R17" t="n">
-        <v>6786847</v>
+        <v>6786907</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,7 +2322,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567004</v>
+        <v>122566983</v>
       </c>
       <c r="B18" t="n">
         <v>78656</v>
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488475</v>
+        <v>488609</v>
       </c>
       <c r="R18" t="n">
-        <v>6786864</v>
+        <v>6786648</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122567022</v>
+        <v>122566913</v>
       </c>
       <c r="B19" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2440,34 +2440,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488137</v>
+        <v>488602</v>
       </c>
       <c r="R19" t="n">
-        <v>6787026</v>
+        <v>6786666</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2500,6 +2505,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2526,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566967</v>
+        <v>122566904</v>
       </c>
       <c r="B20" t="n">
-        <v>78656</v>
+        <v>90859</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2542,21 +2552,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2566,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488387</v>
+        <v>488552</v>
       </c>
       <c r="R20" t="n">
-        <v>6786773</v>
+        <v>6786834</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,7 +2638,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566981</v>
+        <v>122566964</v>
       </c>
       <c r="B21" t="n">
         <v>78656</v>
@@ -2668,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488599</v>
+        <v>488351</v>
       </c>
       <c r="R21" t="n">
-        <v>6786673</v>
+        <v>6786831</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,7 +2740,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566975</v>
+        <v>122566971</v>
       </c>
       <c r="B22" t="n">
         <v>78656</v>
@@ -2770,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488515</v>
+        <v>488461</v>
       </c>
       <c r="R22" t="n">
-        <v>6786685</v>
+        <v>6786736</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567014</v>
+        <v>122566908</v>
       </c>
       <c r="B23" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2848,34 +2858,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488383</v>
+        <v>488892</v>
       </c>
       <c r="R23" t="n">
-        <v>6786912</v>
+        <v>6786620</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2934,10 +2953,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566952</v>
+        <v>122566912</v>
       </c>
       <c r="B24" t="n">
-        <v>80613</v>
+        <v>91123</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2950,21 +2969,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1049</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2974,10 +2993,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488363</v>
+        <v>488895</v>
       </c>
       <c r="R24" t="n">
-        <v>6786907</v>
+        <v>6786588</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3036,10 +3055,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566973</v>
+        <v>122566901</v>
       </c>
       <c r="B25" t="n">
-        <v>78656</v>
+        <v>57536</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3052,21 +3071,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3076,10 +3095,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488482</v>
+        <v>488142</v>
       </c>
       <c r="R25" t="n">
-        <v>6786720</v>
+        <v>6787017</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3138,10 +3157,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566979</v>
+        <v>122567319</v>
       </c>
       <c r="B26" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3150,38 +3169,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488583</v>
+        <v>488869</v>
       </c>
       <c r="R26" t="n">
-        <v>6786676</v>
+        <v>6786685</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3240,7 +3264,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122567324</v>
+        <v>122567289</v>
       </c>
       <c r="B27" t="n">
         <v>8441</v>
@@ -3276,7 +3300,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3285,10 +3309,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488638</v>
+        <v>488322</v>
       </c>
       <c r="R27" t="n">
-        <v>6786764</v>
+        <v>6786810</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3347,10 +3371,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122566985</v>
+        <v>122567307</v>
       </c>
       <c r="B28" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3359,38 +3383,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488698</v>
+        <v>488535</v>
       </c>
       <c r="R28" t="n">
-        <v>6786584</v>
+        <v>6786843</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3449,10 +3478,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567010</v>
+        <v>122567303</v>
       </c>
       <c r="B29" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3461,38 +3490,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488442</v>
+        <v>488600</v>
       </c>
       <c r="R29" t="n">
-        <v>6786881</v>
+        <v>6786772</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,10 +3585,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567018</v>
+        <v>122567318</v>
       </c>
       <c r="B30" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3563,38 +3597,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488345</v>
+        <v>488883</v>
       </c>
       <c r="R30" t="n">
-        <v>6786910</v>
+        <v>6786645</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3653,10 +3692,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567317</v>
+        <v>122566905</v>
       </c>
       <c r="B31" t="n">
-        <v>8441</v>
+        <v>57399</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3665,31 +3704,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3698,10 +3737,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488892</v>
+        <v>488294</v>
       </c>
       <c r="R31" t="n">
-        <v>6786620</v>
+        <v>6786826</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3760,10 +3799,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122567319</v>
+        <v>122566897</v>
       </c>
       <c r="B32" t="n">
-        <v>8441</v>
+        <v>90839</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3772,43 +3811,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488869</v>
+        <v>488892</v>
       </c>
       <c r="R32" t="n">
-        <v>6786685</v>
+        <v>6786591</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3867,10 +3901,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122566999</v>
+        <v>122567027</v>
       </c>
       <c r="B33" t="n">
-        <v>78656</v>
+        <v>78301</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3883,21 +3917,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3907,10 +3941,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488686</v>
+        <v>488618</v>
       </c>
       <c r="R33" t="n">
-        <v>6786738</v>
+        <v>6786631</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3969,7 +4003,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567316</v>
+        <v>122567325</v>
       </c>
       <c r="B34" t="n">
         <v>8441</v>
@@ -4014,10 +4048,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488900</v>
+        <v>488576</v>
       </c>
       <c r="R34" t="n">
-        <v>6786628</v>
+        <v>6786782</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4076,7 +4110,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122567003</v>
+        <v>122566980</v>
       </c>
       <c r="B35" t="n">
         <v>78656</v>
@@ -4116,10 +4150,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488550</v>
+        <v>488590</v>
       </c>
       <c r="R35" t="n">
-        <v>6786822</v>
+        <v>6786665</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4178,10 +4212,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122567026</v>
+        <v>122566970</v>
       </c>
       <c r="B36" t="n">
-        <v>78301</v>
+        <v>78656</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4194,21 +4228,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4218,10 +4252,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488539</v>
+        <v>488469</v>
       </c>
       <c r="R36" t="n">
-        <v>6786689</v>
+        <v>6786751</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4280,10 +4314,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122567290</v>
+        <v>122566965</v>
       </c>
       <c r="B37" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4292,43 +4326,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488345</v>
+        <v>488378</v>
       </c>
       <c r="R37" t="n">
-        <v>6786796</v>
+        <v>6786805</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4387,7 +4416,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122566959</v>
+        <v>122566976</v>
       </c>
       <c r="B38" t="n">
         <v>78656</v>
@@ -4427,10 +4456,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488317</v>
+        <v>488515</v>
       </c>
       <c r="R38" t="n">
-        <v>6786858</v>
+        <v>6786685</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4489,7 +4518,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122566965</v>
+        <v>122566968</v>
       </c>
       <c r="B39" t="n">
         <v>78656</v>
@@ -4529,10 +4558,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488378</v>
+        <v>488431</v>
       </c>
       <c r="R39" t="n">
-        <v>6786805</v>
+        <v>6786772</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4591,10 +4620,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122567303</v>
+        <v>122566984</v>
       </c>
       <c r="B40" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4603,43 +4632,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488600</v>
+        <v>488699</v>
       </c>
       <c r="R40" t="n">
-        <v>6786772</v>
+        <v>6786596</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4698,10 +4722,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122566908</v>
+        <v>122566954</v>
       </c>
       <c r="B41" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4714,43 +4738,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488892</v>
+        <v>488416</v>
       </c>
       <c r="R41" t="n">
-        <v>6786620</v>
+        <v>6786896</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4809,10 +4824,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567314</v>
+        <v>122566960</v>
       </c>
       <c r="B42" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4821,43 +4836,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488747</v>
+        <v>488322</v>
       </c>
       <c r="R42" t="n">
-        <v>6786566</v>
+        <v>6786853</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4916,10 +4926,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567012</v>
+        <v>122567029</v>
       </c>
       <c r="B43" t="n">
-        <v>78656</v>
+        <v>78301</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4932,21 +4942,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4956,10 +4966,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488420</v>
+        <v>488664</v>
       </c>
       <c r="R43" t="n">
-        <v>6786898</v>
+        <v>6786615</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5018,10 +5028,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122566889</v>
+        <v>122567030</v>
       </c>
       <c r="B44" t="n">
-        <v>79274</v>
+        <v>78301</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5034,21 +5044,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5058,10 +5068,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488296</v>
+        <v>488769</v>
       </c>
       <c r="R44" t="n">
-        <v>6786844</v>
+        <v>6786552</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5120,10 +5130,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122567291</v>
+        <v>122566978</v>
       </c>
       <c r="B45" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5132,43 +5142,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488440</v>
+        <v>488583</v>
       </c>
       <c r="R45" t="n">
-        <v>6786759</v>
+        <v>6786679</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5227,10 +5232,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122566902</v>
+        <v>122566957</v>
       </c>
       <c r="B46" t="n">
-        <v>90846</v>
+        <v>78656</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5243,21 +5248,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5267,10 +5272,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488397</v>
+        <v>488300</v>
       </c>
       <c r="R46" t="n">
-        <v>6786809</v>
+        <v>6786820</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5329,7 +5334,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122567323</v>
+        <v>122567305</v>
       </c>
       <c r="B47" t="n">
         <v>8441</v>
@@ -5365,7 +5370,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5374,10 +5379,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488686</v>
+        <v>488519</v>
       </c>
       <c r="R47" t="n">
-        <v>6786745</v>
+        <v>6786844</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5436,10 +5441,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122566966</v>
+        <v>122567301</v>
       </c>
       <c r="B48" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5448,38 +5453,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488390</v>
+        <v>488718</v>
       </c>
       <c r="R48" t="n">
-        <v>6786813</v>
+        <v>6786752</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5538,10 +5548,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567027</v>
+        <v>122567326</v>
       </c>
       <c r="B49" t="n">
-        <v>78301</v>
+        <v>8441</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5550,38 +5560,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488618</v>
+        <v>488545</v>
       </c>
       <c r="R49" t="n">
-        <v>6786631</v>
+        <v>6786849</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5640,10 +5655,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122566968</v>
+        <v>122567296</v>
       </c>
       <c r="B50" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5652,38 +5667,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488431</v>
+        <v>488834</v>
       </c>
       <c r="R50" t="n">
-        <v>6786772</v>
+        <v>6786685</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5742,10 +5762,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567308</v>
+        <v>122566907</v>
       </c>
       <c r="B51" t="n">
-        <v>8441</v>
+        <v>57399</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5754,31 +5774,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5787,10 +5807,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488669</v>
+        <v>488852</v>
       </c>
       <c r="R51" t="n">
-        <v>6786761</v>
+        <v>6786673</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5849,7 +5869,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567006</v>
+        <v>122567009</v>
       </c>
       <c r="B52" t="n">
         <v>78656</v>
@@ -5889,10 +5909,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488556</v>
+        <v>488465</v>
       </c>
       <c r="R52" t="n">
-        <v>6786835</v>
+        <v>6786880</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5951,10 +5971,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567321</v>
+        <v>122566889</v>
       </c>
       <c r="B53" t="n">
-        <v>8441</v>
+        <v>79274</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5963,43 +5983,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488817</v>
+        <v>488296</v>
       </c>
       <c r="R53" t="n">
-        <v>6786693</v>
+        <v>6786844</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6058,10 +6073,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567326</v>
+        <v>122566961</v>
       </c>
       <c r="B54" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6070,43 +6085,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488545</v>
+        <v>488327</v>
       </c>
       <c r="R54" t="n">
-        <v>6786849</v>
+        <v>6786847</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6165,10 +6175,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122566964</v>
+        <v>122566899</v>
       </c>
       <c r="B55" t="n">
-        <v>78656</v>
+        <v>57536</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6181,21 +6191,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6205,10 +6215,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488351</v>
+        <v>488482</v>
       </c>
       <c r="R55" t="n">
-        <v>6786831</v>
+        <v>6786720</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6267,10 +6277,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122567322</v>
+        <v>122567026</v>
       </c>
       <c r="B56" t="n">
-        <v>8441</v>
+        <v>78301</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6279,43 +6289,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488700</v>
+        <v>488539</v>
       </c>
       <c r="R56" t="n">
-        <v>6786746</v>
+        <v>6786689</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6374,10 +6379,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122566958</v>
+        <v>122567315</v>
       </c>
       <c r="B57" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6386,38 +6391,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488301</v>
+        <v>488773</v>
       </c>
       <c r="R57" t="n">
-        <v>6786839</v>
+        <v>6786561</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6476,10 +6486,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122567002</v>
+        <v>122567316</v>
       </c>
       <c r="B58" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6488,38 +6498,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488569</v>
+        <v>488900</v>
       </c>
       <c r="R58" t="n">
-        <v>6786787</v>
+        <v>6786628</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6578,10 +6593,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122567032</v>
+        <v>122566972</v>
       </c>
       <c r="B59" t="n">
-        <v>5173</v>
+        <v>78656</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6590,43 +6605,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488901</v>
+        <v>488465</v>
       </c>
       <c r="R59" t="n">
-        <v>6786589</v>
+        <v>6786729</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6685,10 +6695,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122566904</v>
+        <v>122566953</v>
       </c>
       <c r="B60" t="n">
-        <v>90846</v>
+        <v>98237</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6697,38 +6707,47 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488552</v>
+        <v>488429</v>
       </c>
       <c r="R60" t="n">
-        <v>6786834</v>
+        <v>6786896</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6787,7 +6806,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122566995</v>
+        <v>122566988</v>
       </c>
       <c r="B61" t="n">
         <v>78656</v>
@@ -6827,10 +6846,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488833</v>
+        <v>488803</v>
       </c>
       <c r="R61" t="n">
-        <v>6786674</v>
+        <v>6786562</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6889,10 +6908,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122567312</v>
+        <v>122566902</v>
       </c>
       <c r="B62" t="n">
-        <v>8441</v>
+        <v>90859</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6901,43 +6920,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488341</v>
+        <v>488397</v>
       </c>
       <c r="R62" t="n">
-        <v>6786832</v>
+        <v>6786809</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6996,10 +7010,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122566899</v>
+        <v>122567025</v>
       </c>
       <c r="B63" t="n">
-        <v>57536</v>
+        <v>78301</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7012,21 +7026,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7036,10 +7050,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488482</v>
+        <v>488378</v>
       </c>
       <c r="R63" t="n">
-        <v>6786720</v>
+        <v>6786805</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7098,10 +7112,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122566956</v>
+        <v>122567028</v>
       </c>
       <c r="B64" t="n">
-        <v>78656</v>
+        <v>78301</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7114,21 +7128,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7138,10 +7152,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488309</v>
+        <v>488611</v>
       </c>
       <c r="R64" t="n">
-        <v>6786859</v>
+        <v>6786649</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7200,7 +7214,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122567017</v>
+        <v>122566991</v>
       </c>
       <c r="B65" t="n">
         <v>78656</v>
@@ -7240,10 +7254,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488353</v>
+        <v>488918</v>
       </c>
       <c r="R65" t="n">
-        <v>6786911</v>
+        <v>6786607</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7302,10 +7316,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122567304</v>
+        <v>122567019</v>
       </c>
       <c r="B66" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7314,43 +7328,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488591</v>
+        <v>488297</v>
       </c>
       <c r="R66" t="n">
-        <v>6786769</v>
+        <v>6786946</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7409,10 +7418,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122566970</v>
+        <v>122566896</v>
       </c>
       <c r="B67" t="n">
-        <v>78656</v>
+        <v>90839</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7425,21 +7434,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7449,10 +7458,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488469</v>
+        <v>488882</v>
       </c>
       <c r="R67" t="n">
-        <v>6786751</v>
+        <v>6786607</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7511,10 +7520,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122567011</v>
+        <v>122566898</v>
       </c>
       <c r="B68" t="n">
-        <v>78656</v>
+        <v>57536</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7527,21 +7536,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7551,10 +7560,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488427</v>
+        <v>488296</v>
       </c>
       <c r="R68" t="n">
-        <v>6786888</v>
+        <v>6786844</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7613,7 +7622,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122566982</v>
+        <v>122566962</v>
       </c>
       <c r="B69" t="n">
         <v>78656</v>
@@ -7653,10 +7662,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488600</v>
+        <v>488324</v>
       </c>
       <c r="R69" t="n">
-        <v>6786662</v>
+        <v>6786843</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7715,10 +7724,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122567013</v>
+        <v>122567310</v>
       </c>
       <c r="B70" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7727,38 +7736,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488389</v>
+        <v>488294</v>
       </c>
       <c r="R70" t="n">
-        <v>6786901</v>
+        <v>6786825</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7817,10 +7831,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122567030</v>
+        <v>122567293</v>
       </c>
       <c r="B71" t="n">
-        <v>78301</v>
+        <v>8441</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7829,38 +7843,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488769</v>
+        <v>488790</v>
       </c>
       <c r="R71" t="n">
-        <v>6786552</v>
+        <v>6786547</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7919,10 +7938,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122567293</v>
+        <v>122566890</v>
       </c>
       <c r="B72" t="n">
-        <v>8441</v>
+        <v>79274</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7931,43 +7950,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488790</v>
+        <v>488572</v>
       </c>
       <c r="R72" t="n">
-        <v>6786547</v>
+        <v>6786674</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8026,7 +8040,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122567005</v>
+        <v>122567011</v>
       </c>
       <c r="B73" t="n">
         <v>78656</v>
@@ -8066,10 +8080,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488415</v>
+        <v>488427</v>
       </c>
       <c r="R73" t="n">
-        <v>6786889</v>
+        <v>6786888</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8128,10 +8142,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122566905</v>
+        <v>122566892</v>
       </c>
       <c r="B74" t="n">
-        <v>57399</v>
+        <v>79274</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8144,39 +8158,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488294</v>
+        <v>488699</v>
       </c>
       <c r="R74" t="n">
-        <v>6786826</v>
+        <v>6786599</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8235,7 +8244,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122567019</v>
+        <v>122566986</v>
       </c>
       <c r="B75" t="n">
         <v>78656</v>
@@ -8275,10 +8284,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488297</v>
+        <v>488714</v>
       </c>
       <c r="R75" t="n">
-        <v>6786946</v>
+        <v>6786574</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8337,7 +8346,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122566974</v>
+        <v>122566996</v>
       </c>
       <c r="B76" t="n">
         <v>78656</v>
@@ -8377,10 +8386,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488486</v>
+        <v>488757</v>
       </c>
       <c r="R76" t="n">
-        <v>6786718</v>
+        <v>6786723</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8439,10 +8448,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122567305</v>
+        <v>122566998</v>
       </c>
       <c r="B77" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8451,43 +8460,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488519</v>
+        <v>488700</v>
       </c>
       <c r="R77" t="n">
-        <v>6786844</v>
+        <v>6786744</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8546,10 +8550,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122566907</v>
+        <v>122567003</v>
       </c>
       <c r="B78" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8562,39 +8566,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488852</v>
+        <v>488550</v>
       </c>
       <c r="R78" t="n">
-        <v>6786673</v>
+        <v>6786822</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8653,7 +8652,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122567001</v>
+        <v>122567007</v>
       </c>
       <c r="B79" t="n">
         <v>78656</v>
@@ -8693,10 +8692,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488583</v>
+        <v>488530</v>
       </c>
       <c r="R79" t="n">
-        <v>6786774</v>
+        <v>6786847</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8755,10 +8754,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122567000</v>
+        <v>122567308</v>
       </c>
       <c r="B80" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8767,38 +8766,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488678</v>
+        <v>488669</v>
       </c>
       <c r="R80" t="n">
-        <v>6786753</v>
+        <v>6786761</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8857,10 +8861,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122566960</v>
+        <v>122567295</v>
       </c>
       <c r="B81" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8869,38 +8873,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488322</v>
+        <v>488850</v>
       </c>
       <c r="R81" t="n">
-        <v>6786853</v>
+        <v>6786668</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8959,10 +8968,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122566892</v>
+        <v>122567323</v>
       </c>
       <c r="B82" t="n">
-        <v>79274</v>
+        <v>8441</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8971,38 +8980,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488699</v>
+        <v>488686</v>
       </c>
       <c r="R82" t="n">
-        <v>6786599</v>
+        <v>6786745</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9061,10 +9075,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122566913</v>
+        <v>122567313</v>
       </c>
       <c r="B83" t="n">
-        <v>57383</v>
+        <v>8441</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9073,31 +9087,31 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9106,10 +9120,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488602</v>
+        <v>488616</v>
       </c>
       <c r="R83" t="n">
-        <v>6786666</v>
+        <v>6786649</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9142,11 +9156,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9173,7 +9182,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122566969</v>
+        <v>122567002</v>
       </c>
       <c r="B84" t="n">
         <v>78656</v>
@@ -9213,10 +9222,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488452</v>
+        <v>488569</v>
       </c>
       <c r="R84" t="n">
-        <v>6786772</v>
+        <v>6786787</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9275,10 +9284,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122567292</v>
+        <v>122567005</v>
       </c>
       <c r="B85" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9287,43 +9296,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488533</v>
+        <v>488415</v>
       </c>
       <c r="R85" t="n">
-        <v>6786690</v>
+        <v>6786889</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9382,10 +9386,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122567295</v>
+        <v>122567013</v>
       </c>
       <c r="B86" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9394,43 +9398,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488850</v>
+        <v>488389</v>
       </c>
       <c r="R86" t="n">
-        <v>6786668</v>
+        <v>6786901</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9489,10 +9488,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122566912</v>
+        <v>122567008</v>
       </c>
       <c r="B87" t="n">
-        <v>91110</v>
+        <v>78656</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9505,21 +9504,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9529,10 +9528,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488895</v>
+        <v>488495</v>
       </c>
       <c r="R87" t="n">
-        <v>6786588</v>
+        <v>6786888</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9591,10 +9590,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122567028</v>
+        <v>122567311</v>
       </c>
       <c r="B88" t="n">
-        <v>78301</v>
+        <v>8441</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9603,38 +9602,43 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488611</v>
+        <v>488332</v>
       </c>
       <c r="R88" t="n">
-        <v>6786649</v>
+        <v>6786824</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9693,10 +9697,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122566962</v>
+        <v>122567327</v>
       </c>
       <c r="B89" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9705,38 +9709,43 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488324</v>
+        <v>488442</v>
       </c>
       <c r="R89" t="n">
-        <v>6786843</v>
+        <v>6786881</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9795,10 +9804,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122566893</v>
+        <v>122566994</v>
       </c>
       <c r="B90" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9811,21 +9820,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9835,10 +9844,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488693</v>
+        <v>488883</v>
       </c>
       <c r="R90" t="n">
-        <v>6786741</v>
+        <v>6786645</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9897,7 +9906,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122567016</v>
+        <v>122567000</v>
       </c>
       <c r="B91" t="n">
         <v>78656</v>
@@ -9937,10 +9946,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488360</v>
+        <v>488678</v>
       </c>
       <c r="R91" t="n">
-        <v>6786913</v>
+        <v>6786753</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9999,10 +10008,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122567325</v>
+        <v>122567018</v>
       </c>
       <c r="B92" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10011,43 +10020,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488576</v>
+        <v>488345</v>
       </c>
       <c r="R92" t="n">
-        <v>6786782</v>
+        <v>6786910</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10106,10 +10110,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122567298</v>
+        <v>122566909</v>
       </c>
       <c r="B93" t="n">
-        <v>8441</v>
+        <v>91277</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10118,43 +10122,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>1209</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488789</v>
+        <v>488882</v>
       </c>
       <c r="R93" t="n">
-        <v>6786702</v>
+        <v>6786607</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10213,7 +10212,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122567307</v>
+        <v>122567314</v>
       </c>
       <c r="B94" t="n">
         <v>8441</v>
@@ -10249,7 +10248,7 @@
       <c r="I94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -10258,10 +10257,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488535</v>
+        <v>488747</v>
       </c>
       <c r="R94" t="n">
-        <v>6786843</v>
+        <v>6786566</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10320,10 +10319,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122567023</v>
+        <v>122567304</v>
       </c>
       <c r="B95" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10332,38 +10331,43 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>488135</v>
+        <v>488591</v>
       </c>
       <c r="R95" t="n">
-        <v>6787033</v>
+        <v>6786769</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10422,10 +10426,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122566988</v>
+        <v>122567312</v>
       </c>
       <c r="B96" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10434,38 +10438,43 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>488803</v>
+        <v>488341</v>
       </c>
       <c r="R96" t="n">
-        <v>6786562</v>
+        <v>6786832</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10524,7 +10533,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122567300</v>
+        <v>122567294</v>
       </c>
       <c r="B97" t="n">
         <v>8441</v>
@@ -10569,10 +10578,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>488768</v>
+        <v>488801</v>
       </c>
       <c r="R97" t="n">
-        <v>6786742</v>
+        <v>6786563</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10631,7 +10640,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122567301</v>
+        <v>122567322</v>
       </c>
       <c r="B98" t="n">
         <v>8441</v>
@@ -10667,7 +10676,7 @@
       <c r="I98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -10676,10 +10685,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>488718</v>
+        <v>488700</v>
       </c>
       <c r="R98" t="n">
-        <v>6786752</v>
+        <v>6786746</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10738,10 +10747,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122567029</v>
+        <v>122567317</v>
       </c>
       <c r="B99" t="n">
-        <v>78301</v>
+        <v>8441</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10750,38 +10759,43 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>488664</v>
+        <v>488892</v>
       </c>
       <c r="R99" t="n">
-        <v>6786615</v>
+        <v>6786620</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10840,10 +10854,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122566891</v>
+        <v>122566963</v>
       </c>
       <c r="B100" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10856,21 +10870,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10880,10 +10894,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>488616</v>
+        <v>488341</v>
       </c>
       <c r="R100" t="n">
-        <v>6786648</v>
+        <v>6786832</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10942,10 +10956,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122566986</v>
+        <v>122567032</v>
       </c>
       <c r="B101" t="n">
-        <v>78656</v>
+        <v>5173</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10954,38 +10968,43 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>488714</v>
+        <v>488901</v>
       </c>
       <c r="R101" t="n">
-        <v>6786574</v>
+        <v>6786589</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11044,7 +11063,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122567007</v>
+        <v>122567016</v>
       </c>
       <c r="B102" t="n">
         <v>78656</v>
@@ -11084,10 +11103,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>488530</v>
+        <v>488360</v>
       </c>
       <c r="R102" t="n">
-        <v>6786847</v>
+        <v>6786913</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11146,10 +11165,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122566903</v>
+        <v>122567014</v>
       </c>
       <c r="B103" t="n">
-        <v>90846</v>
+        <v>78656</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11162,21 +11181,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11186,10 +11205,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>488770</v>
+        <v>488383</v>
       </c>
       <c r="R103" t="n">
-        <v>6786732</v>
+        <v>6786912</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11248,10 +11267,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122567297</v>
+        <v>122566956</v>
       </c>
       <c r="B104" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11260,43 +11279,38 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488804</v>
+        <v>488309</v>
       </c>
       <c r="R104" t="n">
-        <v>6786700</v>
+        <v>6786859</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11355,10 +11369,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122566957</v>
+        <v>122567309</v>
       </c>
       <c r="B105" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11367,38 +11381,43 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488300</v>
+        <v>488707</v>
       </c>
       <c r="R105" t="n">
-        <v>6786820</v>
+        <v>6786747</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11457,10 +11476,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122567024</v>
+        <v>122567292</v>
       </c>
       <c r="B106" t="n">
-        <v>91071</v>
+        <v>8441</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11469,38 +11488,43 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>65</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488663</v>
+        <v>488533</v>
       </c>
       <c r="R106" t="n">
-        <v>6786615</v>
+        <v>6786690</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11559,10 +11583,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122567015</v>
+        <v>122567306</v>
       </c>
       <c r="B107" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11571,38 +11595,43 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488366</v>
+        <v>488556</v>
       </c>
       <c r="R107" t="n">
-        <v>6786907</v>
+        <v>6786835</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11661,10 +11690,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122566896</v>
+        <v>122567298</v>
       </c>
       <c r="B108" t="n">
-        <v>90826</v>
+        <v>8441</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11673,38 +11702,43 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>488882</v>
+        <v>488789</v>
       </c>
       <c r="R108" t="n">
-        <v>6786607</v>
+        <v>6786702</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11763,10 +11797,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122567318</v>
+        <v>122566979</v>
       </c>
       <c r="B109" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11775,43 +11809,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488883</v>
+        <v>488583</v>
       </c>
       <c r="R109" t="n">
-        <v>6786645</v>
+        <v>6786676</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11870,10 +11899,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122566890</v>
+        <v>122566999</v>
       </c>
       <c r="B110" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11886,21 +11915,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11910,10 +11939,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>488572</v>
+        <v>488686</v>
       </c>
       <c r="R110" t="n">
-        <v>6786674</v>
+        <v>6786738</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11972,7 +12001,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122566978</v>
+        <v>122566995</v>
       </c>
       <c r="B111" t="n">
         <v>78656</v>
@@ -12012,10 +12041,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>488583</v>
+        <v>488833</v>
       </c>
       <c r="R111" t="n">
-        <v>6786679</v>
+        <v>6786674</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12074,10 +12103,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122567309</v>
+        <v>122567010</v>
       </c>
       <c r="B112" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12086,43 +12115,38 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>488707</v>
+        <v>488442</v>
       </c>
       <c r="R112" t="n">
-        <v>6786747</v>
+        <v>6786881</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12181,10 +12205,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122567296</v>
+        <v>122567023</v>
       </c>
       <c r="B113" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12193,43 +12217,38 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488834</v>
+        <v>488135</v>
       </c>
       <c r="R113" t="n">
-        <v>6786685</v>
+        <v>6787033</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12288,10 +12307,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122566994</v>
+        <v>122567024</v>
       </c>
       <c r="B114" t="n">
-        <v>78656</v>
+        <v>91084</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12300,25 +12319,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12328,10 +12347,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488883</v>
+        <v>488663</v>
       </c>
       <c r="R114" t="n">
-        <v>6786645</v>
+        <v>6786615</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12390,10 +12409,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122566901</v>
+        <v>122567297</v>
       </c>
       <c r="B115" t="n">
-        <v>57536</v>
+        <v>8441</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12402,38 +12421,43 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>488142</v>
+        <v>488804</v>
       </c>
       <c r="R115" t="n">
-        <v>6787017</v>
+        <v>6786700</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12492,7 +12516,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122567289</v>
+        <v>122567300</v>
       </c>
       <c r="B116" t="n">
         <v>8441</v>
@@ -12537,10 +12561,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>488322</v>
+        <v>488768</v>
       </c>
       <c r="R116" t="n">
-        <v>6786810</v>
+        <v>6786742</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12599,10 +12623,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122566911</v>
+        <v>122566987</v>
       </c>
       <c r="B117" t="n">
-        <v>91110</v>
+        <v>78656</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12615,21 +12639,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12639,10 +12663,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>488882</v>
+        <v>488735</v>
       </c>
       <c r="R117" t="n">
-        <v>6786609</v>
+        <v>6786569</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12701,10 +12725,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122567299</v>
+        <v>122567017</v>
       </c>
       <c r="B118" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12713,43 +12737,38 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>488786</v>
+        <v>488353</v>
       </c>
       <c r="R118" t="n">
-        <v>6786723</v>
+        <v>6786911</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12808,7 +12827,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122566980</v>
+        <v>122566973</v>
       </c>
       <c r="B119" t="n">
         <v>78656</v>
@@ -12848,10 +12867,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>488590</v>
+        <v>488482</v>
       </c>
       <c r="R119" t="n">
-        <v>6786665</v>
+        <v>6786720</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12910,10 +12929,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122567020</v>
+        <v>122566893</v>
       </c>
       <c r="B120" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12926,21 +12945,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12950,10 +12969,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>488185</v>
+        <v>488693</v>
       </c>
       <c r="R120" t="n">
-        <v>6787005</v>
+        <v>6786741</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13012,10 +13031,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122567306</v>
+        <v>122567020</v>
       </c>
       <c r="B121" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13024,43 +13043,38 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488556</v>
+        <v>488185</v>
       </c>
       <c r="R121" t="n">
-        <v>6786835</v>
+        <v>6787005</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13119,10 +13133,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122567294</v>
+        <v>122566982</v>
       </c>
       <c r="B122" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13131,43 +13145,38 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488801</v>
+        <v>488600</v>
       </c>
       <c r="R122" t="n">
-        <v>6786563</v>
+        <v>6786662</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13226,10 +13235,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122567008</v>
+        <v>122566891</v>
       </c>
       <c r="B123" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13242,21 +13251,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13266,10 +13275,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>488495</v>
+        <v>488616</v>
       </c>
       <c r="R123" t="n">
-        <v>6786888</v>
+        <v>6786648</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13328,7 +13337,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122567327</v>
+        <v>122567299</v>
       </c>
       <c r="B124" t="n">
         <v>8441</v>
@@ -13364,7 +13373,7 @@
       <c r="I124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -13373,10 +13382,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>488442</v>
+        <v>488786</v>
       </c>
       <c r="R124" t="n">
-        <v>6786881</v>
+        <v>6786723</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13435,10 +13444,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122566953</v>
+        <v>122566894</v>
       </c>
       <c r="B125" t="n">
-        <v>98224</v>
+        <v>79274</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13447,47 +13456,38 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>488429</v>
+        <v>488182</v>
       </c>
       <c r="R125" t="n">
-        <v>6786896</v>
+        <v>6787001</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13546,7 +13546,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122566963</v>
+        <v>122566990</v>
       </c>
       <c r="B126" t="n">
         <v>78656</v>
@@ -13586,10 +13586,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>488341</v>
+        <v>488840</v>
       </c>
       <c r="R126" t="n">
-        <v>6786832</v>
+        <v>6786622</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13648,10 +13648,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122567320</v>
+        <v>122566959</v>
       </c>
       <c r="B127" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13660,43 +13660,38 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>488833</v>
+        <v>488317</v>
       </c>
       <c r="R127" t="n">
-        <v>6786674</v>
+        <v>6786858</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13755,10 +13750,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122567311</v>
+        <v>122566911</v>
       </c>
       <c r="B128" t="n">
-        <v>8441</v>
+        <v>91123</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13767,43 +13762,38 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>658</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>488332</v>
+        <v>488882</v>
       </c>
       <c r="R128" t="n">
-        <v>6786824</v>
+        <v>6786609</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13862,10 +13852,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122566897</v>
+        <v>122567012</v>
       </c>
       <c r="B129" t="n">
-        <v>90826</v>
+        <v>78656</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13878,21 +13868,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13902,10 +13892,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>488892</v>
+        <v>488420</v>
       </c>
       <c r="R129" t="n">
-        <v>6786591</v>
+        <v>6786898</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13964,7 +13954,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122566971</v>
+        <v>122567001</v>
       </c>
       <c r="B130" t="n">
         <v>78656</v>
@@ -14004,10 +13994,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>488461</v>
+        <v>488583</v>
       </c>
       <c r="R130" t="n">
-        <v>6786736</v>
+        <v>6786774</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14066,10 +14056,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122566898</v>
+        <v>122566967</v>
       </c>
       <c r="B131" t="n">
-        <v>57536</v>
+        <v>78656</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14082,21 +14072,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14106,10 +14096,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>488296</v>
+        <v>488387</v>
       </c>
       <c r="R131" t="n">
-        <v>6786844</v>
+        <v>6786773</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14168,10 +14158,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122566983</v>
+        <v>122567290</v>
       </c>
       <c r="B132" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14180,38 +14170,43 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>488609</v>
+        <v>488345</v>
       </c>
       <c r="R132" t="n">
-        <v>6786648</v>
+        <v>6786796</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14270,10 +14265,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>122566998</v>
+        <v>122567321</v>
       </c>
       <c r="B133" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14282,38 +14277,43 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>488700</v>
+        <v>488817</v>
       </c>
       <c r="R133" t="n">
-        <v>6786744</v>
+        <v>6786693</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>

--- a/artfynd/A 61338-2024 artfynd.xlsx
+++ b/artfynd/A 61338-2024 artfynd.xlsx
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567324</v>
+        <v>122567006</v>
       </c>
       <c r="B14" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,43 +1916,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488638</v>
+        <v>488556</v>
       </c>
       <c r="R14" t="n">
-        <v>6786764</v>
+        <v>6786835</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567291</v>
+        <v>122567015</v>
       </c>
       <c r="B15" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2023,43 +2018,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488440</v>
+        <v>488366</v>
       </c>
       <c r="R15" t="n">
-        <v>6786759</v>
+        <v>6786907</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,7 +2108,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567006</v>
+        <v>122566983</v>
       </c>
       <c r="B16" t="n">
         <v>78656</v>
@@ -2158,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488556</v>
+        <v>488609</v>
       </c>
       <c r="R16" t="n">
-        <v>6786835</v>
+        <v>6786648</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122567015</v>
+        <v>122566913</v>
       </c>
       <c r="B17" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2236,34 +2226,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488366</v>
+        <v>488602</v>
       </c>
       <c r="R17" t="n">
-        <v>6786907</v>
+        <v>6786666</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2296,6 +2291,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2322,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566983</v>
+        <v>122567324</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2334,38 +2334,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488609</v>
+        <v>488638</v>
       </c>
       <c r="R18" t="n">
-        <v>6786648</v>
+        <v>6786764</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566913</v>
+        <v>122567291</v>
       </c>
       <c r="B19" t="n">
-        <v>57383</v>
+        <v>8441</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2436,31 +2441,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2469,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488602</v>
+        <v>488440</v>
       </c>
       <c r="R19" t="n">
-        <v>6786666</v>
+        <v>6786759</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2505,11 +2510,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -7214,10 +7214,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122566991</v>
+        <v>122567310</v>
       </c>
       <c r="B65" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7226,38 +7226,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488918</v>
+        <v>488294</v>
       </c>
       <c r="R65" t="n">
-        <v>6786607</v>
+        <v>6786825</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7316,10 +7321,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122567019</v>
+        <v>122567293</v>
       </c>
       <c r="B66" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7328,38 +7333,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488297</v>
+        <v>488790</v>
       </c>
       <c r="R66" t="n">
-        <v>6786946</v>
+        <v>6786547</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7418,10 +7428,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122566896</v>
+        <v>122566991</v>
       </c>
       <c r="B67" t="n">
-        <v>90839</v>
+        <v>78656</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7434,21 +7444,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7458,7 +7468,7 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488882</v>
+        <v>488918</v>
       </c>
       <c r="R67" t="n">
         <v>6786607</v>
@@ -7520,10 +7530,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122566898</v>
+        <v>122567019</v>
       </c>
       <c r="B68" t="n">
-        <v>57536</v>
+        <v>78656</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7536,21 +7546,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7560,10 +7570,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488296</v>
+        <v>488297</v>
       </c>
       <c r="R68" t="n">
-        <v>6786844</v>
+        <v>6786946</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7724,10 +7734,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122567310</v>
+        <v>122566896</v>
       </c>
       <c r="B70" t="n">
-        <v>8441</v>
+        <v>90839</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7736,43 +7746,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488294</v>
+        <v>488882</v>
       </c>
       <c r="R70" t="n">
-        <v>6786825</v>
+        <v>6786607</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7831,10 +7836,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122567293</v>
+        <v>122566898</v>
       </c>
       <c r="B71" t="n">
-        <v>8441</v>
+        <v>57536</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7843,43 +7848,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488790</v>
+        <v>488296</v>
       </c>
       <c r="R71" t="n">
-        <v>6786547</v>
+        <v>6786844</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -10956,10 +10956,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122567032</v>
+        <v>122567016</v>
       </c>
       <c r="B101" t="n">
-        <v>5173</v>
+        <v>78656</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10968,43 +10968,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>488901</v>
+        <v>488360</v>
       </c>
       <c r="R101" t="n">
-        <v>6786589</v>
+        <v>6786913</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11063,7 +11058,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122567016</v>
+        <v>122567014</v>
       </c>
       <c r="B102" t="n">
         <v>78656</v>
@@ -11103,10 +11098,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>488360</v>
+        <v>488383</v>
       </c>
       <c r="R102" t="n">
-        <v>6786913</v>
+        <v>6786912</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11165,7 +11160,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122567014</v>
+        <v>122566956</v>
       </c>
       <c r="B103" t="n">
         <v>78656</v>
@@ -11205,10 +11200,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>488383</v>
+        <v>488309</v>
       </c>
       <c r="R103" t="n">
-        <v>6786912</v>
+        <v>6786859</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11267,10 +11262,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122566956</v>
+        <v>122567032</v>
       </c>
       <c r="B104" t="n">
-        <v>78656</v>
+        <v>5173</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11279,38 +11274,43 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488309</v>
+        <v>488901</v>
       </c>
       <c r="R104" t="n">
-        <v>6786859</v>
+        <v>6786589</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>

--- a/artfynd/A 61338-2024 artfynd.xlsx
+++ b/artfynd/A 61338-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122566981</v>
+        <v>122567312</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488599</v>
+        <v>488341</v>
       </c>
       <c r="R2" t="n">
-        <v>6786673</v>
+        <v>6786832</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122566958</v>
+        <v>122567291</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +794,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488301</v>
+        <v>488440</v>
       </c>
       <c r="R3" t="n">
-        <v>6786839</v>
+        <v>6786759</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567004</v>
+        <v>122566911</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>91123</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488475</v>
+        <v>488882</v>
       </c>
       <c r="R4" t="n">
-        <v>6786864</v>
+        <v>6786609</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122566997</v>
+        <v>122566984</v>
       </c>
       <c r="B5" t="n">
         <v>78656</v>
@@ -1021,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488731</v>
+        <v>488699</v>
       </c>
       <c r="R5" t="n">
-        <v>6786733</v>
+        <v>6786596</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566966</v>
+        <v>122566899</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>57536</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488390</v>
+        <v>488482</v>
       </c>
       <c r="R6" t="n">
-        <v>6786813</v>
+        <v>6786720</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567022</v>
+        <v>122567322</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,38 +1207,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488137</v>
+        <v>488700</v>
       </c>
       <c r="R7" t="n">
-        <v>6787026</v>
+        <v>6786746</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567320</v>
+        <v>122566971</v>
       </c>
       <c r="B8" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,43 +1314,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488833</v>
+        <v>488461</v>
       </c>
       <c r="R8" t="n">
-        <v>6786674</v>
+        <v>6786736</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566974</v>
+        <v>122566972</v>
       </c>
       <c r="B9" t="n">
         <v>78656</v>
@@ -1434,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488486</v>
+        <v>488465</v>
       </c>
       <c r="R9" t="n">
-        <v>6786718</v>
+        <v>6786729</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566969</v>
+        <v>122567017</v>
       </c>
       <c r="B10" t="n">
         <v>78656</v>
@@ -1536,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488452</v>
+        <v>488353</v>
       </c>
       <c r="R10" t="n">
-        <v>6786772</v>
+        <v>6786911</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,7 +1608,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566985</v>
+        <v>122566980</v>
       </c>
       <c r="B11" t="n">
         <v>78656</v>
@@ -1638,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488698</v>
+        <v>488590</v>
       </c>
       <c r="R11" t="n">
-        <v>6786584</v>
+        <v>6786665</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566903</v>
+        <v>122566999</v>
       </c>
       <c r="B12" t="n">
-        <v>90859</v>
+        <v>78656</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488770</v>
+        <v>488686</v>
       </c>
       <c r="R12" t="n">
-        <v>6786732</v>
+        <v>6786738</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566952</v>
+        <v>122567020</v>
       </c>
       <c r="B13" t="n">
-        <v>80613</v>
+        <v>78656</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488363</v>
+        <v>488185</v>
       </c>
       <c r="R13" t="n">
-        <v>6786907</v>
+        <v>6787005</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567006</v>
+        <v>122567015</v>
       </c>
       <c r="B14" t="n">
         <v>78656</v>
@@ -1944,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488556</v>
+        <v>488366</v>
       </c>
       <c r="R14" t="n">
-        <v>6786835</v>
+        <v>6786907</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,7 +2016,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567015</v>
+        <v>122567007</v>
       </c>
       <c r="B15" t="n">
         <v>78656</v>
@@ -2046,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488366</v>
+        <v>488530</v>
       </c>
       <c r="R15" t="n">
-        <v>6786907</v>
+        <v>6786847</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566983</v>
+        <v>122566889</v>
       </c>
       <c r="B16" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488609</v>
+        <v>488296</v>
       </c>
       <c r="R16" t="n">
-        <v>6786648</v>
+        <v>6786844</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566913</v>
+        <v>122566902</v>
       </c>
       <c r="B17" t="n">
-        <v>57383</v>
+        <v>90859</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,39 +2236,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488602</v>
+        <v>488397</v>
       </c>
       <c r="R17" t="n">
-        <v>6786666</v>
+        <v>6786809</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2291,11 +2296,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2322,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567324</v>
+        <v>122567002</v>
       </c>
       <c r="B18" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2334,43 +2334,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488638</v>
+        <v>488569</v>
       </c>
       <c r="R18" t="n">
-        <v>6786764</v>
+        <v>6786787</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,7 +2424,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122567291</v>
+        <v>122567325</v>
       </c>
       <c r="B19" t="n">
         <v>8441</v>
@@ -2465,7 +2460,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2474,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488440</v>
+        <v>488576</v>
       </c>
       <c r="R19" t="n">
-        <v>6786759</v>
+        <v>6786782</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2536,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566904</v>
+        <v>122567292</v>
       </c>
       <c r="B20" t="n">
-        <v>90859</v>
+        <v>8441</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2548,38 +2543,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488552</v>
+        <v>488533</v>
       </c>
       <c r="R20" t="n">
-        <v>6786834</v>
+        <v>6786690</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566964</v>
+        <v>122566953</v>
       </c>
       <c r="B21" t="n">
-        <v>78656</v>
+        <v>98237</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2650,38 +2650,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488351</v>
+        <v>488429</v>
       </c>
       <c r="R21" t="n">
-        <v>6786831</v>
+        <v>6786896</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,10 +2749,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566971</v>
+        <v>122566952</v>
       </c>
       <c r="B22" t="n">
-        <v>78656</v>
+        <v>80613</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2756,21 +2765,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2780,10 +2789,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488461</v>
+        <v>488363</v>
       </c>
       <c r="R22" t="n">
-        <v>6786736</v>
+        <v>6786907</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2842,10 +2851,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566908</v>
+        <v>122566988</v>
       </c>
       <c r="B23" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2858,43 +2867,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488892</v>
+        <v>488803</v>
       </c>
       <c r="R23" t="n">
-        <v>6786620</v>
+        <v>6786562</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2953,10 +2953,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566912</v>
+        <v>122566981</v>
       </c>
       <c r="B24" t="n">
-        <v>91123</v>
+        <v>78656</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2969,21 +2969,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488895</v>
+        <v>488599</v>
       </c>
       <c r="R24" t="n">
-        <v>6786588</v>
+        <v>6786673</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3055,10 +3055,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566901</v>
+        <v>122566960</v>
       </c>
       <c r="B25" t="n">
-        <v>57536</v>
+        <v>78656</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3071,21 +3071,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3095,10 +3095,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488142</v>
+        <v>488322</v>
       </c>
       <c r="R25" t="n">
-        <v>6787017</v>
+        <v>6786853</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3157,10 +3157,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567319</v>
+        <v>122566977</v>
       </c>
       <c r="B26" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3169,40 +3169,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488869</v>
+        <v>488515</v>
       </c>
       <c r="R26" t="n">
         <v>6786685</v>
@@ -3264,7 +3259,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122567289</v>
+        <v>122567304</v>
       </c>
       <c r="B27" t="n">
         <v>8441</v>
@@ -3309,10 +3304,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488322</v>
+        <v>488591</v>
       </c>
       <c r="R27" t="n">
-        <v>6786810</v>
+        <v>6786769</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3371,10 +3366,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567307</v>
+        <v>122566987</v>
       </c>
       <c r="B28" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3383,43 +3378,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488535</v>
+        <v>488735</v>
       </c>
       <c r="R28" t="n">
-        <v>6786843</v>
+        <v>6786569</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3478,10 +3468,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567303</v>
+        <v>122567013</v>
       </c>
       <c r="B29" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3490,43 +3480,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488600</v>
+        <v>488389</v>
       </c>
       <c r="R29" t="n">
-        <v>6786772</v>
+        <v>6786901</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3585,10 +3570,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567318</v>
+        <v>122566997</v>
       </c>
       <c r="B30" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3597,43 +3582,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488883</v>
+        <v>488731</v>
       </c>
       <c r="R30" t="n">
-        <v>6786645</v>
+        <v>6786733</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3692,10 +3672,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122566905</v>
+        <v>122566890</v>
       </c>
       <c r="B31" t="n">
-        <v>57399</v>
+        <v>79274</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3708,39 +3688,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488294</v>
+        <v>488572</v>
       </c>
       <c r="R31" t="n">
-        <v>6786826</v>
+        <v>6786674</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3799,10 +3774,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122566897</v>
+        <v>122566893</v>
       </c>
       <c r="B32" t="n">
-        <v>90839</v>
+        <v>79274</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3815,21 +3790,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3839,10 +3814,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488892</v>
+        <v>488693</v>
       </c>
       <c r="R32" t="n">
-        <v>6786591</v>
+        <v>6786741</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3901,10 +3876,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122567027</v>
+        <v>122566892</v>
       </c>
       <c r="B33" t="n">
-        <v>78301</v>
+        <v>79274</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3917,21 +3892,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3941,10 +3916,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488618</v>
+        <v>488699</v>
       </c>
       <c r="R33" t="n">
-        <v>6786631</v>
+        <v>6786599</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4003,10 +3978,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567325</v>
+        <v>122566891</v>
       </c>
       <c r="B34" t="n">
-        <v>8441</v>
+        <v>79274</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4015,43 +3990,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488576</v>
+        <v>488616</v>
       </c>
       <c r="R34" t="n">
-        <v>6786782</v>
+        <v>6786648</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4110,7 +4080,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122566980</v>
+        <v>122566978</v>
       </c>
       <c r="B35" t="n">
         <v>78656</v>
@@ -4150,10 +4120,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488590</v>
+        <v>488583</v>
       </c>
       <c r="R35" t="n">
-        <v>6786665</v>
+        <v>6786679</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4212,7 +4182,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122566970</v>
+        <v>122566990</v>
       </c>
       <c r="B36" t="n">
         <v>78656</v>
@@ -4252,10 +4222,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488469</v>
+        <v>488840</v>
       </c>
       <c r="R36" t="n">
-        <v>6786751</v>
+        <v>6786622</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4314,7 +4284,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122566965</v>
+        <v>122566995</v>
       </c>
       <c r="B37" t="n">
         <v>78656</v>
@@ -4354,10 +4324,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488378</v>
+        <v>488833</v>
       </c>
       <c r="R37" t="n">
-        <v>6786805</v>
+        <v>6786674</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4416,7 +4386,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122566976</v>
+        <v>122567018</v>
       </c>
       <c r="B38" t="n">
         <v>78656</v>
@@ -4456,10 +4426,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488515</v>
+        <v>488345</v>
       </c>
       <c r="R38" t="n">
-        <v>6786685</v>
+        <v>6786910</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4518,10 +4488,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122566968</v>
+        <v>122567316</v>
       </c>
       <c r="B39" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4530,38 +4500,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488431</v>
+        <v>488900</v>
       </c>
       <c r="R39" t="n">
-        <v>6786772</v>
+        <v>6786628</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4620,10 +4595,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122566984</v>
+        <v>122567303</v>
       </c>
       <c r="B40" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4632,38 +4607,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488699</v>
+        <v>488600</v>
       </c>
       <c r="R40" t="n">
-        <v>6786596</v>
+        <v>6786772</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4722,10 +4702,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122566954</v>
+        <v>122567318</v>
       </c>
       <c r="B41" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4734,38 +4714,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488416</v>
+        <v>488883</v>
       </c>
       <c r="R41" t="n">
-        <v>6786896</v>
+        <v>6786645</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4824,7 +4809,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122566960</v>
+        <v>122567014</v>
       </c>
       <c r="B42" t="n">
         <v>78656</v>
@@ -4864,10 +4849,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488322</v>
+        <v>488383</v>
       </c>
       <c r="R42" t="n">
-        <v>6786853</v>
+        <v>6786912</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4926,10 +4911,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567029</v>
+        <v>122567008</v>
       </c>
       <c r="B43" t="n">
-        <v>78301</v>
+        <v>78656</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4942,21 +4927,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4966,10 +4951,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488664</v>
+        <v>488495</v>
       </c>
       <c r="R43" t="n">
-        <v>6786615</v>
+        <v>6786888</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5028,10 +5013,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122567030</v>
+        <v>122566963</v>
       </c>
       <c r="B44" t="n">
-        <v>78301</v>
+        <v>78656</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5044,21 +5029,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5068,10 +5053,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488769</v>
+        <v>488341</v>
       </c>
       <c r="R44" t="n">
-        <v>6786552</v>
+        <v>6786832</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5130,10 +5115,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122566978</v>
+        <v>122567025</v>
       </c>
       <c r="B45" t="n">
-        <v>78656</v>
+        <v>78301</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5146,21 +5131,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5170,10 +5155,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488583</v>
+        <v>488378</v>
       </c>
       <c r="R45" t="n">
-        <v>6786679</v>
+        <v>6786805</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5232,7 +5217,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122566957</v>
+        <v>122566974</v>
       </c>
       <c r="B46" t="n">
         <v>78656</v>
@@ -5272,10 +5257,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488300</v>
+        <v>488486</v>
       </c>
       <c r="R46" t="n">
-        <v>6786820</v>
+        <v>6786718</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5334,10 +5319,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122567305</v>
+        <v>122566994</v>
       </c>
       <c r="B47" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5346,43 +5331,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488519</v>
+        <v>488883</v>
       </c>
       <c r="R47" t="n">
-        <v>6786844</v>
+        <v>6786645</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5441,10 +5421,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122567301</v>
+        <v>122566998</v>
       </c>
       <c r="B48" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5453,43 +5433,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488718</v>
+        <v>488700</v>
       </c>
       <c r="R48" t="n">
-        <v>6786752</v>
+        <v>6786744</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5548,10 +5523,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567326</v>
+        <v>122566968</v>
       </c>
       <c r="B49" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5560,43 +5535,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488545</v>
+        <v>488431</v>
       </c>
       <c r="R49" t="n">
-        <v>6786849</v>
+        <v>6786772</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5655,10 +5625,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122567296</v>
+        <v>122566979</v>
       </c>
       <c r="B50" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5667,43 +5637,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488834</v>
+        <v>488583</v>
       </c>
       <c r="R50" t="n">
-        <v>6786685</v>
+        <v>6786676</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5762,10 +5727,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122566907</v>
+        <v>122566957</v>
       </c>
       <c r="B51" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5778,39 +5743,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488852</v>
+        <v>488300</v>
       </c>
       <c r="R51" t="n">
-        <v>6786673</v>
+        <v>6786820</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5869,7 +5829,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567009</v>
+        <v>122567010</v>
       </c>
       <c r="B52" t="n">
         <v>78656</v>
@@ -5909,10 +5869,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488465</v>
+        <v>488442</v>
       </c>
       <c r="R52" t="n">
-        <v>6786880</v>
+        <v>6786881</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5971,10 +5931,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122566889</v>
+        <v>122566907</v>
       </c>
       <c r="B53" t="n">
-        <v>79274</v>
+        <v>57399</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5987,34 +5947,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488296</v>
+        <v>488852</v>
       </c>
       <c r="R53" t="n">
-        <v>6786844</v>
+        <v>6786673</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6073,10 +6038,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122566961</v>
+        <v>122566909</v>
       </c>
       <c r="B54" t="n">
-        <v>78656</v>
+        <v>91277</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6085,25 +6050,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6113,10 +6078,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488327</v>
+        <v>488882</v>
       </c>
       <c r="R54" t="n">
-        <v>6786847</v>
+        <v>6786607</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6175,10 +6140,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122566899</v>
+        <v>122567030</v>
       </c>
       <c r="B55" t="n">
-        <v>57536</v>
+        <v>78301</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6191,21 +6156,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6215,10 +6180,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488482</v>
+        <v>488769</v>
       </c>
       <c r="R55" t="n">
-        <v>6786720</v>
+        <v>6786552</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6277,10 +6242,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122567026</v>
+        <v>122567006</v>
       </c>
       <c r="B56" t="n">
-        <v>78301</v>
+        <v>78656</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6293,21 +6258,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6317,10 +6282,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488539</v>
+        <v>488556</v>
       </c>
       <c r="R56" t="n">
-        <v>6786689</v>
+        <v>6786835</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6379,7 +6344,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567315</v>
+        <v>122567320</v>
       </c>
       <c r="B57" t="n">
         <v>8441</v>
@@ -6424,10 +6389,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488773</v>
+        <v>488833</v>
       </c>
       <c r="R57" t="n">
-        <v>6786561</v>
+        <v>6786674</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6486,7 +6451,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122567316</v>
+        <v>122567295</v>
       </c>
       <c r="B58" t="n">
         <v>8441</v>
@@ -6522,7 +6487,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6531,10 +6496,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488900</v>
+        <v>488850</v>
       </c>
       <c r="R58" t="n">
-        <v>6786628</v>
+        <v>6786668</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6593,10 +6558,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122566972</v>
+        <v>122567298</v>
       </c>
       <c r="B59" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6605,38 +6570,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488465</v>
+        <v>488789</v>
       </c>
       <c r="R59" t="n">
-        <v>6786729</v>
+        <v>6786702</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6695,10 +6665,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122566953</v>
+        <v>122567294</v>
       </c>
       <c r="B60" t="n">
-        <v>98237</v>
+        <v>8441</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6707,35 +6677,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6744,10 +6710,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488429</v>
+        <v>488801</v>
       </c>
       <c r="R60" t="n">
-        <v>6786896</v>
+        <v>6786563</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6806,10 +6772,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122566988</v>
+        <v>122567028</v>
       </c>
       <c r="B61" t="n">
-        <v>78656</v>
+        <v>78301</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6822,21 +6788,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6846,10 +6812,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488803</v>
+        <v>488611</v>
       </c>
       <c r="R61" t="n">
-        <v>6786562</v>
+        <v>6786649</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6908,10 +6874,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122566902</v>
+        <v>122567000</v>
       </c>
       <c r="B62" t="n">
-        <v>90859</v>
+        <v>78656</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6924,21 +6890,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6948,10 +6914,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488397</v>
+        <v>488678</v>
       </c>
       <c r="R62" t="n">
-        <v>6786809</v>
+        <v>6786753</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7010,10 +6976,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122567025</v>
+        <v>122566983</v>
       </c>
       <c r="B63" t="n">
-        <v>78301</v>
+        <v>78656</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7026,21 +6992,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7050,10 +7016,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488378</v>
+        <v>488609</v>
       </c>
       <c r="R63" t="n">
-        <v>6786805</v>
+        <v>6786648</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7112,10 +7078,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122567028</v>
+        <v>122566956</v>
       </c>
       <c r="B64" t="n">
-        <v>78301</v>
+        <v>78656</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7128,21 +7094,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7152,10 +7118,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488611</v>
+        <v>488309</v>
       </c>
       <c r="R64" t="n">
-        <v>6786649</v>
+        <v>6786859</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7214,10 +7180,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122567310</v>
+        <v>122567012</v>
       </c>
       <c r="B65" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7226,43 +7192,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488294</v>
+        <v>488420</v>
       </c>
       <c r="R65" t="n">
-        <v>6786825</v>
+        <v>6786898</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7321,10 +7282,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122567293</v>
+        <v>122566985</v>
       </c>
       <c r="B66" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7333,43 +7294,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488790</v>
+        <v>488698</v>
       </c>
       <c r="R66" t="n">
-        <v>6786547</v>
+        <v>6786584</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7428,7 +7384,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122566991</v>
+        <v>122567003</v>
       </c>
       <c r="B67" t="n">
         <v>78656</v>
@@ -7468,10 +7424,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488918</v>
+        <v>488550</v>
       </c>
       <c r="R67" t="n">
-        <v>6786607</v>
+        <v>6786822</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7530,10 +7486,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122567019</v>
+        <v>122567319</v>
       </c>
       <c r="B68" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7542,38 +7498,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488297</v>
+        <v>488869</v>
       </c>
       <c r="R68" t="n">
-        <v>6786946</v>
+        <v>6786685</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7632,10 +7593,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122566962</v>
+        <v>122567289</v>
       </c>
       <c r="B69" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7644,38 +7605,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488324</v>
+        <v>488322</v>
       </c>
       <c r="R69" t="n">
-        <v>6786843</v>
+        <v>6786810</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7734,10 +7700,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122566896</v>
+        <v>122567313</v>
       </c>
       <c r="B70" t="n">
-        <v>90839</v>
+        <v>8441</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7746,38 +7712,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488882</v>
+        <v>488616</v>
       </c>
       <c r="R70" t="n">
-        <v>6786607</v>
+        <v>6786649</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7836,10 +7807,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122566898</v>
+        <v>122567004</v>
       </c>
       <c r="B71" t="n">
-        <v>57536</v>
+        <v>78656</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7852,21 +7823,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7876,10 +7847,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488296</v>
+        <v>488475</v>
       </c>
       <c r="R71" t="n">
-        <v>6786844</v>
+        <v>6786864</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7938,10 +7909,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122566890</v>
+        <v>122566903</v>
       </c>
       <c r="B72" t="n">
-        <v>79274</v>
+        <v>90859</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7954,21 +7925,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7978,10 +7949,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488572</v>
+        <v>488770</v>
       </c>
       <c r="R72" t="n">
-        <v>6786674</v>
+        <v>6786732</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8040,10 +8011,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122567011</v>
+        <v>122567315</v>
       </c>
       <c r="B73" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8052,38 +8023,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488427</v>
+        <v>488773</v>
       </c>
       <c r="R73" t="n">
-        <v>6786888</v>
+        <v>6786561</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8142,10 +8118,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122566892</v>
+        <v>122567307</v>
       </c>
       <c r="B74" t="n">
-        <v>79274</v>
+        <v>8441</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8154,38 +8130,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488699</v>
+        <v>488535</v>
       </c>
       <c r="R74" t="n">
-        <v>6786599</v>
+        <v>6786843</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8244,7 +8225,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122566986</v>
+        <v>122566954</v>
       </c>
       <c r="B75" t="n">
         <v>78656</v>
@@ -8284,10 +8265,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488714</v>
+        <v>488416</v>
       </c>
       <c r="R75" t="n">
-        <v>6786574</v>
+        <v>6786896</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8346,7 +8327,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122566996</v>
+        <v>122567016</v>
       </c>
       <c r="B76" t="n">
         <v>78656</v>
@@ -8386,10 +8367,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488757</v>
+        <v>488360</v>
       </c>
       <c r="R76" t="n">
-        <v>6786723</v>
+        <v>6786913</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8448,7 +8429,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122566998</v>
+        <v>122567022</v>
       </c>
       <c r="B77" t="n">
         <v>78656</v>
@@ -8488,10 +8469,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488700</v>
+        <v>488137</v>
       </c>
       <c r="R77" t="n">
-        <v>6786744</v>
+        <v>6787026</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8550,10 +8531,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122567003</v>
+        <v>122566912</v>
       </c>
       <c r="B78" t="n">
-        <v>78656</v>
+        <v>91123</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8566,21 +8547,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8590,10 +8571,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488550</v>
+        <v>488895</v>
       </c>
       <c r="R78" t="n">
-        <v>6786822</v>
+        <v>6786588</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8652,10 +8633,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122567007</v>
+        <v>122567027</v>
       </c>
       <c r="B79" t="n">
-        <v>78656</v>
+        <v>78301</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8668,21 +8649,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8692,10 +8673,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488530</v>
+        <v>488618</v>
       </c>
       <c r="R79" t="n">
-        <v>6786847</v>
+        <v>6786631</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8754,10 +8735,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122567308</v>
+        <v>122566969</v>
       </c>
       <c r="B80" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8766,43 +8747,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488669</v>
+        <v>488452</v>
       </c>
       <c r="R80" t="n">
-        <v>6786761</v>
+        <v>6786772</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8861,10 +8837,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122567295</v>
+        <v>122566894</v>
       </c>
       <c r="B81" t="n">
-        <v>8441</v>
+        <v>79274</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8873,43 +8849,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488850</v>
+        <v>488182</v>
       </c>
       <c r="R81" t="n">
-        <v>6786668</v>
+        <v>6787001</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8968,10 +8939,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122567323</v>
+        <v>122567032</v>
       </c>
       <c r="B82" t="n">
-        <v>8441</v>
+        <v>5173</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8984,21 +8955,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9013,10 +8984,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488686</v>
+        <v>488901</v>
       </c>
       <c r="R82" t="n">
-        <v>6786745</v>
+        <v>6786589</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9075,7 +9046,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122567313</v>
+        <v>122567308</v>
       </c>
       <c r="B83" t="n">
         <v>8441</v>
@@ -9120,10 +9091,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488616</v>
+        <v>488669</v>
       </c>
       <c r="R83" t="n">
-        <v>6786649</v>
+        <v>6786761</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9182,10 +9153,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122567002</v>
+        <v>122567300</v>
       </c>
       <c r="B84" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9194,38 +9165,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488569</v>
+        <v>488768</v>
       </c>
       <c r="R84" t="n">
-        <v>6786787</v>
+        <v>6786742</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9284,10 +9260,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122567005</v>
+        <v>122567326</v>
       </c>
       <c r="B85" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9296,38 +9272,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488415</v>
+        <v>488545</v>
       </c>
       <c r="R85" t="n">
-        <v>6786889</v>
+        <v>6786849</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9386,10 +9367,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122567013</v>
+        <v>122567299</v>
       </c>
       <c r="B86" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9398,38 +9379,43 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488389</v>
+        <v>488786</v>
       </c>
       <c r="R86" t="n">
-        <v>6786901</v>
+        <v>6786723</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9488,10 +9474,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122567008</v>
+        <v>122567323</v>
       </c>
       <c r="B87" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9500,38 +9486,43 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488495</v>
+        <v>488686</v>
       </c>
       <c r="R87" t="n">
-        <v>6786888</v>
+        <v>6786745</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9590,10 +9581,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122567311</v>
+        <v>122566898</v>
       </c>
       <c r="B88" t="n">
-        <v>8441</v>
+        <v>57536</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9602,43 +9593,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488332</v>
+        <v>488296</v>
       </c>
       <c r="R88" t="n">
-        <v>6786824</v>
+        <v>6786844</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9697,10 +9683,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122567327</v>
+        <v>122566962</v>
       </c>
       <c r="B89" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9709,43 +9695,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488442</v>
+        <v>488324</v>
       </c>
       <c r="R89" t="n">
-        <v>6786881</v>
+        <v>6786843</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9804,7 +9785,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122566994</v>
+        <v>122566970</v>
       </c>
       <c r="B90" t="n">
         <v>78656</v>
@@ -9844,10 +9825,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488883</v>
+        <v>488469</v>
       </c>
       <c r="R90" t="n">
-        <v>6786645</v>
+        <v>6786751</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9906,7 +9887,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122567000</v>
+        <v>122567011</v>
       </c>
       <c r="B91" t="n">
         <v>78656</v>
@@ -9946,10 +9927,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488678</v>
+        <v>488427</v>
       </c>
       <c r="R91" t="n">
-        <v>6786753</v>
+        <v>6786888</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10008,7 +9989,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122567018</v>
+        <v>122566982</v>
       </c>
       <c r="B92" t="n">
         <v>78656</v>
@@ -10048,10 +10029,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488345</v>
+        <v>488600</v>
       </c>
       <c r="R92" t="n">
-        <v>6786910</v>
+        <v>6786662</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10110,10 +10091,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122566909</v>
+        <v>122567296</v>
       </c>
       <c r="B93" t="n">
-        <v>91277</v>
+        <v>8441</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10122,38 +10103,43 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1209</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488882</v>
+        <v>488834</v>
       </c>
       <c r="R93" t="n">
-        <v>6786607</v>
+        <v>6786685</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10212,7 +10198,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122567314</v>
+        <v>122567321</v>
       </c>
       <c r="B94" t="n">
         <v>8441</v>
@@ -10257,10 +10243,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488747</v>
+        <v>488817</v>
       </c>
       <c r="R94" t="n">
-        <v>6786566</v>
+        <v>6786693</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10319,10 +10305,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122567304</v>
+        <v>122566905</v>
       </c>
       <c r="B95" t="n">
-        <v>8441</v>
+        <v>57399</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10331,31 +10317,31 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -10364,10 +10350,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>488591</v>
+        <v>488294</v>
       </c>
       <c r="R95" t="n">
-        <v>6786769</v>
+        <v>6786826</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10426,10 +10412,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122567312</v>
+        <v>122566896</v>
       </c>
       <c r="B96" t="n">
-        <v>8441</v>
+        <v>90839</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10438,43 +10424,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>488341</v>
+        <v>488882</v>
       </c>
       <c r="R96" t="n">
-        <v>6786832</v>
+        <v>6786607</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10533,10 +10514,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122567294</v>
+        <v>122567029</v>
       </c>
       <c r="B97" t="n">
-        <v>8441</v>
+        <v>78301</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10545,43 +10526,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>488801</v>
+        <v>488664</v>
       </c>
       <c r="R97" t="n">
-        <v>6786563</v>
+        <v>6786615</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10640,10 +10616,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122567322</v>
+        <v>122567009</v>
       </c>
       <c r="B98" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10652,43 +10628,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>488700</v>
+        <v>488465</v>
       </c>
       <c r="R98" t="n">
-        <v>6786746</v>
+        <v>6786880</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10747,10 +10718,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122567317</v>
+        <v>122566966</v>
       </c>
       <c r="B99" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10759,43 +10730,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>488892</v>
+        <v>488390</v>
       </c>
       <c r="R99" t="n">
-        <v>6786620</v>
+        <v>6786813</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10854,10 +10820,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122566963</v>
+        <v>122566897</v>
       </c>
       <c r="B100" t="n">
-        <v>78656</v>
+        <v>90839</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10870,21 +10836,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10894,10 +10860,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>488341</v>
+        <v>488892</v>
       </c>
       <c r="R100" t="n">
-        <v>6786832</v>
+        <v>6786591</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10956,10 +10922,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122567016</v>
+        <v>122567290</v>
       </c>
       <c r="B101" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10968,38 +10934,43 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>488360</v>
+        <v>488345</v>
       </c>
       <c r="R101" t="n">
-        <v>6786913</v>
+        <v>6786796</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11058,10 +11029,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122567014</v>
+        <v>122567310</v>
       </c>
       <c r="B102" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11070,38 +11041,43 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>488383</v>
+        <v>488294</v>
       </c>
       <c r="R102" t="n">
-        <v>6786912</v>
+        <v>6786825</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11160,10 +11136,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122566956</v>
+        <v>122567297</v>
       </c>
       <c r="B103" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11172,38 +11148,43 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>488309</v>
+        <v>488804</v>
       </c>
       <c r="R103" t="n">
-        <v>6786859</v>
+        <v>6786700</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11262,10 +11243,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122567032</v>
+        <v>122567305</v>
       </c>
       <c r="B104" t="n">
-        <v>5173</v>
+        <v>8441</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11278,27 +11259,27 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -11307,10 +11288,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488901</v>
+        <v>488519</v>
       </c>
       <c r="R104" t="n">
-        <v>6786589</v>
+        <v>6786844</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11369,7 +11350,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122567309</v>
+        <v>122567324</v>
       </c>
       <c r="B105" t="n">
         <v>8441</v>
@@ -11414,10 +11395,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488707</v>
+        <v>488638</v>
       </c>
       <c r="R105" t="n">
-        <v>6786747</v>
+        <v>6786764</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11476,10 +11457,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122567292</v>
+        <v>122566973</v>
       </c>
       <c r="B106" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11488,43 +11469,38 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488533</v>
+        <v>488482</v>
       </c>
       <c r="R106" t="n">
-        <v>6786690</v>
+        <v>6786720</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11583,10 +11559,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122567306</v>
+        <v>122566958</v>
       </c>
       <c r="B107" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11595,43 +11571,38 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488556</v>
+        <v>488301</v>
       </c>
       <c r="R107" t="n">
-        <v>6786835</v>
+        <v>6786839</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11690,10 +11661,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122567298</v>
+        <v>122567005</v>
       </c>
       <c r="B108" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11702,43 +11673,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>488789</v>
+        <v>488415</v>
       </c>
       <c r="R108" t="n">
-        <v>6786702</v>
+        <v>6786889</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11797,7 +11763,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122566979</v>
+        <v>122566961</v>
       </c>
       <c r="B109" t="n">
         <v>78656</v>
@@ -11837,10 +11803,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488583</v>
+        <v>488327</v>
       </c>
       <c r="R109" t="n">
-        <v>6786676</v>
+        <v>6786847</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11899,7 +11865,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122566999</v>
+        <v>122566986</v>
       </c>
       <c r="B110" t="n">
         <v>78656</v>
@@ -11939,10 +11905,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>488686</v>
+        <v>488714</v>
       </c>
       <c r="R110" t="n">
-        <v>6786738</v>
+        <v>6786574</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12001,7 +11967,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122566995</v>
+        <v>122566967</v>
       </c>
       <c r="B111" t="n">
         <v>78656</v>
@@ -12041,10 +12007,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>488833</v>
+        <v>488387</v>
       </c>
       <c r="R111" t="n">
-        <v>6786674</v>
+        <v>6786773</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12103,10 +12069,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122567010</v>
+        <v>122566904</v>
       </c>
       <c r="B112" t="n">
-        <v>78656</v>
+        <v>90859</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12119,21 +12085,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12143,10 +12109,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>488442</v>
+        <v>488552</v>
       </c>
       <c r="R112" t="n">
-        <v>6786881</v>
+        <v>6786834</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12205,10 +12171,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122567023</v>
+        <v>122566901</v>
       </c>
       <c r="B113" t="n">
-        <v>78656</v>
+        <v>57536</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12221,21 +12187,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12245,10 +12211,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488135</v>
+        <v>488142</v>
       </c>
       <c r="R113" t="n">
-        <v>6787033</v>
+        <v>6787017</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12307,10 +12273,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122567024</v>
+        <v>122567293</v>
       </c>
       <c r="B114" t="n">
-        <v>91084</v>
+        <v>8441</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12319,38 +12285,43 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>65</v>
+        <v>106545</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488663</v>
+        <v>488790</v>
       </c>
       <c r="R114" t="n">
-        <v>6786615</v>
+        <v>6786547</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12409,7 +12380,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122567297</v>
+        <v>122567309</v>
       </c>
       <c r="B115" t="n">
         <v>8441</v>
@@ -12445,7 +12416,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -12454,10 +12425,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>488804</v>
+        <v>488707</v>
       </c>
       <c r="R115" t="n">
-        <v>6786700</v>
+        <v>6786747</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12516,7 +12487,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122567300</v>
+        <v>122567311</v>
       </c>
       <c r="B116" t="n">
         <v>8441</v>
@@ -12552,7 +12523,7 @@
       <c r="I116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -12561,10 +12532,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>488768</v>
+        <v>488332</v>
       </c>
       <c r="R116" t="n">
-        <v>6786742</v>
+        <v>6786824</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12623,10 +12594,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122566987</v>
+        <v>122567327</v>
       </c>
       <c r="B117" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12635,38 +12606,43 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>488735</v>
+        <v>488442</v>
       </c>
       <c r="R117" t="n">
-        <v>6786569</v>
+        <v>6786881</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12725,10 +12701,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122567017</v>
+        <v>122567317</v>
       </c>
       <c r="B118" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12737,38 +12713,43 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>488353</v>
+        <v>488892</v>
       </c>
       <c r="R118" t="n">
-        <v>6786911</v>
+        <v>6786620</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12827,10 +12808,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122566973</v>
+        <v>122567024</v>
       </c>
       <c r="B119" t="n">
-        <v>78656</v>
+        <v>91084</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12839,25 +12820,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12867,10 +12848,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>488482</v>
+        <v>488663</v>
       </c>
       <c r="R119" t="n">
-        <v>6786720</v>
+        <v>6786615</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12929,10 +12910,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122566893</v>
+        <v>122567026</v>
       </c>
       <c r="B120" t="n">
-        <v>79274</v>
+        <v>78301</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12945,21 +12926,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12969,10 +12950,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>488693</v>
+        <v>488539</v>
       </c>
       <c r="R120" t="n">
-        <v>6786741</v>
+        <v>6786689</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13031,7 +13012,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122567020</v>
+        <v>122567001</v>
       </c>
       <c r="B121" t="n">
         <v>78656</v>
@@ -13071,10 +13052,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488185</v>
+        <v>488583</v>
       </c>
       <c r="R121" t="n">
-        <v>6787005</v>
+        <v>6786774</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13133,7 +13114,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122566982</v>
+        <v>122566965</v>
       </c>
       <c r="B122" t="n">
         <v>78656</v>
@@ -13173,10 +13154,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488600</v>
+        <v>488378</v>
       </c>
       <c r="R122" t="n">
-        <v>6786662</v>
+        <v>6786805</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13235,10 +13216,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122566891</v>
+        <v>122567019</v>
       </c>
       <c r="B123" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13251,21 +13232,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13275,10 +13256,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>488616</v>
+        <v>488297</v>
       </c>
       <c r="R123" t="n">
-        <v>6786648</v>
+        <v>6786946</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13337,10 +13318,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122567299</v>
+        <v>122566913</v>
       </c>
       <c r="B124" t="n">
-        <v>8441</v>
+        <v>57383</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13349,31 +13330,31 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -13382,10 +13363,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>488786</v>
+        <v>488602</v>
       </c>
       <c r="R124" t="n">
-        <v>6786723</v>
+        <v>6786666</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13418,6 +13399,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13444,10 +13430,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122566894</v>
+        <v>122567301</v>
       </c>
       <c r="B125" t="n">
-        <v>79274</v>
+        <v>8441</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13456,38 +13442,43 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>488182</v>
+        <v>488718</v>
       </c>
       <c r="R125" t="n">
-        <v>6787001</v>
+        <v>6786752</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13546,7 +13537,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122566990</v>
+        <v>122566991</v>
       </c>
       <c r="B126" t="n">
         <v>78656</v>
@@ -13586,10 +13577,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>488840</v>
+        <v>488918</v>
       </c>
       <c r="R126" t="n">
-        <v>6786622</v>
+        <v>6786607</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13750,10 +13741,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122566911</v>
+        <v>122566964</v>
       </c>
       <c r="B128" t="n">
-        <v>91123</v>
+        <v>78656</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13766,21 +13757,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13790,10 +13781,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>488882</v>
+        <v>488351</v>
       </c>
       <c r="R128" t="n">
-        <v>6786609</v>
+        <v>6786831</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13852,7 +13843,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122567012</v>
+        <v>122566996</v>
       </c>
       <c r="B129" t="n">
         <v>78656</v>
@@ -13892,10 +13883,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>488420</v>
+        <v>488757</v>
       </c>
       <c r="R129" t="n">
-        <v>6786898</v>
+        <v>6786723</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13954,7 +13945,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122567001</v>
+        <v>122567023</v>
       </c>
       <c r="B130" t="n">
         <v>78656</v>
@@ -13994,10 +13985,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>488583</v>
+        <v>488135</v>
       </c>
       <c r="R130" t="n">
-        <v>6786774</v>
+        <v>6787033</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14056,10 +14047,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122566967</v>
+        <v>122566908</v>
       </c>
       <c r="B131" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14072,34 +14063,43 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>488387</v>
+        <v>488892</v>
       </c>
       <c r="R131" t="n">
-        <v>6786773</v>
+        <v>6786620</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14158,7 +14158,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122567290</v>
+        <v>122567314</v>
       </c>
       <c r="B132" t="n">
         <v>8441</v>
@@ -14194,7 +14194,7 @@
       <c r="I132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -14203,10 +14203,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>488345</v>
+        <v>488747</v>
       </c>
       <c r="R132" t="n">
-        <v>6786796</v>
+        <v>6786566</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14265,7 +14265,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>122567321</v>
+        <v>122567306</v>
       </c>
       <c r="B133" t="n">
         <v>8441</v>
@@ -14301,7 +14301,7 @@
       <c r="I133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -14310,10 +14310,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>488817</v>
+        <v>488556</v>
       </c>
       <c r="R133" t="n">
-        <v>6786693</v>
+        <v>6786835</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>

--- a/artfynd/A 61338-2024 artfynd.xlsx
+++ b/artfynd/A 61338-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567312</v>
+        <v>122566911</v>
       </c>
       <c r="B2" t="n">
-        <v>8441</v>
+        <v>91123</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488341</v>
+        <v>488882</v>
       </c>
       <c r="R2" t="n">
-        <v>6786832</v>
+        <v>6786609</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567291</v>
+        <v>122567312</v>
       </c>
       <c r="B3" t="n">
         <v>8441</v>
@@ -818,7 +813,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -827,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488440</v>
+        <v>488341</v>
       </c>
       <c r="R3" t="n">
-        <v>6786759</v>
+        <v>6786832</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122566911</v>
+        <v>122567291</v>
       </c>
       <c r="B4" t="n">
-        <v>91123</v>
+        <v>8441</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,38 +896,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488882</v>
+        <v>488440</v>
       </c>
       <c r="R4" t="n">
-        <v>6786609</v>
+        <v>6786759</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122566984</v>
+        <v>122567322</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,38 +1003,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488699</v>
+        <v>488700</v>
       </c>
       <c r="R5" t="n">
-        <v>6786596</v>
+        <v>6786746</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566899</v>
+        <v>122566984</v>
       </c>
       <c r="B6" t="n">
-        <v>57536</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488482</v>
+        <v>488699</v>
       </c>
       <c r="R6" t="n">
-        <v>6786720</v>
+        <v>6786596</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567322</v>
+        <v>122566971</v>
       </c>
       <c r="B7" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,43 +1212,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488700</v>
+        <v>488461</v>
       </c>
       <c r="R7" t="n">
-        <v>6786746</v>
+        <v>6786736</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566971</v>
+        <v>122566972</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488461</v>
+        <v>488465</v>
       </c>
       <c r="R8" t="n">
-        <v>6786736</v>
+        <v>6786729</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566972</v>
+        <v>122566899</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>57536</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488465</v>
+        <v>488482</v>
       </c>
       <c r="R9" t="n">
-        <v>6786729</v>
+        <v>6786720</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122567292</v>
+        <v>122566952</v>
       </c>
       <c r="B20" t="n">
-        <v>8441</v>
+        <v>80613</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2543,43 +2543,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>1049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488533</v>
+        <v>488363</v>
       </c>
       <c r="R20" t="n">
-        <v>6786690</v>
+        <v>6786907</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566953</v>
+        <v>122566988</v>
       </c>
       <c r="B21" t="n">
-        <v>98237</v>
+        <v>78656</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2650,47 +2645,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488429</v>
+        <v>488803</v>
       </c>
       <c r="R21" t="n">
-        <v>6786896</v>
+        <v>6786562</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2749,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566952</v>
+        <v>122566981</v>
       </c>
       <c r="B22" t="n">
-        <v>80613</v>
+        <v>78656</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2765,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2789,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488363</v>
+        <v>488599</v>
       </c>
       <c r="R22" t="n">
-        <v>6786907</v>
+        <v>6786673</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2851,7 +2837,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566988</v>
+        <v>122566960</v>
       </c>
       <c r="B23" t="n">
         <v>78656</v>
@@ -2891,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488803</v>
+        <v>488322</v>
       </c>
       <c r="R23" t="n">
-        <v>6786562</v>
+        <v>6786853</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2953,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566981</v>
+        <v>122567292</v>
       </c>
       <c r="B24" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2965,38 +2951,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488599</v>
+        <v>488533</v>
       </c>
       <c r="R24" t="n">
-        <v>6786673</v>
+        <v>6786690</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3055,10 +3046,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566960</v>
+        <v>122566953</v>
       </c>
       <c r="B25" t="n">
-        <v>78656</v>
+        <v>98237</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3067,38 +3058,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488322</v>
+        <v>488429</v>
       </c>
       <c r="R25" t="n">
-        <v>6786853</v>
+        <v>6786896</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3157,7 +3157,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566977</v>
+        <v>122566997</v>
       </c>
       <c r="B26" t="n">
         <v>78656</v>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488515</v>
+        <v>488731</v>
       </c>
       <c r="R26" t="n">
-        <v>6786685</v>
+        <v>6786733</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3259,10 +3259,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122567304</v>
+        <v>122566890</v>
       </c>
       <c r="B27" t="n">
-        <v>8441</v>
+        <v>79274</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3271,43 +3271,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488591</v>
+        <v>488572</v>
       </c>
       <c r="R27" t="n">
-        <v>6786769</v>
+        <v>6786674</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3366,10 +3361,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122566987</v>
+        <v>122566893</v>
       </c>
       <c r="B28" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3382,21 +3377,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3406,10 +3401,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488735</v>
+        <v>488693</v>
       </c>
       <c r="R28" t="n">
-        <v>6786569</v>
+        <v>6786741</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3468,7 +3463,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567013</v>
+        <v>122566987</v>
       </c>
       <c r="B29" t="n">
         <v>78656</v>
@@ -3508,10 +3503,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488389</v>
+        <v>488735</v>
       </c>
       <c r="R29" t="n">
-        <v>6786901</v>
+        <v>6786569</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3570,7 +3565,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122566997</v>
+        <v>122566977</v>
       </c>
       <c r="B30" t="n">
         <v>78656</v>
@@ -3610,10 +3605,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488731</v>
+        <v>488515</v>
       </c>
       <c r="R30" t="n">
-        <v>6786733</v>
+        <v>6786685</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3672,10 +3667,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122566890</v>
+        <v>122567013</v>
       </c>
       <c r="B31" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3688,21 +3683,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3712,10 +3707,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488572</v>
+        <v>488389</v>
       </c>
       <c r="R31" t="n">
-        <v>6786674</v>
+        <v>6786901</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3774,7 +3769,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122566893</v>
+        <v>122566892</v>
       </c>
       <c r="B32" t="n">
         <v>79274</v>
@@ -3814,10 +3809,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488693</v>
+        <v>488699</v>
       </c>
       <c r="R32" t="n">
-        <v>6786741</v>
+        <v>6786599</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3876,7 +3871,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122566892</v>
+        <v>122566891</v>
       </c>
       <c r="B33" t="n">
         <v>79274</v>
@@ -3916,10 +3911,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488699</v>
+        <v>488616</v>
       </c>
       <c r="R33" t="n">
-        <v>6786599</v>
+        <v>6786648</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3978,10 +3973,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122566891</v>
+        <v>122567304</v>
       </c>
       <c r="B34" t="n">
-        <v>79274</v>
+        <v>8441</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3990,38 +3985,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488616</v>
+        <v>488591</v>
       </c>
       <c r="R34" t="n">
-        <v>6786648</v>
+        <v>6786769</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5217,7 +5217,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122566974</v>
+        <v>122566968</v>
       </c>
       <c r="B46" t="n">
         <v>78656</v>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488486</v>
+        <v>488431</v>
       </c>
       <c r="R46" t="n">
-        <v>6786718</v>
+        <v>6786772</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5319,7 +5319,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122566994</v>
+        <v>122566974</v>
       </c>
       <c r="B47" t="n">
         <v>78656</v>
@@ -5359,10 +5359,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488883</v>
+        <v>488486</v>
       </c>
       <c r="R47" t="n">
-        <v>6786645</v>
+        <v>6786718</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5421,7 +5421,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122566998</v>
+        <v>122566994</v>
       </c>
       <c r="B48" t="n">
         <v>78656</v>
@@ -5461,10 +5461,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488700</v>
+        <v>488883</v>
       </c>
       <c r="R48" t="n">
-        <v>6786744</v>
+        <v>6786645</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5523,7 +5523,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122566968</v>
+        <v>122566998</v>
       </c>
       <c r="B49" t="n">
         <v>78656</v>
@@ -5563,10 +5563,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488431</v>
+        <v>488700</v>
       </c>
       <c r="R49" t="n">
-        <v>6786772</v>
+        <v>6786744</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -8327,10 +8327,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122567016</v>
+        <v>122566912</v>
       </c>
       <c r="B76" t="n">
-        <v>78656</v>
+        <v>91123</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8343,21 +8343,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488360</v>
+        <v>488895</v>
       </c>
       <c r="R76" t="n">
-        <v>6786913</v>
+        <v>6786588</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8429,10 +8429,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122567022</v>
+        <v>122567027</v>
       </c>
       <c r="B77" t="n">
-        <v>78656</v>
+        <v>78301</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8445,21 +8445,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8469,10 +8469,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488137</v>
+        <v>488618</v>
       </c>
       <c r="R77" t="n">
-        <v>6787026</v>
+        <v>6786631</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8531,10 +8531,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122566912</v>
+        <v>122566894</v>
       </c>
       <c r="B78" t="n">
-        <v>91123</v>
+        <v>79274</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8547,21 +8547,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8571,10 +8571,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488895</v>
+        <v>488182</v>
       </c>
       <c r="R78" t="n">
-        <v>6786588</v>
+        <v>6787001</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8633,10 +8633,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122567027</v>
+        <v>122567032</v>
       </c>
       <c r="B79" t="n">
-        <v>78301</v>
+        <v>5173</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8645,38 +8645,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>100526</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488618</v>
+        <v>488901</v>
       </c>
       <c r="R79" t="n">
-        <v>6786631</v>
+        <v>6786589</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8735,10 +8740,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122566969</v>
+        <v>122566898</v>
       </c>
       <c r="B80" t="n">
-        <v>78656</v>
+        <v>57536</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8751,21 +8756,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8775,10 +8780,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488452</v>
+        <v>488296</v>
       </c>
       <c r="R80" t="n">
-        <v>6786772</v>
+        <v>6786844</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8837,10 +8842,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122566894</v>
+        <v>122567016</v>
       </c>
       <c r="B81" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8853,21 +8858,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8877,10 +8882,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488182</v>
+        <v>488360</v>
       </c>
       <c r="R81" t="n">
-        <v>6787001</v>
+        <v>6786913</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8939,10 +8944,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122567032</v>
+        <v>122566969</v>
       </c>
       <c r="B82" t="n">
-        <v>5173</v>
+        <v>78656</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8951,43 +8956,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488901</v>
+        <v>488452</v>
       </c>
       <c r="R82" t="n">
-        <v>6786589</v>
+        <v>6786772</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9046,10 +9046,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122567308</v>
+        <v>122567022</v>
       </c>
       <c r="B83" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9058,43 +9058,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488669</v>
+        <v>488137</v>
       </c>
       <c r="R83" t="n">
-        <v>6786761</v>
+        <v>6787026</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9153,7 +9148,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122567300</v>
+        <v>122567308</v>
       </c>
       <c r="B84" t="n">
         <v>8441</v>
@@ -9189,7 +9184,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9198,10 +9193,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488768</v>
+        <v>488669</v>
       </c>
       <c r="R84" t="n">
-        <v>6786742</v>
+        <v>6786761</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9260,7 +9255,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122567326</v>
+        <v>122567300</v>
       </c>
       <c r="B85" t="n">
         <v>8441</v>
@@ -9296,7 +9291,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9305,10 +9300,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488545</v>
+        <v>488768</v>
       </c>
       <c r="R85" t="n">
-        <v>6786849</v>
+        <v>6786742</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9367,7 +9362,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122567299</v>
+        <v>122567326</v>
       </c>
       <c r="B86" t="n">
         <v>8441</v>
@@ -9403,7 +9398,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9412,10 +9407,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488786</v>
+        <v>488545</v>
       </c>
       <c r="R86" t="n">
-        <v>6786723</v>
+        <v>6786849</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9474,7 +9469,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122567323</v>
+        <v>122567299</v>
       </c>
       <c r="B87" t="n">
         <v>8441</v>
@@ -9510,7 +9505,7 @@
       <c r="I87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9519,10 +9514,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488686</v>
+        <v>488786</v>
       </c>
       <c r="R87" t="n">
-        <v>6786745</v>
+        <v>6786723</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9581,10 +9576,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122566898</v>
+        <v>122567323</v>
       </c>
       <c r="B88" t="n">
-        <v>57536</v>
+        <v>8441</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9593,38 +9588,43 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488296</v>
+        <v>488686</v>
       </c>
       <c r="R88" t="n">
-        <v>6786844</v>
+        <v>6786745</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -13537,10 +13537,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122566991</v>
+        <v>122566908</v>
       </c>
       <c r="B126" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13553,34 +13553,43 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>488918</v>
+        <v>488892</v>
       </c>
       <c r="R126" t="n">
-        <v>6786607</v>
+        <v>6786620</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13639,7 +13648,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122566959</v>
+        <v>122566991</v>
       </c>
       <c r="B127" t="n">
         <v>78656</v>
@@ -13679,10 +13688,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>488317</v>
+        <v>488918</v>
       </c>
       <c r="R127" t="n">
-        <v>6786858</v>
+        <v>6786607</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13741,7 +13750,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122566964</v>
+        <v>122566959</v>
       </c>
       <c r="B128" t="n">
         <v>78656</v>
@@ -13781,10 +13790,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>488351</v>
+        <v>488317</v>
       </c>
       <c r="R128" t="n">
-        <v>6786831</v>
+        <v>6786858</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13843,7 +13852,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122566996</v>
+        <v>122566964</v>
       </c>
       <c r="B129" t="n">
         <v>78656</v>
@@ -13883,10 +13892,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>488757</v>
+        <v>488351</v>
       </c>
       <c r="R129" t="n">
-        <v>6786723</v>
+        <v>6786831</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13945,7 +13954,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122567023</v>
+        <v>122566996</v>
       </c>
       <c r="B130" t="n">
         <v>78656</v>
@@ -13985,10 +13994,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>488135</v>
+        <v>488757</v>
       </c>
       <c r="R130" t="n">
-        <v>6787033</v>
+        <v>6786723</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14047,10 +14056,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122566908</v>
+        <v>122567023</v>
       </c>
       <c r="B131" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14063,43 +14072,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>488892</v>
+        <v>488135</v>
       </c>
       <c r="R131" t="n">
-        <v>6786620</v>
+        <v>6787033</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>

--- a/artfynd/A 61338-2024 artfynd.xlsx
+++ b/artfynd/A 61338-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122566911</v>
+        <v>122567304</v>
       </c>
       <c r="B2" t="n">
-        <v>91123</v>
+        <v>8441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488882</v>
+        <v>488591</v>
       </c>
       <c r="R2" t="n">
-        <v>6786609</v>
+        <v>6786769</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567312</v>
+        <v>122566981</v>
       </c>
       <c r="B3" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,43 +794,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488341</v>
+        <v>488599</v>
       </c>
       <c r="R3" t="n">
-        <v>6786832</v>
+        <v>6786673</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567291</v>
+        <v>122567002</v>
       </c>
       <c r="B4" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,43 +896,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488440</v>
+        <v>488569</v>
       </c>
       <c r="R4" t="n">
-        <v>6786759</v>
+        <v>6786787</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567322</v>
+        <v>122566970</v>
       </c>
       <c r="B5" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,43 +998,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488700</v>
+        <v>488469</v>
       </c>
       <c r="R5" t="n">
-        <v>6786746</v>
+        <v>6786751</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566984</v>
+        <v>122567025</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>78301</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488699</v>
+        <v>488378</v>
       </c>
       <c r="R6" t="n">
-        <v>6786596</v>
+        <v>6786805</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566971</v>
+        <v>122567290</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,38 +1202,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488461</v>
+        <v>488345</v>
       </c>
       <c r="R7" t="n">
-        <v>6786736</v>
+        <v>6786796</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566972</v>
+        <v>122567320</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,38 +1309,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488465</v>
+        <v>488833</v>
       </c>
       <c r="R8" t="n">
-        <v>6786729</v>
+        <v>6786674</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566899</v>
+        <v>122567311</v>
       </c>
       <c r="B9" t="n">
-        <v>57536</v>
+        <v>8441</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,38 +1416,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488482</v>
+        <v>488332</v>
       </c>
       <c r="R9" t="n">
-        <v>6786720</v>
+        <v>6786824</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122567017</v>
+        <v>122567299</v>
       </c>
       <c r="B10" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,38 +1523,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488353</v>
+        <v>488786</v>
       </c>
       <c r="R10" t="n">
-        <v>6786911</v>
+        <v>6786723</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566980</v>
+        <v>122567295</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,38 +1630,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488590</v>
+        <v>488850</v>
       </c>
       <c r="R11" t="n">
-        <v>6786665</v>
+        <v>6786668</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,7 +1725,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566999</v>
+        <v>122566954</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1750,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488686</v>
+        <v>488416</v>
       </c>
       <c r="R12" t="n">
-        <v>6786738</v>
+        <v>6786896</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,7 +1827,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567020</v>
+        <v>122566963</v>
       </c>
       <c r="B13" t="n">
         <v>78656</v>
@@ -1852,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488185</v>
+        <v>488341</v>
       </c>
       <c r="R13" t="n">
-        <v>6787005</v>
+        <v>6786832</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,7 +1929,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567015</v>
+        <v>122566978</v>
       </c>
       <c r="B14" t="n">
         <v>78656</v>
@@ -1954,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488366</v>
+        <v>488583</v>
       </c>
       <c r="R14" t="n">
-        <v>6786907</v>
+        <v>6786679</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567007</v>
+        <v>122567029</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>78301</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2032,21 +2047,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488530</v>
+        <v>488664</v>
       </c>
       <c r="R15" t="n">
-        <v>6786847</v>
+        <v>6786615</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566889</v>
+        <v>122567312</v>
       </c>
       <c r="B16" t="n">
-        <v>79274</v>
+        <v>8441</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,38 +2145,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488296</v>
+        <v>488341</v>
       </c>
       <c r="R16" t="n">
-        <v>6786844</v>
+        <v>6786832</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566902</v>
+        <v>122566962</v>
       </c>
       <c r="B17" t="n">
-        <v>90859</v>
+        <v>78656</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2236,21 +2256,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488397</v>
+        <v>488324</v>
       </c>
       <c r="R17" t="n">
-        <v>6786809</v>
+        <v>6786843</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,7 +2342,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567002</v>
+        <v>122566957</v>
       </c>
       <c r="B18" t="n">
         <v>78656</v>
@@ -2362,10 +2382,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488569</v>
+        <v>488300</v>
       </c>
       <c r="R18" t="n">
-        <v>6786787</v>
+        <v>6786820</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,10 +2444,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122567325</v>
+        <v>122566964</v>
       </c>
       <c r="B19" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2436,43 +2456,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488576</v>
+        <v>488351</v>
       </c>
       <c r="R19" t="n">
-        <v>6786782</v>
+        <v>6786831</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,10 +2546,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566952</v>
+        <v>122566907</v>
       </c>
       <c r="B20" t="n">
-        <v>80613</v>
+        <v>57399</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,34 +2562,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488363</v>
+        <v>488852</v>
       </c>
       <c r="R20" t="n">
-        <v>6786907</v>
+        <v>6786673</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,10 +2653,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566988</v>
+        <v>122566909</v>
       </c>
       <c r="B21" t="n">
-        <v>78656</v>
+        <v>91278</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2645,25 +2665,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2693,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488803</v>
+        <v>488882</v>
       </c>
       <c r="R21" t="n">
-        <v>6786562</v>
+        <v>6786607</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,10 +2755,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566981</v>
+        <v>122567316</v>
       </c>
       <c r="B22" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2747,38 +2767,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488599</v>
+        <v>488900</v>
       </c>
       <c r="R22" t="n">
-        <v>6786673</v>
+        <v>6786628</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566960</v>
+        <v>122566893</v>
       </c>
       <c r="B23" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2853,21 +2878,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,10 +2902,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488322</v>
+        <v>488693</v>
       </c>
       <c r="R23" t="n">
-        <v>6786853</v>
+        <v>6786741</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,7 +2964,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567292</v>
+        <v>122567319</v>
       </c>
       <c r="B24" t="n">
         <v>8441</v>
@@ -2975,7 +3000,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2984,10 +3009,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488533</v>
+        <v>488869</v>
       </c>
       <c r="R24" t="n">
-        <v>6786690</v>
+        <v>6786685</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,10 +3071,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566953</v>
+        <v>122567309</v>
       </c>
       <c r="B25" t="n">
-        <v>98237</v>
+        <v>8441</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3058,35 +3083,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3095,10 +3116,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488429</v>
+        <v>488707</v>
       </c>
       <c r="R25" t="n">
-        <v>6786896</v>
+        <v>6786747</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3157,10 +3178,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566997</v>
+        <v>122567318</v>
       </c>
       <c r="B26" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3169,38 +3190,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488731</v>
+        <v>488883</v>
       </c>
       <c r="R26" t="n">
-        <v>6786733</v>
+        <v>6786645</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3259,10 +3285,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566890</v>
+        <v>122566973</v>
       </c>
       <c r="B27" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3275,21 +3301,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3299,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488572</v>
+        <v>488482</v>
       </c>
       <c r="R27" t="n">
-        <v>6786674</v>
+        <v>6786720</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3361,10 +3387,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122566893</v>
+        <v>122567009</v>
       </c>
       <c r="B28" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3377,21 +3403,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3401,10 +3427,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488693</v>
+        <v>488465</v>
       </c>
       <c r="R28" t="n">
-        <v>6786741</v>
+        <v>6786880</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3463,7 +3489,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122566987</v>
+        <v>122567015</v>
       </c>
       <c r="B29" t="n">
         <v>78656</v>
@@ -3503,10 +3529,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488735</v>
+        <v>488366</v>
       </c>
       <c r="R29" t="n">
-        <v>6786569</v>
+        <v>6786907</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3565,10 +3591,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122566977</v>
+        <v>122566891</v>
       </c>
       <c r="B30" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3581,21 +3607,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3605,10 +3631,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488515</v>
+        <v>488616</v>
       </c>
       <c r="R30" t="n">
-        <v>6786685</v>
+        <v>6786648</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3667,7 +3693,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567013</v>
+        <v>122567006</v>
       </c>
       <c r="B31" t="n">
         <v>78656</v>
@@ -3707,10 +3733,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488389</v>
+        <v>488556</v>
       </c>
       <c r="R31" t="n">
-        <v>6786901</v>
+        <v>6786835</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3769,10 +3795,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122566892</v>
+        <v>122566986</v>
       </c>
       <c r="B32" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3785,21 +3811,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3809,10 +3835,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488699</v>
+        <v>488714</v>
       </c>
       <c r="R32" t="n">
-        <v>6786599</v>
+        <v>6786574</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3871,10 +3897,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122566891</v>
+        <v>122567030</v>
       </c>
       <c r="B33" t="n">
-        <v>79274</v>
+        <v>78301</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3887,21 +3913,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3911,10 +3937,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488616</v>
+        <v>488769</v>
       </c>
       <c r="R33" t="n">
-        <v>6786648</v>
+        <v>6786552</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3973,7 +3999,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567304</v>
+        <v>122567317</v>
       </c>
       <c r="B34" t="n">
         <v>8441</v>
@@ -4009,7 +4035,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4018,10 +4044,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488591</v>
+        <v>488892</v>
       </c>
       <c r="R34" t="n">
-        <v>6786769</v>
+        <v>6786620</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4080,10 +4106,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122566978</v>
+        <v>122566953</v>
       </c>
       <c r="B35" t="n">
-        <v>78656</v>
+        <v>98240</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4092,38 +4118,47 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488583</v>
+        <v>488429</v>
       </c>
       <c r="R35" t="n">
-        <v>6786679</v>
+        <v>6786896</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4182,7 +4217,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122566990</v>
+        <v>122566977</v>
       </c>
       <c r="B36" t="n">
         <v>78656</v>
@@ -4222,10 +4257,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488840</v>
+        <v>488515</v>
       </c>
       <c r="R36" t="n">
-        <v>6786622</v>
+        <v>6786685</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4284,7 +4319,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122566995</v>
+        <v>122566972</v>
       </c>
       <c r="B37" t="n">
         <v>78656</v>
@@ -4324,10 +4359,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488833</v>
+        <v>488465</v>
       </c>
       <c r="R37" t="n">
-        <v>6786674</v>
+        <v>6786729</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4386,7 +4421,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567018</v>
+        <v>122567008</v>
       </c>
       <c r="B38" t="n">
         <v>78656</v>
@@ -4426,10 +4461,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488345</v>
+        <v>488495</v>
       </c>
       <c r="R38" t="n">
-        <v>6786910</v>
+        <v>6786888</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4488,10 +4523,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122567316</v>
+        <v>122567032</v>
       </c>
       <c r="B39" t="n">
-        <v>8441</v>
+        <v>5173</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4504,21 +4539,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4533,10 +4568,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488900</v>
+        <v>488901</v>
       </c>
       <c r="R39" t="n">
-        <v>6786628</v>
+        <v>6786589</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4595,10 +4630,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122567303</v>
+        <v>122566905</v>
       </c>
       <c r="B40" t="n">
-        <v>8441</v>
+        <v>57399</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4607,31 +4642,31 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4640,10 +4675,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488600</v>
+        <v>488294</v>
       </c>
       <c r="R40" t="n">
-        <v>6786772</v>
+        <v>6786826</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4702,7 +4737,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567318</v>
+        <v>122567306</v>
       </c>
       <c r="B41" t="n">
         <v>8441</v>
@@ -4738,7 +4773,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4747,10 +4782,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488883</v>
+        <v>488556</v>
       </c>
       <c r="R41" t="n">
-        <v>6786645</v>
+        <v>6786835</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4809,10 +4844,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567014</v>
+        <v>122567323</v>
       </c>
       <c r="B42" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4821,38 +4856,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488383</v>
+        <v>488686</v>
       </c>
       <c r="R42" t="n">
-        <v>6786912</v>
+        <v>6786745</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4911,7 +4951,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567008</v>
+        <v>122566959</v>
       </c>
       <c r="B43" t="n">
         <v>78656</v>
@@ -4951,10 +4991,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488495</v>
+        <v>488317</v>
       </c>
       <c r="R43" t="n">
-        <v>6786888</v>
+        <v>6786858</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5013,7 +5053,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122566963</v>
+        <v>122566967</v>
       </c>
       <c r="B44" t="n">
         <v>78656</v>
@@ -5053,10 +5093,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488341</v>
+        <v>488387</v>
       </c>
       <c r="R44" t="n">
-        <v>6786832</v>
+        <v>6786773</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5115,10 +5155,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122567025</v>
+        <v>122566911</v>
       </c>
       <c r="B45" t="n">
-        <v>78301</v>
+        <v>91124</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5131,21 +5171,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5155,10 +5195,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488378</v>
+        <v>488882</v>
       </c>
       <c r="R45" t="n">
-        <v>6786805</v>
+        <v>6786609</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5217,10 +5257,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122566968</v>
+        <v>122566912</v>
       </c>
       <c r="B46" t="n">
-        <v>78656</v>
+        <v>91124</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5233,21 +5273,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5257,10 +5297,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488431</v>
+        <v>488895</v>
       </c>
       <c r="R46" t="n">
-        <v>6786772</v>
+        <v>6786588</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5319,10 +5359,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122566974</v>
+        <v>122567305</v>
       </c>
       <c r="B47" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5331,38 +5371,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488486</v>
+        <v>488519</v>
       </c>
       <c r="R47" t="n">
-        <v>6786718</v>
+        <v>6786844</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5421,10 +5466,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122566994</v>
+        <v>122567307</v>
       </c>
       <c r="B48" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5433,38 +5478,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488883</v>
+        <v>488535</v>
       </c>
       <c r="R48" t="n">
-        <v>6786645</v>
+        <v>6786843</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5523,10 +5573,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122566998</v>
+        <v>122567313</v>
       </c>
       <c r="B49" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5535,38 +5585,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488700</v>
+        <v>488616</v>
       </c>
       <c r="R49" t="n">
-        <v>6786744</v>
+        <v>6786649</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5625,7 +5680,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122566979</v>
+        <v>122566987</v>
       </c>
       <c r="B50" t="n">
         <v>78656</v>
@@ -5665,10 +5720,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488583</v>
+        <v>488735</v>
       </c>
       <c r="R50" t="n">
-        <v>6786676</v>
+        <v>6786569</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5727,7 +5782,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122566957</v>
+        <v>122566990</v>
       </c>
       <c r="B51" t="n">
         <v>78656</v>
@@ -5767,10 +5822,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488300</v>
+        <v>488840</v>
       </c>
       <c r="R51" t="n">
-        <v>6786820</v>
+        <v>6786622</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5829,10 +5884,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567010</v>
+        <v>122566896</v>
       </c>
       <c r="B52" t="n">
-        <v>78656</v>
+        <v>90833</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5845,21 +5900,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5869,10 +5924,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488442</v>
+        <v>488882</v>
       </c>
       <c r="R52" t="n">
-        <v>6786881</v>
+        <v>6786607</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5931,10 +5986,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122566907</v>
+        <v>122566898</v>
       </c>
       <c r="B53" t="n">
-        <v>57399</v>
+        <v>57536</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5947,39 +6002,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488852</v>
+        <v>488296</v>
       </c>
       <c r="R53" t="n">
-        <v>6786673</v>
+        <v>6786844</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6038,10 +6088,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122566909</v>
+        <v>122567012</v>
       </c>
       <c r="B54" t="n">
-        <v>91277</v>
+        <v>78656</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6050,25 +6100,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6078,10 +6128,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488882</v>
+        <v>488420</v>
       </c>
       <c r="R54" t="n">
-        <v>6786607</v>
+        <v>6786898</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6140,10 +6190,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122567030</v>
+        <v>122566995</v>
       </c>
       <c r="B55" t="n">
-        <v>78301</v>
+        <v>78656</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6156,21 +6206,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6180,10 +6230,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488769</v>
+        <v>488833</v>
       </c>
       <c r="R55" t="n">
-        <v>6786552</v>
+        <v>6786674</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6242,7 +6292,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122567006</v>
+        <v>122566984</v>
       </c>
       <c r="B56" t="n">
         <v>78656</v>
@@ -6282,10 +6332,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488556</v>
+        <v>488699</v>
       </c>
       <c r="R56" t="n">
-        <v>6786835</v>
+        <v>6786596</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6344,10 +6394,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567320</v>
+        <v>122567005</v>
       </c>
       <c r="B57" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6356,43 +6406,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488833</v>
+        <v>488415</v>
       </c>
       <c r="R57" t="n">
-        <v>6786674</v>
+        <v>6786889</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6451,10 +6496,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122567295</v>
+        <v>122566889</v>
       </c>
       <c r="B58" t="n">
-        <v>8441</v>
+        <v>79274</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6463,43 +6508,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488850</v>
+        <v>488296</v>
       </c>
       <c r="R58" t="n">
-        <v>6786668</v>
+        <v>6786844</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6558,7 +6598,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122567298</v>
+        <v>122567293</v>
       </c>
       <c r="B59" t="n">
         <v>8441</v>
@@ -6603,10 +6643,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488789</v>
+        <v>488790</v>
       </c>
       <c r="R59" t="n">
-        <v>6786702</v>
+        <v>6786547</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6665,7 +6705,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122567294</v>
+        <v>122567292</v>
       </c>
       <c r="B60" t="n">
         <v>8441</v>
@@ -6710,10 +6750,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488801</v>
+        <v>488533</v>
       </c>
       <c r="R60" t="n">
-        <v>6786563</v>
+        <v>6786690</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6772,10 +6812,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122567028</v>
+        <v>122567291</v>
       </c>
       <c r="B61" t="n">
-        <v>78301</v>
+        <v>8441</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6784,38 +6824,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488611</v>
+        <v>488440</v>
       </c>
       <c r="R61" t="n">
-        <v>6786649</v>
+        <v>6786759</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6874,10 +6919,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122567000</v>
+        <v>122566913</v>
       </c>
       <c r="B62" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6890,34 +6935,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488678</v>
+        <v>488602</v>
       </c>
       <c r="R62" t="n">
-        <v>6786753</v>
+        <v>6786666</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6950,6 +7000,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6976,10 +7031,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122566983</v>
+        <v>122567310</v>
       </c>
       <c r="B63" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6988,38 +7043,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488609</v>
+        <v>488294</v>
       </c>
       <c r="R63" t="n">
-        <v>6786648</v>
+        <v>6786825</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7078,10 +7138,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122566956</v>
+        <v>122567296</v>
       </c>
       <c r="B64" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7090,38 +7150,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488309</v>
+        <v>488834</v>
       </c>
       <c r="R64" t="n">
-        <v>6786859</v>
+        <v>6786685</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7180,10 +7245,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122567012</v>
+        <v>122567324</v>
       </c>
       <c r="B65" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7192,38 +7257,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488420</v>
+        <v>488638</v>
       </c>
       <c r="R65" t="n">
-        <v>6786898</v>
+        <v>6786764</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7282,7 +7352,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122566985</v>
+        <v>122566979</v>
       </c>
       <c r="B66" t="n">
         <v>78656</v>
@@ -7322,10 +7392,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488698</v>
+        <v>488583</v>
       </c>
       <c r="R66" t="n">
-        <v>6786584</v>
+        <v>6786676</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7384,7 +7454,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122567003</v>
+        <v>122566958</v>
       </c>
       <c r="B67" t="n">
         <v>78656</v>
@@ -7424,10 +7494,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488550</v>
+        <v>488301</v>
       </c>
       <c r="R67" t="n">
-        <v>6786822</v>
+        <v>6786839</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7486,10 +7556,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122567319</v>
+        <v>122566966</v>
       </c>
       <c r="B68" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7498,43 +7568,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488869</v>
+        <v>488390</v>
       </c>
       <c r="R68" t="n">
-        <v>6786685</v>
+        <v>6786813</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7593,10 +7658,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122567289</v>
+        <v>122566994</v>
       </c>
       <c r="B69" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7605,43 +7670,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488322</v>
+        <v>488883</v>
       </c>
       <c r="R69" t="n">
-        <v>6786810</v>
+        <v>6786645</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7700,10 +7760,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122567313</v>
+        <v>122566904</v>
       </c>
       <c r="B70" t="n">
-        <v>8441</v>
+        <v>90853</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7712,43 +7772,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488616</v>
+        <v>488552</v>
       </c>
       <c r="R70" t="n">
-        <v>6786649</v>
+        <v>6786834</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7807,10 +7862,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122567004</v>
+        <v>122566903</v>
       </c>
       <c r="B71" t="n">
-        <v>78656</v>
+        <v>90853</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7823,21 +7878,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7847,10 +7902,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488475</v>
+        <v>488770</v>
       </c>
       <c r="R71" t="n">
-        <v>6786864</v>
+        <v>6786732</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7909,10 +7964,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122566903</v>
+        <v>122566980</v>
       </c>
       <c r="B72" t="n">
-        <v>90859</v>
+        <v>78656</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7925,21 +7980,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7949,10 +8004,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488770</v>
+        <v>488590</v>
       </c>
       <c r="R72" t="n">
-        <v>6786732</v>
+        <v>6786665</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8011,10 +8066,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122567315</v>
+        <v>122567016</v>
       </c>
       <c r="B73" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8023,43 +8078,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488773</v>
+        <v>488360</v>
       </c>
       <c r="R73" t="n">
-        <v>6786561</v>
+        <v>6786913</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8118,10 +8168,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122567307</v>
+        <v>122567003</v>
       </c>
       <c r="B74" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8130,43 +8180,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488535</v>
+        <v>488550</v>
       </c>
       <c r="R74" t="n">
-        <v>6786843</v>
+        <v>6786822</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8225,10 +8270,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122566954</v>
+        <v>122567297</v>
       </c>
       <c r="B75" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8237,38 +8282,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488416</v>
+        <v>488804</v>
       </c>
       <c r="R75" t="n">
-        <v>6786896</v>
+        <v>6786700</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8327,10 +8377,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122566912</v>
+        <v>122567322</v>
       </c>
       <c r="B76" t="n">
-        <v>91123</v>
+        <v>8441</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8339,38 +8389,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>658</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488895</v>
+        <v>488700</v>
       </c>
       <c r="R76" t="n">
-        <v>6786588</v>
+        <v>6786746</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8429,10 +8484,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122567027</v>
+        <v>122566965</v>
       </c>
       <c r="B77" t="n">
-        <v>78301</v>
+        <v>78656</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8445,21 +8500,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8469,10 +8524,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488618</v>
+        <v>488378</v>
       </c>
       <c r="R77" t="n">
-        <v>6786631</v>
+        <v>6786805</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8531,10 +8586,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122566894</v>
+        <v>122566988</v>
       </c>
       <c r="B78" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8547,21 +8602,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8571,10 +8626,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488182</v>
+        <v>488803</v>
       </c>
       <c r="R78" t="n">
-        <v>6787001</v>
+        <v>6786562</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8633,10 +8688,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122567032</v>
+        <v>122567026</v>
       </c>
       <c r="B79" t="n">
-        <v>5173</v>
+        <v>78301</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8645,43 +8700,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100526</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488901</v>
+        <v>488539</v>
       </c>
       <c r="R79" t="n">
-        <v>6786589</v>
+        <v>6786689</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8740,10 +8790,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122566898</v>
+        <v>122566890</v>
       </c>
       <c r="B80" t="n">
-        <v>57536</v>
+        <v>79274</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8756,21 +8806,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8780,10 +8830,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488296</v>
+        <v>488572</v>
       </c>
       <c r="R80" t="n">
-        <v>6786844</v>
+        <v>6786674</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8842,7 +8892,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122567016</v>
+        <v>122566960</v>
       </c>
       <c r="B81" t="n">
         <v>78656</v>
@@ -8882,10 +8932,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488360</v>
+        <v>488322</v>
       </c>
       <c r="R81" t="n">
-        <v>6786913</v>
+        <v>6786853</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8944,7 +8994,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122566969</v>
+        <v>122567023</v>
       </c>
       <c r="B82" t="n">
         <v>78656</v>
@@ -8984,10 +9034,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488452</v>
+        <v>488135</v>
       </c>
       <c r="R82" t="n">
-        <v>6786772</v>
+        <v>6787033</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9046,7 +9096,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122567022</v>
+        <v>122567011</v>
       </c>
       <c r="B83" t="n">
         <v>78656</v>
@@ -9086,10 +9136,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488137</v>
+        <v>488427</v>
       </c>
       <c r="R83" t="n">
-        <v>6787026</v>
+        <v>6786888</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9148,10 +9198,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122567308</v>
+        <v>122566971</v>
       </c>
       <c r="B84" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9160,43 +9210,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488669</v>
+        <v>488461</v>
       </c>
       <c r="R84" t="n">
-        <v>6786761</v>
+        <v>6786736</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9255,10 +9300,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122567300</v>
+        <v>122567019</v>
       </c>
       <c r="B85" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9267,43 +9312,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488768</v>
+        <v>488297</v>
       </c>
       <c r="R85" t="n">
-        <v>6786742</v>
+        <v>6786946</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9362,10 +9402,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122567326</v>
+        <v>122567018</v>
       </c>
       <c r="B86" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9374,43 +9414,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488545</v>
+        <v>488345</v>
       </c>
       <c r="R86" t="n">
-        <v>6786849</v>
+        <v>6786910</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9469,10 +9504,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122567299</v>
+        <v>122567013</v>
       </c>
       <c r="B87" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9481,43 +9516,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488786</v>
+        <v>488389</v>
       </c>
       <c r="R87" t="n">
-        <v>6786723</v>
+        <v>6786901</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9576,10 +9606,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122567323</v>
+        <v>122567004</v>
       </c>
       <c r="B88" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9588,43 +9618,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488686</v>
+        <v>488475</v>
       </c>
       <c r="R88" t="n">
-        <v>6786745</v>
+        <v>6786864</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9683,7 +9708,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122566962</v>
+        <v>122566956</v>
       </c>
       <c r="B89" t="n">
         <v>78656</v>
@@ -9723,10 +9748,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488324</v>
+        <v>488309</v>
       </c>
       <c r="R89" t="n">
-        <v>6786843</v>
+        <v>6786859</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9785,10 +9810,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122566970</v>
+        <v>122567028</v>
       </c>
       <c r="B90" t="n">
-        <v>78656</v>
+        <v>78301</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9801,21 +9826,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9825,10 +9850,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488469</v>
+        <v>488611</v>
       </c>
       <c r="R90" t="n">
-        <v>6786751</v>
+        <v>6786649</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9887,10 +9912,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122567011</v>
+        <v>122567303</v>
       </c>
       <c r="B91" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9899,38 +9924,43 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488427</v>
+        <v>488600</v>
       </c>
       <c r="R91" t="n">
-        <v>6786888</v>
+        <v>6786772</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9989,7 +10019,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122566982</v>
+        <v>122566991</v>
       </c>
       <c r="B92" t="n">
         <v>78656</v>
@@ -10029,10 +10059,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488600</v>
+        <v>488918</v>
       </c>
       <c r="R92" t="n">
-        <v>6786662</v>
+        <v>6786607</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10091,10 +10121,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122567296</v>
+        <v>122566902</v>
       </c>
       <c r="B93" t="n">
-        <v>8441</v>
+        <v>90853</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10103,43 +10133,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488834</v>
+        <v>488397</v>
       </c>
       <c r="R93" t="n">
-        <v>6786685</v>
+        <v>6786809</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10198,7 +10223,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122567321</v>
+        <v>122567308</v>
       </c>
       <c r="B94" t="n">
         <v>8441</v>
@@ -10243,10 +10268,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488817</v>
+        <v>488669</v>
       </c>
       <c r="R94" t="n">
-        <v>6786693</v>
+        <v>6786761</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10305,10 +10330,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122566905</v>
+        <v>122567325</v>
       </c>
       <c r="B95" t="n">
-        <v>57399</v>
+        <v>8441</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10317,31 +10342,31 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -10350,10 +10375,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>488294</v>
+        <v>488576</v>
       </c>
       <c r="R95" t="n">
-        <v>6786826</v>
+        <v>6786782</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10412,10 +10437,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122566896</v>
+        <v>122567289</v>
       </c>
       <c r="B96" t="n">
-        <v>90839</v>
+        <v>8441</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10424,38 +10449,43 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>488882</v>
+        <v>488322</v>
       </c>
       <c r="R96" t="n">
-        <v>6786607</v>
+        <v>6786810</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10514,10 +10544,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122567029</v>
+        <v>122566961</v>
       </c>
       <c r="B97" t="n">
-        <v>78301</v>
+        <v>78656</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10530,21 +10560,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10554,10 +10584,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>488664</v>
+        <v>488327</v>
       </c>
       <c r="R97" t="n">
-        <v>6786615</v>
+        <v>6786847</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10616,7 +10646,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122567009</v>
+        <v>122566997</v>
       </c>
       <c r="B98" t="n">
         <v>78656</v>
@@ -10656,10 +10686,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>488465</v>
+        <v>488731</v>
       </c>
       <c r="R98" t="n">
-        <v>6786880</v>
+        <v>6786733</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10718,7 +10748,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122566966</v>
+        <v>122567007</v>
       </c>
       <c r="B99" t="n">
         <v>78656</v>
@@ -10758,10 +10788,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>488390</v>
+        <v>488530</v>
       </c>
       <c r="R99" t="n">
-        <v>6786813</v>
+        <v>6786847</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10820,10 +10850,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122566897</v>
+        <v>122567298</v>
       </c>
       <c r="B100" t="n">
-        <v>90839</v>
+        <v>8441</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10832,38 +10862,43 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>488892</v>
+        <v>488789</v>
       </c>
       <c r="R100" t="n">
-        <v>6786591</v>
+        <v>6786702</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10922,10 +10957,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122567290</v>
+        <v>122566894</v>
       </c>
       <c r="B101" t="n">
-        <v>8441</v>
+        <v>79274</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10934,43 +10969,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>488345</v>
+        <v>488182</v>
       </c>
       <c r="R101" t="n">
-        <v>6786796</v>
+        <v>6787001</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11029,10 +11059,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122567310</v>
+        <v>122567017</v>
       </c>
       <c r="B102" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11041,43 +11071,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>488294</v>
+        <v>488353</v>
       </c>
       <c r="R102" t="n">
-        <v>6786825</v>
+        <v>6786911</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11136,10 +11161,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122567297</v>
+        <v>122567000</v>
       </c>
       <c r="B103" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11148,43 +11173,38 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>488804</v>
+        <v>488678</v>
       </c>
       <c r="R103" t="n">
-        <v>6786700</v>
+        <v>6786753</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11243,10 +11263,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122567305</v>
+        <v>122566996</v>
       </c>
       <c r="B104" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11255,43 +11275,38 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488519</v>
+        <v>488757</v>
       </c>
       <c r="R104" t="n">
-        <v>6786844</v>
+        <v>6786723</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11350,10 +11365,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122567324</v>
+        <v>122567022</v>
       </c>
       <c r="B105" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11362,43 +11377,38 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488638</v>
+        <v>488137</v>
       </c>
       <c r="R105" t="n">
-        <v>6786764</v>
+        <v>6787026</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11457,10 +11467,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122566973</v>
+        <v>122567024</v>
       </c>
       <c r="B106" t="n">
-        <v>78656</v>
+        <v>91085</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11469,25 +11479,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11497,10 +11507,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488482</v>
+        <v>488663</v>
       </c>
       <c r="R106" t="n">
-        <v>6786720</v>
+        <v>6786615</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11559,10 +11569,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122566958</v>
+        <v>122566897</v>
       </c>
       <c r="B107" t="n">
-        <v>78656</v>
+        <v>90833</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11575,21 +11585,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11599,10 +11609,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488301</v>
+        <v>488892</v>
       </c>
       <c r="R107" t="n">
-        <v>6786839</v>
+        <v>6786591</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11661,10 +11671,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122567005</v>
+        <v>122566952</v>
       </c>
       <c r="B108" t="n">
-        <v>78656</v>
+        <v>80613</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11677,21 +11687,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11701,10 +11711,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>488415</v>
+        <v>488363</v>
       </c>
       <c r="R108" t="n">
-        <v>6786889</v>
+        <v>6786907</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11763,10 +11773,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122566961</v>
+        <v>122567027</v>
       </c>
       <c r="B109" t="n">
-        <v>78656</v>
+        <v>78301</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11779,21 +11789,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11803,10 +11813,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488327</v>
+        <v>488618</v>
       </c>
       <c r="R109" t="n">
-        <v>6786847</v>
+        <v>6786631</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11865,10 +11875,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122566986</v>
+        <v>122567326</v>
       </c>
       <c r="B110" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11877,38 +11887,43 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>488714</v>
+        <v>488545</v>
       </c>
       <c r="R110" t="n">
-        <v>6786574</v>
+        <v>6786849</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11967,7 +11982,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122566967</v>
+        <v>122566999</v>
       </c>
       <c r="B111" t="n">
         <v>78656</v>
@@ -12007,10 +12022,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>488387</v>
+        <v>488686</v>
       </c>
       <c r="R111" t="n">
-        <v>6786773</v>
+        <v>6786738</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12069,10 +12084,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122566904</v>
+        <v>122566985</v>
       </c>
       <c r="B112" t="n">
-        <v>90859</v>
+        <v>78656</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12085,21 +12100,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12109,10 +12124,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>488552</v>
+        <v>488698</v>
       </c>
       <c r="R112" t="n">
-        <v>6786834</v>
+        <v>6786584</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12171,10 +12186,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122566901</v>
+        <v>122567001</v>
       </c>
       <c r="B113" t="n">
-        <v>57536</v>
+        <v>78656</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12187,21 +12202,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12211,10 +12226,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488142</v>
+        <v>488583</v>
       </c>
       <c r="R113" t="n">
-        <v>6787017</v>
+        <v>6786774</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12273,7 +12288,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122567293</v>
+        <v>122567294</v>
       </c>
       <c r="B114" t="n">
         <v>8441</v>
@@ -12318,10 +12333,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488790</v>
+        <v>488801</v>
       </c>
       <c r="R114" t="n">
-        <v>6786547</v>
+        <v>6786563</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12380,7 +12395,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122567309</v>
+        <v>122567327</v>
       </c>
       <c r="B115" t="n">
         <v>8441</v>
@@ -12425,10 +12440,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>488707</v>
+        <v>488442</v>
       </c>
       <c r="R115" t="n">
-        <v>6786747</v>
+        <v>6786881</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12487,10 +12502,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122567311</v>
+        <v>122567014</v>
       </c>
       <c r="B116" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12499,43 +12514,38 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>488332</v>
+        <v>488383</v>
       </c>
       <c r="R116" t="n">
-        <v>6786824</v>
+        <v>6786912</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12594,10 +12604,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122567327</v>
+        <v>122566969</v>
       </c>
       <c r="B117" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12606,43 +12616,38 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>488442</v>
+        <v>488452</v>
       </c>
       <c r="R117" t="n">
-        <v>6786881</v>
+        <v>6786772</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12701,10 +12706,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122567317</v>
+        <v>122567010</v>
       </c>
       <c r="B118" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12713,43 +12718,38 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>488892</v>
+        <v>488442</v>
       </c>
       <c r="R118" t="n">
-        <v>6786620</v>
+        <v>6786881</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12808,10 +12808,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122567024</v>
+        <v>122566983</v>
       </c>
       <c r="B119" t="n">
-        <v>91084</v>
+        <v>78656</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12820,25 +12820,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12848,10 +12848,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>488663</v>
+        <v>488609</v>
       </c>
       <c r="R119" t="n">
-        <v>6786615</v>
+        <v>6786648</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12910,10 +12910,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122567026</v>
+        <v>122566968</v>
       </c>
       <c r="B120" t="n">
-        <v>78301</v>
+        <v>78656</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12926,21 +12926,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12950,10 +12950,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>488539</v>
+        <v>488431</v>
       </c>
       <c r="R120" t="n">
-        <v>6786689</v>
+        <v>6786772</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13012,10 +13012,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122567001</v>
+        <v>122566901</v>
       </c>
       <c r="B121" t="n">
-        <v>78656</v>
+        <v>57536</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13028,21 +13028,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13052,10 +13052,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488583</v>
+        <v>488142</v>
       </c>
       <c r="R121" t="n">
-        <v>6786774</v>
+        <v>6787017</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13114,10 +13114,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122566965</v>
+        <v>122566899</v>
       </c>
       <c r="B122" t="n">
-        <v>78656</v>
+        <v>57536</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13130,21 +13130,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13154,10 +13154,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488378</v>
+        <v>488482</v>
       </c>
       <c r="R122" t="n">
-        <v>6786805</v>
+        <v>6786720</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13216,10 +13216,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122567019</v>
+        <v>122567314</v>
       </c>
       <c r="B123" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13228,38 +13228,43 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>488297</v>
+        <v>488747</v>
       </c>
       <c r="R123" t="n">
-        <v>6786946</v>
+        <v>6786566</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13318,10 +13323,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122566913</v>
+        <v>122567300</v>
       </c>
       <c r="B124" t="n">
-        <v>57383</v>
+        <v>8441</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13330,31 +13335,31 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -13363,10 +13368,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>488602</v>
+        <v>488768</v>
       </c>
       <c r="R124" t="n">
-        <v>6786666</v>
+        <v>6786742</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13399,11 +13404,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13537,10 +13537,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122566908</v>
+        <v>122567315</v>
       </c>
       <c r="B126" t="n">
-        <v>57399</v>
+        <v>8441</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13549,35 +13549,31 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -13586,10 +13582,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>488892</v>
+        <v>488773</v>
       </c>
       <c r="R126" t="n">
-        <v>6786620</v>
+        <v>6786561</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13648,7 +13644,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122566991</v>
+        <v>122566974</v>
       </c>
       <c r="B127" t="n">
         <v>78656</v>
@@ -13688,10 +13684,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>488918</v>
+        <v>488486</v>
       </c>
       <c r="R127" t="n">
-        <v>6786607</v>
+        <v>6786718</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13750,10 +13746,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122566959</v>
+        <v>122566892</v>
       </c>
       <c r="B128" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13766,21 +13762,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13790,10 +13786,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>488317</v>
+        <v>488699</v>
       </c>
       <c r="R128" t="n">
-        <v>6786858</v>
+        <v>6786599</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13852,7 +13848,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122566964</v>
+        <v>122566982</v>
       </c>
       <c r="B129" t="n">
         <v>78656</v>
@@ -13892,10 +13888,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>488351</v>
+        <v>488600</v>
       </c>
       <c r="R129" t="n">
-        <v>6786831</v>
+        <v>6786662</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13954,7 +13950,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122566996</v>
+        <v>122566998</v>
       </c>
       <c r="B130" t="n">
         <v>78656</v>
@@ -13994,10 +13990,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>488757</v>
+        <v>488700</v>
       </c>
       <c r="R130" t="n">
-        <v>6786723</v>
+        <v>6786744</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14056,10 +14052,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122567023</v>
+        <v>122566908</v>
       </c>
       <c r="B131" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14072,34 +14068,43 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>488135</v>
+        <v>488892</v>
       </c>
       <c r="R131" t="n">
-        <v>6787033</v>
+        <v>6786620</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14158,10 +14163,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122567314</v>
+        <v>122567020</v>
       </c>
       <c r="B132" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14170,43 +14175,38 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>488747</v>
+        <v>488185</v>
       </c>
       <c r="R132" t="n">
-        <v>6786566</v>
+        <v>6787005</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14265,7 +14265,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>122567306</v>
+        <v>122567321</v>
       </c>
       <c r="B133" t="n">
         <v>8441</v>
@@ -14301,7 +14301,7 @@
       <c r="I133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -14310,10 +14310,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>488556</v>
+        <v>488817</v>
       </c>
       <c r="R133" t="n">
-        <v>6786835</v>
+        <v>6786693</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>

--- a/artfynd/A 61338-2024 artfynd.xlsx
+++ b/artfynd/A 61338-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567304</v>
+        <v>122567326</v>
       </c>
       <c r="B2" t="n">
         <v>8441</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488591</v>
+        <v>488545</v>
       </c>
       <c r="R2" t="n">
-        <v>6786769</v>
+        <v>6786849</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122566981</v>
+        <v>122567324</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +794,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488599</v>
+        <v>488638</v>
       </c>
       <c r="R3" t="n">
-        <v>6786673</v>
+        <v>6786764</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567002</v>
+        <v>122567306</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,38 +901,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488569</v>
+        <v>488556</v>
       </c>
       <c r="R4" t="n">
-        <v>6786787</v>
+        <v>6786835</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122566970</v>
+        <v>122567011</v>
       </c>
       <c r="B5" t="n">
         <v>78656</v>
@@ -1026,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488469</v>
+        <v>488427</v>
       </c>
       <c r="R5" t="n">
-        <v>6786751</v>
+        <v>6786888</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567025</v>
+        <v>122567006</v>
       </c>
       <c r="B6" t="n">
-        <v>78301</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488378</v>
+        <v>488556</v>
       </c>
       <c r="R6" t="n">
-        <v>6786805</v>
+        <v>6786835</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567290</v>
+        <v>122567005</v>
       </c>
       <c r="B7" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,43 +1212,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488345</v>
+        <v>488415</v>
       </c>
       <c r="R7" t="n">
-        <v>6786796</v>
+        <v>6786889</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567320</v>
+        <v>122566964</v>
       </c>
       <c r="B8" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,43 +1314,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488833</v>
+        <v>488351</v>
       </c>
       <c r="R8" t="n">
-        <v>6786674</v>
+        <v>6786831</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122567311</v>
+        <v>122567003</v>
       </c>
       <c r="B9" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,43 +1416,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488332</v>
+        <v>488550</v>
       </c>
       <c r="R9" t="n">
-        <v>6786824</v>
+        <v>6786822</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122567299</v>
+        <v>122566966</v>
       </c>
       <c r="B10" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1523,43 +1518,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488786</v>
+        <v>488390</v>
       </c>
       <c r="R10" t="n">
-        <v>6786723</v>
+        <v>6786813</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567295</v>
+        <v>122566991</v>
       </c>
       <c r="B11" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1630,43 +1620,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488850</v>
+        <v>488918</v>
       </c>
       <c r="R11" t="n">
-        <v>6786668</v>
+        <v>6786607</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,7 +1710,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566954</v>
+        <v>122567015</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1765,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488416</v>
+        <v>488366</v>
       </c>
       <c r="R12" t="n">
-        <v>6786896</v>
+        <v>6786907</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,7 +1812,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566963</v>
+        <v>122566975</v>
       </c>
       <c r="B13" t="n">
         <v>78656</v>
@@ -1867,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488341</v>
+        <v>488515</v>
       </c>
       <c r="R13" t="n">
-        <v>6786832</v>
+        <v>6786685</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566978</v>
+        <v>122567014</v>
       </c>
       <c r="B14" t="n">
         <v>78656</v>
@@ -1969,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488583</v>
+        <v>488383</v>
       </c>
       <c r="R14" t="n">
-        <v>6786679</v>
+        <v>6786912</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567029</v>
+        <v>122567013</v>
       </c>
       <c r="B15" t="n">
-        <v>78301</v>
+        <v>78656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2047,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2071,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488664</v>
+        <v>488389</v>
       </c>
       <c r="R15" t="n">
-        <v>6786615</v>
+        <v>6786901</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567312</v>
+        <v>122567032</v>
       </c>
       <c r="B16" t="n">
-        <v>8441</v>
+        <v>5173</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2149,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2178,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488341</v>
+        <v>488901</v>
       </c>
       <c r="R16" t="n">
-        <v>6786832</v>
+        <v>6786589</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2240,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566962</v>
+        <v>122567309</v>
       </c>
       <c r="B17" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2252,38 +2237,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488324</v>
+        <v>488707</v>
       </c>
       <c r="R17" t="n">
-        <v>6786843</v>
+        <v>6786747</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2342,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566957</v>
+        <v>122566901</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>57536</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2358,21 +2348,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2382,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488300</v>
+        <v>488142</v>
       </c>
       <c r="R18" t="n">
-        <v>6786820</v>
+        <v>6787017</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2444,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566964</v>
+        <v>122566894</v>
       </c>
       <c r="B19" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2460,21 +2450,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2484,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488351</v>
+        <v>488182</v>
       </c>
       <c r="R19" t="n">
-        <v>6786831</v>
+        <v>6787001</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2546,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566907</v>
+        <v>122567017</v>
       </c>
       <c r="B20" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2562,39 +2552,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488852</v>
+        <v>488353</v>
       </c>
       <c r="R20" t="n">
-        <v>6786673</v>
+        <v>6786911</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566909</v>
+        <v>122566970</v>
       </c>
       <c r="B21" t="n">
-        <v>91278</v>
+        <v>78656</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2665,25 +2650,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2693,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488882</v>
+        <v>488469</v>
       </c>
       <c r="R21" t="n">
-        <v>6786607</v>
+        <v>6786751</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2755,10 +2740,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567316</v>
+        <v>122566897</v>
       </c>
       <c r="B22" t="n">
-        <v>8441</v>
+        <v>90833</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2767,43 +2752,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488900</v>
+        <v>488892</v>
       </c>
       <c r="R22" t="n">
-        <v>6786628</v>
+        <v>6786591</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2862,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566893</v>
+        <v>122567307</v>
       </c>
       <c r="B23" t="n">
-        <v>79274</v>
+        <v>8441</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2874,38 +2854,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488693</v>
+        <v>488535</v>
       </c>
       <c r="R23" t="n">
-        <v>6786741</v>
+        <v>6786843</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2964,10 +2949,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567319</v>
+        <v>122566890</v>
       </c>
       <c r="B24" t="n">
-        <v>8441</v>
+        <v>79274</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2976,43 +2961,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488869</v>
+        <v>488572</v>
       </c>
       <c r="R24" t="n">
-        <v>6786685</v>
+        <v>6786674</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3071,10 +3051,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122567309</v>
+        <v>122566987</v>
       </c>
       <c r="B25" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3083,43 +3063,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488707</v>
+        <v>488735</v>
       </c>
       <c r="R25" t="n">
-        <v>6786747</v>
+        <v>6786569</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3178,10 +3153,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567318</v>
+        <v>122566969</v>
       </c>
       <c r="B26" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3190,43 +3165,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488883</v>
+        <v>488452</v>
       </c>
       <c r="R26" t="n">
-        <v>6786645</v>
+        <v>6786772</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3285,7 +3255,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566973</v>
+        <v>122566986</v>
       </c>
       <c r="B27" t="n">
         <v>78656</v>
@@ -3325,10 +3295,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488482</v>
+        <v>488714</v>
       </c>
       <c r="R27" t="n">
-        <v>6786720</v>
+        <v>6786574</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3387,7 +3357,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567009</v>
+        <v>122566983</v>
       </c>
       <c r="B28" t="n">
         <v>78656</v>
@@ -3427,10 +3397,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488465</v>
+        <v>488609</v>
       </c>
       <c r="R28" t="n">
-        <v>6786880</v>
+        <v>6786648</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3489,7 +3459,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567015</v>
+        <v>122566963</v>
       </c>
       <c r="B29" t="n">
         <v>78656</v>
@@ -3529,10 +3499,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488366</v>
+        <v>488341</v>
       </c>
       <c r="R29" t="n">
-        <v>6786907</v>
+        <v>6786832</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3591,10 +3561,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122566891</v>
+        <v>122566898</v>
       </c>
       <c r="B30" t="n">
-        <v>79274</v>
+        <v>57536</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3607,21 +3577,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3631,10 +3601,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488616</v>
+        <v>488296</v>
       </c>
       <c r="R30" t="n">
-        <v>6786648</v>
+        <v>6786844</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3693,10 +3663,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567006</v>
+        <v>122567321</v>
       </c>
       <c r="B31" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3705,38 +3675,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488556</v>
+        <v>488817</v>
       </c>
       <c r="R31" t="n">
-        <v>6786835</v>
+        <v>6786693</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3795,10 +3770,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122566986</v>
+        <v>122567310</v>
       </c>
       <c r="B32" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3807,38 +3782,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488714</v>
+        <v>488294</v>
       </c>
       <c r="R32" t="n">
-        <v>6786574</v>
+        <v>6786825</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3897,10 +3877,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122567030</v>
+        <v>122567318</v>
       </c>
       <c r="B33" t="n">
-        <v>78301</v>
+        <v>8441</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3909,38 +3889,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488769</v>
+        <v>488883</v>
       </c>
       <c r="R33" t="n">
-        <v>6786552</v>
+        <v>6786645</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3999,7 +3984,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567317</v>
+        <v>122567301</v>
       </c>
       <c r="B34" t="n">
         <v>8441</v>
@@ -4035,7 +4020,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4044,10 +4029,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488892</v>
+        <v>488718</v>
       </c>
       <c r="R34" t="n">
-        <v>6786620</v>
+        <v>6786752</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4217,10 +4202,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122566977</v>
+        <v>122566891</v>
       </c>
       <c r="B36" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4233,21 +4218,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4257,10 +4242,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488515</v>
+        <v>488616</v>
       </c>
       <c r="R36" t="n">
-        <v>6786685</v>
+        <v>6786648</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4319,7 +4304,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122566972</v>
+        <v>122566988</v>
       </c>
       <c r="B37" t="n">
         <v>78656</v>
@@ -4359,10 +4344,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488465</v>
+        <v>488803</v>
       </c>
       <c r="R37" t="n">
-        <v>6786729</v>
+        <v>6786562</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4421,7 +4406,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567008</v>
+        <v>122566973</v>
       </c>
       <c r="B38" t="n">
         <v>78656</v>
@@ -4461,10 +4446,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488495</v>
+        <v>488482</v>
       </c>
       <c r="R38" t="n">
-        <v>6786888</v>
+        <v>6786720</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4523,10 +4508,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122567032</v>
+        <v>122567000</v>
       </c>
       <c r="B39" t="n">
-        <v>5173</v>
+        <v>78656</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4535,43 +4520,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488901</v>
+        <v>488678</v>
       </c>
       <c r="R39" t="n">
-        <v>6786589</v>
+        <v>6786753</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4630,7 +4610,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122566905</v>
+        <v>122566907</v>
       </c>
       <c r="B40" t="n">
         <v>57399</v>
@@ -4666,7 +4646,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4675,10 +4655,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488294</v>
+        <v>488852</v>
       </c>
       <c r="R40" t="n">
-        <v>6786826</v>
+        <v>6786673</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4737,7 +4717,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567306</v>
+        <v>122567319</v>
       </c>
       <c r="B41" t="n">
         <v>8441</v>
@@ -4773,7 +4753,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4782,10 +4762,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488556</v>
+        <v>488869</v>
       </c>
       <c r="R41" t="n">
-        <v>6786835</v>
+        <v>6786685</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4844,10 +4824,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567323</v>
+        <v>122567012</v>
       </c>
       <c r="B42" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4856,43 +4836,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488686</v>
+        <v>488420</v>
       </c>
       <c r="R42" t="n">
-        <v>6786745</v>
+        <v>6786898</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4951,10 +4926,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122566959</v>
+        <v>122567304</v>
       </c>
       <c r="B43" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4963,38 +4938,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488317</v>
+        <v>488591</v>
       </c>
       <c r="R43" t="n">
-        <v>6786858</v>
+        <v>6786769</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5053,7 +5033,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122566967</v>
+        <v>122566979</v>
       </c>
       <c r="B44" t="n">
         <v>78656</v>
@@ -5093,10 +5073,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488387</v>
+        <v>488583</v>
       </c>
       <c r="R44" t="n">
-        <v>6786773</v>
+        <v>6786676</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5155,10 +5135,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122566911</v>
+        <v>122566985</v>
       </c>
       <c r="B45" t="n">
-        <v>91124</v>
+        <v>78656</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5171,21 +5151,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5195,10 +5175,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488882</v>
+        <v>488698</v>
       </c>
       <c r="R45" t="n">
-        <v>6786609</v>
+        <v>6786584</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5257,10 +5237,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122566912</v>
+        <v>122567019</v>
       </c>
       <c r="B46" t="n">
-        <v>91124</v>
+        <v>78656</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5273,21 +5253,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5297,10 +5277,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488895</v>
+        <v>488297</v>
       </c>
       <c r="R46" t="n">
-        <v>6786588</v>
+        <v>6786946</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5359,10 +5339,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122567305</v>
+        <v>122566972</v>
       </c>
       <c r="B47" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5371,43 +5351,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488519</v>
+        <v>488465</v>
       </c>
       <c r="R47" t="n">
-        <v>6786844</v>
+        <v>6786729</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5466,10 +5441,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122567307</v>
+        <v>122567026</v>
       </c>
       <c r="B48" t="n">
-        <v>8441</v>
+        <v>78301</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5478,43 +5453,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488535</v>
+        <v>488539</v>
       </c>
       <c r="R48" t="n">
-        <v>6786843</v>
+        <v>6786689</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5573,7 +5543,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567313</v>
+        <v>122567289</v>
       </c>
       <c r="B49" t="n">
         <v>8441</v>
@@ -5609,7 +5579,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5618,10 +5588,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488616</v>
+        <v>488322</v>
       </c>
       <c r="R49" t="n">
-        <v>6786649</v>
+        <v>6786810</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5680,10 +5650,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122566987</v>
+        <v>122567024</v>
       </c>
       <c r="B50" t="n">
-        <v>78656</v>
+        <v>91085</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5692,25 +5662,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5720,10 +5690,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488735</v>
+        <v>488663</v>
       </c>
       <c r="R50" t="n">
-        <v>6786569</v>
+        <v>6786615</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5782,10 +5752,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122566990</v>
+        <v>122566904</v>
       </c>
       <c r="B51" t="n">
-        <v>78656</v>
+        <v>90853</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5798,21 +5768,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5822,10 +5792,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488840</v>
+        <v>488552</v>
       </c>
       <c r="R51" t="n">
-        <v>6786622</v>
+        <v>6786834</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5884,10 +5854,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122566896</v>
+        <v>122566984</v>
       </c>
       <c r="B52" t="n">
-        <v>90833</v>
+        <v>78656</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5900,21 +5870,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5924,10 +5894,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488882</v>
+        <v>488699</v>
       </c>
       <c r="R52" t="n">
-        <v>6786607</v>
+        <v>6786596</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5986,10 +5956,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122566898</v>
+        <v>122566981</v>
       </c>
       <c r="B53" t="n">
-        <v>57536</v>
+        <v>78656</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6002,21 +5972,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6026,10 +5996,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488296</v>
+        <v>488599</v>
       </c>
       <c r="R53" t="n">
-        <v>6786844</v>
+        <v>6786673</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6088,7 +6058,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567012</v>
+        <v>122566990</v>
       </c>
       <c r="B54" t="n">
         <v>78656</v>
@@ -6128,10 +6098,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488420</v>
+        <v>488840</v>
       </c>
       <c r="R54" t="n">
-        <v>6786898</v>
+        <v>6786622</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6190,7 +6160,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122566995</v>
+        <v>122566959</v>
       </c>
       <c r="B55" t="n">
         <v>78656</v>
@@ -6230,10 +6200,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488833</v>
+        <v>488317</v>
       </c>
       <c r="R55" t="n">
-        <v>6786674</v>
+        <v>6786858</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6292,10 +6262,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122566984</v>
+        <v>122567025</v>
       </c>
       <c r="B56" t="n">
-        <v>78656</v>
+        <v>78301</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6308,21 +6278,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6332,10 +6302,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488699</v>
+        <v>488378</v>
       </c>
       <c r="R56" t="n">
-        <v>6786596</v>
+        <v>6786805</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6394,10 +6364,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567005</v>
+        <v>122567030</v>
       </c>
       <c r="B57" t="n">
-        <v>78656</v>
+        <v>78301</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6410,21 +6380,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6434,10 +6404,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488415</v>
+        <v>488769</v>
       </c>
       <c r="R57" t="n">
-        <v>6786889</v>
+        <v>6786552</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6496,10 +6466,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122566889</v>
+        <v>122567028</v>
       </c>
       <c r="B58" t="n">
-        <v>79274</v>
+        <v>78301</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6512,21 +6482,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6536,10 +6506,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488296</v>
+        <v>488611</v>
       </c>
       <c r="R58" t="n">
-        <v>6786844</v>
+        <v>6786649</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6598,7 +6568,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122567293</v>
+        <v>122567294</v>
       </c>
       <c r="B59" t="n">
         <v>8441</v>
@@ -6643,10 +6613,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488790</v>
+        <v>488801</v>
       </c>
       <c r="R59" t="n">
-        <v>6786547</v>
+        <v>6786563</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6705,7 +6675,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122567292</v>
+        <v>122567325</v>
       </c>
       <c r="B60" t="n">
         <v>8441</v>
@@ -6741,7 +6711,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6750,10 +6720,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488533</v>
+        <v>488576</v>
       </c>
       <c r="R60" t="n">
-        <v>6786690</v>
+        <v>6786782</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6812,7 +6782,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122567291</v>
+        <v>122567313</v>
       </c>
       <c r="B61" t="n">
         <v>8441</v>
@@ -6848,7 +6818,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6857,10 +6827,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488440</v>
+        <v>488616</v>
       </c>
       <c r="R61" t="n">
-        <v>6786759</v>
+        <v>6786649</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6919,10 +6889,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122566913</v>
+        <v>122567029</v>
       </c>
       <c r="B62" t="n">
-        <v>57383</v>
+        <v>78301</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6935,39 +6905,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488602</v>
+        <v>488664</v>
       </c>
       <c r="R62" t="n">
-        <v>6786666</v>
+        <v>6786615</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7000,11 +6965,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7031,10 +6991,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122567310</v>
+        <v>122566954</v>
       </c>
       <c r="B63" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7043,43 +7003,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488294</v>
+        <v>488416</v>
       </c>
       <c r="R63" t="n">
-        <v>6786825</v>
+        <v>6786896</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7138,10 +7093,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122567296</v>
+        <v>122566903</v>
       </c>
       <c r="B64" t="n">
-        <v>8441</v>
+        <v>90853</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7150,43 +7105,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488834</v>
+        <v>488770</v>
       </c>
       <c r="R64" t="n">
-        <v>6786685</v>
+        <v>6786732</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7245,10 +7195,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122567324</v>
+        <v>122566905</v>
       </c>
       <c r="B65" t="n">
-        <v>8441</v>
+        <v>57399</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7257,31 +7207,31 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7290,10 +7240,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488638</v>
+        <v>488294</v>
       </c>
       <c r="R65" t="n">
-        <v>6786764</v>
+        <v>6786826</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7352,10 +7302,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122566979</v>
+        <v>122567298</v>
       </c>
       <c r="B66" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7364,38 +7314,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488583</v>
+        <v>488789</v>
       </c>
       <c r="R66" t="n">
-        <v>6786676</v>
+        <v>6786702</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7454,10 +7409,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122566958</v>
+        <v>122567308</v>
       </c>
       <c r="B67" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7466,38 +7421,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488301</v>
+        <v>488669</v>
       </c>
       <c r="R67" t="n">
-        <v>6786839</v>
+        <v>6786761</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7556,7 +7516,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122566966</v>
+        <v>122566978</v>
       </c>
       <c r="B68" t="n">
         <v>78656</v>
@@ -7596,10 +7556,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488390</v>
+        <v>488583</v>
       </c>
       <c r="R68" t="n">
-        <v>6786813</v>
+        <v>6786679</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7658,7 +7618,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122566994</v>
+        <v>122566960</v>
       </c>
       <c r="B69" t="n">
         <v>78656</v>
@@ -7698,10 +7658,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488883</v>
+        <v>488322</v>
       </c>
       <c r="R69" t="n">
-        <v>6786645</v>
+        <v>6786853</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7760,10 +7720,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122566904</v>
+        <v>122567322</v>
       </c>
       <c r="B70" t="n">
-        <v>90853</v>
+        <v>8441</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7772,38 +7732,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488552</v>
+        <v>488700</v>
       </c>
       <c r="R70" t="n">
-        <v>6786834</v>
+        <v>6786746</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7862,10 +7827,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122566903</v>
+        <v>122567320</v>
       </c>
       <c r="B71" t="n">
-        <v>90853</v>
+        <v>8441</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7874,38 +7839,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488770</v>
+        <v>488833</v>
       </c>
       <c r="R71" t="n">
-        <v>6786732</v>
+        <v>6786674</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7964,10 +7934,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122566980</v>
+        <v>122566892</v>
       </c>
       <c r="B72" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7980,21 +7950,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8004,10 +7974,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488590</v>
+        <v>488699</v>
       </c>
       <c r="R72" t="n">
-        <v>6786665</v>
+        <v>6786599</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8168,7 +8138,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122567003</v>
+        <v>122566995</v>
       </c>
       <c r="B74" t="n">
         <v>78656</v>
@@ -8208,10 +8178,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488550</v>
+        <v>488833</v>
       </c>
       <c r="R74" t="n">
-        <v>6786822</v>
+        <v>6786674</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8270,10 +8240,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122567297</v>
+        <v>122567020</v>
       </c>
       <c r="B75" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8282,43 +8252,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488804</v>
+        <v>488185</v>
       </c>
       <c r="R75" t="n">
-        <v>6786700</v>
+        <v>6787005</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8377,10 +8342,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122567322</v>
+        <v>122567010</v>
       </c>
       <c r="B76" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8389,43 +8354,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488700</v>
+        <v>488442</v>
       </c>
       <c r="R76" t="n">
-        <v>6786746</v>
+        <v>6786881</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8484,7 +8444,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122566965</v>
+        <v>122566998</v>
       </c>
       <c r="B77" t="n">
         <v>78656</v>
@@ -8524,10 +8484,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488378</v>
+        <v>488700</v>
       </c>
       <c r="R77" t="n">
-        <v>6786805</v>
+        <v>6786744</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8586,10 +8546,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122566988</v>
+        <v>122566909</v>
       </c>
       <c r="B78" t="n">
-        <v>78656</v>
+        <v>91278</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8598,25 +8558,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8626,10 +8586,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488803</v>
+        <v>488882</v>
       </c>
       <c r="R78" t="n">
-        <v>6786562</v>
+        <v>6786607</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8688,10 +8648,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122567026</v>
+        <v>122567303</v>
       </c>
       <c r="B79" t="n">
-        <v>78301</v>
+        <v>8441</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8700,38 +8660,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488539</v>
+        <v>488600</v>
       </c>
       <c r="R79" t="n">
-        <v>6786689</v>
+        <v>6786772</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8790,10 +8755,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122566890</v>
+        <v>122567323</v>
       </c>
       <c r="B80" t="n">
-        <v>79274</v>
+        <v>8441</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8802,38 +8767,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488572</v>
+        <v>488686</v>
       </c>
       <c r="R80" t="n">
-        <v>6786674</v>
+        <v>6786745</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8892,7 +8862,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122566960</v>
+        <v>122567002</v>
       </c>
       <c r="B81" t="n">
         <v>78656</v>
@@ -8932,10 +8902,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488322</v>
+        <v>488569</v>
       </c>
       <c r="R81" t="n">
-        <v>6786853</v>
+        <v>6786787</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8994,7 +8964,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122567023</v>
+        <v>122566994</v>
       </c>
       <c r="B82" t="n">
         <v>78656</v>
@@ -9034,10 +9004,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488135</v>
+        <v>488883</v>
       </c>
       <c r="R82" t="n">
-        <v>6787033</v>
+        <v>6786645</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9096,7 +9066,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122567011</v>
+        <v>122567009</v>
       </c>
       <c r="B83" t="n">
         <v>78656</v>
@@ -9136,10 +9106,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488427</v>
+        <v>488465</v>
       </c>
       <c r="R83" t="n">
-        <v>6786888</v>
+        <v>6786880</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9198,7 +9168,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122566971</v>
+        <v>122567008</v>
       </c>
       <c r="B84" t="n">
         <v>78656</v>
@@ -9238,10 +9208,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488461</v>
+        <v>488495</v>
       </c>
       <c r="R84" t="n">
-        <v>6786736</v>
+        <v>6786888</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9300,7 +9270,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122567019</v>
+        <v>122567007</v>
       </c>
       <c r="B85" t="n">
         <v>78656</v>
@@ -9340,10 +9310,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488297</v>
+        <v>488530</v>
       </c>
       <c r="R85" t="n">
-        <v>6786946</v>
+        <v>6786847</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9402,7 +9372,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122567018</v>
+        <v>122567023</v>
       </c>
       <c r="B86" t="n">
         <v>78656</v>
@@ -9442,10 +9412,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488345</v>
+        <v>488135</v>
       </c>
       <c r="R86" t="n">
-        <v>6786910</v>
+        <v>6787033</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9504,10 +9474,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122567013</v>
+        <v>122567027</v>
       </c>
       <c r="B87" t="n">
-        <v>78656</v>
+        <v>78301</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9520,21 +9490,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9544,10 +9514,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488389</v>
+        <v>488618</v>
       </c>
       <c r="R87" t="n">
-        <v>6786901</v>
+        <v>6786631</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9606,7 +9576,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122567004</v>
+        <v>122566965</v>
       </c>
       <c r="B88" t="n">
         <v>78656</v>
@@ -9646,10 +9616,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488475</v>
+        <v>488378</v>
       </c>
       <c r="R88" t="n">
-        <v>6786864</v>
+        <v>6786805</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9708,7 +9678,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122566956</v>
+        <v>122566982</v>
       </c>
       <c r="B89" t="n">
         <v>78656</v>
@@ -9748,10 +9718,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488309</v>
+        <v>488600</v>
       </c>
       <c r="R89" t="n">
-        <v>6786859</v>
+        <v>6786662</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9810,10 +9780,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122567028</v>
+        <v>122566962</v>
       </c>
       <c r="B90" t="n">
-        <v>78301</v>
+        <v>78656</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9826,21 +9796,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9850,10 +9820,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488611</v>
+        <v>488324</v>
       </c>
       <c r="R90" t="n">
-        <v>6786649</v>
+        <v>6786843</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9912,10 +9882,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122567303</v>
+        <v>122566952</v>
       </c>
       <c r="B91" t="n">
-        <v>8441</v>
+        <v>80613</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9924,43 +9894,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>106545</v>
+        <v>1049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488600</v>
+        <v>488363</v>
       </c>
       <c r="R91" t="n">
-        <v>6786772</v>
+        <v>6786907</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10019,10 +9984,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122566991</v>
+        <v>122567291</v>
       </c>
       <c r="B92" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10031,38 +9996,43 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488918</v>
+        <v>488440</v>
       </c>
       <c r="R92" t="n">
-        <v>6786607</v>
+        <v>6786759</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10121,10 +10091,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122566902</v>
+        <v>122567317</v>
       </c>
       <c r="B93" t="n">
-        <v>90853</v>
+        <v>8441</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10133,38 +10103,43 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488397</v>
+        <v>488892</v>
       </c>
       <c r="R93" t="n">
-        <v>6786809</v>
+        <v>6786620</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10223,10 +10198,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122567308</v>
+        <v>122567001</v>
       </c>
       <c r="B94" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10235,43 +10210,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488669</v>
+        <v>488583</v>
       </c>
       <c r="R94" t="n">
-        <v>6786761</v>
+        <v>6786774</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10330,10 +10300,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122567325</v>
+        <v>122567004</v>
       </c>
       <c r="B95" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10342,43 +10312,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>488576</v>
+        <v>488475</v>
       </c>
       <c r="R95" t="n">
-        <v>6786782</v>
+        <v>6786864</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10437,10 +10402,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122567289</v>
+        <v>122566956</v>
       </c>
       <c r="B96" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10449,43 +10414,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>488322</v>
+        <v>488309</v>
       </c>
       <c r="R96" t="n">
-        <v>6786810</v>
+        <v>6786859</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10544,10 +10504,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122566961</v>
+        <v>122567315</v>
       </c>
       <c r="B97" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10556,38 +10516,43 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>488327</v>
+        <v>488773</v>
       </c>
       <c r="R97" t="n">
-        <v>6786847</v>
+        <v>6786561</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10646,7 +10611,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122566997</v>
+        <v>122567022</v>
       </c>
       <c r="B98" t="n">
         <v>78656</v>
@@ -10686,10 +10651,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>488731</v>
+        <v>488137</v>
       </c>
       <c r="R98" t="n">
-        <v>6786733</v>
+        <v>6787026</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10748,10 +10713,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122567007</v>
+        <v>122567295</v>
       </c>
       <c r="B99" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10760,38 +10725,43 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>488530</v>
+        <v>488850</v>
       </c>
       <c r="R99" t="n">
-        <v>6786847</v>
+        <v>6786668</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10850,7 +10820,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122567298</v>
+        <v>122567299</v>
       </c>
       <c r="B100" t="n">
         <v>8441</v>
@@ -10895,10 +10865,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>488789</v>
+        <v>488786</v>
       </c>
       <c r="R100" t="n">
-        <v>6786702</v>
+        <v>6786723</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10957,10 +10927,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122566894</v>
+        <v>122567292</v>
       </c>
       <c r="B101" t="n">
-        <v>79274</v>
+        <v>8441</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10969,38 +10939,43 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>488182</v>
+        <v>488533</v>
       </c>
       <c r="R101" t="n">
-        <v>6787001</v>
+        <v>6786690</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11059,10 +11034,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122567017</v>
+        <v>122567312</v>
       </c>
       <c r="B102" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11071,38 +11046,43 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>488353</v>
+        <v>488341</v>
       </c>
       <c r="R102" t="n">
-        <v>6786911</v>
+        <v>6786832</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11161,10 +11141,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122567000</v>
+        <v>122567311</v>
       </c>
       <c r="B103" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11173,38 +11153,43 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>488678</v>
+        <v>488332</v>
       </c>
       <c r="R103" t="n">
-        <v>6786753</v>
+        <v>6786824</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11263,7 +11248,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122566996</v>
+        <v>122566980</v>
       </c>
       <c r="B104" t="n">
         <v>78656</v>
@@ -11303,10 +11288,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488757</v>
+        <v>488590</v>
       </c>
       <c r="R104" t="n">
-        <v>6786723</v>
+        <v>6786665</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11365,7 +11350,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122567022</v>
+        <v>122566999</v>
       </c>
       <c r="B105" t="n">
         <v>78656</v>
@@ -11405,10 +11390,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488137</v>
+        <v>488686</v>
       </c>
       <c r="R105" t="n">
-        <v>6787026</v>
+        <v>6786738</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11467,10 +11452,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122567024</v>
+        <v>122566958</v>
       </c>
       <c r="B106" t="n">
-        <v>91085</v>
+        <v>78656</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11479,25 +11464,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11507,10 +11492,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488663</v>
+        <v>488301</v>
       </c>
       <c r="R106" t="n">
-        <v>6786615</v>
+        <v>6786839</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11569,10 +11554,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122566897</v>
+        <v>122566957</v>
       </c>
       <c r="B107" t="n">
-        <v>90833</v>
+        <v>78656</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11585,21 +11570,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11609,10 +11594,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488892</v>
+        <v>488300</v>
       </c>
       <c r="R107" t="n">
-        <v>6786591</v>
+        <v>6786820</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11671,10 +11656,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122566952</v>
+        <v>122566911</v>
       </c>
       <c r="B108" t="n">
-        <v>80613</v>
+        <v>91124</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11687,21 +11672,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1049</v>
+        <v>658</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11711,10 +11696,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>488363</v>
+        <v>488882</v>
       </c>
       <c r="R108" t="n">
-        <v>6786907</v>
+        <v>6786609</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11773,10 +11758,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122567027</v>
+        <v>122566896</v>
       </c>
       <c r="B109" t="n">
-        <v>78301</v>
+        <v>90833</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11789,21 +11774,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11813,10 +11798,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488618</v>
+        <v>488882</v>
       </c>
       <c r="R109" t="n">
-        <v>6786631</v>
+        <v>6786607</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11875,10 +11860,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122567326</v>
+        <v>122566908</v>
       </c>
       <c r="B110" t="n">
-        <v>8441</v>
+        <v>57399</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11887,31 +11872,35 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -11920,10 +11909,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>488545</v>
+        <v>488892</v>
       </c>
       <c r="R110" t="n">
-        <v>6786849</v>
+        <v>6786620</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11982,10 +11971,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122566999</v>
+        <v>122567327</v>
       </c>
       <c r="B111" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11994,38 +11983,43 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>488686</v>
+        <v>488442</v>
       </c>
       <c r="R111" t="n">
-        <v>6786738</v>
+        <v>6786881</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12084,10 +12078,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122566985</v>
+        <v>122566893</v>
       </c>
       <c r="B112" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12100,21 +12094,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12124,10 +12118,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>488698</v>
+        <v>488693</v>
       </c>
       <c r="R112" t="n">
-        <v>6786584</v>
+        <v>6786741</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12186,10 +12180,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122567001</v>
+        <v>122566889</v>
       </c>
       <c r="B113" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12202,21 +12196,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12226,10 +12220,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488583</v>
+        <v>488296</v>
       </c>
       <c r="R113" t="n">
-        <v>6786774</v>
+        <v>6786844</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12288,10 +12282,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122567294</v>
+        <v>122566913</v>
       </c>
       <c r="B114" t="n">
-        <v>8441</v>
+        <v>57383</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12300,31 +12294,31 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -12333,10 +12327,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488801</v>
+        <v>488602</v>
       </c>
       <c r="R114" t="n">
-        <v>6786563</v>
+        <v>6786666</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12369,6 +12363,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12395,7 +12394,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122567327</v>
+        <v>122567297</v>
       </c>
       <c r="B115" t="n">
         <v>8441</v>
@@ -12431,7 +12430,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -12440,10 +12439,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>488442</v>
+        <v>488804</v>
       </c>
       <c r="R115" t="n">
-        <v>6786881</v>
+        <v>6786700</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12502,7 +12501,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122567014</v>
+        <v>122566971</v>
       </c>
       <c r="B116" t="n">
         <v>78656</v>
@@ -12542,10 +12541,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>488383</v>
+        <v>488461</v>
       </c>
       <c r="R116" t="n">
-        <v>6786912</v>
+        <v>6786736</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12604,7 +12603,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122566969</v>
+        <v>122566968</v>
       </c>
       <c r="B117" t="n">
         <v>78656</v>
@@ -12644,7 +12643,7 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>488452</v>
+        <v>488431</v>
       </c>
       <c r="R117" t="n">
         <v>6786772</v>
@@ -12706,7 +12705,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122567010</v>
+        <v>122566967</v>
       </c>
       <c r="B118" t="n">
         <v>78656</v>
@@ -12746,10 +12745,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>488442</v>
+        <v>488387</v>
       </c>
       <c r="R118" t="n">
-        <v>6786881</v>
+        <v>6786773</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12808,7 +12807,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122566983</v>
+        <v>122566997</v>
       </c>
       <c r="B119" t="n">
         <v>78656</v>
@@ -12848,10 +12847,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>488609</v>
+        <v>488731</v>
       </c>
       <c r="R119" t="n">
-        <v>6786648</v>
+        <v>6786733</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12910,10 +12909,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122566968</v>
+        <v>122567300</v>
       </c>
       <c r="B120" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12922,38 +12921,43 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>488431</v>
+        <v>488768</v>
       </c>
       <c r="R120" t="n">
-        <v>6786772</v>
+        <v>6786742</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13012,10 +13016,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122566901</v>
+        <v>122567305</v>
       </c>
       <c r="B121" t="n">
-        <v>57536</v>
+        <v>8441</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13024,38 +13028,43 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488142</v>
+        <v>488519</v>
       </c>
       <c r="R121" t="n">
-        <v>6787017</v>
+        <v>6786844</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13114,10 +13123,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122566899</v>
+        <v>122566902</v>
       </c>
       <c r="B122" t="n">
-        <v>57536</v>
+        <v>90853</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13130,21 +13139,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13154,10 +13163,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488482</v>
+        <v>488397</v>
       </c>
       <c r="R122" t="n">
-        <v>6786720</v>
+        <v>6786809</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13216,10 +13225,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122567314</v>
+        <v>122566961</v>
       </c>
       <c r="B123" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13228,43 +13237,38 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>488747</v>
+        <v>488327</v>
       </c>
       <c r="R123" t="n">
-        <v>6786566</v>
+        <v>6786847</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13323,10 +13327,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122567300</v>
+        <v>122566996</v>
       </c>
       <c r="B124" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13335,43 +13339,38 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>488768</v>
+        <v>488757</v>
       </c>
       <c r="R124" t="n">
-        <v>6786742</v>
+        <v>6786723</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13430,10 +13429,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122567301</v>
+        <v>122566899</v>
       </c>
       <c r="B125" t="n">
-        <v>8441</v>
+        <v>57536</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13442,43 +13441,38 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>488718</v>
+        <v>488482</v>
       </c>
       <c r="R125" t="n">
-        <v>6786752</v>
+        <v>6786720</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13537,7 +13531,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122567315</v>
+        <v>122567314</v>
       </c>
       <c r="B126" t="n">
         <v>8441</v>
@@ -13582,10 +13576,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>488773</v>
+        <v>488747</v>
       </c>
       <c r="R126" t="n">
-        <v>6786561</v>
+        <v>6786566</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13644,10 +13638,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122566974</v>
+        <v>122566912</v>
       </c>
       <c r="B127" t="n">
-        <v>78656</v>
+        <v>91124</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13660,21 +13654,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13684,10 +13678,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>488486</v>
+        <v>488895</v>
       </c>
       <c r="R127" t="n">
-        <v>6786718</v>
+        <v>6786588</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13746,10 +13740,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122566892</v>
+        <v>122566974</v>
       </c>
       <c r="B128" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13762,21 +13756,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13786,10 +13780,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>488699</v>
+        <v>488486</v>
       </c>
       <c r="R128" t="n">
-        <v>6786599</v>
+        <v>6786718</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13848,7 +13842,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122566982</v>
+        <v>122567018</v>
       </c>
       <c r="B129" t="n">
         <v>78656</v>
@@ -13888,10 +13882,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>488600</v>
+        <v>488345</v>
       </c>
       <c r="R129" t="n">
-        <v>6786662</v>
+        <v>6786910</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13950,10 +13944,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122566998</v>
+        <v>122567296</v>
       </c>
       <c r="B130" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13962,38 +13956,43 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>488700</v>
+        <v>488834</v>
       </c>
       <c r="R130" t="n">
-        <v>6786744</v>
+        <v>6786685</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14052,10 +14051,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122566908</v>
+        <v>122567293</v>
       </c>
       <c r="B131" t="n">
-        <v>57399</v>
+        <v>8441</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14064,35 +14063,31 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="M131" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -14101,10 +14096,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>488892</v>
+        <v>488790</v>
       </c>
       <c r="R131" t="n">
-        <v>6786620</v>
+        <v>6786547</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14163,10 +14158,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122567020</v>
+        <v>122567290</v>
       </c>
       <c r="B132" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14175,38 +14170,43 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>488185</v>
+        <v>488345</v>
       </c>
       <c r="R132" t="n">
-        <v>6787005</v>
+        <v>6786796</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14265,7 +14265,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>122567321</v>
+        <v>122567316</v>
       </c>
       <c r="B133" t="n">
         <v>8441</v>
@@ -14310,10 +14310,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>488817</v>
+        <v>488900</v>
       </c>
       <c r="R133" t="n">
-        <v>6786693</v>
+        <v>6786628</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>

--- a/artfynd/A 61338-2024 artfynd.xlsx
+++ b/artfynd/A 61338-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567326</v>
+        <v>122566994</v>
       </c>
       <c r="B2" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488545</v>
+        <v>488883</v>
       </c>
       <c r="R2" t="n">
-        <v>6786849</v>
+        <v>6786645</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567324</v>
+        <v>122566899</v>
       </c>
       <c r="B3" t="n">
-        <v>8441</v>
+        <v>57537</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,43 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488638</v>
+        <v>488482</v>
       </c>
       <c r="R3" t="n">
-        <v>6786764</v>
+        <v>6786720</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567306</v>
+        <v>122566977</v>
       </c>
       <c r="B4" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,43 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488556</v>
+        <v>488515</v>
       </c>
       <c r="R4" t="n">
-        <v>6786835</v>
+        <v>6786685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567011</v>
+        <v>122566997</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488427</v>
+        <v>488731</v>
       </c>
       <c r="R5" t="n">
-        <v>6786888</v>
+        <v>6786733</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567006</v>
+        <v>122566905</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>57400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,34 +1099,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488556</v>
+        <v>488294</v>
       </c>
       <c r="R6" t="n">
-        <v>6786835</v>
+        <v>6786826</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567005</v>
+        <v>122566908</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>57400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,34 +1206,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488415</v>
+        <v>488892</v>
       </c>
       <c r="R7" t="n">
-        <v>6786889</v>
+        <v>6786620</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566964</v>
+        <v>122567301</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,38 +1313,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488351</v>
+        <v>488718</v>
       </c>
       <c r="R8" t="n">
-        <v>6786831</v>
+        <v>6786752</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122567003</v>
+        <v>122566904</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>90854</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1424,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1448,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488550</v>
+        <v>488552</v>
       </c>
       <c r="R9" t="n">
-        <v>6786822</v>
+        <v>6786834</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1510,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566966</v>
+        <v>122566963</v>
       </c>
       <c r="B10" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,10 +1550,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488390</v>
+        <v>488341</v>
       </c>
       <c r="R10" t="n">
-        <v>6786813</v>
+        <v>6786832</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566991</v>
+        <v>122567009</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,10 +1652,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488918</v>
+        <v>488465</v>
       </c>
       <c r="R11" t="n">
-        <v>6786607</v>
+        <v>6786880</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1714,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567015</v>
+        <v>122566982</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1750,10 +1754,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488366</v>
+        <v>488600</v>
       </c>
       <c r="R12" t="n">
-        <v>6786907</v>
+        <v>6786662</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,10 +1816,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566975</v>
+        <v>122567026</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>78302</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,21 +1832,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1856,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488515</v>
+        <v>488539</v>
       </c>
       <c r="R13" t="n">
-        <v>6786685</v>
+        <v>6786689</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,10 +1918,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567014</v>
+        <v>122567025</v>
       </c>
       <c r="B14" t="n">
-        <v>78656</v>
+        <v>78302</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,21 +1934,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488383</v>
+        <v>488378</v>
       </c>
       <c r="R14" t="n">
-        <v>6786912</v>
+        <v>6786805</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,10 +2020,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567013</v>
+        <v>122566980</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2056,10 +2060,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488389</v>
+        <v>488590</v>
       </c>
       <c r="R15" t="n">
-        <v>6786901</v>
+        <v>6786665</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,10 +2122,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567032</v>
+        <v>122566998</v>
       </c>
       <c r="B16" t="n">
-        <v>5173</v>
+        <v>78657</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,43 +2134,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488901</v>
+        <v>488700</v>
       </c>
       <c r="R16" t="n">
-        <v>6786589</v>
+        <v>6786744</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,10 +2224,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122567309</v>
+        <v>122566902</v>
       </c>
       <c r="B17" t="n">
-        <v>8441</v>
+        <v>90854</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2237,43 +2236,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488707</v>
+        <v>488397</v>
       </c>
       <c r="R17" t="n">
-        <v>6786747</v>
+        <v>6786809</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,10 +2326,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566901</v>
+        <v>122567324</v>
       </c>
       <c r="B18" t="n">
-        <v>57536</v>
+        <v>8441</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2344,38 +2338,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488142</v>
+        <v>488638</v>
       </c>
       <c r="R18" t="n">
-        <v>6787017</v>
+        <v>6786764</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2434,10 +2433,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566894</v>
+        <v>122567294</v>
       </c>
       <c r="B19" t="n">
-        <v>79274</v>
+        <v>8441</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2446,38 +2445,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488182</v>
+        <v>488801</v>
       </c>
       <c r="R19" t="n">
-        <v>6787001</v>
+        <v>6786563</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2536,10 +2540,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122567017</v>
+        <v>122566984</v>
       </c>
       <c r="B20" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2576,10 +2580,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488353</v>
+        <v>488699</v>
       </c>
       <c r="R20" t="n">
-        <v>6786911</v>
+        <v>6786596</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,10 +2642,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566970</v>
+        <v>122566971</v>
       </c>
       <c r="B21" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2678,10 +2682,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488469</v>
+        <v>488461</v>
       </c>
       <c r="R21" t="n">
-        <v>6786751</v>
+        <v>6786736</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,10 +2744,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566897</v>
+        <v>122566912</v>
       </c>
       <c r="B22" t="n">
-        <v>90833</v>
+        <v>91125</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2756,21 +2760,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2780,10 +2784,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488892</v>
+        <v>488895</v>
       </c>
       <c r="R22" t="n">
-        <v>6786591</v>
+        <v>6786588</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2842,7 +2846,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567307</v>
+        <v>122567314</v>
       </c>
       <c r="B23" t="n">
         <v>8441</v>
@@ -2878,7 +2882,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2887,10 +2891,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488535</v>
+        <v>488747</v>
       </c>
       <c r="R23" t="n">
-        <v>6786843</v>
+        <v>6786566</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2949,10 +2953,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566890</v>
+        <v>122567310</v>
       </c>
       <c r="B24" t="n">
-        <v>79274</v>
+        <v>8441</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2961,38 +2965,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488572</v>
+        <v>488294</v>
       </c>
       <c r="R24" t="n">
-        <v>6786674</v>
+        <v>6786825</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3051,10 +3060,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566987</v>
+        <v>122567308</v>
       </c>
       <c r="B25" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3063,38 +3072,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488735</v>
+        <v>488669</v>
       </c>
       <c r="R25" t="n">
-        <v>6786569</v>
+        <v>6786761</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3153,10 +3167,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566969</v>
+        <v>122567289</v>
       </c>
       <c r="B26" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3165,38 +3179,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488452</v>
+        <v>488322</v>
       </c>
       <c r="R26" t="n">
-        <v>6786772</v>
+        <v>6786810</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3255,10 +3274,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566986</v>
+        <v>122567292</v>
       </c>
       <c r="B27" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3267,38 +3286,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488714</v>
+        <v>488533</v>
       </c>
       <c r="R27" t="n">
-        <v>6786574</v>
+        <v>6786690</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3357,10 +3381,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122566983</v>
+        <v>122567029</v>
       </c>
       <c r="B28" t="n">
-        <v>78656</v>
+        <v>78302</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3373,21 +3397,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3397,10 +3421,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488609</v>
+        <v>488664</v>
       </c>
       <c r="R28" t="n">
-        <v>6786648</v>
+        <v>6786615</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3459,10 +3483,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122566963</v>
+        <v>122566969</v>
       </c>
       <c r="B29" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3499,10 +3523,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488341</v>
+        <v>488452</v>
       </c>
       <c r="R29" t="n">
-        <v>6786832</v>
+        <v>6786772</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3561,10 +3585,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122566898</v>
+        <v>122566965</v>
       </c>
       <c r="B30" t="n">
-        <v>57536</v>
+        <v>78657</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3577,21 +3601,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3601,10 +3625,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488296</v>
+        <v>488378</v>
       </c>
       <c r="R30" t="n">
-        <v>6786844</v>
+        <v>6786805</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3663,10 +3687,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567321</v>
+        <v>122567019</v>
       </c>
       <c r="B31" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3675,43 +3699,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488817</v>
+        <v>488297</v>
       </c>
       <c r="R31" t="n">
-        <v>6786693</v>
+        <v>6786946</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3770,10 +3789,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122567310</v>
+        <v>122567003</v>
       </c>
       <c r="B32" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3782,43 +3801,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488294</v>
+        <v>488550</v>
       </c>
       <c r="R32" t="n">
-        <v>6786825</v>
+        <v>6786822</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3877,10 +3891,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122567318</v>
+        <v>122566970</v>
       </c>
       <c r="B33" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3889,43 +3903,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488883</v>
+        <v>488469</v>
       </c>
       <c r="R33" t="n">
-        <v>6786645</v>
+        <v>6786751</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3984,10 +3993,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567301</v>
+        <v>122567023</v>
       </c>
       <c r="B34" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3996,43 +4005,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488718</v>
+        <v>488135</v>
       </c>
       <c r="R34" t="n">
-        <v>6786752</v>
+        <v>6787033</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4091,10 +4095,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122566953</v>
+        <v>122566903</v>
       </c>
       <c r="B35" t="n">
-        <v>98240</v>
+        <v>90854</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4103,47 +4107,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488429</v>
+        <v>488770</v>
       </c>
       <c r="R35" t="n">
-        <v>6786896</v>
+        <v>6786732</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4202,10 +4197,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122566891</v>
+        <v>122567017</v>
       </c>
       <c r="B36" t="n">
-        <v>79274</v>
+        <v>78657</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4218,21 +4213,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4242,10 +4237,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488616</v>
+        <v>488353</v>
       </c>
       <c r="R36" t="n">
-        <v>6786648</v>
+        <v>6786911</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4304,10 +4299,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122566988</v>
+        <v>122566991</v>
       </c>
       <c r="B37" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4344,10 +4339,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488803</v>
+        <v>488918</v>
       </c>
       <c r="R37" t="n">
-        <v>6786562</v>
+        <v>6786607</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4406,10 +4401,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122566973</v>
+        <v>122567015</v>
       </c>
       <c r="B38" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4446,10 +4441,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488482</v>
+        <v>488366</v>
       </c>
       <c r="R38" t="n">
-        <v>6786720</v>
+        <v>6786907</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4508,10 +4503,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122567000</v>
+        <v>122566978</v>
       </c>
       <c r="B39" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4548,10 +4543,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488678</v>
+        <v>488583</v>
       </c>
       <c r="R39" t="n">
-        <v>6786753</v>
+        <v>6786679</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4610,10 +4605,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122566907</v>
+        <v>122567005</v>
       </c>
       <c r="B40" t="n">
-        <v>57399</v>
+        <v>78657</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4626,39 +4621,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488852</v>
+        <v>488415</v>
       </c>
       <c r="R40" t="n">
-        <v>6786673</v>
+        <v>6786889</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4717,7 +4707,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567319</v>
+        <v>122567318</v>
       </c>
       <c r="B41" t="n">
         <v>8441</v>
@@ -4762,10 +4752,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488869</v>
+        <v>488883</v>
       </c>
       <c r="R41" t="n">
-        <v>6786685</v>
+        <v>6786645</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4824,10 +4814,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567012</v>
+        <v>122566983</v>
       </c>
       <c r="B42" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4864,10 +4854,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488420</v>
+        <v>488609</v>
       </c>
       <c r="R42" t="n">
-        <v>6786898</v>
+        <v>6786648</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4926,7 +4916,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567304</v>
+        <v>122567300</v>
       </c>
       <c r="B43" t="n">
         <v>8441</v>
@@ -4971,10 +4961,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488591</v>
+        <v>488768</v>
       </c>
       <c r="R43" t="n">
-        <v>6786769</v>
+        <v>6786742</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5033,10 +5023,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122566979</v>
+        <v>122567296</v>
       </c>
       <c r="B44" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5045,38 +5035,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488583</v>
+        <v>488834</v>
       </c>
       <c r="R44" t="n">
-        <v>6786676</v>
+        <v>6786685</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5135,10 +5130,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122566985</v>
+        <v>122567295</v>
       </c>
       <c r="B45" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5147,38 +5142,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488698</v>
+        <v>488850</v>
       </c>
       <c r="R45" t="n">
-        <v>6786584</v>
+        <v>6786668</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5237,10 +5237,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122567019</v>
+        <v>122567291</v>
       </c>
       <c r="B46" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5249,38 +5249,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488297</v>
+        <v>488440</v>
       </c>
       <c r="R46" t="n">
-        <v>6786946</v>
+        <v>6786759</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5339,10 +5344,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122566972</v>
+        <v>122567303</v>
       </c>
       <c r="B47" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5351,38 +5356,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488465</v>
+        <v>488600</v>
       </c>
       <c r="R47" t="n">
-        <v>6786729</v>
+        <v>6786772</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5441,10 +5451,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122567026</v>
+        <v>122567012</v>
       </c>
       <c r="B48" t="n">
-        <v>78301</v>
+        <v>78657</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5457,21 +5467,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5481,10 +5491,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488539</v>
+        <v>488420</v>
       </c>
       <c r="R48" t="n">
-        <v>6786689</v>
+        <v>6786898</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5543,10 +5553,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567289</v>
+        <v>122566995</v>
       </c>
       <c r="B49" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5555,43 +5565,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488322</v>
+        <v>488833</v>
       </c>
       <c r="R49" t="n">
-        <v>6786810</v>
+        <v>6786674</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5650,10 +5655,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122567024</v>
+        <v>122566987</v>
       </c>
       <c r="B50" t="n">
-        <v>91085</v>
+        <v>78657</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5662,25 +5667,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5690,10 +5695,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488663</v>
+        <v>488735</v>
       </c>
       <c r="R50" t="n">
-        <v>6786615</v>
+        <v>6786569</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5752,10 +5757,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122566904</v>
+        <v>122566959</v>
       </c>
       <c r="B51" t="n">
-        <v>90853</v>
+        <v>78657</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5768,21 +5773,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5792,10 +5797,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488552</v>
+        <v>488317</v>
       </c>
       <c r="R51" t="n">
-        <v>6786834</v>
+        <v>6786858</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5854,10 +5859,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122566984</v>
+        <v>122566894</v>
       </c>
       <c r="B52" t="n">
-        <v>78656</v>
+        <v>79275</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5870,21 +5875,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5894,10 +5899,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488699</v>
+        <v>488182</v>
       </c>
       <c r="R52" t="n">
-        <v>6786596</v>
+        <v>6787001</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5956,10 +5961,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122566981</v>
+        <v>122566953</v>
       </c>
       <c r="B53" t="n">
-        <v>78656</v>
+        <v>98241</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5968,38 +5973,47 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488599</v>
+        <v>488429</v>
       </c>
       <c r="R53" t="n">
-        <v>6786673</v>
+        <v>6786896</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6058,10 +6072,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122566990</v>
+        <v>122567305</v>
       </c>
       <c r="B54" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6070,38 +6084,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488840</v>
+        <v>488519</v>
       </c>
       <c r="R54" t="n">
-        <v>6786622</v>
+        <v>6786844</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6160,10 +6179,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122566959</v>
+        <v>122566896</v>
       </c>
       <c r="B55" t="n">
-        <v>78656</v>
+        <v>90834</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6176,21 +6195,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6200,10 +6219,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488317</v>
+        <v>488882</v>
       </c>
       <c r="R55" t="n">
-        <v>6786858</v>
+        <v>6786607</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6262,10 +6281,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122567025</v>
+        <v>122567016</v>
       </c>
       <c r="B56" t="n">
-        <v>78301</v>
+        <v>78657</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6278,21 +6297,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6302,10 +6321,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488378</v>
+        <v>488360</v>
       </c>
       <c r="R56" t="n">
-        <v>6786805</v>
+        <v>6786913</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6364,10 +6383,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567030</v>
+        <v>122567293</v>
       </c>
       <c r="B57" t="n">
-        <v>78301</v>
+        <v>8441</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6376,38 +6395,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488769</v>
+        <v>488790</v>
       </c>
       <c r="R57" t="n">
-        <v>6786552</v>
+        <v>6786547</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6466,10 +6490,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122567028</v>
+        <v>122567322</v>
       </c>
       <c r="B58" t="n">
-        <v>78301</v>
+        <v>8441</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6478,38 +6502,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488611</v>
+        <v>488700</v>
       </c>
       <c r="R58" t="n">
-        <v>6786649</v>
+        <v>6786746</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6568,7 +6597,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122567294</v>
+        <v>122567327</v>
       </c>
       <c r="B59" t="n">
         <v>8441</v>
@@ -6604,7 +6633,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6613,10 +6642,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488801</v>
+        <v>488442</v>
       </c>
       <c r="R59" t="n">
-        <v>6786563</v>
+        <v>6786881</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6675,10 +6704,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122567325</v>
+        <v>122566961</v>
       </c>
       <c r="B60" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6687,43 +6716,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488576</v>
+        <v>488327</v>
       </c>
       <c r="R60" t="n">
-        <v>6786782</v>
+        <v>6786847</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6782,7 +6806,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122567313</v>
+        <v>122567290</v>
       </c>
       <c r="B61" t="n">
         <v>8441</v>
@@ -6818,7 +6842,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6827,10 +6851,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488616</v>
+        <v>488345</v>
       </c>
       <c r="R61" t="n">
-        <v>6786649</v>
+        <v>6786796</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6889,10 +6913,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122567029</v>
+        <v>122567309</v>
       </c>
       <c r="B62" t="n">
-        <v>78301</v>
+        <v>8441</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6901,38 +6925,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488664</v>
+        <v>488707</v>
       </c>
       <c r="R62" t="n">
-        <v>6786615</v>
+        <v>6786747</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6991,10 +7020,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122566954</v>
+        <v>122567325</v>
       </c>
       <c r="B63" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7003,38 +7032,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488416</v>
+        <v>488576</v>
       </c>
       <c r="R63" t="n">
-        <v>6786896</v>
+        <v>6786782</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7093,10 +7127,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122566903</v>
+        <v>122567299</v>
       </c>
       <c r="B64" t="n">
-        <v>90853</v>
+        <v>8441</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7105,38 +7139,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488770</v>
+        <v>488786</v>
       </c>
       <c r="R64" t="n">
-        <v>6786732</v>
+        <v>6786723</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7195,10 +7234,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122566905</v>
+        <v>122566996</v>
       </c>
       <c r="B65" t="n">
-        <v>57399</v>
+        <v>78657</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7211,39 +7250,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488294</v>
+        <v>488757</v>
       </c>
       <c r="R65" t="n">
-        <v>6786826</v>
+        <v>6786723</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7302,10 +7336,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122567298</v>
+        <v>122566956</v>
       </c>
       <c r="B66" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7314,43 +7348,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488789</v>
+        <v>488309</v>
       </c>
       <c r="R66" t="n">
-        <v>6786702</v>
+        <v>6786859</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7409,10 +7438,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122567308</v>
+        <v>122567014</v>
       </c>
       <c r="B67" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7421,43 +7450,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488669</v>
+        <v>488383</v>
       </c>
       <c r="R67" t="n">
-        <v>6786761</v>
+        <v>6786912</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7516,10 +7540,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122566978</v>
+        <v>122566892</v>
       </c>
       <c r="B68" t="n">
-        <v>78656</v>
+        <v>79275</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7532,21 +7556,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7556,10 +7580,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488583</v>
+        <v>488699</v>
       </c>
       <c r="R68" t="n">
-        <v>6786679</v>
+        <v>6786599</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7618,10 +7642,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122566960</v>
+        <v>122567030</v>
       </c>
       <c r="B69" t="n">
-        <v>78656</v>
+        <v>78302</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7634,21 +7658,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7658,10 +7682,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488322</v>
+        <v>488769</v>
       </c>
       <c r="R69" t="n">
-        <v>6786853</v>
+        <v>6786552</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7720,10 +7744,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122567322</v>
+        <v>122566988</v>
       </c>
       <c r="B70" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7732,43 +7756,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488700</v>
+        <v>488803</v>
       </c>
       <c r="R70" t="n">
-        <v>6786746</v>
+        <v>6786562</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7827,7 +7846,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122567320</v>
+        <v>122567307</v>
       </c>
       <c r="B71" t="n">
         <v>8441</v>
@@ -7863,7 +7882,7 @@
       <c r="I71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -7872,10 +7891,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488833</v>
+        <v>488535</v>
       </c>
       <c r="R71" t="n">
-        <v>6786674</v>
+        <v>6786843</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7934,10 +7953,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122566892</v>
+        <v>122567313</v>
       </c>
       <c r="B72" t="n">
-        <v>79274</v>
+        <v>8441</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7946,38 +7965,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488699</v>
+        <v>488616</v>
       </c>
       <c r="R72" t="n">
-        <v>6786599</v>
+        <v>6786649</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8036,10 +8060,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122567016</v>
+        <v>122566957</v>
       </c>
       <c r="B73" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8076,10 +8100,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488360</v>
+        <v>488300</v>
       </c>
       <c r="R73" t="n">
-        <v>6786913</v>
+        <v>6786820</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8138,10 +8162,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122566995</v>
+        <v>122567013</v>
       </c>
       <c r="B74" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8178,10 +8202,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488833</v>
+        <v>488389</v>
       </c>
       <c r="R74" t="n">
-        <v>6786674</v>
+        <v>6786901</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8240,10 +8264,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122567020</v>
+        <v>122567027</v>
       </c>
       <c r="B75" t="n">
-        <v>78656</v>
+        <v>78302</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8256,21 +8280,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8280,10 +8304,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488185</v>
+        <v>488618</v>
       </c>
       <c r="R75" t="n">
-        <v>6787005</v>
+        <v>6786631</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8342,10 +8366,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122567010</v>
+        <v>122567000</v>
       </c>
       <c r="B76" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8382,10 +8406,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488442</v>
+        <v>488678</v>
       </c>
       <c r="R76" t="n">
-        <v>6786881</v>
+        <v>6786753</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8444,10 +8468,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122566998</v>
+        <v>122567008</v>
       </c>
       <c r="B77" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8484,10 +8508,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488700</v>
+        <v>488495</v>
       </c>
       <c r="R77" t="n">
-        <v>6786744</v>
+        <v>6786888</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8546,10 +8570,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122566909</v>
+        <v>122566891</v>
       </c>
       <c r="B78" t="n">
-        <v>91278</v>
+        <v>79275</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8558,25 +8582,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1209</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8586,10 +8610,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488882</v>
+        <v>488616</v>
       </c>
       <c r="R78" t="n">
-        <v>6786607</v>
+        <v>6786648</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8648,7 +8672,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122567303</v>
+        <v>122567323</v>
       </c>
       <c r="B79" t="n">
         <v>8441</v>
@@ -8684,7 +8708,7 @@
       <c r="I79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8693,10 +8717,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488600</v>
+        <v>488686</v>
       </c>
       <c r="R79" t="n">
-        <v>6786772</v>
+        <v>6786745</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8755,10 +8779,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122567323</v>
+        <v>122567022</v>
       </c>
       <c r="B80" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8767,43 +8791,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488686</v>
+        <v>488137</v>
       </c>
       <c r="R80" t="n">
-        <v>6786745</v>
+        <v>6787026</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8862,10 +8881,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122567002</v>
+        <v>122566893</v>
       </c>
       <c r="B81" t="n">
-        <v>78656</v>
+        <v>79275</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8878,21 +8897,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8902,10 +8921,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488569</v>
+        <v>488693</v>
       </c>
       <c r="R81" t="n">
-        <v>6786787</v>
+        <v>6786741</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8964,10 +8983,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122566994</v>
+        <v>122566890</v>
       </c>
       <c r="B82" t="n">
-        <v>78656</v>
+        <v>79275</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8980,21 +8999,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9004,10 +9023,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488883</v>
+        <v>488572</v>
       </c>
       <c r="R82" t="n">
-        <v>6786645</v>
+        <v>6786674</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9066,10 +9085,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122567009</v>
+        <v>122566907</v>
       </c>
       <c r="B83" t="n">
-        <v>78656</v>
+        <v>57400</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9082,34 +9101,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488465</v>
+        <v>488852</v>
       </c>
       <c r="R83" t="n">
-        <v>6786880</v>
+        <v>6786673</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9168,10 +9192,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122567008</v>
+        <v>122567321</v>
       </c>
       <c r="B84" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9180,38 +9204,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488495</v>
+        <v>488817</v>
       </c>
       <c r="R84" t="n">
-        <v>6786888</v>
+        <v>6786693</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9270,10 +9299,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122567007</v>
+        <v>122567316</v>
       </c>
       <c r="B85" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9282,38 +9311,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488530</v>
+        <v>488900</v>
       </c>
       <c r="R85" t="n">
-        <v>6786847</v>
+        <v>6786628</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9372,10 +9406,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122567023</v>
+        <v>122567024</v>
       </c>
       <c r="B86" t="n">
-        <v>78656</v>
+        <v>91086</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9384,25 +9418,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9412,10 +9446,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488135</v>
+        <v>488663</v>
       </c>
       <c r="R86" t="n">
-        <v>6787033</v>
+        <v>6786615</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9474,10 +9508,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122567027</v>
+        <v>122566985</v>
       </c>
       <c r="B87" t="n">
-        <v>78301</v>
+        <v>78657</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9490,21 +9524,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9514,10 +9548,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488618</v>
+        <v>488698</v>
       </c>
       <c r="R87" t="n">
-        <v>6786631</v>
+        <v>6786584</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9576,10 +9610,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122566965</v>
+        <v>122566986</v>
       </c>
       <c r="B88" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9616,10 +9650,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488378</v>
+        <v>488714</v>
       </c>
       <c r="R88" t="n">
-        <v>6786805</v>
+        <v>6786574</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9678,10 +9712,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122566982</v>
+        <v>122567018</v>
       </c>
       <c r="B89" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9718,10 +9752,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488600</v>
+        <v>488345</v>
       </c>
       <c r="R89" t="n">
-        <v>6786662</v>
+        <v>6786910</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9780,10 +9814,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122566962</v>
+        <v>122566968</v>
       </c>
       <c r="B90" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9820,10 +9854,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488324</v>
+        <v>488431</v>
       </c>
       <c r="R90" t="n">
-        <v>6786843</v>
+        <v>6786772</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9882,10 +9916,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122566952</v>
+        <v>122566964</v>
       </c>
       <c r="B91" t="n">
-        <v>80613</v>
+        <v>78657</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9898,21 +9932,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9922,10 +9956,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488363</v>
+        <v>488351</v>
       </c>
       <c r="R91" t="n">
-        <v>6786907</v>
+        <v>6786831</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9984,10 +10018,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122567291</v>
+        <v>122566911</v>
       </c>
       <c r="B92" t="n">
-        <v>8441</v>
+        <v>91125</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9996,43 +10030,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>658</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488440</v>
+        <v>488882</v>
       </c>
       <c r="R92" t="n">
-        <v>6786759</v>
+        <v>6786609</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10091,10 +10120,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122567317</v>
+        <v>122567020</v>
       </c>
       <c r="B93" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10103,43 +10132,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488892</v>
+        <v>488185</v>
       </c>
       <c r="R93" t="n">
-        <v>6786620</v>
+        <v>6787005</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10198,10 +10222,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122567001</v>
+        <v>122567297</v>
       </c>
       <c r="B94" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10210,38 +10234,43 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488583</v>
+        <v>488804</v>
       </c>
       <c r="R94" t="n">
-        <v>6786774</v>
+        <v>6786700</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10300,10 +10329,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122567004</v>
+        <v>122566990</v>
       </c>
       <c r="B95" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10340,10 +10369,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>488475</v>
+        <v>488840</v>
       </c>
       <c r="R95" t="n">
-        <v>6786864</v>
+        <v>6786622</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10402,10 +10431,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122566956</v>
+        <v>122567312</v>
       </c>
       <c r="B96" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10414,38 +10443,43 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>488309</v>
+        <v>488341</v>
       </c>
       <c r="R96" t="n">
-        <v>6786859</v>
+        <v>6786832</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10504,7 +10538,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122567315</v>
+        <v>122567298</v>
       </c>
       <c r="B97" t="n">
         <v>8441</v>
@@ -10540,7 +10574,7 @@
       <c r="I97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -10549,10 +10583,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>488773</v>
+        <v>488789</v>
       </c>
       <c r="R97" t="n">
-        <v>6786561</v>
+        <v>6786702</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10611,10 +10645,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122567022</v>
+        <v>122567001</v>
       </c>
       <c r="B98" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10651,10 +10685,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>488137</v>
+        <v>488583</v>
       </c>
       <c r="R98" t="n">
-        <v>6787026</v>
+        <v>6786774</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10713,10 +10747,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122567295</v>
+        <v>122566901</v>
       </c>
       <c r="B99" t="n">
-        <v>8441</v>
+        <v>57537</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10725,43 +10759,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>488850</v>
+        <v>488142</v>
       </c>
       <c r="R99" t="n">
-        <v>6786668</v>
+        <v>6787017</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10820,10 +10849,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122567299</v>
+        <v>122566972</v>
       </c>
       <c r="B100" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10832,43 +10861,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>488786</v>
+        <v>488465</v>
       </c>
       <c r="R100" t="n">
-        <v>6786723</v>
+        <v>6786729</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10927,10 +10951,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122567292</v>
+        <v>122566966</v>
       </c>
       <c r="B101" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10939,43 +10963,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>488533</v>
+        <v>488390</v>
       </c>
       <c r="R101" t="n">
-        <v>6786690</v>
+        <v>6786813</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11034,7 +11053,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122567312</v>
+        <v>122567304</v>
       </c>
       <c r="B102" t="n">
         <v>8441</v>
@@ -11070,7 +11089,7 @@
       <c r="I102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -11079,10 +11098,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>488341</v>
+        <v>488591</v>
       </c>
       <c r="R102" t="n">
-        <v>6786832</v>
+        <v>6786769</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11141,7 +11160,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122567311</v>
+        <v>122567326</v>
       </c>
       <c r="B103" t="n">
         <v>8441</v>
@@ -11186,10 +11205,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>488332</v>
+        <v>488545</v>
       </c>
       <c r="R103" t="n">
-        <v>6786824</v>
+        <v>6786849</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11248,10 +11267,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122566980</v>
+        <v>122566979</v>
       </c>
       <c r="B104" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11288,10 +11307,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488590</v>
+        <v>488583</v>
       </c>
       <c r="R104" t="n">
-        <v>6786665</v>
+        <v>6786676</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11350,10 +11369,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122566999</v>
+        <v>122566960</v>
       </c>
       <c r="B105" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11390,10 +11409,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488686</v>
+        <v>488322</v>
       </c>
       <c r="R105" t="n">
-        <v>6786738</v>
+        <v>6786853</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11452,10 +11471,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122566958</v>
+        <v>122566962</v>
       </c>
       <c r="B106" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11492,10 +11511,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488301</v>
+        <v>488324</v>
       </c>
       <c r="R106" t="n">
-        <v>6786839</v>
+        <v>6786843</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11554,10 +11573,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122566957</v>
+        <v>122566889</v>
       </c>
       <c r="B107" t="n">
-        <v>78656</v>
+        <v>79275</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11570,21 +11589,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11594,10 +11613,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488300</v>
+        <v>488296</v>
       </c>
       <c r="R107" t="n">
-        <v>6786820</v>
+        <v>6786844</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11656,10 +11675,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122566911</v>
+        <v>122567032</v>
       </c>
       <c r="B108" t="n">
-        <v>91124</v>
+        <v>5173</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11668,38 +11687,43 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>658</v>
+        <v>100526</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>488882</v>
+        <v>488901</v>
       </c>
       <c r="R108" t="n">
-        <v>6786609</v>
+        <v>6786589</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11758,10 +11782,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122566896</v>
+        <v>122566913</v>
       </c>
       <c r="B109" t="n">
-        <v>90833</v>
+        <v>57384</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11774,34 +11798,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488882</v>
+        <v>488602</v>
       </c>
       <c r="R109" t="n">
-        <v>6786607</v>
+        <v>6786666</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11834,6 +11863,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11860,10 +11894,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122566908</v>
+        <v>122567311</v>
       </c>
       <c r="B110" t="n">
-        <v>57399</v>
+        <v>8441</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11872,35 +11906,31 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -11909,10 +11939,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>488892</v>
+        <v>488332</v>
       </c>
       <c r="R110" t="n">
-        <v>6786620</v>
+        <v>6786824</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11971,10 +12001,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122567327</v>
+        <v>122567028</v>
       </c>
       <c r="B111" t="n">
-        <v>8441</v>
+        <v>78302</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11983,43 +12013,38 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>488442</v>
+        <v>488611</v>
       </c>
       <c r="R111" t="n">
-        <v>6786881</v>
+        <v>6786649</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12078,10 +12103,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122566893</v>
+        <v>122566897</v>
       </c>
       <c r="B112" t="n">
-        <v>79274</v>
+        <v>90834</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12094,21 +12119,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12118,10 +12143,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>488693</v>
+        <v>488892</v>
       </c>
       <c r="R112" t="n">
-        <v>6786741</v>
+        <v>6786591</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12180,10 +12205,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122566889</v>
+        <v>122567320</v>
       </c>
       <c r="B113" t="n">
-        <v>79274</v>
+        <v>8441</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12192,38 +12217,43 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488296</v>
+        <v>488833</v>
       </c>
       <c r="R113" t="n">
-        <v>6786844</v>
+        <v>6786674</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12282,10 +12312,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122566913</v>
+        <v>122566952</v>
       </c>
       <c r="B114" t="n">
-        <v>57383</v>
+        <v>80614</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12298,39 +12328,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>1049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488602</v>
+        <v>488363</v>
       </c>
       <c r="R114" t="n">
-        <v>6786666</v>
+        <v>6786907</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12363,11 +12388,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12394,10 +12414,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122567297</v>
+        <v>122566973</v>
       </c>
       <c r="B115" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12406,43 +12426,38 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>488804</v>
+        <v>488482</v>
       </c>
       <c r="R115" t="n">
-        <v>6786700</v>
+        <v>6786720</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12501,10 +12516,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122566971</v>
+        <v>122566981</v>
       </c>
       <c r="B116" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12541,10 +12556,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>488461</v>
+        <v>488599</v>
       </c>
       <c r="R116" t="n">
-        <v>6786736</v>
+        <v>6786673</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12603,10 +12618,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122566968</v>
+        <v>122566974</v>
       </c>
       <c r="B117" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12643,10 +12658,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>488431</v>
+        <v>488486</v>
       </c>
       <c r="R117" t="n">
-        <v>6786772</v>
+        <v>6786718</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12705,10 +12720,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122566967</v>
+        <v>122566999</v>
       </c>
       <c r="B118" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12745,10 +12760,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>488387</v>
+        <v>488686</v>
       </c>
       <c r="R118" t="n">
-        <v>6786773</v>
+        <v>6786738</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12807,10 +12822,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122566997</v>
+        <v>122567007</v>
       </c>
       <c r="B119" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12847,10 +12862,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>488731</v>
+        <v>488530</v>
       </c>
       <c r="R119" t="n">
-        <v>6786733</v>
+        <v>6786847</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12909,7 +12924,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122567300</v>
+        <v>122567306</v>
       </c>
       <c r="B120" t="n">
         <v>8441</v>
@@ -12954,10 +12969,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>488768</v>
+        <v>488556</v>
       </c>
       <c r="R120" t="n">
-        <v>6786742</v>
+        <v>6786835</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13016,10 +13031,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122567305</v>
+        <v>122566958</v>
       </c>
       <c r="B121" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13028,43 +13043,38 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488519</v>
+        <v>488301</v>
       </c>
       <c r="R121" t="n">
-        <v>6786844</v>
+        <v>6786839</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13123,10 +13133,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122566902</v>
+        <v>122566954</v>
       </c>
       <c r="B122" t="n">
-        <v>90853</v>
+        <v>78657</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13139,21 +13149,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13163,10 +13173,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488397</v>
+        <v>488416</v>
       </c>
       <c r="R122" t="n">
-        <v>6786809</v>
+        <v>6786896</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13225,10 +13235,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122566961</v>
+        <v>122567004</v>
       </c>
       <c r="B123" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13265,10 +13275,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>488327</v>
+        <v>488475</v>
       </c>
       <c r="R123" t="n">
-        <v>6786847</v>
+        <v>6786864</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13327,10 +13337,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122566996</v>
+        <v>122567319</v>
       </c>
       <c r="B124" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13339,38 +13349,43 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>488757</v>
+        <v>488869</v>
       </c>
       <c r="R124" t="n">
-        <v>6786723</v>
+        <v>6786685</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13429,10 +13444,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122566899</v>
+        <v>122567002</v>
       </c>
       <c r="B125" t="n">
-        <v>57536</v>
+        <v>78657</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13445,21 +13460,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13469,10 +13484,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>488482</v>
+        <v>488569</v>
       </c>
       <c r="R125" t="n">
-        <v>6786720</v>
+        <v>6786787</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13531,10 +13546,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122567314</v>
+        <v>122567006</v>
       </c>
       <c r="B126" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13543,43 +13558,38 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>488747</v>
+        <v>488556</v>
       </c>
       <c r="R126" t="n">
-        <v>6786566</v>
+        <v>6786835</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13638,10 +13648,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122566912</v>
+        <v>122566898</v>
       </c>
       <c r="B127" t="n">
-        <v>91124</v>
+        <v>57537</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13654,21 +13664,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13678,10 +13688,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>488895</v>
+        <v>488296</v>
       </c>
       <c r="R127" t="n">
-        <v>6786588</v>
+        <v>6786844</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13740,10 +13750,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122566974</v>
+        <v>122566909</v>
       </c>
       <c r="B128" t="n">
-        <v>78656</v>
+        <v>91279</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13752,25 +13762,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13780,10 +13790,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>488486</v>
+        <v>488882</v>
       </c>
       <c r="R128" t="n">
-        <v>6786718</v>
+        <v>6786607</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13842,10 +13852,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122567018</v>
+        <v>122567315</v>
       </c>
       <c r="B129" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13854,38 +13864,43 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>488345</v>
+        <v>488773</v>
       </c>
       <c r="R129" t="n">
-        <v>6786910</v>
+        <v>6786561</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13944,7 +13959,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122567296</v>
+        <v>122567317</v>
       </c>
       <c r="B130" t="n">
         <v>8441</v>
@@ -13980,7 +13995,7 @@
       <c r="I130" t="inlineStr"/>
       <c r="M130" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -13989,10 +14004,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>488834</v>
+        <v>488892</v>
       </c>
       <c r="R130" t="n">
-        <v>6786685</v>
+        <v>6786620</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14051,10 +14066,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122567293</v>
+        <v>122567011</v>
       </c>
       <c r="B131" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14063,43 +14078,38 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>488790</v>
+        <v>488427</v>
       </c>
       <c r="R131" t="n">
-        <v>6786547</v>
+        <v>6786888</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14158,10 +14168,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122567290</v>
+        <v>122567010</v>
       </c>
       <c r="B132" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14170,43 +14180,38 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>488345</v>
+        <v>488442</v>
       </c>
       <c r="R132" t="n">
-        <v>6786796</v>
+        <v>6786881</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14265,10 +14270,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>122567316</v>
+        <v>122566967</v>
       </c>
       <c r="B133" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14277,43 +14282,38 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>488900</v>
+        <v>488387</v>
       </c>
       <c r="R133" t="n">
-        <v>6786628</v>
+        <v>6786773</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>

--- a/artfynd/A 61338-2024 artfynd.xlsx
+++ b/artfynd/A 61338-2024 artfynd.xlsx
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566904</v>
+        <v>122566980</v>
       </c>
       <c r="B9" t="n">
-        <v>90854</v>
+        <v>78657</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1424,21 +1424,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1448,10 +1448,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488552</v>
+        <v>488590</v>
       </c>
       <c r="R9" t="n">
-        <v>6786834</v>
+        <v>6786665</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,7 +1510,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566963</v>
+        <v>122566998</v>
       </c>
       <c r="B10" t="n">
         <v>78657</v>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488341</v>
+        <v>488700</v>
       </c>
       <c r="R10" t="n">
-        <v>6786832</v>
+        <v>6786744</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,7 +1612,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567009</v>
+        <v>122566963</v>
       </c>
       <c r="B11" t="n">
         <v>78657</v>
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488465</v>
+        <v>488341</v>
       </c>
       <c r="R11" t="n">
-        <v>6786880</v>
+        <v>6786832</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,10 +1714,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566982</v>
+        <v>122567026</v>
       </c>
       <c r="B12" t="n">
-        <v>78657</v>
+        <v>78302</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1730,21 +1730,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488600</v>
+        <v>488539</v>
       </c>
       <c r="R12" t="n">
-        <v>6786662</v>
+        <v>6786689</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,7 +1816,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567026</v>
+        <v>122567025</v>
       </c>
       <c r="B13" t="n">
         <v>78302</v>
@@ -1856,10 +1856,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488539</v>
+        <v>488378</v>
       </c>
       <c r="R13" t="n">
-        <v>6786689</v>
+        <v>6786805</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567025</v>
+        <v>122566904</v>
       </c>
       <c r="B14" t="n">
-        <v>78302</v>
+        <v>90854</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1934,21 +1934,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488378</v>
+        <v>488552</v>
       </c>
       <c r="R14" t="n">
-        <v>6786805</v>
+        <v>6786834</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566980</v>
+        <v>122567009</v>
       </c>
       <c r="B15" t="n">
         <v>78657</v>
@@ -2060,10 +2060,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488590</v>
+        <v>488465</v>
       </c>
       <c r="R15" t="n">
-        <v>6786665</v>
+        <v>6786880</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,7 +2122,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566998</v>
+        <v>122566982</v>
       </c>
       <c r="B16" t="n">
         <v>78657</v>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488700</v>
+        <v>488600</v>
       </c>
       <c r="R16" t="n">
-        <v>6786744</v>
+        <v>6786662</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2224,10 +2224,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566902</v>
+        <v>122566984</v>
       </c>
       <c r="B17" t="n">
-        <v>90854</v>
+        <v>78657</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2240,21 +2240,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488397</v>
+        <v>488699</v>
       </c>
       <c r="R17" t="n">
-        <v>6786809</v>
+        <v>6786596</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567324</v>
+        <v>122566971</v>
       </c>
       <c r="B18" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,43 +2338,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488638</v>
+        <v>488461</v>
       </c>
       <c r="R18" t="n">
-        <v>6786764</v>
+        <v>6786736</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2433,10 +2428,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122567294</v>
+        <v>122566902</v>
       </c>
       <c r="B19" t="n">
-        <v>8441</v>
+        <v>90854</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2445,43 +2440,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488801</v>
+        <v>488397</v>
       </c>
       <c r="R19" t="n">
-        <v>6786563</v>
+        <v>6786809</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,10 +2530,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566984</v>
+        <v>122567324</v>
       </c>
       <c r="B20" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,38 +2542,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488699</v>
+        <v>488638</v>
       </c>
       <c r="R20" t="n">
-        <v>6786596</v>
+        <v>6786764</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,10 +2637,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566971</v>
+        <v>122567294</v>
       </c>
       <c r="B21" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2654,38 +2649,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488461</v>
+        <v>488801</v>
       </c>
       <c r="R21" t="n">
-        <v>6786736</v>
+        <v>6786563</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567314</v>
+        <v>122567029</v>
       </c>
       <c r="B23" t="n">
-        <v>8441</v>
+        <v>78302</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2858,43 +2858,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488747</v>
+        <v>488664</v>
       </c>
       <c r="R23" t="n">
-        <v>6786566</v>
+        <v>6786615</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2953,10 +2948,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567310</v>
+        <v>122566969</v>
       </c>
       <c r="B24" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2965,43 +2960,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488294</v>
+        <v>488452</v>
       </c>
       <c r="R24" t="n">
-        <v>6786825</v>
+        <v>6786772</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3060,10 +3050,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122567308</v>
+        <v>122566965</v>
       </c>
       <c r="B25" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3072,43 +3062,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488669</v>
+        <v>488378</v>
       </c>
       <c r="R25" t="n">
-        <v>6786761</v>
+        <v>6786805</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3167,10 +3152,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567289</v>
+        <v>122567019</v>
       </c>
       <c r="B26" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3179,43 +3164,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488322</v>
+        <v>488297</v>
       </c>
       <c r="R26" t="n">
-        <v>6786810</v>
+        <v>6786946</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3274,10 +3254,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122567292</v>
+        <v>122567003</v>
       </c>
       <c r="B27" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3286,43 +3266,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488533</v>
+        <v>488550</v>
       </c>
       <c r="R27" t="n">
-        <v>6786690</v>
+        <v>6786822</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3381,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567029</v>
+        <v>122566970</v>
       </c>
       <c r="B28" t="n">
-        <v>78302</v>
+        <v>78657</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3397,21 +3372,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3421,10 +3396,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488664</v>
+        <v>488469</v>
       </c>
       <c r="R28" t="n">
-        <v>6786615</v>
+        <v>6786751</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3483,7 +3458,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122566969</v>
+        <v>122567023</v>
       </c>
       <c r="B29" t="n">
         <v>78657</v>
@@ -3523,10 +3498,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488452</v>
+        <v>488135</v>
       </c>
       <c r="R29" t="n">
-        <v>6786772</v>
+        <v>6787033</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3585,10 +3560,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122566965</v>
+        <v>122567314</v>
       </c>
       <c r="B30" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3597,38 +3572,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488378</v>
+        <v>488747</v>
       </c>
       <c r="R30" t="n">
-        <v>6786805</v>
+        <v>6786566</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3687,10 +3667,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567019</v>
+        <v>122567310</v>
       </c>
       <c r="B31" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3699,38 +3679,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488297</v>
+        <v>488294</v>
       </c>
       <c r="R31" t="n">
-        <v>6786946</v>
+        <v>6786825</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3789,10 +3774,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122567003</v>
+        <v>122567308</v>
       </c>
       <c r="B32" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3801,38 +3786,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488550</v>
+        <v>488669</v>
       </c>
       <c r="R32" t="n">
-        <v>6786822</v>
+        <v>6786761</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3891,10 +3881,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122566970</v>
+        <v>122567289</v>
       </c>
       <c r="B33" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3903,38 +3893,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488469</v>
+        <v>488322</v>
       </c>
       <c r="R33" t="n">
-        <v>6786751</v>
+        <v>6786810</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3993,10 +3988,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567023</v>
+        <v>122567292</v>
       </c>
       <c r="B34" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4005,38 +4000,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488135</v>
+        <v>488533</v>
       </c>
       <c r="R34" t="n">
-        <v>6787033</v>
+        <v>6786690</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4197,7 +4197,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122567017</v>
+        <v>122567005</v>
       </c>
       <c r="B36" t="n">
         <v>78657</v>
@@ -4237,10 +4237,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488353</v>
+        <v>488415</v>
       </c>
       <c r="R36" t="n">
-        <v>6786911</v>
+        <v>6786889</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4299,10 +4299,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122566991</v>
+        <v>122567318</v>
       </c>
       <c r="B37" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4311,38 +4311,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488918</v>
+        <v>488883</v>
       </c>
       <c r="R37" t="n">
-        <v>6786607</v>
+        <v>6786645</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4401,7 +4406,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567015</v>
+        <v>122567017</v>
       </c>
       <c r="B38" t="n">
         <v>78657</v>
@@ -4441,10 +4446,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488366</v>
+        <v>488353</v>
       </c>
       <c r="R38" t="n">
-        <v>6786907</v>
+        <v>6786911</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4503,7 +4508,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122566978</v>
+        <v>122566991</v>
       </c>
       <c r="B39" t="n">
         <v>78657</v>
@@ -4543,10 +4548,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488583</v>
+        <v>488918</v>
       </c>
       <c r="R39" t="n">
-        <v>6786679</v>
+        <v>6786607</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4605,7 +4610,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122567005</v>
+        <v>122567015</v>
       </c>
       <c r="B40" t="n">
         <v>78657</v>
@@ -4645,10 +4650,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488415</v>
+        <v>488366</v>
       </c>
       <c r="R40" t="n">
-        <v>6786889</v>
+        <v>6786907</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4707,10 +4712,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567318</v>
+        <v>122566978</v>
       </c>
       <c r="B41" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4719,43 +4724,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488883</v>
+        <v>488583</v>
       </c>
       <c r="R41" t="n">
-        <v>6786645</v>
+        <v>6786679</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5961,10 +5961,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122566953</v>
+        <v>122567305</v>
       </c>
       <c r="B53" t="n">
-        <v>98241</v>
+        <v>8441</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5973,35 +5973,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6010,10 +6006,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488429</v>
+        <v>488519</v>
       </c>
       <c r="R53" t="n">
-        <v>6786896</v>
+        <v>6786844</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6072,10 +6068,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567305</v>
+        <v>122566953</v>
       </c>
       <c r="B54" t="n">
-        <v>8441</v>
+        <v>98241</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6084,31 +6080,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6117,10 +6117,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488519</v>
+        <v>488429</v>
       </c>
       <c r="R54" t="n">
-        <v>6786844</v>
+        <v>6786896</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6281,7 +6281,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122567016</v>
+        <v>122566961</v>
       </c>
       <c r="B56" t="n">
         <v>78657</v>
@@ -6321,10 +6321,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488360</v>
+        <v>488327</v>
       </c>
       <c r="R56" t="n">
-        <v>6786913</v>
+        <v>6786847</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6383,10 +6383,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567293</v>
+        <v>122567016</v>
       </c>
       <c r="B57" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6395,43 +6395,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488790</v>
+        <v>488360</v>
       </c>
       <c r="R57" t="n">
-        <v>6786547</v>
+        <v>6786913</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6490,7 +6485,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122567322</v>
+        <v>122567293</v>
       </c>
       <c r="B58" t="n">
         <v>8441</v>
@@ -6526,7 +6521,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6535,10 +6530,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488700</v>
+        <v>488790</v>
       </c>
       <c r="R58" t="n">
-        <v>6786746</v>
+        <v>6786547</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6597,7 +6592,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122567327</v>
+        <v>122567322</v>
       </c>
       <c r="B59" t="n">
         <v>8441</v>
@@ -6642,10 +6637,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488442</v>
+        <v>488700</v>
       </c>
       <c r="R59" t="n">
-        <v>6786881</v>
+        <v>6786746</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6704,10 +6699,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122566961</v>
+        <v>122567327</v>
       </c>
       <c r="B60" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6716,38 +6711,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488327</v>
+        <v>488442</v>
       </c>
       <c r="R60" t="n">
-        <v>6786847</v>
+        <v>6786881</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6806,10 +6806,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122567290</v>
+        <v>122567014</v>
       </c>
       <c r="B61" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6818,43 +6818,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488345</v>
+        <v>488383</v>
       </c>
       <c r="R61" t="n">
-        <v>6786796</v>
+        <v>6786912</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6913,10 +6908,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122567309</v>
+        <v>122566892</v>
       </c>
       <c r="B62" t="n">
-        <v>8441</v>
+        <v>79275</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6925,43 +6920,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488707</v>
+        <v>488699</v>
       </c>
       <c r="R62" t="n">
-        <v>6786747</v>
+        <v>6786599</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7020,7 +7010,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122567325</v>
+        <v>122567290</v>
       </c>
       <c r="B63" t="n">
         <v>8441</v>
@@ -7056,7 +7046,7 @@
       <c r="I63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7065,10 +7055,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488576</v>
+        <v>488345</v>
       </c>
       <c r="R63" t="n">
-        <v>6786782</v>
+        <v>6786796</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7127,7 +7117,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122567299</v>
+        <v>122567309</v>
       </c>
       <c r="B64" t="n">
         <v>8441</v>
@@ -7163,7 +7153,7 @@
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7172,10 +7162,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488786</v>
+        <v>488707</v>
       </c>
       <c r="R64" t="n">
-        <v>6786723</v>
+        <v>6786747</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7234,10 +7224,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122566996</v>
+        <v>122567325</v>
       </c>
       <c r="B65" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7246,38 +7236,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488757</v>
+        <v>488576</v>
       </c>
       <c r="R65" t="n">
-        <v>6786723</v>
+        <v>6786782</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7336,10 +7331,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122566956</v>
+        <v>122567299</v>
       </c>
       <c r="B66" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7348,38 +7343,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488309</v>
+        <v>488786</v>
       </c>
       <c r="R66" t="n">
-        <v>6786859</v>
+        <v>6786723</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7438,7 +7438,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122567014</v>
+        <v>122566996</v>
       </c>
       <c r="B67" t="n">
         <v>78657</v>
@@ -7478,10 +7478,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488383</v>
+        <v>488757</v>
       </c>
       <c r="R67" t="n">
-        <v>6786912</v>
+        <v>6786723</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7540,10 +7540,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122566892</v>
+        <v>122566956</v>
       </c>
       <c r="B68" t="n">
-        <v>79275</v>
+        <v>78657</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7556,21 +7556,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7580,10 +7580,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488699</v>
+        <v>488309</v>
       </c>
       <c r="R68" t="n">
-        <v>6786599</v>
+        <v>6786859</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8468,7 +8468,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122567008</v>
+        <v>122567022</v>
       </c>
       <c r="B77" t="n">
         <v>78657</v>
@@ -8508,10 +8508,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488495</v>
+        <v>488137</v>
       </c>
       <c r="R77" t="n">
-        <v>6786888</v>
+        <v>6787026</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8570,10 +8570,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122566891</v>
+        <v>122567008</v>
       </c>
       <c r="B78" t="n">
-        <v>79275</v>
+        <v>78657</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8586,21 +8586,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8610,10 +8610,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488616</v>
+        <v>488495</v>
       </c>
       <c r="R78" t="n">
-        <v>6786648</v>
+        <v>6786888</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8672,10 +8672,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122567323</v>
+        <v>122566893</v>
       </c>
       <c r="B79" t="n">
-        <v>8441</v>
+        <v>79275</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8684,43 +8684,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488686</v>
+        <v>488693</v>
       </c>
       <c r="R79" t="n">
-        <v>6786745</v>
+        <v>6786741</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8779,10 +8774,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122567022</v>
+        <v>122566891</v>
       </c>
       <c r="B80" t="n">
-        <v>78657</v>
+        <v>79275</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8795,21 +8790,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8819,10 +8814,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488137</v>
+        <v>488616</v>
       </c>
       <c r="R80" t="n">
-        <v>6787026</v>
+        <v>6786648</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8881,10 +8876,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122566893</v>
+        <v>122567323</v>
       </c>
       <c r="B81" t="n">
-        <v>79275</v>
+        <v>8441</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8893,38 +8888,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488693</v>
+        <v>488686</v>
       </c>
       <c r="R81" t="n">
-        <v>6786741</v>
+        <v>6786745</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9508,7 +9508,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122566985</v>
+        <v>122567020</v>
       </c>
       <c r="B87" t="n">
         <v>78657</v>
@@ -9548,10 +9548,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488698</v>
+        <v>488185</v>
       </c>
       <c r="R87" t="n">
-        <v>6786584</v>
+        <v>6787005</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9610,7 +9610,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122566986</v>
+        <v>122566964</v>
       </c>
       <c r="B88" t="n">
         <v>78657</v>
@@ -9650,10 +9650,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488714</v>
+        <v>488351</v>
       </c>
       <c r="R88" t="n">
-        <v>6786574</v>
+        <v>6786831</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9712,10 +9712,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122567018</v>
+        <v>122567297</v>
       </c>
       <c r="B89" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9724,38 +9724,43 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488345</v>
+        <v>488804</v>
       </c>
       <c r="R89" t="n">
-        <v>6786910</v>
+        <v>6786700</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9814,10 +9819,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122566968</v>
+        <v>122566911</v>
       </c>
       <c r="B90" t="n">
-        <v>78657</v>
+        <v>91125</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9830,21 +9835,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9854,10 +9859,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488431</v>
+        <v>488882</v>
       </c>
       <c r="R90" t="n">
-        <v>6786772</v>
+        <v>6786609</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9916,7 +9921,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122566964</v>
+        <v>122566985</v>
       </c>
       <c r="B91" t="n">
         <v>78657</v>
@@ -9956,10 +9961,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488351</v>
+        <v>488698</v>
       </c>
       <c r="R91" t="n">
-        <v>6786831</v>
+        <v>6786584</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10018,10 +10023,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122566911</v>
+        <v>122566986</v>
       </c>
       <c r="B92" t="n">
-        <v>91125</v>
+        <v>78657</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10034,21 +10039,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10058,10 +10063,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488882</v>
+        <v>488714</v>
       </c>
       <c r="R92" t="n">
-        <v>6786609</v>
+        <v>6786574</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10120,7 +10125,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122567020</v>
+        <v>122567018</v>
       </c>
       <c r="B93" t="n">
         <v>78657</v>
@@ -10160,10 +10165,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488185</v>
+        <v>488345</v>
       </c>
       <c r="R93" t="n">
-        <v>6787005</v>
+        <v>6786910</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10222,10 +10227,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122567297</v>
+        <v>122566968</v>
       </c>
       <c r="B94" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10234,43 +10239,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488804</v>
+        <v>488431</v>
       </c>
       <c r="R94" t="n">
-        <v>6786700</v>
+        <v>6786772</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10431,10 +10431,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122567312</v>
+        <v>122566901</v>
       </c>
       <c r="B96" t="n">
-        <v>8441</v>
+        <v>57537</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10443,43 +10443,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>488341</v>
+        <v>488142</v>
       </c>
       <c r="R96" t="n">
-        <v>6786832</v>
+        <v>6787017</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10538,7 +10533,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122567298</v>
+        <v>122567312</v>
       </c>
       <c r="B97" t="n">
         <v>8441</v>
@@ -10574,7 +10569,7 @@
       <c r="I97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -10583,10 +10578,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>488789</v>
+        <v>488341</v>
       </c>
       <c r="R97" t="n">
-        <v>6786702</v>
+        <v>6786832</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10645,10 +10640,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122567001</v>
+        <v>122567298</v>
       </c>
       <c r="B98" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10657,38 +10652,43 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>488583</v>
+        <v>488789</v>
       </c>
       <c r="R98" t="n">
-        <v>6786774</v>
+        <v>6786702</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10747,10 +10747,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122566901</v>
+        <v>122567001</v>
       </c>
       <c r="B99" t="n">
-        <v>57537</v>
+        <v>78657</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10763,21 +10763,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10787,10 +10787,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>488142</v>
+        <v>488583</v>
       </c>
       <c r="R99" t="n">
-        <v>6787017</v>
+        <v>6786774</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12312,10 +12312,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122566952</v>
+        <v>122567306</v>
       </c>
       <c r="B114" t="n">
-        <v>80614</v>
+        <v>8441</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12324,38 +12324,43 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1049</v>
+        <v>106545</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488363</v>
+        <v>488556</v>
       </c>
       <c r="R114" t="n">
-        <v>6786907</v>
+        <v>6786835</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12414,10 +12419,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122566973</v>
+        <v>122566952</v>
       </c>
       <c r="B115" t="n">
-        <v>78657</v>
+        <v>80614</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12430,21 +12435,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12454,10 +12459,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>488482</v>
+        <v>488363</v>
       </c>
       <c r="R115" t="n">
-        <v>6786720</v>
+        <v>6786907</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12516,7 +12521,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122566981</v>
+        <v>122566973</v>
       </c>
       <c r="B116" t="n">
         <v>78657</v>
@@ -12556,10 +12561,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>488599</v>
+        <v>488482</v>
       </c>
       <c r="R116" t="n">
-        <v>6786673</v>
+        <v>6786720</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12618,7 +12623,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122566974</v>
+        <v>122566981</v>
       </c>
       <c r="B117" t="n">
         <v>78657</v>
@@ -12658,10 +12663,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>488486</v>
+        <v>488599</v>
       </c>
       <c r="R117" t="n">
-        <v>6786718</v>
+        <v>6786673</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12720,7 +12725,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122566999</v>
+        <v>122566974</v>
       </c>
       <c r="B118" t="n">
         <v>78657</v>
@@ -12760,10 +12765,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>488686</v>
+        <v>488486</v>
       </c>
       <c r="R118" t="n">
-        <v>6786738</v>
+        <v>6786718</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12822,7 +12827,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122567007</v>
+        <v>122566999</v>
       </c>
       <c r="B119" t="n">
         <v>78657</v>
@@ -12862,10 +12867,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>488530</v>
+        <v>488686</v>
       </c>
       <c r="R119" t="n">
-        <v>6786847</v>
+        <v>6786738</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12924,10 +12929,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122567306</v>
+        <v>122567007</v>
       </c>
       <c r="B120" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12936,43 +12941,38 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>488556</v>
+        <v>488530</v>
       </c>
       <c r="R120" t="n">
-        <v>6786835</v>
+        <v>6786847</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13031,7 +13031,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122566958</v>
+        <v>122567004</v>
       </c>
       <c r="B121" t="n">
         <v>78657</v>
@@ -13071,10 +13071,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488301</v>
+        <v>488475</v>
       </c>
       <c r="R121" t="n">
-        <v>6786839</v>
+        <v>6786864</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13133,7 +13133,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122566954</v>
+        <v>122566958</v>
       </c>
       <c r="B122" t="n">
         <v>78657</v>
@@ -13173,10 +13173,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488416</v>
+        <v>488301</v>
       </c>
       <c r="R122" t="n">
-        <v>6786896</v>
+        <v>6786839</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13235,7 +13235,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122567004</v>
+        <v>122566954</v>
       </c>
       <c r="B123" t="n">
         <v>78657</v>
@@ -13275,10 +13275,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>488475</v>
+        <v>488416</v>
       </c>
       <c r="R123" t="n">
-        <v>6786864</v>
+        <v>6786896</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13337,10 +13337,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122567319</v>
+        <v>122566909</v>
       </c>
       <c r="B124" t="n">
-        <v>8441</v>
+        <v>91279</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13349,43 +13349,38 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>1209</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>488869</v>
+        <v>488882</v>
       </c>
       <c r="R124" t="n">
-        <v>6786685</v>
+        <v>6786607</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13444,10 +13439,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122567002</v>
+        <v>122566898</v>
       </c>
       <c r="B125" t="n">
-        <v>78657</v>
+        <v>57537</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13460,21 +13455,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13484,10 +13479,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>488569</v>
+        <v>488296</v>
       </c>
       <c r="R125" t="n">
-        <v>6786787</v>
+        <v>6786844</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13546,7 +13541,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122567006</v>
+        <v>122567002</v>
       </c>
       <c r="B126" t="n">
         <v>78657</v>
@@ -13586,10 +13581,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>488556</v>
+        <v>488569</v>
       </c>
       <c r="R126" t="n">
-        <v>6786835</v>
+        <v>6786787</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13648,10 +13643,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122566898</v>
+        <v>122567006</v>
       </c>
       <c r="B127" t="n">
-        <v>57537</v>
+        <v>78657</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13664,21 +13659,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13688,10 +13683,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>488296</v>
+        <v>488556</v>
       </c>
       <c r="R127" t="n">
-        <v>6786844</v>
+        <v>6786835</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13750,10 +13745,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122566909</v>
+        <v>122567319</v>
       </c>
       <c r="B128" t="n">
-        <v>91279</v>
+        <v>8441</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13762,38 +13757,43 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1209</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>488882</v>
+        <v>488869</v>
       </c>
       <c r="R128" t="n">
-        <v>6786607</v>
+        <v>6786685</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13852,10 +13852,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122567315</v>
+        <v>122567011</v>
       </c>
       <c r="B129" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13864,43 +13864,38 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>488773</v>
+        <v>488427</v>
       </c>
       <c r="R129" t="n">
-        <v>6786561</v>
+        <v>6786888</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13959,10 +13954,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122567317</v>
+        <v>122567010</v>
       </c>
       <c r="B130" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13971,43 +13966,38 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>488892</v>
+        <v>488442</v>
       </c>
       <c r="R130" t="n">
-        <v>6786620</v>
+        <v>6786881</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14066,7 +14056,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122567011</v>
+        <v>122566967</v>
       </c>
       <c r="B131" t="n">
         <v>78657</v>
@@ -14106,10 +14096,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>488427</v>
+        <v>488387</v>
       </c>
       <c r="R131" t="n">
-        <v>6786888</v>
+        <v>6786773</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14168,10 +14158,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122567010</v>
+        <v>122567315</v>
       </c>
       <c r="B132" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14180,38 +14170,43 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>488442</v>
+        <v>488773</v>
       </c>
       <c r="R132" t="n">
-        <v>6786881</v>
+        <v>6786561</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14270,10 +14265,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>122566967</v>
+        <v>122567317</v>
       </c>
       <c r="B133" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14282,38 +14277,43 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>488387</v>
+        <v>488892</v>
       </c>
       <c r="R133" t="n">
-        <v>6786773</v>
+        <v>6786620</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>

--- a/artfynd/A 61338-2024 artfynd.xlsx
+++ b/artfynd/A 61338-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122566994</v>
+        <v>122566908</v>
       </c>
       <c r="B2" t="n">
-        <v>78657</v>
+        <v>57400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488883</v>
+        <v>488892</v>
       </c>
       <c r="R2" t="n">
-        <v>6786645</v>
+        <v>6786620</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122566899</v>
+        <v>122566986</v>
       </c>
       <c r="B3" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488482</v>
+        <v>488714</v>
       </c>
       <c r="R3" t="n">
-        <v>6786720</v>
+        <v>6786574</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122566977</v>
+        <v>122566972</v>
       </c>
       <c r="B4" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488515</v>
+        <v>488465</v>
       </c>
       <c r="R4" t="n">
-        <v>6786685</v>
+        <v>6786729</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122566997</v>
+        <v>122567008</v>
       </c>
       <c r="B5" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488731</v>
+        <v>488495</v>
       </c>
       <c r="R5" t="n">
-        <v>6786733</v>
+        <v>6786888</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566905</v>
+        <v>122566967</v>
       </c>
       <c r="B6" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,39 +1108,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488294</v>
+        <v>488387</v>
       </c>
       <c r="R6" t="n">
-        <v>6786826</v>
+        <v>6786773</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566908</v>
+        <v>122567314</v>
       </c>
       <c r="B7" t="n">
-        <v>57400</v>
+        <v>8441</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,35 +1206,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488892</v>
+        <v>488747</v>
       </c>
       <c r="R7" t="n">
-        <v>6786620</v>
+        <v>6786566</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,7 +1301,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567301</v>
+        <v>122567296</v>
       </c>
       <c r="B8" t="n">
         <v>8441</v>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488718</v>
+        <v>488834</v>
       </c>
       <c r="R8" t="n">
-        <v>6786752</v>
+        <v>6786685</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566980</v>
+        <v>122567321</v>
       </c>
       <c r="B9" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,38 +1420,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488590</v>
+        <v>488817</v>
       </c>
       <c r="R9" t="n">
-        <v>6786665</v>
+        <v>6786693</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566998</v>
+        <v>122567313</v>
       </c>
       <c r="B10" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,38 +1527,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488700</v>
+        <v>488616</v>
       </c>
       <c r="R10" t="n">
-        <v>6786744</v>
+        <v>6786649</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566963</v>
+        <v>122566954</v>
       </c>
       <c r="B11" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488341</v>
+        <v>488416</v>
       </c>
       <c r="R11" t="n">
-        <v>6786832</v>
+        <v>6786896</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,10 +1724,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567026</v>
+        <v>122566999</v>
       </c>
       <c r="B12" t="n">
-        <v>78302</v>
+        <v>78660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1730,21 +1740,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,10 +1764,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488539</v>
+        <v>488686</v>
       </c>
       <c r="R12" t="n">
-        <v>6786689</v>
+        <v>6786738</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,10 +1826,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567025</v>
+        <v>122567018</v>
       </c>
       <c r="B13" t="n">
-        <v>78302</v>
+        <v>78660</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1832,21 +1842,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1856,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488378</v>
+        <v>488345</v>
       </c>
       <c r="R13" t="n">
-        <v>6786805</v>
+        <v>6786910</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,10 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566904</v>
+        <v>122566956</v>
       </c>
       <c r="B14" t="n">
-        <v>90854</v>
+        <v>78660</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1934,21 +1944,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,10 +1968,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488552</v>
+        <v>488309</v>
       </c>
       <c r="R14" t="n">
-        <v>6786834</v>
+        <v>6786859</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,10 +2030,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567009</v>
+        <v>122567025</v>
       </c>
       <c r="B15" t="n">
-        <v>78657</v>
+        <v>78305</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2036,21 +2046,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2060,10 +2070,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488465</v>
+        <v>488378</v>
       </c>
       <c r="R15" t="n">
-        <v>6786880</v>
+        <v>6786805</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566982</v>
+        <v>122567028</v>
       </c>
       <c r="B16" t="n">
-        <v>78657</v>
+        <v>78305</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2138,21 +2148,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2162,10 +2172,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488600</v>
+        <v>488611</v>
       </c>
       <c r="R16" t="n">
-        <v>6786662</v>
+        <v>6786649</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2224,10 +2234,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566984</v>
+        <v>122566911</v>
       </c>
       <c r="B17" t="n">
-        <v>78657</v>
+        <v>91128</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2240,21 +2250,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2264,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488699</v>
+        <v>488882</v>
       </c>
       <c r="R17" t="n">
-        <v>6786596</v>
+        <v>6786609</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2326,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566971</v>
+        <v>122567005</v>
       </c>
       <c r="B18" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2366,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488461</v>
+        <v>488415</v>
       </c>
       <c r="R18" t="n">
-        <v>6786736</v>
+        <v>6786889</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2428,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566902</v>
+        <v>122567001</v>
       </c>
       <c r="B19" t="n">
-        <v>90854</v>
+        <v>78660</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2444,21 +2454,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2468,10 +2478,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488397</v>
+        <v>488583</v>
       </c>
       <c r="R19" t="n">
-        <v>6786809</v>
+        <v>6786774</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2530,10 +2540,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122567324</v>
+        <v>122566899</v>
       </c>
       <c r="B20" t="n">
-        <v>8441</v>
+        <v>57537</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2542,43 +2552,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488638</v>
+        <v>488482</v>
       </c>
       <c r="R20" t="n">
-        <v>6786764</v>
+        <v>6786720</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2637,10 +2642,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567294</v>
+        <v>122567026</v>
       </c>
       <c r="B21" t="n">
-        <v>8441</v>
+        <v>78305</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2649,43 +2654,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488801</v>
+        <v>488539</v>
       </c>
       <c r="R21" t="n">
-        <v>6786563</v>
+        <v>6786689</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,10 +2744,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566912</v>
+        <v>122566958</v>
       </c>
       <c r="B22" t="n">
-        <v>91125</v>
+        <v>78660</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2760,21 +2760,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488895</v>
+        <v>488301</v>
       </c>
       <c r="R22" t="n">
-        <v>6786588</v>
+        <v>6786839</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567029</v>
+        <v>122566994</v>
       </c>
       <c r="B23" t="n">
-        <v>78302</v>
+        <v>78660</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2862,21 +2862,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488664</v>
+        <v>488883</v>
       </c>
       <c r="R23" t="n">
-        <v>6786615</v>
+        <v>6786645</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2948,10 +2948,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566969</v>
+        <v>122566997</v>
       </c>
       <c r="B24" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488452</v>
+        <v>488731</v>
       </c>
       <c r="R24" t="n">
-        <v>6786772</v>
+        <v>6786733</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566965</v>
+        <v>122567305</v>
       </c>
       <c r="B25" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3062,38 +3062,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488378</v>
+        <v>488519</v>
       </c>
       <c r="R25" t="n">
-        <v>6786805</v>
+        <v>6786844</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3152,10 +3157,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567019</v>
+        <v>122567309</v>
       </c>
       <c r="B26" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3164,38 +3169,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488297</v>
+        <v>488707</v>
       </c>
       <c r="R26" t="n">
-        <v>6786946</v>
+        <v>6786747</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3254,10 +3264,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122567003</v>
+        <v>122567324</v>
       </c>
       <c r="B27" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3266,38 +3276,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488550</v>
+        <v>488638</v>
       </c>
       <c r="R27" t="n">
-        <v>6786822</v>
+        <v>6786764</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3356,10 +3371,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122566970</v>
+        <v>122567315</v>
       </c>
       <c r="B28" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3368,38 +3383,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488469</v>
+        <v>488773</v>
       </c>
       <c r="R28" t="n">
-        <v>6786751</v>
+        <v>6786561</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3458,10 +3478,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567023</v>
+        <v>122567299</v>
       </c>
       <c r="B29" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3470,38 +3490,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488135</v>
+        <v>488786</v>
       </c>
       <c r="R29" t="n">
-        <v>6787033</v>
+        <v>6786723</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3560,7 +3585,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567314</v>
+        <v>122567295</v>
       </c>
       <c r="B30" t="n">
         <v>8441</v>
@@ -3596,7 +3621,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3605,10 +3630,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488747</v>
+        <v>488850</v>
       </c>
       <c r="R30" t="n">
-        <v>6786566</v>
+        <v>6786668</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3667,10 +3692,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567310</v>
+        <v>122566979</v>
       </c>
       <c r="B31" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3679,43 +3704,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488294</v>
+        <v>488583</v>
       </c>
       <c r="R31" t="n">
-        <v>6786825</v>
+        <v>6786676</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3774,10 +3794,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122567308</v>
+        <v>122566974</v>
       </c>
       <c r="B32" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3786,43 +3806,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488669</v>
+        <v>488486</v>
       </c>
       <c r="R32" t="n">
-        <v>6786761</v>
+        <v>6786718</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3881,10 +3896,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122567289</v>
+        <v>122566985</v>
       </c>
       <c r="B33" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3893,43 +3908,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488322</v>
+        <v>488698</v>
       </c>
       <c r="R33" t="n">
-        <v>6786810</v>
+        <v>6786584</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3988,10 +3998,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567292</v>
+        <v>122566996</v>
       </c>
       <c r="B34" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4000,43 +4010,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488533</v>
+        <v>488757</v>
       </c>
       <c r="R34" t="n">
-        <v>6786690</v>
+        <v>6786723</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4095,10 +4100,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122566903</v>
+        <v>122566889</v>
       </c>
       <c r="B35" t="n">
-        <v>90854</v>
+        <v>79278</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4111,21 +4116,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4135,10 +4140,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488770</v>
+        <v>488296</v>
       </c>
       <c r="R35" t="n">
-        <v>6786732</v>
+        <v>6786844</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4197,10 +4202,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122567005</v>
+        <v>122566987</v>
       </c>
       <c r="B36" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4237,10 +4242,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488415</v>
+        <v>488735</v>
       </c>
       <c r="R36" t="n">
-        <v>6786889</v>
+        <v>6786569</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4299,10 +4304,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122567318</v>
+        <v>122566973</v>
       </c>
       <c r="B37" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4311,43 +4316,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488883</v>
+        <v>488482</v>
       </c>
       <c r="R37" t="n">
-        <v>6786645</v>
+        <v>6786720</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4406,10 +4406,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567017</v>
+        <v>122567016</v>
       </c>
       <c r="B38" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4446,10 +4446,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488353</v>
+        <v>488360</v>
       </c>
       <c r="R38" t="n">
-        <v>6786911</v>
+        <v>6786913</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4508,10 +4508,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122566991</v>
+        <v>122567002</v>
       </c>
       <c r="B39" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488918</v>
+        <v>488569</v>
       </c>
       <c r="R39" t="n">
-        <v>6786607</v>
+        <v>6786787</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4610,10 +4610,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122567015</v>
+        <v>122567023</v>
       </c>
       <c r="B40" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488366</v>
+        <v>488135</v>
       </c>
       <c r="R40" t="n">
-        <v>6786907</v>
+        <v>6787033</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4712,10 +4712,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122566978</v>
+        <v>122567304</v>
       </c>
       <c r="B41" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4724,38 +4724,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488583</v>
+        <v>488591</v>
       </c>
       <c r="R41" t="n">
-        <v>6786679</v>
+        <v>6786769</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4814,10 +4819,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122566983</v>
+        <v>122567298</v>
       </c>
       <c r="B42" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4826,38 +4831,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488609</v>
+        <v>488789</v>
       </c>
       <c r="R42" t="n">
-        <v>6786648</v>
+        <v>6786702</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4916,7 +4926,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567300</v>
+        <v>122567322</v>
       </c>
       <c r="B43" t="n">
         <v>8441</v>
@@ -4952,7 +4962,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4961,10 +4971,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488768</v>
+        <v>488700</v>
       </c>
       <c r="R43" t="n">
-        <v>6786742</v>
+        <v>6786746</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5023,7 +5033,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122567296</v>
+        <v>122567317</v>
       </c>
       <c r="B44" t="n">
         <v>8441</v>
@@ -5059,7 +5069,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5068,10 +5078,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488834</v>
+        <v>488892</v>
       </c>
       <c r="R44" t="n">
-        <v>6786685</v>
+        <v>6786620</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5130,7 +5140,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122567295</v>
+        <v>122567297</v>
       </c>
       <c r="B45" t="n">
         <v>8441</v>
@@ -5175,10 +5185,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488850</v>
+        <v>488804</v>
       </c>
       <c r="R45" t="n">
-        <v>6786668</v>
+        <v>6786700</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5451,10 +5461,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122567012</v>
+        <v>122567030</v>
       </c>
       <c r="B48" t="n">
-        <v>78657</v>
+        <v>78305</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5467,21 +5477,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5491,10 +5501,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488420</v>
+        <v>488769</v>
       </c>
       <c r="R48" t="n">
-        <v>6786898</v>
+        <v>6786552</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5553,10 +5563,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122566995</v>
+        <v>122566909</v>
       </c>
       <c r="B49" t="n">
-        <v>78657</v>
+        <v>91282</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5565,25 +5575,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5593,10 +5603,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488833</v>
+        <v>488882</v>
       </c>
       <c r="R49" t="n">
-        <v>6786674</v>
+        <v>6786607</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5655,10 +5665,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122566987</v>
+        <v>122566977</v>
       </c>
       <c r="B50" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5695,10 +5705,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488735</v>
+        <v>488515</v>
       </c>
       <c r="R50" t="n">
-        <v>6786569</v>
+        <v>6786685</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5757,10 +5767,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122566959</v>
+        <v>122567020</v>
       </c>
       <c r="B51" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5797,10 +5807,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488317</v>
+        <v>488185</v>
       </c>
       <c r="R51" t="n">
-        <v>6786858</v>
+        <v>6787005</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5859,10 +5869,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122566894</v>
+        <v>122566968</v>
       </c>
       <c r="B52" t="n">
-        <v>79275</v>
+        <v>78660</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5875,21 +5885,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5899,10 +5909,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488182</v>
+        <v>488431</v>
       </c>
       <c r="R52" t="n">
-        <v>6787001</v>
+        <v>6786772</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5961,10 +5971,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567305</v>
+        <v>122567017</v>
       </c>
       <c r="B53" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5973,43 +5983,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488519</v>
+        <v>488353</v>
       </c>
       <c r="R53" t="n">
-        <v>6786844</v>
+        <v>6786911</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6068,10 +6073,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122566953</v>
+        <v>122567011</v>
       </c>
       <c r="B54" t="n">
-        <v>98241</v>
+        <v>78660</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6080,47 +6085,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488429</v>
+        <v>488427</v>
       </c>
       <c r="R54" t="n">
-        <v>6786896</v>
+        <v>6786888</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6179,10 +6175,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122566896</v>
+        <v>122566965</v>
       </c>
       <c r="B55" t="n">
-        <v>90834</v>
+        <v>78660</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6195,21 +6191,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6219,10 +6215,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488882</v>
+        <v>488378</v>
       </c>
       <c r="R55" t="n">
-        <v>6786607</v>
+        <v>6786805</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6281,10 +6277,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122566961</v>
+        <v>122566890</v>
       </c>
       <c r="B56" t="n">
-        <v>78657</v>
+        <v>79278</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6297,21 +6293,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6321,10 +6317,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488327</v>
+        <v>488572</v>
       </c>
       <c r="R56" t="n">
-        <v>6786847</v>
+        <v>6786674</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6383,10 +6379,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567016</v>
+        <v>122566964</v>
       </c>
       <c r="B57" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6423,10 +6419,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488360</v>
+        <v>488351</v>
       </c>
       <c r="R57" t="n">
-        <v>6786913</v>
+        <v>6786831</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6485,10 +6481,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122567293</v>
+        <v>122567007</v>
       </c>
       <c r="B58" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6497,43 +6493,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488790</v>
+        <v>488530</v>
       </c>
       <c r="R58" t="n">
-        <v>6786547</v>
+        <v>6786847</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6592,10 +6583,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122567322</v>
+        <v>122566903</v>
       </c>
       <c r="B59" t="n">
-        <v>8441</v>
+        <v>90857</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6604,43 +6595,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488700</v>
+        <v>488770</v>
       </c>
       <c r="R59" t="n">
-        <v>6786746</v>
+        <v>6786732</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6699,7 +6685,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122567327</v>
+        <v>122567319</v>
       </c>
       <c r="B60" t="n">
         <v>8441</v>
@@ -6744,10 +6730,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488442</v>
+        <v>488869</v>
       </c>
       <c r="R60" t="n">
-        <v>6786881</v>
+        <v>6786685</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6806,10 +6792,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122567014</v>
+        <v>122567326</v>
       </c>
       <c r="B61" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6818,38 +6804,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488383</v>
+        <v>488545</v>
       </c>
       <c r="R61" t="n">
-        <v>6786912</v>
+        <v>6786849</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6908,10 +6899,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122566892</v>
+        <v>122566998</v>
       </c>
       <c r="B62" t="n">
-        <v>79275</v>
+        <v>78660</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6924,21 +6915,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6948,10 +6939,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488699</v>
+        <v>488700</v>
       </c>
       <c r="R62" t="n">
-        <v>6786599</v>
+        <v>6786744</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7010,10 +7001,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122567290</v>
+        <v>122566894</v>
       </c>
       <c r="B63" t="n">
-        <v>8441</v>
+        <v>79278</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7022,43 +7013,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488345</v>
+        <v>488182</v>
       </c>
       <c r="R63" t="n">
-        <v>6786796</v>
+        <v>6787001</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7117,7 +7103,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122567309</v>
+        <v>122567290</v>
       </c>
       <c r="B64" t="n">
         <v>8441</v>
@@ -7153,7 +7139,7 @@
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7162,10 +7148,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488707</v>
+        <v>488345</v>
       </c>
       <c r="R64" t="n">
-        <v>6786747</v>
+        <v>6786796</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7224,10 +7210,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122567325</v>
+        <v>122566991</v>
       </c>
       <c r="B65" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7236,43 +7222,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488576</v>
+        <v>488918</v>
       </c>
       <c r="R65" t="n">
-        <v>6786782</v>
+        <v>6786607</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7331,10 +7312,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122567299</v>
+        <v>122567022</v>
       </c>
       <c r="B66" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7343,43 +7324,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488786</v>
+        <v>488137</v>
       </c>
       <c r="R66" t="n">
-        <v>6786723</v>
+        <v>6787026</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7438,10 +7414,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122566996</v>
+        <v>122567032</v>
       </c>
       <c r="B67" t="n">
-        <v>78657</v>
+        <v>5173</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7450,38 +7426,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488757</v>
+        <v>488901</v>
       </c>
       <c r="R67" t="n">
-        <v>6786723</v>
+        <v>6786589</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7540,10 +7521,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122566956</v>
+        <v>122566953</v>
       </c>
       <c r="B68" t="n">
-        <v>78657</v>
+        <v>98244</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7552,38 +7533,47 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488309</v>
+        <v>488429</v>
       </c>
       <c r="R68" t="n">
-        <v>6786859</v>
+        <v>6786896</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7642,10 +7632,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122567030</v>
+        <v>122566952</v>
       </c>
       <c r="B69" t="n">
-        <v>78302</v>
+        <v>80617</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7658,21 +7648,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7682,10 +7672,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488769</v>
+        <v>488363</v>
       </c>
       <c r="R69" t="n">
-        <v>6786552</v>
+        <v>6786907</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7744,10 +7734,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122566988</v>
+        <v>122566990</v>
       </c>
       <c r="B70" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7784,10 +7774,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488803</v>
+        <v>488840</v>
       </c>
       <c r="R70" t="n">
-        <v>6786562</v>
+        <v>6786622</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7846,10 +7836,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122567307</v>
+        <v>122566892</v>
       </c>
       <c r="B71" t="n">
-        <v>8441</v>
+        <v>79278</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7858,43 +7848,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488535</v>
+        <v>488699</v>
       </c>
       <c r="R71" t="n">
-        <v>6786843</v>
+        <v>6786599</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7953,10 +7938,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122567313</v>
+        <v>122567012</v>
       </c>
       <c r="B72" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7965,43 +7950,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488616</v>
+        <v>488420</v>
       </c>
       <c r="R72" t="n">
-        <v>6786649</v>
+        <v>6786898</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8060,10 +8040,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122566957</v>
+        <v>122567009</v>
       </c>
       <c r="B73" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8100,10 +8080,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488300</v>
+        <v>488465</v>
       </c>
       <c r="R73" t="n">
-        <v>6786820</v>
+        <v>6786880</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8162,10 +8142,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122567013</v>
+        <v>122566960</v>
       </c>
       <c r="B74" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8202,10 +8182,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488389</v>
+        <v>488322</v>
       </c>
       <c r="R74" t="n">
-        <v>6786901</v>
+        <v>6786853</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8264,10 +8244,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122567027</v>
+        <v>122567013</v>
       </c>
       <c r="B75" t="n">
-        <v>78302</v>
+        <v>78660</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8280,21 +8260,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8304,10 +8284,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488618</v>
+        <v>488389</v>
       </c>
       <c r="R75" t="n">
-        <v>6786631</v>
+        <v>6786901</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8366,10 +8346,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122567000</v>
+        <v>122567003</v>
       </c>
       <c r="B76" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8406,10 +8386,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488678</v>
+        <v>488550</v>
       </c>
       <c r="R76" t="n">
-        <v>6786753</v>
+        <v>6786822</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8468,10 +8448,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122567022</v>
+        <v>122566893</v>
       </c>
       <c r="B77" t="n">
-        <v>78657</v>
+        <v>79278</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8484,21 +8464,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8508,10 +8488,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488137</v>
+        <v>488693</v>
       </c>
       <c r="R77" t="n">
-        <v>6787026</v>
+        <v>6786741</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8570,10 +8550,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122567008</v>
+        <v>122567325</v>
       </c>
       <c r="B78" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8582,38 +8562,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488495</v>
+        <v>488576</v>
       </c>
       <c r="R78" t="n">
-        <v>6786888</v>
+        <v>6786782</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8672,10 +8657,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122566893</v>
+        <v>122567323</v>
       </c>
       <c r="B79" t="n">
-        <v>79275</v>
+        <v>8441</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8684,38 +8669,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488693</v>
+        <v>488686</v>
       </c>
       <c r="R79" t="n">
-        <v>6786741</v>
+        <v>6786745</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8774,10 +8764,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122566891</v>
+        <v>122567029</v>
       </c>
       <c r="B80" t="n">
-        <v>79275</v>
+        <v>78305</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8790,21 +8780,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8814,10 +8804,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488616</v>
+        <v>488664</v>
       </c>
       <c r="R80" t="n">
-        <v>6786648</v>
+        <v>6786615</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8876,10 +8866,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122567323</v>
+        <v>122566904</v>
       </c>
       <c r="B81" t="n">
-        <v>8441</v>
+        <v>90857</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8888,43 +8878,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488686</v>
+        <v>488552</v>
       </c>
       <c r="R81" t="n">
-        <v>6786745</v>
+        <v>6786834</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8983,10 +8968,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122566890</v>
+        <v>122566970</v>
       </c>
       <c r="B82" t="n">
-        <v>79275</v>
+        <v>78660</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8999,21 +8984,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9023,10 +9008,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488572</v>
+        <v>488469</v>
       </c>
       <c r="R82" t="n">
-        <v>6786674</v>
+        <v>6786751</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9085,10 +9070,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122566907</v>
+        <v>122566981</v>
       </c>
       <c r="B83" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9101,36 +9086,31 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488852</v>
+        <v>488599</v>
       </c>
       <c r="R83" t="n">
         <v>6786673</v>
@@ -9192,10 +9172,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122567321</v>
+        <v>122566959</v>
       </c>
       <c r="B84" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9204,43 +9184,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488817</v>
+        <v>488317</v>
       </c>
       <c r="R84" t="n">
-        <v>6786693</v>
+        <v>6786858</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9299,10 +9274,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122567316</v>
+        <v>122567000</v>
       </c>
       <c r="B85" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9311,43 +9286,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488900</v>
+        <v>488678</v>
       </c>
       <c r="R85" t="n">
-        <v>6786628</v>
+        <v>6786753</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9406,10 +9376,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122567024</v>
+        <v>122566982</v>
       </c>
       <c r="B86" t="n">
-        <v>91086</v>
+        <v>78660</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9418,25 +9388,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9446,10 +9416,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488663</v>
+        <v>488600</v>
       </c>
       <c r="R86" t="n">
-        <v>6786615</v>
+        <v>6786662</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9508,10 +9478,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122567020</v>
+        <v>122566891</v>
       </c>
       <c r="B87" t="n">
-        <v>78657</v>
+        <v>79278</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9524,21 +9494,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9548,10 +9518,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488185</v>
+        <v>488616</v>
       </c>
       <c r="R87" t="n">
-        <v>6787005</v>
+        <v>6786648</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9610,10 +9580,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122566964</v>
+        <v>122567014</v>
       </c>
       <c r="B88" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9650,10 +9620,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488351</v>
+        <v>488383</v>
       </c>
       <c r="R88" t="n">
-        <v>6786831</v>
+        <v>6786912</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9712,7 +9682,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122567297</v>
+        <v>122567301</v>
       </c>
       <c r="B89" t="n">
         <v>8441</v>
@@ -9757,10 +9727,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488804</v>
+        <v>488718</v>
       </c>
       <c r="R89" t="n">
-        <v>6786700</v>
+        <v>6786752</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9819,10 +9789,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122566911</v>
+        <v>122567312</v>
       </c>
       <c r="B90" t="n">
-        <v>91125</v>
+        <v>8441</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9831,38 +9801,43 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>658</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488882</v>
+        <v>488341</v>
       </c>
       <c r="R90" t="n">
-        <v>6786609</v>
+        <v>6786832</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9921,10 +9896,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122566985</v>
+        <v>122567327</v>
       </c>
       <c r="B91" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9933,38 +9908,43 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488698</v>
+        <v>488442</v>
       </c>
       <c r="R91" t="n">
-        <v>6786584</v>
+        <v>6786881</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10023,10 +10003,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122566986</v>
+        <v>122566898</v>
       </c>
       <c r="B92" t="n">
-        <v>78657</v>
+        <v>57537</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10039,21 +10019,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10063,10 +10043,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488714</v>
+        <v>488296</v>
       </c>
       <c r="R92" t="n">
-        <v>6786574</v>
+        <v>6786844</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10125,10 +10105,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122567018</v>
+        <v>122567310</v>
       </c>
       <c r="B93" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10137,38 +10117,43 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488345</v>
+        <v>488294</v>
       </c>
       <c r="R93" t="n">
-        <v>6786910</v>
+        <v>6786825</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10227,10 +10212,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122566968</v>
+        <v>122567293</v>
       </c>
       <c r="B94" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10239,38 +10224,43 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488431</v>
+        <v>488790</v>
       </c>
       <c r="R94" t="n">
-        <v>6786772</v>
+        <v>6786547</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10329,10 +10319,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122566990</v>
+        <v>122566988</v>
       </c>
       <c r="B95" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10369,10 +10359,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>488840</v>
+        <v>488803</v>
       </c>
       <c r="R95" t="n">
-        <v>6786622</v>
+        <v>6786562</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10431,10 +10421,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122566901</v>
+        <v>122567006</v>
       </c>
       <c r="B96" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10447,21 +10437,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10471,10 +10461,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>488142</v>
+        <v>488556</v>
       </c>
       <c r="R96" t="n">
-        <v>6787017</v>
+        <v>6786835</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10533,10 +10523,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122567312</v>
+        <v>122567015</v>
       </c>
       <c r="B97" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10545,43 +10535,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>488341</v>
+        <v>488366</v>
       </c>
       <c r="R97" t="n">
-        <v>6786832</v>
+        <v>6786907</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10640,10 +10625,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122567298</v>
+        <v>122566978</v>
       </c>
       <c r="B98" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10652,43 +10637,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>488789</v>
+        <v>488583</v>
       </c>
       <c r="R98" t="n">
-        <v>6786702</v>
+        <v>6786679</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10747,10 +10727,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122567001</v>
+        <v>122566957</v>
       </c>
       <c r="B99" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10787,10 +10767,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>488583</v>
+        <v>488300</v>
       </c>
       <c r="R99" t="n">
-        <v>6786774</v>
+        <v>6786820</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10849,10 +10829,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122566972</v>
+        <v>122566902</v>
       </c>
       <c r="B100" t="n">
-        <v>78657</v>
+        <v>90857</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10865,21 +10845,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10889,10 +10869,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>488465</v>
+        <v>488397</v>
       </c>
       <c r="R100" t="n">
-        <v>6786729</v>
+        <v>6786809</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10951,10 +10931,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122566966</v>
+        <v>122567024</v>
       </c>
       <c r="B101" t="n">
-        <v>78657</v>
+        <v>91089</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10963,25 +10943,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10991,10 +10971,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>488390</v>
+        <v>488663</v>
       </c>
       <c r="R101" t="n">
-        <v>6786813</v>
+        <v>6786615</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11053,7 +11033,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122567304</v>
+        <v>122567307</v>
       </c>
       <c r="B102" t="n">
         <v>8441</v>
@@ -11098,10 +11078,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>488591</v>
+        <v>488535</v>
       </c>
       <c r="R102" t="n">
-        <v>6786769</v>
+        <v>6786843</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11160,7 +11140,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122567326</v>
+        <v>122567294</v>
       </c>
       <c r="B103" t="n">
         <v>8441</v>
@@ -11196,7 +11176,7 @@
       <c r="I103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11205,10 +11185,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>488545</v>
+        <v>488801</v>
       </c>
       <c r="R103" t="n">
-        <v>6786849</v>
+        <v>6786563</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11267,10 +11247,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122566979</v>
+        <v>122566896</v>
       </c>
       <c r="B104" t="n">
-        <v>78657</v>
+        <v>90837</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11283,21 +11263,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11307,10 +11287,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488583</v>
+        <v>488882</v>
       </c>
       <c r="R104" t="n">
-        <v>6786676</v>
+        <v>6786607</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11369,10 +11349,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122566960</v>
+        <v>122567004</v>
       </c>
       <c r="B105" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11409,10 +11389,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488322</v>
+        <v>488475</v>
       </c>
       <c r="R105" t="n">
-        <v>6786853</v>
+        <v>6786864</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11471,10 +11451,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122566962</v>
+        <v>122566913</v>
       </c>
       <c r="B106" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11487,34 +11467,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488324</v>
+        <v>488602</v>
       </c>
       <c r="R106" t="n">
-        <v>6786843</v>
+        <v>6786666</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11547,6 +11532,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11573,10 +11563,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122566889</v>
+        <v>122566912</v>
       </c>
       <c r="B107" t="n">
-        <v>79275</v>
+        <v>91128</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11589,21 +11579,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11613,10 +11603,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488296</v>
+        <v>488895</v>
       </c>
       <c r="R107" t="n">
-        <v>6786844</v>
+        <v>6786588</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11675,10 +11665,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122567032</v>
+        <v>122566969</v>
       </c>
       <c r="B108" t="n">
-        <v>5173</v>
+        <v>78660</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11687,43 +11677,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>488901</v>
+        <v>488452</v>
       </c>
       <c r="R108" t="n">
-        <v>6786589</v>
+        <v>6786772</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11782,10 +11767,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122566913</v>
+        <v>122566966</v>
       </c>
       <c r="B109" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11798,39 +11783,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488602</v>
+        <v>488390</v>
       </c>
       <c r="R109" t="n">
-        <v>6786666</v>
+        <v>6786813</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11863,11 +11843,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11894,10 +11869,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122567311</v>
+        <v>122566901</v>
       </c>
       <c r="B110" t="n">
-        <v>8441</v>
+        <v>57537</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11906,43 +11881,38 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>488332</v>
+        <v>488142</v>
       </c>
       <c r="R110" t="n">
-        <v>6786824</v>
+        <v>6787017</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12001,10 +11971,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122567028</v>
+        <v>122567289</v>
       </c>
       <c r="B111" t="n">
-        <v>78302</v>
+        <v>8441</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12013,38 +11983,43 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>488611</v>
+        <v>488322</v>
       </c>
       <c r="R111" t="n">
-        <v>6786649</v>
+        <v>6786810</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12103,10 +12078,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122566897</v>
+        <v>122567292</v>
       </c>
       <c r="B112" t="n">
-        <v>90834</v>
+        <v>8441</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12115,38 +12090,43 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>488892</v>
+        <v>488533</v>
       </c>
       <c r="R112" t="n">
-        <v>6786591</v>
+        <v>6786690</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12205,7 +12185,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122567320</v>
+        <v>122567306</v>
       </c>
       <c r="B113" t="n">
         <v>8441</v>
@@ -12241,7 +12221,7 @@
       <c r="I113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -12250,10 +12230,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488833</v>
+        <v>488556</v>
       </c>
       <c r="R113" t="n">
-        <v>6786674</v>
+        <v>6786835</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12312,10 +12292,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122567306</v>
+        <v>122566971</v>
       </c>
       <c r="B114" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12324,43 +12304,38 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488556</v>
+        <v>488461</v>
       </c>
       <c r="R114" t="n">
-        <v>6786835</v>
+        <v>6786736</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12419,10 +12394,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122566952</v>
+        <v>122567300</v>
       </c>
       <c r="B115" t="n">
-        <v>80614</v>
+        <v>8441</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12431,38 +12406,43 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1049</v>
+        <v>106545</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>488363</v>
+        <v>488768</v>
       </c>
       <c r="R115" t="n">
-        <v>6786907</v>
+        <v>6786742</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12521,10 +12501,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122566973</v>
+        <v>122567311</v>
       </c>
       <c r="B116" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12533,38 +12513,43 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>488482</v>
+        <v>488332</v>
       </c>
       <c r="R116" t="n">
-        <v>6786720</v>
+        <v>6786824</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12623,10 +12608,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122566981</v>
+        <v>122566984</v>
       </c>
       <c r="B117" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12663,10 +12648,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>488599</v>
+        <v>488699</v>
       </c>
       <c r="R117" t="n">
-        <v>6786673</v>
+        <v>6786596</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12725,10 +12710,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122566974</v>
+        <v>122567027</v>
       </c>
       <c r="B118" t="n">
-        <v>78657</v>
+        <v>78305</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12741,21 +12726,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12765,10 +12750,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>488486</v>
+        <v>488618</v>
       </c>
       <c r="R118" t="n">
-        <v>6786718</v>
+        <v>6786631</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12827,10 +12812,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122566999</v>
+        <v>122566897</v>
       </c>
       <c r="B119" t="n">
-        <v>78657</v>
+        <v>90837</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12843,21 +12828,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12867,10 +12852,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>488686</v>
+        <v>488892</v>
       </c>
       <c r="R119" t="n">
-        <v>6786738</v>
+        <v>6786591</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12929,10 +12914,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122567007</v>
+        <v>122566995</v>
       </c>
       <c r="B120" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12969,10 +12954,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>488530</v>
+        <v>488833</v>
       </c>
       <c r="R120" t="n">
-        <v>6786847</v>
+        <v>6786674</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13031,10 +13016,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122567004</v>
+        <v>122567010</v>
       </c>
       <c r="B121" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13071,10 +13056,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488475</v>
+        <v>488442</v>
       </c>
       <c r="R121" t="n">
-        <v>6786864</v>
+        <v>6786881</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13133,10 +13118,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122566958</v>
+        <v>122567019</v>
       </c>
       <c r="B122" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13173,10 +13158,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488301</v>
+        <v>488297</v>
       </c>
       <c r="R122" t="n">
-        <v>6786839</v>
+        <v>6786946</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13235,10 +13220,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122566954</v>
+        <v>122566983</v>
       </c>
       <c r="B123" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13275,10 +13260,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>488416</v>
+        <v>488609</v>
       </c>
       <c r="R123" t="n">
-        <v>6786896</v>
+        <v>6786648</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13337,10 +13322,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122566909</v>
+        <v>122566905</v>
       </c>
       <c r="B124" t="n">
-        <v>91279</v>
+        <v>57400</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13349,38 +13334,43 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>488882</v>
+        <v>488294</v>
       </c>
       <c r="R124" t="n">
-        <v>6786607</v>
+        <v>6786826</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13439,10 +13429,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122566898</v>
+        <v>122567308</v>
       </c>
       <c r="B125" t="n">
-        <v>57537</v>
+        <v>8441</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13451,38 +13441,43 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>488296</v>
+        <v>488669</v>
       </c>
       <c r="R125" t="n">
-        <v>6786844</v>
+        <v>6786761</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13541,10 +13536,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122567002</v>
+        <v>122566980</v>
       </c>
       <c r="B126" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13581,10 +13576,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>488569</v>
+        <v>488590</v>
       </c>
       <c r="R126" t="n">
-        <v>6786787</v>
+        <v>6786665</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13643,10 +13638,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122567006</v>
+        <v>122566961</v>
       </c>
       <c r="B127" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13683,10 +13678,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>488556</v>
+        <v>488327</v>
       </c>
       <c r="R127" t="n">
-        <v>6786835</v>
+        <v>6786847</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13745,10 +13740,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122567319</v>
+        <v>122566963</v>
       </c>
       <c r="B128" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13757,43 +13752,38 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>488869</v>
+        <v>488341</v>
       </c>
       <c r="R128" t="n">
-        <v>6786685</v>
+        <v>6786832</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13852,10 +13842,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122567011</v>
+        <v>122566907</v>
       </c>
       <c r="B129" t="n">
-        <v>78657</v>
+        <v>57400</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13868,34 +13858,39 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>488427</v>
+        <v>488852</v>
       </c>
       <c r="R129" t="n">
-        <v>6786888</v>
+        <v>6786673</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13954,10 +13949,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122567010</v>
+        <v>122567316</v>
       </c>
       <c r="B130" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13966,38 +13961,43 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>488442</v>
+        <v>488900</v>
       </c>
       <c r="R130" t="n">
-        <v>6786881</v>
+        <v>6786628</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14056,10 +14056,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122566967</v>
+        <v>122566962</v>
       </c>
       <c r="B131" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14096,10 +14096,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>488387</v>
+        <v>488324</v>
       </c>
       <c r="R131" t="n">
-        <v>6786773</v>
+        <v>6786843</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14158,7 +14158,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122567315</v>
+        <v>122567320</v>
       </c>
       <c r="B132" t="n">
         <v>8441</v>
@@ -14203,10 +14203,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>488773</v>
+        <v>488833</v>
       </c>
       <c r="R132" t="n">
-        <v>6786561</v>
+        <v>6786674</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14265,7 +14265,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>122567317</v>
+        <v>122567318</v>
       </c>
       <c r="B133" t="n">
         <v>8441</v>
@@ -14310,10 +14310,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>488892</v>
+        <v>488883</v>
       </c>
       <c r="R133" t="n">
-        <v>6786620</v>
+        <v>6786645</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>

--- a/artfynd/A 61338-2024 artfynd.xlsx
+++ b/artfynd/A 61338-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122566908</v>
+        <v>122566981</v>
       </c>
       <c r="B2" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,43 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488892</v>
+        <v>488599</v>
       </c>
       <c r="R2" t="n">
-        <v>6786620</v>
+        <v>6786673</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122566986</v>
+        <v>122567018</v>
       </c>
       <c r="B3" t="n">
         <v>78660</v>
@@ -826,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488714</v>
+        <v>488345</v>
       </c>
       <c r="R3" t="n">
-        <v>6786574</v>
+        <v>6786910</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122566972</v>
+        <v>122567319</v>
       </c>
       <c r="B4" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,38 +891,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488465</v>
+        <v>488869</v>
       </c>
       <c r="R4" t="n">
-        <v>6786729</v>
+        <v>6786685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567008</v>
+        <v>122567296</v>
       </c>
       <c r="B5" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,38 +998,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488495</v>
+        <v>488834</v>
       </c>
       <c r="R5" t="n">
-        <v>6786888</v>
+        <v>6786685</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566967</v>
+        <v>122567327</v>
       </c>
       <c r="B6" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,38 +1105,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488387</v>
+        <v>488442</v>
       </c>
       <c r="R6" t="n">
-        <v>6786773</v>
+        <v>6786881</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567314</v>
+        <v>122566890</v>
       </c>
       <c r="B7" t="n">
-        <v>8441</v>
+        <v>79278</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,43 +1212,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488747</v>
+        <v>488572</v>
       </c>
       <c r="R7" t="n">
-        <v>6786566</v>
+        <v>6786674</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567296</v>
+        <v>122566995</v>
       </c>
       <c r="B8" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,43 +1314,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488834</v>
+        <v>488833</v>
       </c>
       <c r="R8" t="n">
-        <v>6786685</v>
+        <v>6786674</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122567321</v>
+        <v>122567005</v>
       </c>
       <c r="B9" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,43 +1416,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488817</v>
+        <v>488415</v>
       </c>
       <c r="R9" t="n">
-        <v>6786693</v>
+        <v>6786889</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122567313</v>
+        <v>122567000</v>
       </c>
       <c r="B10" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,43 +1518,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488616</v>
+        <v>488678</v>
       </c>
       <c r="R10" t="n">
-        <v>6786649</v>
+        <v>6786753</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566954</v>
+        <v>122567297</v>
       </c>
       <c r="B11" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,38 +1620,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488416</v>
+        <v>488804</v>
       </c>
       <c r="R11" t="n">
-        <v>6786896</v>
+        <v>6786700</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566999</v>
+        <v>122567303</v>
       </c>
       <c r="B12" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,38 +1727,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488686</v>
+        <v>488600</v>
       </c>
       <c r="R12" t="n">
-        <v>6786738</v>
+        <v>6786772</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567018</v>
+        <v>122567026</v>
       </c>
       <c r="B13" t="n">
-        <v>78660</v>
+        <v>78305</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1842,21 +1838,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1866,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488345</v>
+        <v>488539</v>
       </c>
       <c r="R13" t="n">
-        <v>6786910</v>
+        <v>6786689</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566956</v>
+        <v>122566911</v>
       </c>
       <c r="B14" t="n">
-        <v>78660</v>
+        <v>91128</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1944,21 +1940,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1968,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488309</v>
+        <v>488882</v>
       </c>
       <c r="R14" t="n">
-        <v>6786859</v>
+        <v>6786609</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567025</v>
+        <v>122566984</v>
       </c>
       <c r="B15" t="n">
-        <v>78305</v>
+        <v>78660</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2046,21 +2042,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2070,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488378</v>
+        <v>488699</v>
       </c>
       <c r="R15" t="n">
-        <v>6786805</v>
+        <v>6786596</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567028</v>
+        <v>122566996</v>
       </c>
       <c r="B16" t="n">
-        <v>78305</v>
+        <v>78660</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2148,21 +2144,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2172,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488611</v>
+        <v>488757</v>
       </c>
       <c r="R16" t="n">
-        <v>6786649</v>
+        <v>6786723</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566911</v>
+        <v>122567309</v>
       </c>
       <c r="B17" t="n">
-        <v>91128</v>
+        <v>8441</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,38 +2242,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488882</v>
+        <v>488707</v>
       </c>
       <c r="R17" t="n">
-        <v>6786609</v>
+        <v>6786747</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567005</v>
+        <v>122567312</v>
       </c>
       <c r="B18" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2348,38 +2349,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488415</v>
+        <v>488341</v>
       </c>
       <c r="R18" t="n">
-        <v>6786889</v>
+        <v>6786832</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,10 +2444,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122567001</v>
+        <v>122567306</v>
       </c>
       <c r="B19" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,38 +2456,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488583</v>
+        <v>488556</v>
       </c>
       <c r="R19" t="n">
-        <v>6786774</v>
+        <v>6786835</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566899</v>
+        <v>122566963</v>
       </c>
       <c r="B20" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2556,21 +2567,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2580,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488482</v>
+        <v>488341</v>
       </c>
       <c r="R20" t="n">
-        <v>6786720</v>
+        <v>6786832</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,10 +2653,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567026</v>
+        <v>122566904</v>
       </c>
       <c r="B21" t="n">
-        <v>78305</v>
+        <v>90857</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2658,21 +2669,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2682,10 +2693,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488539</v>
+        <v>488552</v>
       </c>
       <c r="R21" t="n">
-        <v>6786689</v>
+        <v>6786834</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,10 +2755,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566958</v>
+        <v>122566903</v>
       </c>
       <c r="B22" t="n">
-        <v>78660</v>
+        <v>90857</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2760,21 +2771,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2784,10 +2795,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488301</v>
+        <v>488770</v>
       </c>
       <c r="R22" t="n">
-        <v>6786839</v>
+        <v>6786732</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,10 +2857,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566994</v>
+        <v>122567032</v>
       </c>
       <c r="B23" t="n">
-        <v>78660</v>
+        <v>5173</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2858,38 +2869,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488883</v>
+        <v>488901</v>
       </c>
       <c r="R23" t="n">
-        <v>6786645</v>
+        <v>6786589</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2948,10 +2964,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566997</v>
+        <v>122567301</v>
       </c>
       <c r="B24" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2960,38 +2976,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488731</v>
+        <v>488718</v>
       </c>
       <c r="R24" t="n">
-        <v>6786733</v>
+        <v>6786752</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3050,7 +3071,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122567305</v>
+        <v>122567311</v>
       </c>
       <c r="B25" t="n">
         <v>8441</v>
@@ -3086,7 +3107,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3095,10 +3116,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488519</v>
+        <v>488332</v>
       </c>
       <c r="R25" t="n">
-        <v>6786844</v>
+        <v>6786824</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3157,7 +3178,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567309</v>
+        <v>122567291</v>
       </c>
       <c r="B26" t="n">
         <v>8441</v>
@@ -3193,7 +3214,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3202,10 +3223,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488707</v>
+        <v>488440</v>
       </c>
       <c r="R26" t="n">
-        <v>6786747</v>
+        <v>6786759</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3264,10 +3285,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122567324</v>
+        <v>122566964</v>
       </c>
       <c r="B27" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3276,43 +3297,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488638</v>
+        <v>488351</v>
       </c>
       <c r="R27" t="n">
-        <v>6786764</v>
+        <v>6786831</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3371,10 +3387,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567315</v>
+        <v>122567013</v>
       </c>
       <c r="B28" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3383,43 +3399,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488773</v>
+        <v>488389</v>
       </c>
       <c r="R28" t="n">
-        <v>6786561</v>
+        <v>6786901</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3478,10 +3489,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567299</v>
+        <v>122567015</v>
       </c>
       <c r="B29" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3490,43 +3501,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488786</v>
+        <v>488366</v>
       </c>
       <c r="R29" t="n">
-        <v>6786723</v>
+        <v>6786907</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3585,10 +3591,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567295</v>
+        <v>122566976</v>
       </c>
       <c r="B30" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3597,43 +3603,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488850</v>
+        <v>488515</v>
       </c>
       <c r="R30" t="n">
-        <v>6786668</v>
+        <v>6786685</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3692,7 +3693,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122566979</v>
+        <v>122566966</v>
       </c>
       <c r="B31" t="n">
         <v>78660</v>
@@ -3732,10 +3733,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488583</v>
+        <v>488390</v>
       </c>
       <c r="R31" t="n">
-        <v>6786676</v>
+        <v>6786813</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3794,10 +3795,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122566974</v>
+        <v>122567314</v>
       </c>
       <c r="B32" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3806,38 +3807,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488486</v>
+        <v>488747</v>
       </c>
       <c r="R32" t="n">
-        <v>6786718</v>
+        <v>6786566</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3896,10 +3902,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122566985</v>
+        <v>122567321</v>
       </c>
       <c r="B33" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3908,38 +3914,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488698</v>
+        <v>488817</v>
       </c>
       <c r="R33" t="n">
-        <v>6786584</v>
+        <v>6786693</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3998,10 +4009,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122566996</v>
+        <v>122567299</v>
       </c>
       <c r="B34" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4010,35 +4021,40 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488757</v>
+        <v>488786</v>
       </c>
       <c r="R34" t="n">
         <v>6786723</v>
@@ -4100,10 +4116,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122566889</v>
+        <v>122567294</v>
       </c>
       <c r="B35" t="n">
-        <v>79278</v>
+        <v>8441</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4112,38 +4128,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488296</v>
+        <v>488801</v>
       </c>
       <c r="R35" t="n">
-        <v>6786844</v>
+        <v>6786563</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4202,10 +4223,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122566987</v>
+        <v>122567324</v>
       </c>
       <c r="B36" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4214,38 +4235,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488735</v>
+        <v>488638</v>
       </c>
       <c r="R36" t="n">
-        <v>6786569</v>
+        <v>6786764</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4304,10 +4330,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122566973</v>
+        <v>122567310</v>
       </c>
       <c r="B37" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4316,38 +4342,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488482</v>
+        <v>488294</v>
       </c>
       <c r="R37" t="n">
-        <v>6786720</v>
+        <v>6786825</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4406,7 +4437,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567016</v>
+        <v>122566970</v>
       </c>
       <c r="B38" t="n">
         <v>78660</v>
@@ -4446,10 +4477,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488360</v>
+        <v>488469</v>
       </c>
       <c r="R38" t="n">
-        <v>6786913</v>
+        <v>6786751</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4508,7 +4539,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122567002</v>
+        <v>122567001</v>
       </c>
       <c r="B39" t="n">
         <v>78660</v>
@@ -4548,10 +4579,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488569</v>
+        <v>488583</v>
       </c>
       <c r="R39" t="n">
-        <v>6786787</v>
+        <v>6786774</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4610,7 +4641,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122567023</v>
+        <v>122566961</v>
       </c>
       <c r="B40" t="n">
         <v>78660</v>
@@ -4650,10 +4681,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488135</v>
+        <v>488327</v>
       </c>
       <c r="R40" t="n">
-        <v>6787033</v>
+        <v>6786847</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4712,10 +4743,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567304</v>
+        <v>122566971</v>
       </c>
       <c r="B41" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4724,43 +4755,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488591</v>
+        <v>488461</v>
       </c>
       <c r="R41" t="n">
-        <v>6786769</v>
+        <v>6786736</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4819,10 +4845,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567298</v>
+        <v>122566956</v>
       </c>
       <c r="B42" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4831,43 +4857,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488789</v>
+        <v>488309</v>
       </c>
       <c r="R42" t="n">
-        <v>6786702</v>
+        <v>6786859</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4926,10 +4947,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567322</v>
+        <v>122566912</v>
       </c>
       <c r="B43" t="n">
-        <v>8441</v>
+        <v>91128</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4938,43 +4959,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488700</v>
+        <v>488895</v>
       </c>
       <c r="R43" t="n">
-        <v>6786746</v>
+        <v>6786588</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5033,7 +5049,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122567317</v>
+        <v>122567298</v>
       </c>
       <c r="B44" t="n">
         <v>8441</v>
@@ -5069,7 +5085,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5078,10 +5094,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488892</v>
+        <v>488789</v>
       </c>
       <c r="R44" t="n">
-        <v>6786620</v>
+        <v>6786702</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5140,10 +5156,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122567297</v>
+        <v>122566908</v>
       </c>
       <c r="B45" t="n">
-        <v>8441</v>
+        <v>57400</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5152,31 +5168,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5185,10 +5205,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488804</v>
+        <v>488892</v>
       </c>
       <c r="R45" t="n">
-        <v>6786700</v>
+        <v>6786620</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5247,7 +5267,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122567291</v>
+        <v>122567320</v>
       </c>
       <c r="B46" t="n">
         <v>8441</v>
@@ -5283,7 +5303,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5292,10 +5312,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488440</v>
+        <v>488833</v>
       </c>
       <c r="R46" t="n">
-        <v>6786759</v>
+        <v>6786674</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5354,7 +5374,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122567303</v>
+        <v>122567326</v>
       </c>
       <c r="B47" t="n">
         <v>8441</v>
@@ -5390,7 +5410,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5399,10 +5419,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488600</v>
+        <v>488545</v>
       </c>
       <c r="R47" t="n">
-        <v>6786772</v>
+        <v>6786849</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5461,10 +5481,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122567030</v>
+        <v>122567292</v>
       </c>
       <c r="B48" t="n">
-        <v>78305</v>
+        <v>8441</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5473,38 +5493,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488769</v>
+        <v>488533</v>
       </c>
       <c r="R48" t="n">
-        <v>6786552</v>
+        <v>6786690</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5563,10 +5588,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122566909</v>
+        <v>122566978</v>
       </c>
       <c r="B49" t="n">
-        <v>91282</v>
+        <v>78660</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5575,25 +5600,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5603,10 +5628,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488882</v>
+        <v>488583</v>
       </c>
       <c r="R49" t="n">
-        <v>6786607</v>
+        <v>6786679</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5665,7 +5690,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122566977</v>
+        <v>122567002</v>
       </c>
       <c r="B50" t="n">
         <v>78660</v>
@@ -5705,10 +5730,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488515</v>
+        <v>488569</v>
       </c>
       <c r="R50" t="n">
-        <v>6786685</v>
+        <v>6786787</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5767,7 +5792,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567020</v>
+        <v>122567009</v>
       </c>
       <c r="B51" t="n">
         <v>78660</v>
@@ -5807,10 +5832,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488185</v>
+        <v>488465</v>
       </c>
       <c r="R51" t="n">
-        <v>6787005</v>
+        <v>6786880</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5869,7 +5894,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122566968</v>
+        <v>122566986</v>
       </c>
       <c r="B52" t="n">
         <v>78660</v>
@@ -5909,10 +5934,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488431</v>
+        <v>488714</v>
       </c>
       <c r="R52" t="n">
-        <v>6786772</v>
+        <v>6786574</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5971,7 +5996,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567017</v>
+        <v>122566968</v>
       </c>
       <c r="B53" t="n">
         <v>78660</v>
@@ -6011,10 +6036,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488353</v>
+        <v>488431</v>
       </c>
       <c r="R53" t="n">
-        <v>6786911</v>
+        <v>6786772</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6073,7 +6098,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567011</v>
+        <v>122567016</v>
       </c>
       <c r="B54" t="n">
         <v>78660</v>
@@ -6113,10 +6138,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488427</v>
+        <v>488360</v>
       </c>
       <c r="R54" t="n">
-        <v>6786888</v>
+        <v>6786913</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6175,7 +6200,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122566965</v>
+        <v>122567011</v>
       </c>
       <c r="B55" t="n">
         <v>78660</v>
@@ -6215,10 +6240,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488378</v>
+        <v>488427</v>
       </c>
       <c r="R55" t="n">
-        <v>6786805</v>
+        <v>6786888</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6277,10 +6302,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122566890</v>
+        <v>122566960</v>
       </c>
       <c r="B56" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6293,21 +6318,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6317,10 +6342,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488572</v>
+        <v>488322</v>
       </c>
       <c r="R56" t="n">
-        <v>6786674</v>
+        <v>6786853</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6379,7 +6404,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122566964</v>
+        <v>122567007</v>
       </c>
       <c r="B57" t="n">
         <v>78660</v>
@@ -6419,10 +6444,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488351</v>
+        <v>488530</v>
       </c>
       <c r="R57" t="n">
-        <v>6786831</v>
+        <v>6786847</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6481,10 +6506,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122567007</v>
+        <v>122567030</v>
       </c>
       <c r="B58" t="n">
-        <v>78660</v>
+        <v>78305</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6497,21 +6522,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6521,10 +6546,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488530</v>
+        <v>488769</v>
       </c>
       <c r="R58" t="n">
-        <v>6786847</v>
+        <v>6786552</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6583,10 +6608,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122566903</v>
+        <v>122567028</v>
       </c>
       <c r="B59" t="n">
-        <v>90857</v>
+        <v>78305</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6599,21 +6624,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6623,10 +6648,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488770</v>
+        <v>488611</v>
       </c>
       <c r="R59" t="n">
-        <v>6786732</v>
+        <v>6786649</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6685,7 +6710,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122567319</v>
+        <v>122567304</v>
       </c>
       <c r="B60" t="n">
         <v>8441</v>
@@ -6721,7 +6746,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6730,10 +6755,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488869</v>
+        <v>488591</v>
       </c>
       <c r="R60" t="n">
-        <v>6786685</v>
+        <v>6786769</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6792,7 +6817,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122567326</v>
+        <v>122567289</v>
       </c>
       <c r="B61" t="n">
         <v>8441</v>
@@ -6828,7 +6853,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6837,10 +6862,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488545</v>
+        <v>488322</v>
       </c>
       <c r="R61" t="n">
-        <v>6786849</v>
+        <v>6786810</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6899,10 +6924,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122566998</v>
+        <v>122566894</v>
       </c>
       <c r="B62" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6915,21 +6940,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6939,10 +6964,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488700</v>
+        <v>488182</v>
       </c>
       <c r="R62" t="n">
-        <v>6786744</v>
+        <v>6787001</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7001,10 +7026,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122566894</v>
+        <v>122567012</v>
       </c>
       <c r="B63" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7017,21 +7042,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7041,10 +7066,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488182</v>
+        <v>488420</v>
       </c>
       <c r="R63" t="n">
-        <v>6787001</v>
+        <v>6786898</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7103,10 +7128,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122567290</v>
+        <v>122566896</v>
       </c>
       <c r="B64" t="n">
-        <v>8441</v>
+        <v>90837</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7115,43 +7140,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488345</v>
+        <v>488882</v>
       </c>
       <c r="R64" t="n">
-        <v>6786796</v>
+        <v>6786607</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7210,10 +7230,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122566991</v>
+        <v>122566902</v>
       </c>
       <c r="B65" t="n">
-        <v>78660</v>
+        <v>90857</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7226,21 +7246,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7250,10 +7270,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488918</v>
+        <v>488397</v>
       </c>
       <c r="R65" t="n">
-        <v>6786607</v>
+        <v>6786809</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7312,7 +7332,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122567022</v>
+        <v>122566999</v>
       </c>
       <c r="B66" t="n">
         <v>78660</v>
@@ -7352,10 +7372,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488137</v>
+        <v>488686</v>
       </c>
       <c r="R66" t="n">
-        <v>6787026</v>
+        <v>6786738</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7414,10 +7434,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122567032</v>
+        <v>122567010</v>
       </c>
       <c r="B67" t="n">
-        <v>5173</v>
+        <v>78660</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7426,43 +7446,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488901</v>
+        <v>488442</v>
       </c>
       <c r="R67" t="n">
-        <v>6786589</v>
+        <v>6786881</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7521,10 +7536,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122566953</v>
+        <v>122566954</v>
       </c>
       <c r="B68" t="n">
-        <v>98244</v>
+        <v>78660</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7533,44 +7548,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488429</v>
+        <v>488416</v>
       </c>
       <c r="R68" t="n">
         <v>6786896</v>
@@ -7632,10 +7638,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122566952</v>
+        <v>122566892</v>
       </c>
       <c r="B69" t="n">
-        <v>80617</v>
+        <v>79278</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7648,21 +7654,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7672,10 +7678,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488363</v>
+        <v>488699</v>
       </c>
       <c r="R69" t="n">
-        <v>6786907</v>
+        <v>6786599</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7734,7 +7740,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122566990</v>
+        <v>122567023</v>
       </c>
       <c r="B70" t="n">
         <v>78660</v>
@@ -7774,10 +7780,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488840</v>
+        <v>488135</v>
       </c>
       <c r="R70" t="n">
-        <v>6786622</v>
+        <v>6787033</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7836,10 +7842,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122566892</v>
+        <v>122567315</v>
       </c>
       <c r="B71" t="n">
-        <v>79278</v>
+        <v>8441</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7848,38 +7854,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488699</v>
+        <v>488773</v>
       </c>
       <c r="R71" t="n">
-        <v>6786599</v>
+        <v>6786561</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7938,10 +7949,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122567012</v>
+        <v>122566898</v>
       </c>
       <c r="B72" t="n">
-        <v>78660</v>
+        <v>57537</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7954,21 +7965,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7978,10 +7989,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488420</v>
+        <v>488296</v>
       </c>
       <c r="R72" t="n">
-        <v>6786898</v>
+        <v>6786844</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8040,10 +8051,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122567009</v>
+        <v>122566893</v>
       </c>
       <c r="B73" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8056,21 +8067,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8080,10 +8091,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488465</v>
+        <v>488693</v>
       </c>
       <c r="R73" t="n">
-        <v>6786880</v>
+        <v>6786741</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8142,10 +8153,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122566960</v>
+        <v>122566897</v>
       </c>
       <c r="B74" t="n">
-        <v>78660</v>
+        <v>90837</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8158,21 +8169,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8182,10 +8193,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488322</v>
+        <v>488892</v>
       </c>
       <c r="R74" t="n">
-        <v>6786853</v>
+        <v>6786591</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8244,10 +8255,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122567013</v>
+        <v>122567325</v>
       </c>
       <c r="B75" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8256,38 +8267,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488389</v>
+        <v>488576</v>
       </c>
       <c r="R75" t="n">
-        <v>6786901</v>
+        <v>6786782</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8346,10 +8362,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122567003</v>
+        <v>122567322</v>
       </c>
       <c r="B76" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8358,38 +8374,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488550</v>
+        <v>488700</v>
       </c>
       <c r="R76" t="n">
-        <v>6786822</v>
+        <v>6786746</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8448,10 +8469,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122566893</v>
+        <v>122567017</v>
       </c>
       <c r="B77" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8464,21 +8485,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8488,10 +8509,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488693</v>
+        <v>488353</v>
       </c>
       <c r="R77" t="n">
-        <v>6786741</v>
+        <v>6786911</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8550,10 +8571,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122567325</v>
+        <v>122566979</v>
       </c>
       <c r="B78" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8562,43 +8583,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488576</v>
+        <v>488583</v>
       </c>
       <c r="R78" t="n">
-        <v>6786782</v>
+        <v>6786676</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8657,10 +8673,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122567323</v>
+        <v>122566990</v>
       </c>
       <c r="B79" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8669,43 +8685,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488686</v>
+        <v>488840</v>
       </c>
       <c r="R79" t="n">
-        <v>6786745</v>
+        <v>6786622</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8764,10 +8775,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122567029</v>
+        <v>122567020</v>
       </c>
       <c r="B80" t="n">
-        <v>78305</v>
+        <v>78660</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8780,21 +8791,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8804,10 +8815,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488664</v>
+        <v>488185</v>
       </c>
       <c r="R80" t="n">
-        <v>6786615</v>
+        <v>6787005</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8866,10 +8877,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122566904</v>
+        <v>122566965</v>
       </c>
       <c r="B81" t="n">
-        <v>90857</v>
+        <v>78660</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8882,21 +8893,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8906,10 +8917,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488552</v>
+        <v>488378</v>
       </c>
       <c r="R81" t="n">
-        <v>6786834</v>
+        <v>6786805</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8968,10 +8979,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122566970</v>
+        <v>122566891</v>
       </c>
       <c r="B82" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8984,21 +8995,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9008,10 +9019,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488469</v>
+        <v>488616</v>
       </c>
       <c r="R82" t="n">
-        <v>6786751</v>
+        <v>6786648</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9070,7 +9081,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122566981</v>
+        <v>122567014</v>
       </c>
       <c r="B83" t="n">
         <v>78660</v>
@@ -9110,10 +9121,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488599</v>
+        <v>488383</v>
       </c>
       <c r="R83" t="n">
-        <v>6786673</v>
+        <v>6786912</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9172,7 +9183,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122566959</v>
+        <v>122566972</v>
       </c>
       <c r="B84" t="n">
         <v>78660</v>
@@ -9212,10 +9223,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488317</v>
+        <v>488465</v>
       </c>
       <c r="R84" t="n">
-        <v>6786858</v>
+        <v>6786729</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9274,10 +9285,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122567000</v>
+        <v>122567029</v>
       </c>
       <c r="B85" t="n">
-        <v>78660</v>
+        <v>78305</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9290,21 +9301,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9314,10 +9325,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488678</v>
+        <v>488664</v>
       </c>
       <c r="R85" t="n">
-        <v>6786753</v>
+        <v>6786615</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9376,10 +9387,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122566982</v>
+        <v>122567024</v>
       </c>
       <c r="B86" t="n">
-        <v>78660</v>
+        <v>91089</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9388,25 +9399,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9416,10 +9427,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488600</v>
+        <v>488663</v>
       </c>
       <c r="R86" t="n">
-        <v>6786662</v>
+        <v>6786615</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9478,10 +9489,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122566891</v>
+        <v>122566907</v>
       </c>
       <c r="B87" t="n">
-        <v>79278</v>
+        <v>57400</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9494,34 +9505,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488616</v>
+        <v>488852</v>
       </c>
       <c r="R87" t="n">
-        <v>6786648</v>
+        <v>6786673</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9580,10 +9596,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122567014</v>
+        <v>122567300</v>
       </c>
       <c r="B88" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9592,38 +9608,43 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488383</v>
+        <v>488768</v>
       </c>
       <c r="R88" t="n">
-        <v>6786912</v>
+        <v>6786742</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9682,10 +9703,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122567301</v>
+        <v>122566905</v>
       </c>
       <c r="B89" t="n">
-        <v>8441</v>
+        <v>57400</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9694,31 +9715,31 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -9727,10 +9748,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488718</v>
+        <v>488294</v>
       </c>
       <c r="R89" t="n">
-        <v>6786752</v>
+        <v>6786826</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9789,10 +9810,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122567312</v>
+        <v>122566987</v>
       </c>
       <c r="B90" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9801,43 +9822,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488341</v>
+        <v>488735</v>
       </c>
       <c r="R90" t="n">
-        <v>6786832</v>
+        <v>6786569</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9896,10 +9912,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122567327</v>
+        <v>122566958</v>
       </c>
       <c r="B91" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9908,43 +9924,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488442</v>
+        <v>488301</v>
       </c>
       <c r="R91" t="n">
-        <v>6786881</v>
+        <v>6786839</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10003,10 +10014,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122566898</v>
+        <v>122566889</v>
       </c>
       <c r="B92" t="n">
-        <v>57537</v>
+        <v>79278</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10019,21 +10030,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10105,10 +10116,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122567310</v>
+        <v>122567022</v>
       </c>
       <c r="B93" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10117,43 +10128,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488294</v>
+        <v>488137</v>
       </c>
       <c r="R93" t="n">
-        <v>6786825</v>
+        <v>6787026</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10212,10 +10218,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122567293</v>
+        <v>122566967</v>
       </c>
       <c r="B94" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10224,43 +10230,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488790</v>
+        <v>488387</v>
       </c>
       <c r="R94" t="n">
-        <v>6786547</v>
+        <v>6786773</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10319,10 +10320,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122566988</v>
+        <v>122566913</v>
       </c>
       <c r="B95" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10335,34 +10336,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>488803</v>
+        <v>488602</v>
       </c>
       <c r="R95" t="n">
-        <v>6786562</v>
+        <v>6786666</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10395,6 +10401,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10421,10 +10432,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122567006</v>
+        <v>122567313</v>
       </c>
       <c r="B96" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10433,38 +10444,43 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>488556</v>
+        <v>488616</v>
       </c>
       <c r="R96" t="n">
-        <v>6786835</v>
+        <v>6786649</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10523,10 +10539,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122567015</v>
+        <v>122566899</v>
       </c>
       <c r="B97" t="n">
-        <v>78660</v>
+        <v>57537</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10539,21 +10555,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10563,10 +10579,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>488366</v>
+        <v>488482</v>
       </c>
       <c r="R97" t="n">
-        <v>6786907</v>
+        <v>6786720</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10625,7 +10641,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122566978</v>
+        <v>122567006</v>
       </c>
       <c r="B98" t="n">
         <v>78660</v>
@@ -10665,10 +10681,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>488583</v>
+        <v>488556</v>
       </c>
       <c r="R98" t="n">
-        <v>6786679</v>
+        <v>6786835</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10727,7 +10743,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122566957</v>
+        <v>122567003</v>
       </c>
       <c r="B99" t="n">
         <v>78660</v>
@@ -10767,10 +10783,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>488300</v>
+        <v>488550</v>
       </c>
       <c r="R99" t="n">
-        <v>6786820</v>
+        <v>6786822</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10829,10 +10845,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122566902</v>
+        <v>122566962</v>
       </c>
       <c r="B100" t="n">
-        <v>90857</v>
+        <v>78660</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10845,21 +10861,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10869,10 +10885,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>488397</v>
+        <v>488324</v>
       </c>
       <c r="R100" t="n">
-        <v>6786809</v>
+        <v>6786843</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10931,10 +10947,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122567024</v>
+        <v>122567307</v>
       </c>
       <c r="B101" t="n">
-        <v>91089</v>
+        <v>8441</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10943,38 +10959,43 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>65</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>488663</v>
+        <v>488535</v>
       </c>
       <c r="R101" t="n">
-        <v>6786615</v>
+        <v>6786843</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11033,7 +11054,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122567307</v>
+        <v>122567318</v>
       </c>
       <c r="B102" t="n">
         <v>8441</v>
@@ -11069,7 +11090,7 @@
       <c r="I102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -11078,10 +11099,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>488535</v>
+        <v>488883</v>
       </c>
       <c r="R102" t="n">
-        <v>6786843</v>
+        <v>6786645</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11140,10 +11161,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122567294</v>
+        <v>122567027</v>
       </c>
       <c r="B103" t="n">
-        <v>8441</v>
+        <v>78305</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11152,43 +11173,38 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>488801</v>
+        <v>488618</v>
       </c>
       <c r="R103" t="n">
-        <v>6786563</v>
+        <v>6786631</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11247,10 +11263,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122566896</v>
+        <v>122566988</v>
       </c>
       <c r="B104" t="n">
-        <v>90837</v>
+        <v>78660</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11263,21 +11279,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11287,10 +11303,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488882</v>
+        <v>488803</v>
       </c>
       <c r="R104" t="n">
-        <v>6786607</v>
+        <v>6786562</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11349,7 +11365,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122567004</v>
+        <v>122566994</v>
       </c>
       <c r="B105" t="n">
         <v>78660</v>
@@ -11389,10 +11405,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488475</v>
+        <v>488883</v>
       </c>
       <c r="R105" t="n">
-        <v>6786864</v>
+        <v>6786645</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11451,10 +11467,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122566913</v>
+        <v>122566991</v>
       </c>
       <c r="B106" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11467,39 +11483,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488602</v>
+        <v>488918</v>
       </c>
       <c r="R106" t="n">
-        <v>6786666</v>
+        <v>6786607</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11532,11 +11543,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11563,10 +11569,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122566912</v>
+        <v>122566959</v>
       </c>
       <c r="B107" t="n">
-        <v>91128</v>
+        <v>78660</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11579,21 +11585,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11603,10 +11609,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488895</v>
+        <v>488317</v>
       </c>
       <c r="R107" t="n">
-        <v>6786588</v>
+        <v>6786858</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11665,7 +11671,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122566969</v>
+        <v>122567019</v>
       </c>
       <c r="B108" t="n">
         <v>78660</v>
@@ -11705,10 +11711,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>488452</v>
+        <v>488297</v>
       </c>
       <c r="R108" t="n">
-        <v>6786772</v>
+        <v>6786946</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11767,10 +11773,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122566966</v>
+        <v>122567293</v>
       </c>
       <c r="B109" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11779,38 +11785,43 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488390</v>
+        <v>488790</v>
       </c>
       <c r="R109" t="n">
-        <v>6786813</v>
+        <v>6786547</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11869,10 +11880,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122566901</v>
+        <v>122567316</v>
       </c>
       <c r="B110" t="n">
-        <v>57537</v>
+        <v>8441</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11881,38 +11892,43 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>488142</v>
+        <v>488900</v>
       </c>
       <c r="R110" t="n">
-        <v>6787017</v>
+        <v>6786628</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11971,7 +11987,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122567289</v>
+        <v>122567295</v>
       </c>
       <c r="B111" t="n">
         <v>8441</v>
@@ -12016,10 +12032,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>488322</v>
+        <v>488850</v>
       </c>
       <c r="R111" t="n">
-        <v>6786810</v>
+        <v>6786668</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12078,10 +12094,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122567292</v>
+        <v>122567004</v>
       </c>
       <c r="B112" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12090,43 +12106,38 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>488533</v>
+        <v>488475</v>
       </c>
       <c r="R112" t="n">
-        <v>6786690</v>
+        <v>6786864</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12185,7 +12196,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122567306</v>
+        <v>122567305</v>
       </c>
       <c r="B113" t="n">
         <v>8441</v>
@@ -12230,10 +12241,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488556</v>
+        <v>488519</v>
       </c>
       <c r="R113" t="n">
-        <v>6786835</v>
+        <v>6786844</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12292,10 +12303,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122566971</v>
+        <v>122567317</v>
       </c>
       <c r="B114" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12304,38 +12315,43 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488461</v>
+        <v>488892</v>
       </c>
       <c r="R114" t="n">
-        <v>6786736</v>
+        <v>6786620</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12394,10 +12410,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122567300</v>
+        <v>122566973</v>
       </c>
       <c r="B115" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12406,43 +12422,38 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>488768</v>
+        <v>488482</v>
       </c>
       <c r="R115" t="n">
-        <v>6786742</v>
+        <v>6786720</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12501,10 +12512,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122567311</v>
+        <v>122566969</v>
       </c>
       <c r="B116" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12513,43 +12524,38 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>488332</v>
+        <v>488452</v>
       </c>
       <c r="R116" t="n">
-        <v>6786824</v>
+        <v>6786772</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12608,7 +12614,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122566984</v>
+        <v>122566982</v>
       </c>
       <c r="B117" t="n">
         <v>78660</v>
@@ -12648,10 +12654,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>488699</v>
+        <v>488600</v>
       </c>
       <c r="R117" t="n">
-        <v>6786596</v>
+        <v>6786662</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12710,10 +12716,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122567027</v>
+        <v>122566952</v>
       </c>
       <c r="B118" t="n">
-        <v>78305</v>
+        <v>80617</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12726,21 +12732,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12750,10 +12756,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>488618</v>
+        <v>488363</v>
       </c>
       <c r="R118" t="n">
-        <v>6786631</v>
+        <v>6786907</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12812,10 +12818,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122566897</v>
+        <v>122567323</v>
       </c>
       <c r="B119" t="n">
-        <v>90837</v>
+        <v>8441</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12824,38 +12830,43 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>488892</v>
+        <v>488686</v>
       </c>
       <c r="R119" t="n">
-        <v>6786591</v>
+        <v>6786745</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12914,10 +12925,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122566995</v>
+        <v>122567308</v>
       </c>
       <c r="B120" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12926,38 +12937,43 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>488833</v>
+        <v>488669</v>
       </c>
       <c r="R120" t="n">
-        <v>6786674</v>
+        <v>6786761</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13016,7 +13032,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122567010</v>
+        <v>122566985</v>
       </c>
       <c r="B121" t="n">
         <v>78660</v>
@@ -13056,10 +13072,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488442</v>
+        <v>488698</v>
       </c>
       <c r="R121" t="n">
-        <v>6786881</v>
+        <v>6786584</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13118,7 +13134,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122567019</v>
+        <v>122566983</v>
       </c>
       <c r="B122" t="n">
         <v>78660</v>
@@ -13158,10 +13174,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488297</v>
+        <v>488609</v>
       </c>
       <c r="R122" t="n">
-        <v>6786946</v>
+        <v>6786648</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13220,10 +13236,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122566983</v>
+        <v>122566909</v>
       </c>
       <c r="B123" t="n">
-        <v>78660</v>
+        <v>91282</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13232,25 +13248,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13260,10 +13276,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>488609</v>
+        <v>488882</v>
       </c>
       <c r="R123" t="n">
-        <v>6786648</v>
+        <v>6786607</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13322,10 +13338,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122566905</v>
+        <v>122566980</v>
       </c>
       <c r="B124" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13338,39 +13354,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>488294</v>
+        <v>488590</v>
       </c>
       <c r="R124" t="n">
-        <v>6786826</v>
+        <v>6786665</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13429,10 +13440,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122567308</v>
+        <v>122566974</v>
       </c>
       <c r="B125" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13441,43 +13452,38 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>488669</v>
+        <v>488486</v>
       </c>
       <c r="R125" t="n">
-        <v>6786761</v>
+        <v>6786718</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13536,7 +13542,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122566980</v>
+        <v>122566957</v>
       </c>
       <c r="B126" t="n">
         <v>78660</v>
@@ -13576,10 +13582,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>488590</v>
+        <v>488300</v>
       </c>
       <c r="R126" t="n">
-        <v>6786665</v>
+        <v>6786820</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13638,7 +13644,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122566961</v>
+        <v>122567008</v>
       </c>
       <c r="B127" t="n">
         <v>78660</v>
@@ -13678,10 +13684,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>488327</v>
+        <v>488495</v>
       </c>
       <c r="R127" t="n">
-        <v>6786847</v>
+        <v>6786888</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13740,7 +13746,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122566963</v>
+        <v>122566998</v>
       </c>
       <c r="B128" t="n">
         <v>78660</v>
@@ -13780,10 +13786,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>488341</v>
+        <v>488700</v>
       </c>
       <c r="R128" t="n">
-        <v>6786832</v>
+        <v>6786744</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13842,10 +13848,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122566907</v>
+        <v>122566997</v>
       </c>
       <c r="B129" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13858,39 +13864,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>488852</v>
+        <v>488731</v>
       </c>
       <c r="R129" t="n">
-        <v>6786673</v>
+        <v>6786733</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13949,10 +13950,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122567316</v>
+        <v>122567025</v>
       </c>
       <c r="B130" t="n">
-        <v>8441</v>
+        <v>78305</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13961,43 +13962,38 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>488900</v>
+        <v>488378</v>
       </c>
       <c r="R130" t="n">
-        <v>6786628</v>
+        <v>6786805</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14056,10 +14052,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122566962</v>
+        <v>122567290</v>
       </c>
       <c r="B131" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14068,38 +14064,43 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>488324</v>
+        <v>488345</v>
       </c>
       <c r="R131" t="n">
-        <v>6786843</v>
+        <v>6786796</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14158,10 +14159,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122567320</v>
+        <v>122566901</v>
       </c>
       <c r="B132" t="n">
-        <v>8441</v>
+        <v>57537</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14170,43 +14171,38 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>488833</v>
+        <v>488142</v>
       </c>
       <c r="R132" t="n">
-        <v>6786674</v>
+        <v>6787017</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14265,10 +14261,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>122567318</v>
+        <v>122566953</v>
       </c>
       <c r="B133" t="n">
-        <v>8441</v>
+        <v>98244</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14277,31 +14273,35 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -14310,10 +14310,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>488883</v>
+        <v>488429</v>
       </c>
       <c r="R133" t="n">
-        <v>6786645</v>
+        <v>6786896</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>

--- a/artfynd/A 61338-2024 artfynd.xlsx
+++ b/artfynd/A 61338-2024 artfynd.xlsx
@@ -2551,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566963</v>
+        <v>122566904</v>
       </c>
       <c r="B20" t="n">
-        <v>78660</v>
+        <v>90857</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2567,21 +2567,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488341</v>
+        <v>488552</v>
       </c>
       <c r="R20" t="n">
-        <v>6786832</v>
+        <v>6786834</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,7 +2653,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566904</v>
+        <v>122566903</v>
       </c>
       <c r="B21" t="n">
         <v>90857</v>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488552</v>
+        <v>488770</v>
       </c>
       <c r="R21" t="n">
-        <v>6786834</v>
+        <v>6786732</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2755,10 +2755,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566903</v>
+        <v>122567301</v>
       </c>
       <c r="B22" t="n">
-        <v>90857</v>
+        <v>8441</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2767,38 +2767,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488770</v>
+        <v>488718</v>
       </c>
       <c r="R22" t="n">
-        <v>6786732</v>
+        <v>6786752</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2857,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567032</v>
+        <v>122567311</v>
       </c>
       <c r="B23" t="n">
-        <v>5173</v>
+        <v>8441</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2873,21 +2878,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2902,10 +2907,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488901</v>
+        <v>488332</v>
       </c>
       <c r="R23" t="n">
-        <v>6786589</v>
+        <v>6786824</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2964,7 +2969,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567301</v>
+        <v>122567291</v>
       </c>
       <c r="B24" t="n">
         <v>8441</v>
@@ -3009,10 +3014,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488718</v>
+        <v>488440</v>
       </c>
       <c r="R24" t="n">
-        <v>6786752</v>
+        <v>6786759</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3071,10 +3076,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122567311</v>
+        <v>122566963</v>
       </c>
       <c r="B25" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3083,43 +3088,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488332</v>
+        <v>488341</v>
       </c>
       <c r="R25" t="n">
-        <v>6786824</v>
+        <v>6786832</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3178,10 +3178,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567291</v>
+        <v>122567032</v>
       </c>
       <c r="B26" t="n">
-        <v>8441</v>
+        <v>5173</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3194,27 +3194,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488440</v>
+        <v>488901</v>
       </c>
       <c r="R26" t="n">
-        <v>6786759</v>
+        <v>6786589</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -5049,10 +5049,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122567298</v>
+        <v>122566908</v>
       </c>
       <c r="B44" t="n">
-        <v>8441</v>
+        <v>57400</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5061,31 +5061,35 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5094,10 +5098,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488789</v>
+        <v>488892</v>
       </c>
       <c r="R44" t="n">
-        <v>6786702</v>
+        <v>6786620</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5156,10 +5160,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122566908</v>
+        <v>122567298</v>
       </c>
       <c r="B45" t="n">
-        <v>57400</v>
+        <v>8441</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5168,35 +5172,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5205,10 +5205,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488892</v>
+        <v>488789</v>
       </c>
       <c r="R45" t="n">
-        <v>6786620</v>
+        <v>6786702</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -8153,10 +8153,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122566897</v>
+        <v>122567325</v>
       </c>
       <c r="B74" t="n">
-        <v>90837</v>
+        <v>8441</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8165,38 +8165,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488892</v>
+        <v>488576</v>
       </c>
       <c r="R74" t="n">
-        <v>6786591</v>
+        <v>6786782</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8255,7 +8260,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122567325</v>
+        <v>122567322</v>
       </c>
       <c r="B75" t="n">
         <v>8441</v>
@@ -8300,10 +8305,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488576</v>
+        <v>488700</v>
       </c>
       <c r="R75" t="n">
-        <v>6786782</v>
+        <v>6786746</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8362,10 +8367,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122567322</v>
+        <v>122566897</v>
       </c>
       <c r="B76" t="n">
-        <v>8441</v>
+        <v>90837</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8374,43 +8379,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488700</v>
+        <v>488892</v>
       </c>
       <c r="R76" t="n">
-        <v>6786746</v>
+        <v>6786591</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8469,10 +8469,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122567017</v>
+        <v>122566907</v>
       </c>
       <c r="B77" t="n">
-        <v>78660</v>
+        <v>57400</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8485,34 +8485,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488353</v>
+        <v>488852</v>
       </c>
       <c r="R77" t="n">
-        <v>6786911</v>
+        <v>6786673</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8571,7 +8576,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122566979</v>
+        <v>122567017</v>
       </c>
       <c r="B78" t="n">
         <v>78660</v>
@@ -8611,10 +8616,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488583</v>
+        <v>488353</v>
       </c>
       <c r="R78" t="n">
-        <v>6786676</v>
+        <v>6786911</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8673,7 +8678,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122566990</v>
+        <v>122566979</v>
       </c>
       <c r="B79" t="n">
         <v>78660</v>
@@ -8713,10 +8718,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488840</v>
+        <v>488583</v>
       </c>
       <c r="R79" t="n">
-        <v>6786622</v>
+        <v>6786676</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8775,7 +8780,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122567020</v>
+        <v>122566990</v>
       </c>
       <c r="B80" t="n">
         <v>78660</v>
@@ -8815,10 +8820,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488185</v>
+        <v>488840</v>
       </c>
       <c r="R80" t="n">
-        <v>6787005</v>
+        <v>6786622</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8877,7 +8882,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122566965</v>
+        <v>122567020</v>
       </c>
       <c r="B81" t="n">
         <v>78660</v>
@@ -8917,10 +8922,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488378</v>
+        <v>488185</v>
       </c>
       <c r="R81" t="n">
-        <v>6786805</v>
+        <v>6787005</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8979,10 +8984,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122566891</v>
+        <v>122566965</v>
       </c>
       <c r="B82" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8995,21 +9000,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9019,10 +9024,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488616</v>
+        <v>488378</v>
       </c>
       <c r="R82" t="n">
-        <v>6786648</v>
+        <v>6786805</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9081,10 +9086,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122567014</v>
+        <v>122566891</v>
       </c>
       <c r="B83" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9097,21 +9102,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9121,10 +9126,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488383</v>
+        <v>488616</v>
       </c>
       <c r="R83" t="n">
-        <v>6786912</v>
+        <v>6786648</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9183,7 +9188,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122566972</v>
+        <v>122567014</v>
       </c>
       <c r="B84" t="n">
         <v>78660</v>
@@ -9223,10 +9228,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488465</v>
+        <v>488383</v>
       </c>
       <c r="R84" t="n">
-        <v>6786729</v>
+        <v>6786912</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9285,10 +9290,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122567029</v>
+        <v>122566972</v>
       </c>
       <c r="B85" t="n">
-        <v>78305</v>
+        <v>78660</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9301,21 +9306,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9325,10 +9330,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488664</v>
+        <v>488465</v>
       </c>
       <c r="R85" t="n">
-        <v>6786615</v>
+        <v>6786729</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9387,10 +9392,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122567024</v>
+        <v>122567029</v>
       </c>
       <c r="B86" t="n">
-        <v>91089</v>
+        <v>78305</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9399,25 +9404,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9427,7 +9432,7 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488663</v>
+        <v>488664</v>
       </c>
       <c r="R86" t="n">
         <v>6786615</v>
@@ -9489,10 +9494,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122566907</v>
+        <v>122567024</v>
       </c>
       <c r="B87" t="n">
-        <v>57400</v>
+        <v>91089</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9501,43 +9506,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>65</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488852</v>
+        <v>488663</v>
       </c>
       <c r="R87" t="n">
-        <v>6786673</v>
+        <v>6786615</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9703,10 +9703,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122566905</v>
+        <v>122567313</v>
       </c>
       <c r="B89" t="n">
-        <v>57400</v>
+        <v>8441</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9715,31 +9715,31 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -9748,10 +9748,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488294</v>
+        <v>488616</v>
       </c>
       <c r="R89" t="n">
-        <v>6786826</v>
+        <v>6786649</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10432,10 +10432,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122567313</v>
+        <v>122566905</v>
       </c>
       <c r="B96" t="n">
-        <v>8441</v>
+        <v>57400</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10444,31 +10444,31 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -10477,10 +10477,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>488616</v>
+        <v>488294</v>
       </c>
       <c r="R96" t="n">
-        <v>6786649</v>
+        <v>6786826</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10641,10 +10641,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122567006</v>
+        <v>122567027</v>
       </c>
       <c r="B98" t="n">
-        <v>78660</v>
+        <v>78305</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10657,21 +10657,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10681,10 +10681,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>488556</v>
+        <v>488618</v>
       </c>
       <c r="R98" t="n">
-        <v>6786835</v>
+        <v>6786631</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10743,7 +10743,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122567003</v>
+        <v>122567006</v>
       </c>
       <c r="B99" t="n">
         <v>78660</v>
@@ -10783,10 +10783,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>488550</v>
+        <v>488556</v>
       </c>
       <c r="R99" t="n">
-        <v>6786822</v>
+        <v>6786835</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10845,7 +10845,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122566962</v>
+        <v>122567003</v>
       </c>
       <c r="B100" t="n">
         <v>78660</v>
@@ -10885,10 +10885,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>488324</v>
+        <v>488550</v>
       </c>
       <c r="R100" t="n">
-        <v>6786843</v>
+        <v>6786822</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10947,10 +10947,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122567307</v>
+        <v>122566962</v>
       </c>
       <c r="B101" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10959,40 +10959,35 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>488535</v>
+        <v>488324</v>
       </c>
       <c r="R101" t="n">
         <v>6786843</v>
@@ -11054,7 +11049,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122567318</v>
+        <v>122567307</v>
       </c>
       <c r="B102" t="n">
         <v>8441</v>
@@ -11090,7 +11085,7 @@
       <c r="I102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -11099,10 +11094,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>488883</v>
+        <v>488535</v>
       </c>
       <c r="R102" t="n">
-        <v>6786645</v>
+        <v>6786843</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11161,10 +11156,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122567027</v>
+        <v>122567318</v>
       </c>
       <c r="B103" t="n">
-        <v>78305</v>
+        <v>8441</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11173,38 +11168,43 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>488618</v>
+        <v>488883</v>
       </c>
       <c r="R103" t="n">
-        <v>6786631</v>
+        <v>6786645</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12925,10 +12925,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122567308</v>
+        <v>122566983</v>
       </c>
       <c r="B120" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12937,43 +12937,38 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>488669</v>
+        <v>488609</v>
       </c>
       <c r="R120" t="n">
-        <v>6786761</v>
+        <v>6786648</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13134,10 +13129,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122566983</v>
+        <v>122566909</v>
       </c>
       <c r="B122" t="n">
-        <v>78660</v>
+        <v>91282</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13146,25 +13141,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13174,10 +13169,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488609</v>
+        <v>488882</v>
       </c>
       <c r="R122" t="n">
-        <v>6786648</v>
+        <v>6786607</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13236,10 +13231,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122566909</v>
+        <v>122567308</v>
       </c>
       <c r="B123" t="n">
-        <v>91282</v>
+        <v>8441</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13248,38 +13243,43 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1209</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>488882</v>
+        <v>488669</v>
       </c>
       <c r="R123" t="n">
-        <v>6786607</v>
+        <v>6786761</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13338,10 +13338,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122566980</v>
+        <v>122567025</v>
       </c>
       <c r="B124" t="n">
-        <v>78660</v>
+        <v>78305</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13354,21 +13354,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13378,10 +13378,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>488590</v>
+        <v>488378</v>
       </c>
       <c r="R124" t="n">
-        <v>6786665</v>
+        <v>6786805</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13440,10 +13440,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122566974</v>
+        <v>122567290</v>
       </c>
       <c r="B125" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13452,38 +13452,43 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>488486</v>
+        <v>488345</v>
       </c>
       <c r="R125" t="n">
-        <v>6786718</v>
+        <v>6786796</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13542,10 +13547,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122566957</v>
+        <v>122566901</v>
       </c>
       <c r="B126" t="n">
-        <v>78660</v>
+        <v>57537</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13558,21 +13563,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13582,10 +13587,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>488300</v>
+        <v>488142</v>
       </c>
       <c r="R126" t="n">
-        <v>6786820</v>
+        <v>6787017</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13644,10 +13649,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122567008</v>
+        <v>122566953</v>
       </c>
       <c r="B127" t="n">
-        <v>78660</v>
+        <v>98244</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13656,38 +13661,47 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>488495</v>
+        <v>488429</v>
       </c>
       <c r="R127" t="n">
-        <v>6786888</v>
+        <v>6786896</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13746,7 +13760,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122566998</v>
+        <v>122566980</v>
       </c>
       <c r="B128" t="n">
         <v>78660</v>
@@ -13786,10 +13800,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>488700</v>
+        <v>488590</v>
       </c>
       <c r="R128" t="n">
-        <v>6786744</v>
+        <v>6786665</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13848,7 +13862,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122566997</v>
+        <v>122566974</v>
       </c>
       <c r="B129" t="n">
         <v>78660</v>
@@ -13888,10 +13902,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>488731</v>
+        <v>488486</v>
       </c>
       <c r="R129" t="n">
-        <v>6786733</v>
+        <v>6786718</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13950,10 +13964,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122567025</v>
+        <v>122566957</v>
       </c>
       <c r="B130" t="n">
-        <v>78305</v>
+        <v>78660</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13966,21 +13980,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13990,10 +14004,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>488378</v>
+        <v>488300</v>
       </c>
       <c r="R130" t="n">
-        <v>6786805</v>
+        <v>6786820</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14052,10 +14066,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122567290</v>
+        <v>122567008</v>
       </c>
       <c r="B131" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14064,43 +14078,38 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>488345</v>
+        <v>488495</v>
       </c>
       <c r="R131" t="n">
-        <v>6786796</v>
+        <v>6786888</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14159,10 +14168,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122566901</v>
+        <v>122566998</v>
       </c>
       <c r="B132" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14175,21 +14184,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14199,10 +14208,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>488142</v>
+        <v>488700</v>
       </c>
       <c r="R132" t="n">
-        <v>6787017</v>
+        <v>6786744</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14261,10 +14270,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>122566953</v>
+        <v>122566997</v>
       </c>
       <c r="B133" t="n">
-        <v>98244</v>
+        <v>78660</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14273,47 +14282,38 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>488429</v>
+        <v>488731</v>
       </c>
       <c r="R133" t="n">
-        <v>6786896</v>
+        <v>6786733</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>

--- a/artfynd/A 61338-2024 artfynd.xlsx
+++ b/artfynd/A 61338-2024 artfynd.xlsx
@@ -2551,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566904</v>
+        <v>122566963</v>
       </c>
       <c r="B20" t="n">
-        <v>90857</v>
+        <v>78660</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2567,21 +2567,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488552</v>
+        <v>488341</v>
       </c>
       <c r="R20" t="n">
-        <v>6786834</v>
+        <v>6786832</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,7 +2653,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566903</v>
+        <v>122566904</v>
       </c>
       <c r="B21" t="n">
         <v>90857</v>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488770</v>
+        <v>488552</v>
       </c>
       <c r="R21" t="n">
-        <v>6786732</v>
+        <v>6786834</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2755,10 +2755,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567301</v>
+        <v>122566903</v>
       </c>
       <c r="B22" t="n">
-        <v>8441</v>
+        <v>90857</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2767,43 +2767,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488718</v>
+        <v>488770</v>
       </c>
       <c r="R22" t="n">
-        <v>6786752</v>
+        <v>6786732</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2862,10 +2857,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567311</v>
+        <v>122567032</v>
       </c>
       <c r="B23" t="n">
-        <v>8441</v>
+        <v>5173</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2878,21 +2873,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2907,10 +2902,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488332</v>
+        <v>488901</v>
       </c>
       <c r="R23" t="n">
-        <v>6786824</v>
+        <v>6786589</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2969,7 +2964,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567291</v>
+        <v>122567301</v>
       </c>
       <c r="B24" t="n">
         <v>8441</v>
@@ -3014,10 +3009,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488440</v>
+        <v>488718</v>
       </c>
       <c r="R24" t="n">
-        <v>6786759</v>
+        <v>6786752</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3076,10 +3071,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566963</v>
+        <v>122567311</v>
       </c>
       <c r="B25" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3088,38 +3083,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488341</v>
+        <v>488332</v>
       </c>
       <c r="R25" t="n">
-        <v>6786832</v>
+        <v>6786824</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3178,10 +3178,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567032</v>
+        <v>122567291</v>
       </c>
       <c r="B26" t="n">
-        <v>5173</v>
+        <v>8441</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3194,27 +3194,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488901</v>
+        <v>488440</v>
       </c>
       <c r="R26" t="n">
-        <v>6786589</v>
+        <v>6786759</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3387,7 +3387,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567013</v>
+        <v>122567015</v>
       </c>
       <c r="B28" t="n">
         <v>78660</v>
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488389</v>
+        <v>488366</v>
       </c>
       <c r="R28" t="n">
-        <v>6786901</v>
+        <v>6786907</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3489,7 +3489,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567015</v>
+        <v>122567013</v>
       </c>
       <c r="B29" t="n">
         <v>78660</v>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488366</v>
+        <v>488389</v>
       </c>
       <c r="R29" t="n">
-        <v>6786907</v>
+        <v>6786901</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4223,7 +4223,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122567324</v>
+        <v>122567310</v>
       </c>
       <c r="B36" t="n">
         <v>8441</v>
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488638</v>
+        <v>488294</v>
       </c>
       <c r="R36" t="n">
-        <v>6786764</v>
+        <v>6786825</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4330,7 +4330,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122567310</v>
+        <v>122567324</v>
       </c>
       <c r="B37" t="n">
         <v>8441</v>
@@ -4375,10 +4375,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488294</v>
+        <v>488638</v>
       </c>
       <c r="R37" t="n">
-        <v>6786825</v>
+        <v>6786764</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -7434,7 +7434,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122567010</v>
+        <v>122566954</v>
       </c>
       <c r="B67" t="n">
         <v>78660</v>
@@ -7474,10 +7474,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488442</v>
+        <v>488416</v>
       </c>
       <c r="R67" t="n">
-        <v>6786881</v>
+        <v>6786896</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7536,10 +7536,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122566954</v>
+        <v>122566892</v>
       </c>
       <c r="B68" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7552,21 +7552,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7576,10 +7576,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488416</v>
+        <v>488699</v>
       </c>
       <c r="R68" t="n">
-        <v>6786896</v>
+        <v>6786599</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7638,10 +7638,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122566892</v>
+        <v>122567010</v>
       </c>
       <c r="B69" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7654,21 +7654,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7678,10 +7678,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488699</v>
+        <v>488442</v>
       </c>
       <c r="R69" t="n">
-        <v>6786599</v>
+        <v>6786881</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7740,10 +7740,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122567023</v>
+        <v>122567315</v>
       </c>
       <c r="B70" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7752,38 +7752,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488135</v>
+        <v>488773</v>
       </c>
       <c r="R70" t="n">
-        <v>6787033</v>
+        <v>6786561</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7842,10 +7847,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122567315</v>
+        <v>122566898</v>
       </c>
       <c r="B71" t="n">
-        <v>8441</v>
+        <v>57537</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7854,43 +7859,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488773</v>
+        <v>488296</v>
       </c>
       <c r="R71" t="n">
-        <v>6786561</v>
+        <v>6786844</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7949,10 +7949,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122566898</v>
+        <v>122567023</v>
       </c>
       <c r="B72" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7965,21 +7965,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7989,10 +7989,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488296</v>
+        <v>488135</v>
       </c>
       <c r="R72" t="n">
-        <v>6786844</v>
+        <v>6787033</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9703,10 +9703,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122567313</v>
+        <v>122566905</v>
       </c>
       <c r="B89" t="n">
-        <v>8441</v>
+        <v>57400</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9715,31 +9715,31 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -9748,10 +9748,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488616</v>
+        <v>488294</v>
       </c>
       <c r="R89" t="n">
-        <v>6786649</v>
+        <v>6786826</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10432,10 +10432,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122566905</v>
+        <v>122567313</v>
       </c>
       <c r="B96" t="n">
-        <v>57400</v>
+        <v>8441</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10444,31 +10444,31 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -10477,10 +10477,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>488294</v>
+        <v>488616</v>
       </c>
       <c r="R96" t="n">
-        <v>6786826</v>
+        <v>6786649</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>

--- a/artfynd/A 61338-2024 artfynd.xlsx
+++ b/artfynd/A 61338-2024 artfynd.xlsx
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566890</v>
+        <v>122567297</v>
       </c>
       <c r="B7" t="n">
-        <v>79278</v>
+        <v>8441</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,38 +1212,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488572</v>
+        <v>488804</v>
       </c>
       <c r="R7" t="n">
-        <v>6786674</v>
+        <v>6786700</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566995</v>
+        <v>122567303</v>
       </c>
       <c r="B8" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,38 +1319,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488833</v>
+        <v>488600</v>
       </c>
       <c r="R8" t="n">
-        <v>6786674</v>
+        <v>6786772</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122567005</v>
+        <v>122566890</v>
       </c>
       <c r="B9" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488415</v>
+        <v>488572</v>
       </c>
       <c r="R9" t="n">
-        <v>6786889</v>
+        <v>6786674</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122567000</v>
+        <v>122566995</v>
       </c>
       <c r="B10" t="n">
         <v>78660</v>
@@ -1546,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488678</v>
+        <v>488833</v>
       </c>
       <c r="R10" t="n">
-        <v>6786753</v>
+        <v>6786674</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567297</v>
+        <v>122567005</v>
       </c>
       <c r="B11" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,43 +1630,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488804</v>
+        <v>488415</v>
       </c>
       <c r="R11" t="n">
-        <v>6786700</v>
+        <v>6786889</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567303</v>
+        <v>122567000</v>
       </c>
       <c r="B12" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1727,43 +1732,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488600</v>
+        <v>488678</v>
       </c>
       <c r="R12" t="n">
-        <v>6786772</v>
+        <v>6786753</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2551,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566963</v>
+        <v>122566904</v>
       </c>
       <c r="B20" t="n">
-        <v>78660</v>
+        <v>90857</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2567,21 +2567,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488341</v>
+        <v>488552</v>
       </c>
       <c r="R20" t="n">
-        <v>6786832</v>
+        <v>6786834</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,7 +2653,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566904</v>
+        <v>122566903</v>
       </c>
       <c r="B21" t="n">
         <v>90857</v>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488552</v>
+        <v>488770</v>
       </c>
       <c r="R21" t="n">
-        <v>6786834</v>
+        <v>6786732</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2755,10 +2755,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566903</v>
+        <v>122567301</v>
       </c>
       <c r="B22" t="n">
-        <v>90857</v>
+        <v>8441</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2767,38 +2767,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488770</v>
+        <v>488718</v>
       </c>
       <c r="R22" t="n">
-        <v>6786732</v>
+        <v>6786752</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2857,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567032</v>
+        <v>122567311</v>
       </c>
       <c r="B23" t="n">
-        <v>5173</v>
+        <v>8441</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2873,21 +2878,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2902,10 +2907,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488901</v>
+        <v>488332</v>
       </c>
       <c r="R23" t="n">
-        <v>6786589</v>
+        <v>6786824</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2964,7 +2969,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567301</v>
+        <v>122567291</v>
       </c>
       <c r="B24" t="n">
         <v>8441</v>
@@ -3009,10 +3014,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488718</v>
+        <v>488440</v>
       </c>
       <c r="R24" t="n">
-        <v>6786752</v>
+        <v>6786759</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3071,10 +3076,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122567311</v>
+        <v>122566963</v>
       </c>
       <c r="B25" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3083,43 +3088,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488332</v>
+        <v>488341</v>
       </c>
       <c r="R25" t="n">
-        <v>6786824</v>
+        <v>6786832</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3178,10 +3178,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567291</v>
+        <v>122567032</v>
       </c>
       <c r="B26" t="n">
-        <v>8441</v>
+        <v>5173</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3194,27 +3194,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488440</v>
+        <v>488901</v>
       </c>
       <c r="R26" t="n">
-        <v>6786759</v>
+        <v>6786589</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -5049,10 +5049,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122566908</v>
+        <v>122567298</v>
       </c>
       <c r="B44" t="n">
-        <v>57400</v>
+        <v>8441</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5061,35 +5061,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5098,10 +5094,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488892</v>
+        <v>488789</v>
       </c>
       <c r="R44" t="n">
-        <v>6786620</v>
+        <v>6786702</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5160,10 +5156,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122567298</v>
+        <v>122566908</v>
       </c>
       <c r="B45" t="n">
-        <v>8441</v>
+        <v>57400</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5172,31 +5168,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5205,10 +5205,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488789</v>
+        <v>488892</v>
       </c>
       <c r="R45" t="n">
-        <v>6786702</v>
+        <v>6786620</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6098,10 +6098,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567016</v>
+        <v>122567304</v>
       </c>
       <c r="B54" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6110,38 +6110,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488360</v>
+        <v>488591</v>
       </c>
       <c r="R54" t="n">
-        <v>6786913</v>
+        <v>6786769</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6200,10 +6205,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122567011</v>
+        <v>122567289</v>
       </c>
       <c r="B55" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6212,38 +6217,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488427</v>
+        <v>488322</v>
       </c>
       <c r="R55" t="n">
-        <v>6786888</v>
+        <v>6786810</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6302,7 +6312,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122566960</v>
+        <v>122567016</v>
       </c>
       <c r="B56" t="n">
         <v>78660</v>
@@ -6342,10 +6352,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488322</v>
+        <v>488360</v>
       </c>
       <c r="R56" t="n">
-        <v>6786853</v>
+        <v>6786913</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6404,7 +6414,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567007</v>
+        <v>122567011</v>
       </c>
       <c r="B57" t="n">
         <v>78660</v>
@@ -6444,10 +6454,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488530</v>
+        <v>488427</v>
       </c>
       <c r="R57" t="n">
-        <v>6786847</v>
+        <v>6786888</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6506,10 +6516,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122567030</v>
+        <v>122566960</v>
       </c>
       <c r="B58" t="n">
-        <v>78305</v>
+        <v>78660</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6522,21 +6532,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6546,10 +6556,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488769</v>
+        <v>488322</v>
       </c>
       <c r="R58" t="n">
-        <v>6786552</v>
+        <v>6786853</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6608,10 +6618,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122567028</v>
+        <v>122567007</v>
       </c>
       <c r="B59" t="n">
-        <v>78305</v>
+        <v>78660</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6624,21 +6634,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6648,10 +6658,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488611</v>
+        <v>488530</v>
       </c>
       <c r="R59" t="n">
-        <v>6786649</v>
+        <v>6786847</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6710,10 +6720,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122567304</v>
+        <v>122567030</v>
       </c>
       <c r="B60" t="n">
-        <v>8441</v>
+        <v>78305</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6722,43 +6732,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488591</v>
+        <v>488769</v>
       </c>
       <c r="R60" t="n">
-        <v>6786769</v>
+        <v>6786552</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6817,10 +6822,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122567289</v>
+        <v>122567028</v>
       </c>
       <c r="B61" t="n">
-        <v>8441</v>
+        <v>78305</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6829,43 +6834,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488322</v>
+        <v>488611</v>
       </c>
       <c r="R61" t="n">
-        <v>6786810</v>
+        <v>6786649</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8153,10 +8153,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122567325</v>
+        <v>122566897</v>
       </c>
       <c r="B74" t="n">
-        <v>8441</v>
+        <v>90837</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8165,43 +8165,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488576</v>
+        <v>488892</v>
       </c>
       <c r="R74" t="n">
-        <v>6786782</v>
+        <v>6786591</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8260,7 +8255,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122567322</v>
+        <v>122567325</v>
       </c>
       <c r="B75" t="n">
         <v>8441</v>
@@ -8305,10 +8300,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488700</v>
+        <v>488576</v>
       </c>
       <c r="R75" t="n">
-        <v>6786746</v>
+        <v>6786782</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8367,10 +8362,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122566897</v>
+        <v>122567322</v>
       </c>
       <c r="B76" t="n">
-        <v>90837</v>
+        <v>8441</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8379,38 +8374,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488892</v>
+        <v>488700</v>
       </c>
       <c r="R76" t="n">
-        <v>6786591</v>
+        <v>6786746</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10641,10 +10641,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122567027</v>
+        <v>122567006</v>
       </c>
       <c r="B98" t="n">
-        <v>78305</v>
+        <v>78660</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10657,21 +10657,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10681,10 +10681,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>488618</v>
+        <v>488556</v>
       </c>
       <c r="R98" t="n">
-        <v>6786631</v>
+        <v>6786835</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10743,7 +10743,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122567006</v>
+        <v>122567003</v>
       </c>
       <c r="B99" t="n">
         <v>78660</v>
@@ -10783,10 +10783,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>488556</v>
+        <v>488550</v>
       </c>
       <c r="R99" t="n">
-        <v>6786835</v>
+        <v>6786822</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10845,7 +10845,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122567003</v>
+        <v>122566962</v>
       </c>
       <c r="B100" t="n">
         <v>78660</v>
@@ -10885,10 +10885,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>488550</v>
+        <v>488324</v>
       </c>
       <c r="R100" t="n">
-        <v>6786822</v>
+        <v>6786843</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10947,10 +10947,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122566962</v>
+        <v>122567307</v>
       </c>
       <c r="B101" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10959,35 +10959,40 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>488324</v>
+        <v>488535</v>
       </c>
       <c r="R101" t="n">
         <v>6786843</v>
@@ -11049,7 +11054,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122567307</v>
+        <v>122567318</v>
       </c>
       <c r="B102" t="n">
         <v>8441</v>
@@ -11085,7 +11090,7 @@
       <c r="I102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -11094,10 +11099,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>488535</v>
+        <v>488883</v>
       </c>
       <c r="R102" t="n">
-        <v>6786843</v>
+        <v>6786645</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11156,10 +11161,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122567318</v>
+        <v>122567027</v>
       </c>
       <c r="B103" t="n">
-        <v>8441</v>
+        <v>78305</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11168,43 +11173,38 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>488883</v>
+        <v>488618</v>
       </c>
       <c r="R103" t="n">
-        <v>6786645</v>
+        <v>6786631</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11263,7 +11263,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122566988</v>
+        <v>122566994</v>
       </c>
       <c r="B104" t="n">
         <v>78660</v>
@@ -11303,10 +11303,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488803</v>
+        <v>488883</v>
       </c>
       <c r="R104" t="n">
-        <v>6786562</v>
+        <v>6786645</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11365,7 +11365,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122566994</v>
+        <v>122567019</v>
       </c>
       <c r="B105" t="n">
         <v>78660</v>
@@ -11405,10 +11405,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488883</v>
+        <v>488297</v>
       </c>
       <c r="R105" t="n">
-        <v>6786645</v>
+        <v>6786946</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11467,10 +11467,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122566991</v>
+        <v>122567293</v>
       </c>
       <c r="B106" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11479,38 +11479,43 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488918</v>
+        <v>488790</v>
       </c>
       <c r="R106" t="n">
-        <v>6786607</v>
+        <v>6786547</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11569,10 +11574,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122566959</v>
+        <v>122567316</v>
       </c>
       <c r="B107" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11581,38 +11586,43 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488317</v>
+        <v>488900</v>
       </c>
       <c r="R107" t="n">
-        <v>6786858</v>
+        <v>6786628</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11671,10 +11681,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122567019</v>
+        <v>122567295</v>
       </c>
       <c r="B108" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11683,38 +11693,43 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>488297</v>
+        <v>488850</v>
       </c>
       <c r="R108" t="n">
-        <v>6786946</v>
+        <v>6786668</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11773,10 +11788,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122567293</v>
+        <v>122566988</v>
       </c>
       <c r="B109" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11785,43 +11800,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488790</v>
+        <v>488803</v>
       </c>
       <c r="R109" t="n">
-        <v>6786547</v>
+        <v>6786562</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11880,10 +11890,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122567316</v>
+        <v>122566991</v>
       </c>
       <c r="B110" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11892,43 +11902,38 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>488900</v>
+        <v>488918</v>
       </c>
       <c r="R110" t="n">
-        <v>6786628</v>
+        <v>6786607</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11987,10 +11992,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122567295</v>
+        <v>122566959</v>
       </c>
       <c r="B111" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11999,43 +12004,38 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>488850</v>
+        <v>488317</v>
       </c>
       <c r="R111" t="n">
-        <v>6786668</v>
+        <v>6786858</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>

--- a/artfynd/A 61338-2024 artfynd.xlsx
+++ b/artfynd/A 61338-2024 artfynd.xlsx
@@ -1822,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567026</v>
+        <v>122566984</v>
       </c>
       <c r="B13" t="n">
-        <v>78305</v>
+        <v>78660</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488539</v>
+        <v>488699</v>
       </c>
       <c r="R13" t="n">
-        <v>6786689</v>
+        <v>6786596</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566911</v>
+        <v>122566996</v>
       </c>
       <c r="B14" t="n">
-        <v>91128</v>
+        <v>78660</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,21 +1940,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488882</v>
+        <v>488757</v>
       </c>
       <c r="R14" t="n">
-        <v>6786609</v>
+        <v>6786723</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566984</v>
+        <v>122567026</v>
       </c>
       <c r="B15" t="n">
-        <v>78660</v>
+        <v>78305</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,21 +2042,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488699</v>
+        <v>488539</v>
       </c>
       <c r="R15" t="n">
-        <v>6786596</v>
+        <v>6786689</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2128,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566996</v>
+        <v>122566911</v>
       </c>
       <c r="B16" t="n">
-        <v>78660</v>
+        <v>91128</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,21 +2144,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488757</v>
+        <v>488882</v>
       </c>
       <c r="R16" t="n">
-        <v>6786723</v>
+        <v>6786609</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -4223,7 +4223,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122567310</v>
+        <v>122567324</v>
       </c>
       <c r="B36" t="n">
         <v>8441</v>
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488294</v>
+        <v>488638</v>
       </c>
       <c r="R36" t="n">
-        <v>6786825</v>
+        <v>6786764</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4330,7 +4330,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122567324</v>
+        <v>122567310</v>
       </c>
       <c r="B37" t="n">
         <v>8441</v>
@@ -4375,10 +4375,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488638</v>
+        <v>488294</v>
       </c>
       <c r="R37" t="n">
-        <v>6786764</v>
+        <v>6786825</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -6924,10 +6924,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122566894</v>
+        <v>122566896</v>
       </c>
       <c r="B62" t="n">
-        <v>79278</v>
+        <v>90837</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488182</v>
+        <v>488882</v>
       </c>
       <c r="R62" t="n">
-        <v>6787001</v>
+        <v>6786607</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7026,10 +7026,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122567012</v>
+        <v>122566902</v>
       </c>
       <c r="B63" t="n">
-        <v>78660</v>
+        <v>90857</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7042,21 +7042,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7066,10 +7066,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488420</v>
+        <v>488397</v>
       </c>
       <c r="R63" t="n">
-        <v>6786898</v>
+        <v>6786809</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7128,10 +7128,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122566896</v>
+        <v>122566894</v>
       </c>
       <c r="B64" t="n">
-        <v>90837</v>
+        <v>79278</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7144,21 +7144,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7168,10 +7168,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488882</v>
+        <v>488182</v>
       </c>
       <c r="R64" t="n">
-        <v>6786607</v>
+        <v>6787001</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7230,10 +7230,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122566902</v>
+        <v>122567012</v>
       </c>
       <c r="B65" t="n">
-        <v>90857</v>
+        <v>78660</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7246,21 +7246,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7270,10 +7270,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488397</v>
+        <v>488420</v>
       </c>
       <c r="R65" t="n">
-        <v>6786809</v>
+        <v>6786898</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8153,10 +8153,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122566897</v>
+        <v>122567325</v>
       </c>
       <c r="B74" t="n">
-        <v>90837</v>
+        <v>8441</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8165,38 +8165,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488892</v>
+        <v>488576</v>
       </c>
       <c r="R74" t="n">
-        <v>6786591</v>
+        <v>6786782</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8255,7 +8260,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122567325</v>
+        <v>122567322</v>
       </c>
       <c r="B75" t="n">
         <v>8441</v>
@@ -8300,10 +8305,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488576</v>
+        <v>488700</v>
       </c>
       <c r="R75" t="n">
-        <v>6786782</v>
+        <v>6786746</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8362,10 +8367,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122567322</v>
+        <v>122566897</v>
       </c>
       <c r="B76" t="n">
-        <v>8441</v>
+        <v>90837</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8374,43 +8379,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488700</v>
+        <v>488892</v>
       </c>
       <c r="R76" t="n">
-        <v>6786746</v>
+        <v>6786591</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -12925,10 +12925,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122566983</v>
+        <v>122567308</v>
       </c>
       <c r="B120" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12937,38 +12937,43 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>488609</v>
+        <v>488669</v>
       </c>
       <c r="R120" t="n">
-        <v>6786648</v>
+        <v>6786761</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13129,10 +13134,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122566909</v>
+        <v>122566983</v>
       </c>
       <c r="B122" t="n">
-        <v>91282</v>
+        <v>78660</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13141,25 +13146,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13169,10 +13174,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488882</v>
+        <v>488609</v>
       </c>
       <c r="R122" t="n">
-        <v>6786607</v>
+        <v>6786648</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13231,10 +13236,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122567308</v>
+        <v>122566909</v>
       </c>
       <c r="B123" t="n">
-        <v>8441</v>
+        <v>91282</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13243,43 +13248,38 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>1209</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>488669</v>
+        <v>488882</v>
       </c>
       <c r="R123" t="n">
-        <v>6786761</v>
+        <v>6786607</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13338,10 +13338,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122567025</v>
+        <v>122566980</v>
       </c>
       <c r="B124" t="n">
-        <v>78305</v>
+        <v>78660</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13354,21 +13354,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13378,10 +13378,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>488378</v>
+        <v>488590</v>
       </c>
       <c r="R124" t="n">
-        <v>6786805</v>
+        <v>6786665</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13440,10 +13440,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122567290</v>
+        <v>122566974</v>
       </c>
       <c r="B125" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13452,43 +13452,38 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>488345</v>
+        <v>488486</v>
       </c>
       <c r="R125" t="n">
-        <v>6786796</v>
+        <v>6786718</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13547,10 +13542,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122566901</v>
+        <v>122566957</v>
       </c>
       <c r="B126" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13563,21 +13558,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13587,10 +13582,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>488142</v>
+        <v>488300</v>
       </c>
       <c r="R126" t="n">
-        <v>6787017</v>
+        <v>6786820</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13649,10 +13644,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122566953</v>
+        <v>122567008</v>
       </c>
       <c r="B127" t="n">
-        <v>98244</v>
+        <v>78660</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13661,47 +13656,38 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>488429</v>
+        <v>488495</v>
       </c>
       <c r="R127" t="n">
-        <v>6786896</v>
+        <v>6786888</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13760,7 +13746,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122566980</v>
+        <v>122566998</v>
       </c>
       <c r="B128" t="n">
         <v>78660</v>
@@ -13800,10 +13786,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>488590</v>
+        <v>488700</v>
       </c>
       <c r="R128" t="n">
-        <v>6786665</v>
+        <v>6786744</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13862,7 +13848,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122566974</v>
+        <v>122566997</v>
       </c>
       <c r="B129" t="n">
         <v>78660</v>
@@ -13902,10 +13888,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>488486</v>
+        <v>488731</v>
       </c>
       <c r="R129" t="n">
-        <v>6786718</v>
+        <v>6786733</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13964,10 +13950,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122566957</v>
+        <v>122567025</v>
       </c>
       <c r="B130" t="n">
-        <v>78660</v>
+        <v>78305</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13980,21 +13966,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14004,10 +13990,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>488300</v>
+        <v>488378</v>
       </c>
       <c r="R130" t="n">
-        <v>6786820</v>
+        <v>6786805</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14066,10 +14052,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122567008</v>
+        <v>122567290</v>
       </c>
       <c r="B131" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14078,38 +14064,43 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>488495</v>
+        <v>488345</v>
       </c>
       <c r="R131" t="n">
-        <v>6786888</v>
+        <v>6786796</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14168,10 +14159,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122566998</v>
+        <v>122566901</v>
       </c>
       <c r="B132" t="n">
-        <v>78660</v>
+        <v>57537</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14184,21 +14175,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14208,10 +14199,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>488700</v>
+        <v>488142</v>
       </c>
       <c r="R132" t="n">
-        <v>6786744</v>
+        <v>6787017</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14270,10 +14261,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>122566997</v>
+        <v>122566953</v>
       </c>
       <c r="B133" t="n">
-        <v>78660</v>
+        <v>98244</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14282,38 +14273,47 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>488731</v>
+        <v>488429</v>
       </c>
       <c r="R133" t="n">
-        <v>6786733</v>
+        <v>6786896</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>

--- a/artfynd/A 61338-2024 artfynd.xlsx
+++ b/artfynd/A 61338-2024 artfynd.xlsx
@@ -4223,7 +4223,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122567324</v>
+        <v>122567310</v>
       </c>
       <c r="B36" t="n">
         <v>8441</v>
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488638</v>
+        <v>488294</v>
       </c>
       <c r="R36" t="n">
-        <v>6786764</v>
+        <v>6786825</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4330,7 +4330,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122567310</v>
+        <v>122567324</v>
       </c>
       <c r="B37" t="n">
         <v>8441</v>
@@ -4375,10 +4375,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488294</v>
+        <v>488638</v>
       </c>
       <c r="R37" t="n">
-        <v>6786825</v>
+        <v>6786764</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -6924,10 +6924,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122566896</v>
+        <v>122566894</v>
       </c>
       <c r="B62" t="n">
-        <v>90837</v>
+        <v>79278</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488882</v>
+        <v>488182</v>
       </c>
       <c r="R62" t="n">
-        <v>6786607</v>
+        <v>6787001</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7026,10 +7026,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122566902</v>
+        <v>122567012</v>
       </c>
       <c r="B63" t="n">
-        <v>90857</v>
+        <v>78660</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7042,21 +7042,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7066,10 +7066,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488397</v>
+        <v>488420</v>
       </c>
       <c r="R63" t="n">
-        <v>6786809</v>
+        <v>6786898</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7128,10 +7128,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122566894</v>
+        <v>122566896</v>
       </c>
       <c r="B64" t="n">
-        <v>79278</v>
+        <v>90837</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7144,21 +7144,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7168,10 +7168,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488182</v>
+        <v>488882</v>
       </c>
       <c r="R64" t="n">
-        <v>6787001</v>
+        <v>6786607</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7230,10 +7230,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122567012</v>
+        <v>122566902</v>
       </c>
       <c r="B65" t="n">
-        <v>78660</v>
+        <v>90857</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7246,21 +7246,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7270,10 +7270,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488420</v>
+        <v>488397</v>
       </c>
       <c r="R65" t="n">
-        <v>6786898</v>
+        <v>6786809</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7434,7 +7434,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122566954</v>
+        <v>122567010</v>
       </c>
       <c r="B67" t="n">
         <v>78660</v>
@@ -7474,10 +7474,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488416</v>
+        <v>488442</v>
       </c>
       <c r="R67" t="n">
-        <v>6786896</v>
+        <v>6786881</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7536,10 +7536,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122566892</v>
+        <v>122566954</v>
       </c>
       <c r="B68" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7552,21 +7552,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7576,10 +7576,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488699</v>
+        <v>488416</v>
       </c>
       <c r="R68" t="n">
-        <v>6786599</v>
+        <v>6786896</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7638,10 +7638,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122567010</v>
+        <v>122566892</v>
       </c>
       <c r="B69" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7654,21 +7654,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7678,10 +7678,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488442</v>
+        <v>488699</v>
       </c>
       <c r="R69" t="n">
-        <v>6786881</v>
+        <v>6786599</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7740,10 +7740,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122567315</v>
+        <v>122567023</v>
       </c>
       <c r="B70" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7752,43 +7752,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488773</v>
+        <v>488135</v>
       </c>
       <c r="R70" t="n">
-        <v>6786561</v>
+        <v>6787033</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7847,10 +7842,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122566898</v>
+        <v>122567315</v>
       </c>
       <c r="B71" t="n">
-        <v>57537</v>
+        <v>8441</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7859,38 +7854,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488296</v>
+        <v>488773</v>
       </c>
       <c r="R71" t="n">
-        <v>6786844</v>
+        <v>6786561</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7949,10 +7949,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122567023</v>
+        <v>122566898</v>
       </c>
       <c r="B72" t="n">
-        <v>78660</v>
+        <v>57537</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7965,21 +7965,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7989,10 +7989,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488135</v>
+        <v>488296</v>
       </c>
       <c r="R72" t="n">
-        <v>6787033</v>
+        <v>6786844</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8469,10 +8469,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122566907</v>
+        <v>122567017</v>
       </c>
       <c r="B77" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8485,39 +8485,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488852</v>
+        <v>488353</v>
       </c>
       <c r="R77" t="n">
-        <v>6786673</v>
+        <v>6786911</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8576,7 +8571,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122567017</v>
+        <v>122566979</v>
       </c>
       <c r="B78" t="n">
         <v>78660</v>
@@ -8616,10 +8611,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488353</v>
+        <v>488583</v>
       </c>
       <c r="R78" t="n">
-        <v>6786911</v>
+        <v>6786676</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8678,7 +8673,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122566979</v>
+        <v>122566990</v>
       </c>
       <c r="B79" t="n">
         <v>78660</v>
@@ -8718,10 +8713,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488583</v>
+        <v>488840</v>
       </c>
       <c r="R79" t="n">
-        <v>6786676</v>
+        <v>6786622</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8780,7 +8775,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122566990</v>
+        <v>122567020</v>
       </c>
       <c r="B80" t="n">
         <v>78660</v>
@@ -8820,10 +8815,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488840</v>
+        <v>488185</v>
       </c>
       <c r="R80" t="n">
-        <v>6786622</v>
+        <v>6787005</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8882,7 +8877,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122567020</v>
+        <v>122566965</v>
       </c>
       <c r="B81" t="n">
         <v>78660</v>
@@ -8922,10 +8917,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488185</v>
+        <v>488378</v>
       </c>
       <c r="R81" t="n">
-        <v>6787005</v>
+        <v>6786805</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8984,10 +8979,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122566965</v>
+        <v>122566891</v>
       </c>
       <c r="B82" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9000,21 +8995,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9024,10 +9019,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488378</v>
+        <v>488616</v>
       </c>
       <c r="R82" t="n">
-        <v>6786805</v>
+        <v>6786648</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9086,10 +9081,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122566891</v>
+        <v>122567014</v>
       </c>
       <c r="B83" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9102,21 +9097,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9126,10 +9121,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488616</v>
+        <v>488383</v>
       </c>
       <c r="R83" t="n">
-        <v>6786648</v>
+        <v>6786912</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9188,7 +9183,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122567014</v>
+        <v>122566972</v>
       </c>
       <c r="B84" t="n">
         <v>78660</v>
@@ -9228,10 +9223,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488383</v>
+        <v>488465</v>
       </c>
       <c r="R84" t="n">
-        <v>6786912</v>
+        <v>6786729</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9290,10 +9285,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122566972</v>
+        <v>122567029</v>
       </c>
       <c r="B85" t="n">
-        <v>78660</v>
+        <v>78305</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9306,21 +9301,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9330,10 +9325,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488465</v>
+        <v>488664</v>
       </c>
       <c r="R85" t="n">
-        <v>6786729</v>
+        <v>6786615</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9392,10 +9387,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122567029</v>
+        <v>122567024</v>
       </c>
       <c r="B86" t="n">
-        <v>78305</v>
+        <v>91089</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9404,25 +9399,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9432,7 +9427,7 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488664</v>
+        <v>488663</v>
       </c>
       <c r="R86" t="n">
         <v>6786615</v>
@@ -9494,10 +9489,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122567024</v>
+        <v>122566907</v>
       </c>
       <c r="B87" t="n">
-        <v>91089</v>
+        <v>57400</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9506,38 +9501,43 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>65</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488663</v>
+        <v>488852</v>
       </c>
       <c r="R87" t="n">
-        <v>6786615</v>
+        <v>6786673</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9703,10 +9703,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122566905</v>
+        <v>122567313</v>
       </c>
       <c r="B89" t="n">
-        <v>57400</v>
+        <v>8441</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9715,31 +9715,31 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -9748,10 +9748,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488294</v>
+        <v>488616</v>
       </c>
       <c r="R89" t="n">
-        <v>6786826</v>
+        <v>6786649</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10432,10 +10432,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122567313</v>
+        <v>122566905</v>
       </c>
       <c r="B96" t="n">
-        <v>8441</v>
+        <v>57400</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10444,31 +10444,31 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -10477,10 +10477,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>488616</v>
+        <v>488294</v>
       </c>
       <c r="R96" t="n">
-        <v>6786649</v>
+        <v>6786826</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11263,7 +11263,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122566994</v>
+        <v>122566988</v>
       </c>
       <c r="B104" t="n">
         <v>78660</v>
@@ -11303,10 +11303,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488883</v>
+        <v>488803</v>
       </c>
       <c r="R104" t="n">
-        <v>6786645</v>
+        <v>6786562</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11365,7 +11365,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122567019</v>
+        <v>122566994</v>
       </c>
       <c r="B105" t="n">
         <v>78660</v>
@@ -11405,10 +11405,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488297</v>
+        <v>488883</v>
       </c>
       <c r="R105" t="n">
-        <v>6786946</v>
+        <v>6786645</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11467,10 +11467,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122567293</v>
+        <v>122566991</v>
       </c>
       <c r="B106" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11479,43 +11479,38 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488790</v>
+        <v>488918</v>
       </c>
       <c r="R106" t="n">
-        <v>6786547</v>
+        <v>6786607</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11574,10 +11569,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122567316</v>
+        <v>122566959</v>
       </c>
       <c r="B107" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11586,43 +11581,38 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488900</v>
+        <v>488317</v>
       </c>
       <c r="R107" t="n">
-        <v>6786628</v>
+        <v>6786858</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11681,10 +11671,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122567295</v>
+        <v>122567019</v>
       </c>
       <c r="B108" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11693,43 +11683,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>488850</v>
+        <v>488297</v>
       </c>
       <c r="R108" t="n">
-        <v>6786668</v>
+        <v>6786946</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11788,10 +11773,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122566988</v>
+        <v>122567293</v>
       </c>
       <c r="B109" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11800,38 +11785,43 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488803</v>
+        <v>488790</v>
       </c>
       <c r="R109" t="n">
-        <v>6786562</v>
+        <v>6786547</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11890,10 +11880,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122566991</v>
+        <v>122567316</v>
       </c>
       <c r="B110" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11902,38 +11892,43 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>488918</v>
+        <v>488900</v>
       </c>
       <c r="R110" t="n">
-        <v>6786607</v>
+        <v>6786628</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11992,10 +11987,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122566959</v>
+        <v>122567295</v>
       </c>
       <c r="B111" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12004,38 +11999,43 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>488317</v>
+        <v>488850</v>
       </c>
       <c r="R111" t="n">
-        <v>6786858</v>
+        <v>6786668</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>

--- a/artfynd/A 61338-2024 artfynd.xlsx
+++ b/artfynd/A 61338-2024 artfynd.xlsx
@@ -10320,10 +10320,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122566913</v>
+        <v>122566905</v>
       </c>
       <c r="B95" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10336,16 +10336,16 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -10365,10 +10365,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>488602</v>
+        <v>488294</v>
       </c>
       <c r="R95" t="n">
-        <v>6786666</v>
+        <v>6786826</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10401,11 +10401,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10432,10 +10427,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122566905</v>
+        <v>122566899</v>
       </c>
       <c r="B96" t="n">
-        <v>57400</v>
+        <v>57537</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10448,39 +10443,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>488294</v>
+        <v>488482</v>
       </c>
       <c r="R96" t="n">
-        <v>6786826</v>
+        <v>6786720</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10539,10 +10529,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122566899</v>
+        <v>122567027</v>
       </c>
       <c r="B97" t="n">
-        <v>57537</v>
+        <v>78305</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10555,21 +10545,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10579,10 +10569,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>488482</v>
+        <v>488618</v>
       </c>
       <c r="R97" t="n">
-        <v>6786720</v>
+        <v>6786631</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11161,10 +11151,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122567027</v>
+        <v>122566988</v>
       </c>
       <c r="B103" t="n">
-        <v>78305</v>
+        <v>78660</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11177,21 +11167,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11201,10 +11191,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>488618</v>
+        <v>488803</v>
       </c>
       <c r="R103" t="n">
-        <v>6786631</v>
+        <v>6786562</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11263,7 +11253,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122566988</v>
+        <v>122566994</v>
       </c>
       <c r="B104" t="n">
         <v>78660</v>
@@ -11303,10 +11293,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488803</v>
+        <v>488883</v>
       </c>
       <c r="R104" t="n">
-        <v>6786562</v>
+        <v>6786645</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11365,7 +11355,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122566994</v>
+        <v>122566991</v>
       </c>
       <c r="B105" t="n">
         <v>78660</v>
@@ -11405,10 +11395,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488883</v>
+        <v>488918</v>
       </c>
       <c r="R105" t="n">
-        <v>6786645</v>
+        <v>6786607</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11467,7 +11457,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122566991</v>
+        <v>122566959</v>
       </c>
       <c r="B106" t="n">
         <v>78660</v>
@@ -11507,10 +11497,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488918</v>
+        <v>488317</v>
       </c>
       <c r="R106" t="n">
-        <v>6786607</v>
+        <v>6786858</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11569,7 +11559,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122566959</v>
+        <v>122567019</v>
       </c>
       <c r="B107" t="n">
         <v>78660</v>
@@ -11609,10 +11599,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488317</v>
+        <v>488297</v>
       </c>
       <c r="R107" t="n">
-        <v>6786858</v>
+        <v>6786946</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11671,10 +11661,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122567019</v>
+        <v>122567293</v>
       </c>
       <c r="B108" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11683,38 +11673,43 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>488297</v>
+        <v>488790</v>
       </c>
       <c r="R108" t="n">
-        <v>6786946</v>
+        <v>6786547</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11773,7 +11768,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122567293</v>
+        <v>122567316</v>
       </c>
       <c r="B109" t="n">
         <v>8441</v>
@@ -11809,7 +11804,7 @@
       <c r="I109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -11818,10 +11813,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488790</v>
+        <v>488900</v>
       </c>
       <c r="R109" t="n">
-        <v>6786547</v>
+        <v>6786628</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11880,7 +11875,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122567316</v>
+        <v>122567295</v>
       </c>
       <c r="B110" t="n">
         <v>8441</v>
@@ -11916,7 +11911,7 @@
       <c r="I110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -11925,10 +11920,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>488900</v>
+        <v>488850</v>
       </c>
       <c r="R110" t="n">
-        <v>6786628</v>
+        <v>6786668</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11987,10 +11982,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122567295</v>
+        <v>122567004</v>
       </c>
       <c r="B111" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11999,43 +11994,38 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>488850</v>
+        <v>488475</v>
       </c>
       <c r="R111" t="n">
-        <v>6786668</v>
+        <v>6786864</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12094,10 +12084,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122567004</v>
+        <v>122567305</v>
       </c>
       <c r="B112" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12106,38 +12096,43 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>488475</v>
+        <v>488519</v>
       </c>
       <c r="R112" t="n">
-        <v>6786864</v>
+        <v>6786844</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12196,7 +12191,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122567305</v>
+        <v>122567317</v>
       </c>
       <c r="B113" t="n">
         <v>8441</v>
@@ -12232,7 +12227,7 @@
       <c r="I113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -12241,10 +12236,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488519</v>
+        <v>488892</v>
       </c>
       <c r="R113" t="n">
-        <v>6786844</v>
+        <v>6786620</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12303,10 +12298,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122567317</v>
+        <v>122566973</v>
       </c>
       <c r="B114" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12315,43 +12310,38 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488892</v>
+        <v>488482</v>
       </c>
       <c r="R114" t="n">
-        <v>6786620</v>
+        <v>6786720</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12410,7 +12400,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122566973</v>
+        <v>122566969</v>
       </c>
       <c r="B115" t="n">
         <v>78660</v>
@@ -12450,10 +12440,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>488482</v>
+        <v>488452</v>
       </c>
       <c r="R115" t="n">
-        <v>6786720</v>
+        <v>6786772</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12512,7 +12502,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122566969</v>
+        <v>122566982</v>
       </c>
       <c r="B116" t="n">
         <v>78660</v>
@@ -12552,10 +12542,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>488452</v>
+        <v>488600</v>
       </c>
       <c r="R116" t="n">
-        <v>6786772</v>
+        <v>6786662</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12614,10 +12604,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122566982</v>
+        <v>122566952</v>
       </c>
       <c r="B117" t="n">
-        <v>78660</v>
+        <v>80617</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12630,21 +12620,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12654,10 +12644,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>488600</v>
+        <v>488363</v>
       </c>
       <c r="R117" t="n">
-        <v>6786662</v>
+        <v>6786907</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12716,10 +12706,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122566952</v>
+        <v>122567323</v>
       </c>
       <c r="B118" t="n">
-        <v>80617</v>
+        <v>8441</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12728,38 +12718,43 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1049</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>488363</v>
+        <v>488686</v>
       </c>
       <c r="R118" t="n">
-        <v>6786907</v>
+        <v>6786745</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12818,7 +12813,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122567323</v>
+        <v>122567308</v>
       </c>
       <c r="B119" t="n">
         <v>8441</v>
@@ -12863,10 +12858,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>488686</v>
+        <v>488669</v>
       </c>
       <c r="R119" t="n">
-        <v>6786745</v>
+        <v>6786761</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12925,10 +12920,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122567308</v>
+        <v>122566985</v>
       </c>
       <c r="B120" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12937,43 +12932,38 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>488669</v>
+        <v>488698</v>
       </c>
       <c r="R120" t="n">
-        <v>6786761</v>
+        <v>6786584</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13032,7 +13022,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122566985</v>
+        <v>122566983</v>
       </c>
       <c r="B121" t="n">
         <v>78660</v>
@@ -13072,10 +13062,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488698</v>
+        <v>488609</v>
       </c>
       <c r="R121" t="n">
-        <v>6786584</v>
+        <v>6786648</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13134,10 +13124,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122566983</v>
+        <v>122566909</v>
       </c>
       <c r="B122" t="n">
-        <v>78660</v>
+        <v>91282</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13146,25 +13136,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13174,10 +13164,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488609</v>
+        <v>488882</v>
       </c>
       <c r="R122" t="n">
-        <v>6786648</v>
+        <v>6786607</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13236,10 +13226,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122566909</v>
+        <v>122566980</v>
       </c>
       <c r="B123" t="n">
-        <v>91282</v>
+        <v>78660</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13248,25 +13238,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13276,10 +13266,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>488882</v>
+        <v>488590</v>
       </c>
       <c r="R123" t="n">
-        <v>6786607</v>
+        <v>6786665</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13338,7 +13328,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122566980</v>
+        <v>122566974</v>
       </c>
       <c r="B124" t="n">
         <v>78660</v>
@@ -13378,10 +13368,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>488590</v>
+        <v>488486</v>
       </c>
       <c r="R124" t="n">
-        <v>6786665</v>
+        <v>6786718</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13440,7 +13430,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122566974</v>
+        <v>122566957</v>
       </c>
       <c r="B125" t="n">
         <v>78660</v>
@@ -13480,10 +13470,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>488486</v>
+        <v>488300</v>
       </c>
       <c r="R125" t="n">
-        <v>6786718</v>
+        <v>6786820</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13542,7 +13532,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122566957</v>
+        <v>122567008</v>
       </c>
       <c r="B126" t="n">
         <v>78660</v>
@@ -13582,10 +13572,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>488300</v>
+        <v>488495</v>
       </c>
       <c r="R126" t="n">
-        <v>6786820</v>
+        <v>6786888</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13644,7 +13634,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122567008</v>
+        <v>122566998</v>
       </c>
       <c r="B127" t="n">
         <v>78660</v>
@@ -13684,10 +13674,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>488495</v>
+        <v>488700</v>
       </c>
       <c r="R127" t="n">
-        <v>6786888</v>
+        <v>6786744</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13746,7 +13736,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122566998</v>
+        <v>122566997</v>
       </c>
       <c r="B128" t="n">
         <v>78660</v>
@@ -13786,10 +13776,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>488700</v>
+        <v>488731</v>
       </c>
       <c r="R128" t="n">
-        <v>6786744</v>
+        <v>6786733</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13848,10 +13838,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122566997</v>
+        <v>122567025</v>
       </c>
       <c r="B129" t="n">
-        <v>78660</v>
+        <v>78305</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13864,21 +13854,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13888,10 +13878,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>488731</v>
+        <v>488378</v>
       </c>
       <c r="R129" t="n">
-        <v>6786733</v>
+        <v>6786805</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13950,10 +13940,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122567025</v>
+        <v>122567290</v>
       </c>
       <c r="B130" t="n">
-        <v>78305</v>
+        <v>8441</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13962,38 +13952,43 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>488378</v>
+        <v>488345</v>
       </c>
       <c r="R130" t="n">
-        <v>6786805</v>
+        <v>6786796</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14052,10 +14047,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122567290</v>
+        <v>122566901</v>
       </c>
       <c r="B131" t="n">
-        <v>8441</v>
+        <v>57537</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14064,43 +14059,38 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>488345</v>
+        <v>488142</v>
       </c>
       <c r="R131" t="n">
-        <v>6786796</v>
+        <v>6787017</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14159,10 +14149,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122566901</v>
+        <v>122566953</v>
       </c>
       <c r="B132" t="n">
-        <v>57537</v>
+        <v>98244</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14171,38 +14161,47 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>488142</v>
+        <v>488429</v>
       </c>
       <c r="R132" t="n">
-        <v>6787017</v>
+        <v>6786896</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14261,10 +14260,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>122566953</v>
+        <v>122566913</v>
       </c>
       <c r="B133" t="n">
-        <v>98244</v>
+        <v>57478</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14273,35 +14272,31 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -14310,10 +14305,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>488429</v>
+        <v>488602</v>
       </c>
       <c r="R133" t="n">
-        <v>6786896</v>
+        <v>6786666</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14346,6 +14341,11 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD133" t="b">

--- a/artfynd/A 61338-2024 artfynd.xlsx
+++ b/artfynd/A 61338-2024 artfynd.xlsx
@@ -2220,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566997</v>
+        <v>122566953</v>
       </c>
       <c r="B17" t="n">
-        <v>78762</v>
+        <v>98347</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2232,38 +2232,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488731</v>
+        <v>488429</v>
       </c>
       <c r="R17" t="n">
-        <v>6786733</v>
+        <v>6786896</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,10 +2331,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566892</v>
+        <v>122566997</v>
       </c>
       <c r="B18" t="n">
-        <v>79380</v>
+        <v>78762</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,21 +2347,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2362,10 +2371,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488699</v>
+        <v>488731</v>
       </c>
       <c r="R18" t="n">
-        <v>6786599</v>
+        <v>6786733</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,10 +2433,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566967</v>
+        <v>122566892</v>
       </c>
       <c r="B19" t="n">
-        <v>78762</v>
+        <v>79380</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2440,21 +2449,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488387</v>
+        <v>488699</v>
       </c>
       <c r="R19" t="n">
-        <v>6786773</v>
+        <v>6786599</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566953</v>
+        <v>122566967</v>
       </c>
       <c r="B20" t="n">
-        <v>98347</v>
+        <v>78762</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2538,47 +2547,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488429</v>
+        <v>488387</v>
       </c>
       <c r="R20" t="n">
-        <v>6786896</v>
+        <v>6786773</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3896,10 +3896,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122566908</v>
+        <v>122566899</v>
       </c>
       <c r="B33" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3912,43 +3912,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488892</v>
+        <v>488482</v>
       </c>
       <c r="R33" t="n">
-        <v>6786620</v>
+        <v>6786720</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4007,10 +3998,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122566974</v>
+        <v>122567294</v>
       </c>
       <c r="B34" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4019,38 +4010,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488486</v>
+        <v>488801</v>
       </c>
       <c r="R34" t="n">
-        <v>6786718</v>
+        <v>6786563</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4109,10 +4105,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122567020</v>
+        <v>122567030</v>
       </c>
       <c r="B35" t="n">
-        <v>78762</v>
+        <v>78407</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4125,21 +4121,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4149,10 +4145,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488185</v>
+        <v>488769</v>
       </c>
       <c r="R35" t="n">
-        <v>6787005</v>
+        <v>6786552</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4211,10 +4207,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122567030</v>
+        <v>122566908</v>
       </c>
       <c r="B36" t="n">
-        <v>78407</v>
+        <v>57494</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4227,34 +4223,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488769</v>
+        <v>488892</v>
       </c>
       <c r="R36" t="n">
-        <v>6786552</v>
+        <v>6786620</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4313,10 +4318,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122566899</v>
+        <v>122566974</v>
       </c>
       <c r="B37" t="n">
-        <v>57631</v>
+        <v>78762</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4329,21 +4334,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4353,10 +4358,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488482</v>
+        <v>488486</v>
       </c>
       <c r="R37" t="n">
-        <v>6786720</v>
+        <v>6786718</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4415,10 +4420,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567294</v>
+        <v>122567020</v>
       </c>
       <c r="B38" t="n">
-        <v>8441</v>
+        <v>78762</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4427,43 +4432,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488801</v>
+        <v>488185</v>
       </c>
       <c r="R38" t="n">
-        <v>6786563</v>
+        <v>6787005</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4629,10 +4629,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122566998</v>
+        <v>122567321</v>
       </c>
       <c r="B40" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4641,38 +4641,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488700</v>
+        <v>488817</v>
       </c>
       <c r="R40" t="n">
-        <v>6786744</v>
+        <v>6786693</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4731,10 +4736,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567016</v>
+        <v>122567326</v>
       </c>
       <c r="B41" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4743,38 +4748,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488360</v>
+        <v>488545</v>
       </c>
       <c r="R41" t="n">
-        <v>6786913</v>
+        <v>6786849</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4833,7 +4843,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122566954</v>
+        <v>122566998</v>
       </c>
       <c r="B42" t="n">
         <v>78762</v>
@@ -4873,10 +4883,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488416</v>
+        <v>488700</v>
       </c>
       <c r="R42" t="n">
-        <v>6786896</v>
+        <v>6786744</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4935,7 +4945,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122566990</v>
+        <v>122567016</v>
       </c>
       <c r="B43" t="n">
         <v>78762</v>
@@ -4975,10 +4985,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488840</v>
+        <v>488360</v>
       </c>
       <c r="R43" t="n">
-        <v>6786622</v>
+        <v>6786913</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5037,10 +5047,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122566898</v>
+        <v>122566954</v>
       </c>
       <c r="B44" t="n">
-        <v>57631</v>
+        <v>78762</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5053,21 +5063,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5077,10 +5087,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488296</v>
+        <v>488416</v>
       </c>
       <c r="R44" t="n">
-        <v>6786844</v>
+        <v>6786896</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5139,10 +5149,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122567321</v>
+        <v>122566990</v>
       </c>
       <c r="B45" t="n">
-        <v>8441</v>
+        <v>78762</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5151,43 +5161,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488817</v>
+        <v>488840</v>
       </c>
       <c r="R45" t="n">
-        <v>6786693</v>
+        <v>6786622</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5246,10 +5251,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122567326</v>
+        <v>122566898</v>
       </c>
       <c r="B46" t="n">
-        <v>8441</v>
+        <v>57631</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5258,43 +5263,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488545</v>
+        <v>488296</v>
       </c>
       <c r="R46" t="n">
-        <v>6786849</v>
+        <v>6786844</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6281,10 +6281,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122566972</v>
+        <v>122567029</v>
       </c>
       <c r="B56" t="n">
-        <v>78762</v>
+        <v>78407</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6297,21 +6297,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6321,10 +6321,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488465</v>
+        <v>488664</v>
       </c>
       <c r="R56" t="n">
-        <v>6786729</v>
+        <v>6786615</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6383,10 +6383,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567007</v>
+        <v>122566912</v>
       </c>
       <c r="B57" t="n">
-        <v>78762</v>
+        <v>91231</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6399,21 +6399,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6423,10 +6423,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488530</v>
+        <v>488895</v>
       </c>
       <c r="R57" t="n">
-        <v>6786847</v>
+        <v>6786588</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6485,10 +6485,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122567014</v>
+        <v>122567320</v>
       </c>
       <c r="B58" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6497,38 +6497,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488383</v>
+        <v>488833</v>
       </c>
       <c r="R58" t="n">
-        <v>6786912</v>
+        <v>6786674</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6587,10 +6592,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122566985</v>
+        <v>122567295</v>
       </c>
       <c r="B59" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6599,38 +6604,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488698</v>
+        <v>488850</v>
       </c>
       <c r="R59" t="n">
-        <v>6786584</v>
+        <v>6786668</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6689,10 +6699,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122566999</v>
+        <v>122567307</v>
       </c>
       <c r="B60" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6701,38 +6711,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488686</v>
+        <v>488535</v>
       </c>
       <c r="R60" t="n">
-        <v>6786738</v>
+        <v>6786843</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6791,7 +6806,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122567320</v>
+        <v>122567313</v>
       </c>
       <c r="B61" t="n">
         <v>8441</v>
@@ -6836,10 +6851,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488833</v>
+        <v>488616</v>
       </c>
       <c r="R61" t="n">
-        <v>6786674</v>
+        <v>6786649</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6898,10 +6913,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122567295</v>
+        <v>122566972</v>
       </c>
       <c r="B62" t="n">
-        <v>8441</v>
+        <v>78762</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6910,43 +6925,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488850</v>
+        <v>488465</v>
       </c>
       <c r="R62" t="n">
-        <v>6786668</v>
+        <v>6786729</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7005,10 +7015,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122567307</v>
+        <v>122567007</v>
       </c>
       <c r="B63" t="n">
-        <v>8441</v>
+        <v>78762</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7017,43 +7027,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488535</v>
+        <v>488530</v>
       </c>
       <c r="R63" t="n">
-        <v>6786843</v>
+        <v>6786847</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7112,10 +7117,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122567313</v>
+        <v>122567014</v>
       </c>
       <c r="B64" t="n">
-        <v>8441</v>
+        <v>78762</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7124,43 +7129,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488616</v>
+        <v>488383</v>
       </c>
       <c r="R64" t="n">
-        <v>6786649</v>
+        <v>6786912</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7219,10 +7219,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122567029</v>
+        <v>122566985</v>
       </c>
       <c r="B65" t="n">
-        <v>78407</v>
+        <v>78762</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7235,21 +7235,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7259,10 +7259,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488664</v>
+        <v>488698</v>
       </c>
       <c r="R65" t="n">
-        <v>6786615</v>
+        <v>6786584</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7321,10 +7321,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122566912</v>
+        <v>122566999</v>
       </c>
       <c r="B66" t="n">
-        <v>91231</v>
+        <v>78762</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7337,21 +7337,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7361,10 +7361,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488895</v>
+        <v>488686</v>
       </c>
       <c r="R66" t="n">
-        <v>6786588</v>
+        <v>6786738</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8769,10 +8769,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122567027</v>
+        <v>122566957</v>
       </c>
       <c r="B80" t="n">
-        <v>78407</v>
+        <v>78762</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8785,21 +8785,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8809,10 +8809,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488618</v>
+        <v>488300</v>
       </c>
       <c r="R80" t="n">
-        <v>6786631</v>
+        <v>6786820</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8871,10 +8871,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122566957</v>
+        <v>122567027</v>
       </c>
       <c r="B81" t="n">
-        <v>78762</v>
+        <v>78407</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8887,21 +8887,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8911,10 +8911,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488300</v>
+        <v>488618</v>
       </c>
       <c r="R81" t="n">
-        <v>6786820</v>
+        <v>6786631</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9804,10 +9804,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122567026</v>
+        <v>122566903</v>
       </c>
       <c r="B90" t="n">
-        <v>78407</v>
+        <v>90960</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9820,21 +9820,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9844,10 +9844,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488539</v>
+        <v>488770</v>
       </c>
       <c r="R90" t="n">
-        <v>6786689</v>
+        <v>6786732</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9906,10 +9906,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122566903</v>
+        <v>122567026</v>
       </c>
       <c r="B91" t="n">
-        <v>90960</v>
+        <v>78407</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9922,21 +9922,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9946,10 +9946,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488770</v>
+        <v>488539</v>
       </c>
       <c r="R91" t="n">
-        <v>6786732</v>
+        <v>6786689</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10212,10 +10212,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122566901</v>
+        <v>122567006</v>
       </c>
       <c r="B94" t="n">
-        <v>57631</v>
+        <v>78762</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10228,21 +10228,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488142</v>
+        <v>488556</v>
       </c>
       <c r="R94" t="n">
-        <v>6787017</v>
+        <v>6786835</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10314,10 +10314,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122567296</v>
+        <v>122566901</v>
       </c>
       <c r="B95" t="n">
-        <v>8441</v>
+        <v>57631</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10326,43 +10326,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>488834</v>
+        <v>488142</v>
       </c>
       <c r="R95" t="n">
-        <v>6786685</v>
+        <v>6787017</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10421,7 +10416,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122567325</v>
+        <v>122567296</v>
       </c>
       <c r="B96" t="n">
         <v>8441</v>
@@ -10457,7 +10452,7 @@
       <c r="I96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -10466,10 +10461,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>488576</v>
+        <v>488834</v>
       </c>
       <c r="R96" t="n">
-        <v>6786782</v>
+        <v>6786685</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10528,10 +10523,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122567006</v>
+        <v>122567325</v>
       </c>
       <c r="B97" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10540,38 +10535,43 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>488556</v>
+        <v>488576</v>
       </c>
       <c r="R97" t="n">
-        <v>6786835</v>
+        <v>6786782</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -13006,10 +13006,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122567314</v>
+        <v>122566905</v>
       </c>
       <c r="B121" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13018,31 +13018,31 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -13051,10 +13051,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488747</v>
+        <v>488294</v>
       </c>
       <c r="R121" t="n">
-        <v>6786566</v>
+        <v>6786826</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13113,10 +13113,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122567312</v>
+        <v>122566971</v>
       </c>
       <c r="B122" t="n">
-        <v>8441</v>
+        <v>78762</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13125,43 +13125,38 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488341</v>
+        <v>488461</v>
       </c>
       <c r="R122" t="n">
-        <v>6786832</v>
+        <v>6786736</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13220,10 +13215,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122567306</v>
+        <v>122567017</v>
       </c>
       <c r="B123" t="n">
-        <v>8441</v>
+        <v>78762</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13232,43 +13227,38 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>488556</v>
+        <v>488353</v>
       </c>
       <c r="R123" t="n">
-        <v>6786835</v>
+        <v>6786911</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13327,10 +13317,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122567303</v>
+        <v>122566960</v>
       </c>
       <c r="B124" t="n">
-        <v>8441</v>
+        <v>78762</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13339,43 +13329,38 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>488600</v>
+        <v>488322</v>
       </c>
       <c r="R124" t="n">
-        <v>6786772</v>
+        <v>6786853</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13434,10 +13419,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122567323</v>
+        <v>122567018</v>
       </c>
       <c r="B125" t="n">
-        <v>8441</v>
+        <v>78762</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13446,43 +13431,38 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>488686</v>
+        <v>488345</v>
       </c>
       <c r="R125" t="n">
-        <v>6786745</v>
+        <v>6786910</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13541,10 +13521,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122566905</v>
+        <v>122566890</v>
       </c>
       <c r="B126" t="n">
-        <v>57494</v>
+        <v>79380</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13557,39 +13537,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>488294</v>
+        <v>488572</v>
       </c>
       <c r="R126" t="n">
-        <v>6786826</v>
+        <v>6786674</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13648,7 +13623,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122566971</v>
+        <v>122567002</v>
       </c>
       <c r="B127" t="n">
         <v>78762</v>
@@ -13688,10 +13663,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>488461</v>
+        <v>488569</v>
       </c>
       <c r="R127" t="n">
-        <v>6786736</v>
+        <v>6786787</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13750,10 +13725,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122567017</v>
+        <v>122567314</v>
       </c>
       <c r="B128" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13762,38 +13737,43 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>488353</v>
+        <v>488747</v>
       </c>
       <c r="R128" t="n">
-        <v>6786911</v>
+        <v>6786566</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13852,10 +13832,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122566960</v>
+        <v>122567312</v>
       </c>
       <c r="B129" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13864,38 +13844,43 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>488322</v>
+        <v>488341</v>
       </c>
       <c r="R129" t="n">
-        <v>6786853</v>
+        <v>6786832</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13954,10 +13939,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122567018</v>
+        <v>122567306</v>
       </c>
       <c r="B130" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13966,38 +13951,43 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>488345</v>
+        <v>488556</v>
       </c>
       <c r="R130" t="n">
-        <v>6786910</v>
+        <v>6786835</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14056,10 +14046,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122566890</v>
+        <v>122567303</v>
       </c>
       <c r="B131" t="n">
-        <v>79380</v>
+        <v>8441</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14068,38 +14058,43 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>488572</v>
+        <v>488600</v>
       </c>
       <c r="R131" t="n">
-        <v>6786674</v>
+        <v>6786772</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14158,10 +14153,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122567002</v>
+        <v>122567323</v>
       </c>
       <c r="B132" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14170,38 +14165,43 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>488569</v>
+        <v>488686</v>
       </c>
       <c r="R132" t="n">
-        <v>6786787</v>
+        <v>6786745</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>

--- a/artfynd/A 61338-2024 artfynd.xlsx
+++ b/artfynd/A 61338-2024 artfynd.xlsx
@@ -2220,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566953</v>
+        <v>122566997</v>
       </c>
       <c r="B17" t="n">
-        <v>98347</v>
+        <v>78762</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2232,47 +2232,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488429</v>
+        <v>488731</v>
       </c>
       <c r="R17" t="n">
-        <v>6786896</v>
+        <v>6786733</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566997</v>
+        <v>122566892</v>
       </c>
       <c r="B18" t="n">
-        <v>78762</v>
+        <v>79380</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2347,21 +2338,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2371,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488731</v>
+        <v>488699</v>
       </c>
       <c r="R18" t="n">
-        <v>6786733</v>
+        <v>6786599</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2433,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566892</v>
+        <v>122566967</v>
       </c>
       <c r="B19" t="n">
-        <v>79380</v>
+        <v>78762</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,21 +2440,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488699</v>
+        <v>488387</v>
       </c>
       <c r="R19" t="n">
-        <v>6786599</v>
+        <v>6786773</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566967</v>
+        <v>122566953</v>
       </c>
       <c r="B20" t="n">
-        <v>78762</v>
+        <v>98347</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,38 +2538,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488387</v>
+        <v>488429</v>
       </c>
       <c r="R20" t="n">
-        <v>6786773</v>
+        <v>6786896</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3896,10 +3896,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122566899</v>
+        <v>122566908</v>
       </c>
       <c r="B33" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3912,34 +3912,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488482</v>
+        <v>488892</v>
       </c>
       <c r="R33" t="n">
-        <v>6786720</v>
+        <v>6786620</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3998,10 +4007,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567294</v>
+        <v>122566974</v>
       </c>
       <c r="B34" t="n">
-        <v>8441</v>
+        <v>78762</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4010,43 +4019,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488801</v>
+        <v>488486</v>
       </c>
       <c r="R34" t="n">
-        <v>6786563</v>
+        <v>6786718</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4105,10 +4109,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122567030</v>
+        <v>122567020</v>
       </c>
       <c r="B35" t="n">
-        <v>78407</v>
+        <v>78762</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4121,21 +4125,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4145,10 +4149,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488769</v>
+        <v>488185</v>
       </c>
       <c r="R35" t="n">
-        <v>6786552</v>
+        <v>6787005</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4207,10 +4211,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122566908</v>
+        <v>122567030</v>
       </c>
       <c r="B36" t="n">
-        <v>57494</v>
+        <v>78407</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4223,43 +4227,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488892</v>
+        <v>488769</v>
       </c>
       <c r="R36" t="n">
-        <v>6786620</v>
+        <v>6786552</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4318,10 +4313,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122566974</v>
+        <v>122566899</v>
       </c>
       <c r="B37" t="n">
-        <v>78762</v>
+        <v>57631</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4334,21 +4329,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4358,10 +4353,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488486</v>
+        <v>488482</v>
       </c>
       <c r="R37" t="n">
-        <v>6786718</v>
+        <v>6786720</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4420,10 +4415,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567020</v>
+        <v>122567294</v>
       </c>
       <c r="B38" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4432,38 +4427,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488185</v>
+        <v>488801</v>
       </c>
       <c r="R38" t="n">
-        <v>6787005</v>
+        <v>6786563</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -8351,10 +8351,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122566978</v>
+        <v>122567301</v>
       </c>
       <c r="B76" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8363,38 +8363,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488583</v>
+        <v>488718</v>
       </c>
       <c r="R76" t="n">
-        <v>6786679</v>
+        <v>6786752</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8453,10 +8458,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122566897</v>
+        <v>122567324</v>
       </c>
       <c r="B77" t="n">
-        <v>90940</v>
+        <v>8441</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8465,38 +8470,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488892</v>
+        <v>488638</v>
       </c>
       <c r="R77" t="n">
-        <v>6786591</v>
+        <v>6786764</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8555,10 +8565,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122567301</v>
+        <v>122566897</v>
       </c>
       <c r="B78" t="n">
-        <v>8441</v>
+        <v>90940</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8567,43 +8577,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488718</v>
+        <v>488892</v>
       </c>
       <c r="R78" t="n">
-        <v>6786752</v>
+        <v>6786591</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8662,10 +8667,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122567324</v>
+        <v>122566978</v>
       </c>
       <c r="B79" t="n">
-        <v>8441</v>
+        <v>78762</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8674,43 +8679,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488638</v>
+        <v>488583</v>
       </c>
       <c r="R79" t="n">
-        <v>6786764</v>
+        <v>6786679</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -13006,10 +13006,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122566905</v>
+        <v>122567314</v>
       </c>
       <c r="B121" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13018,31 +13018,31 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -13051,10 +13051,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488294</v>
+        <v>488747</v>
       </c>
       <c r="R121" t="n">
-        <v>6786826</v>
+        <v>6786566</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13113,10 +13113,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122566971</v>
+        <v>122567312</v>
       </c>
       <c r="B122" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13125,38 +13125,43 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488461</v>
+        <v>488341</v>
       </c>
       <c r="R122" t="n">
-        <v>6786736</v>
+        <v>6786832</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13215,10 +13220,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122567017</v>
+        <v>122567306</v>
       </c>
       <c r="B123" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13227,38 +13232,43 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>488353</v>
+        <v>488556</v>
       </c>
       <c r="R123" t="n">
-        <v>6786911</v>
+        <v>6786835</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13317,10 +13327,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122566960</v>
+        <v>122567303</v>
       </c>
       <c r="B124" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13329,38 +13339,43 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>488322</v>
+        <v>488600</v>
       </c>
       <c r="R124" t="n">
-        <v>6786853</v>
+        <v>6786772</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13419,10 +13434,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122567018</v>
+        <v>122567323</v>
       </c>
       <c r="B125" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13431,38 +13446,43 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>488345</v>
+        <v>488686</v>
       </c>
       <c r="R125" t="n">
-        <v>6786910</v>
+        <v>6786745</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13521,10 +13541,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122566890</v>
+        <v>122566905</v>
       </c>
       <c r="B126" t="n">
-        <v>79380</v>
+        <v>57494</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13537,34 +13557,39 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>488572</v>
+        <v>488294</v>
       </c>
       <c r="R126" t="n">
-        <v>6786674</v>
+        <v>6786826</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13623,7 +13648,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122567002</v>
+        <v>122566971</v>
       </c>
       <c r="B127" t="n">
         <v>78762</v>
@@ -13663,10 +13688,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>488569</v>
+        <v>488461</v>
       </c>
       <c r="R127" t="n">
-        <v>6786787</v>
+        <v>6786736</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13725,10 +13750,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122567314</v>
+        <v>122567017</v>
       </c>
       <c r="B128" t="n">
-        <v>8441</v>
+        <v>78762</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13737,43 +13762,38 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>488747</v>
+        <v>488353</v>
       </c>
       <c r="R128" t="n">
-        <v>6786566</v>
+        <v>6786911</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13832,10 +13852,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122567312</v>
+        <v>122566960</v>
       </c>
       <c r="B129" t="n">
-        <v>8441</v>
+        <v>78762</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13844,43 +13864,38 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>488341</v>
+        <v>488322</v>
       </c>
       <c r="R129" t="n">
-        <v>6786832</v>
+        <v>6786853</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13939,10 +13954,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122567306</v>
+        <v>122567018</v>
       </c>
       <c r="B130" t="n">
-        <v>8441</v>
+        <v>78762</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13951,43 +13966,38 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>488556</v>
+        <v>488345</v>
       </c>
       <c r="R130" t="n">
-        <v>6786835</v>
+        <v>6786910</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14046,10 +14056,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122567303</v>
+        <v>122566890</v>
       </c>
       <c r="B131" t="n">
-        <v>8441</v>
+        <v>79380</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14058,43 +14068,38 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>488600</v>
+        <v>488572</v>
       </c>
       <c r="R131" t="n">
-        <v>6786772</v>
+        <v>6786674</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14153,10 +14158,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122567323</v>
+        <v>122567002</v>
       </c>
       <c r="B132" t="n">
-        <v>8441</v>
+        <v>78762</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14165,43 +14170,38 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>488686</v>
+        <v>488569</v>
       </c>
       <c r="R132" t="n">
-        <v>6786745</v>
+        <v>6786787</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>

--- a/artfynd/A 61338-2024 artfynd.xlsx
+++ b/artfynd/A 61338-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122566976</v>
+        <v>122567289</v>
       </c>
       <c r="B2" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488515</v>
+        <v>488322</v>
       </c>
       <c r="R2" t="n">
-        <v>6786685</v>
+        <v>6786810</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567013</v>
+        <v>122566953</v>
       </c>
       <c r="B3" t="n">
-        <v>78762</v>
+        <v>98355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +794,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488389</v>
+        <v>488429</v>
       </c>
       <c r="R3" t="n">
-        <v>6786901</v>
+        <v>6786896</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567289</v>
+        <v>122567028</v>
       </c>
       <c r="B4" t="n">
-        <v>8441</v>
+        <v>78411</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,43 +905,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488322</v>
+        <v>488611</v>
       </c>
       <c r="R4" t="n">
-        <v>6786810</v>
+        <v>6786649</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122566966</v>
+        <v>122566996</v>
       </c>
       <c r="B5" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488390</v>
+        <v>488757</v>
       </c>
       <c r="R5" t="n">
-        <v>6786813</v>
+        <v>6786723</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566988</v>
+        <v>122566983</v>
       </c>
       <c r="B6" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488803</v>
+        <v>488609</v>
       </c>
       <c r="R6" t="n">
-        <v>6786562</v>
+        <v>6786648</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566959</v>
+        <v>122567018</v>
       </c>
       <c r="B7" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488317</v>
+        <v>488345</v>
       </c>
       <c r="R7" t="n">
-        <v>6786858</v>
+        <v>6786910</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567005</v>
+        <v>122566958</v>
       </c>
       <c r="B8" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488415</v>
+        <v>488301</v>
       </c>
       <c r="R8" t="n">
-        <v>6786889</v>
+        <v>6786839</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566994</v>
+        <v>122566896</v>
       </c>
       <c r="B9" t="n">
-        <v>78762</v>
+        <v>90944</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488883</v>
+        <v>488882</v>
       </c>
       <c r="R9" t="n">
-        <v>6786645</v>
+        <v>6786607</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566981</v>
+        <v>122566911</v>
       </c>
       <c r="B10" t="n">
-        <v>78762</v>
+        <v>91235</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1521,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488599</v>
+        <v>488882</v>
       </c>
       <c r="R10" t="n">
-        <v>6786673</v>
+        <v>6786609</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1607,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567011</v>
+        <v>122566890</v>
       </c>
       <c r="B11" t="n">
-        <v>78762</v>
+        <v>79384</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1623,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1647,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488427</v>
+        <v>488572</v>
       </c>
       <c r="R11" t="n">
-        <v>6786888</v>
+        <v>6786674</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567032</v>
+        <v>122566954</v>
       </c>
       <c r="B12" t="n">
-        <v>5173</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,43 +1721,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488901</v>
+        <v>488416</v>
       </c>
       <c r="R12" t="n">
-        <v>6786589</v>
+        <v>6786896</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566979</v>
+        <v>122566960</v>
       </c>
       <c r="B13" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1847,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488583</v>
+        <v>488322</v>
       </c>
       <c r="R13" t="n">
-        <v>6786676</v>
+        <v>6786853</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,10 +1913,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566964</v>
+        <v>122566976</v>
       </c>
       <c r="B14" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1949,10 +1953,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488351</v>
+        <v>488515</v>
       </c>
       <c r="R14" t="n">
-        <v>6786831</v>
+        <v>6786685</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2015,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567003</v>
+        <v>122567017</v>
       </c>
       <c r="B15" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2051,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488550</v>
+        <v>488353</v>
       </c>
       <c r="R15" t="n">
-        <v>6786822</v>
+        <v>6786911</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2117,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567315</v>
+        <v>122567019</v>
       </c>
       <c r="B16" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2125,43 +2129,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488773</v>
+        <v>488297</v>
       </c>
       <c r="R16" t="n">
-        <v>6786561</v>
+        <v>6786946</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,10 +2219,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566997</v>
+        <v>122567308</v>
       </c>
       <c r="B17" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2232,38 +2231,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488731</v>
+        <v>488669</v>
       </c>
       <c r="R17" t="n">
-        <v>6786733</v>
+        <v>6786761</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,10 +2326,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566892</v>
+        <v>122567300</v>
       </c>
       <c r="B18" t="n">
-        <v>79380</v>
+        <v>8441</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2334,38 +2338,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488699</v>
+        <v>488768</v>
       </c>
       <c r="R18" t="n">
-        <v>6786599</v>
+        <v>6786742</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,10 +2433,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566967</v>
+        <v>122567294</v>
       </c>
       <c r="B19" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2436,38 +2445,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488387</v>
+        <v>488801</v>
       </c>
       <c r="R19" t="n">
-        <v>6786773</v>
+        <v>6786563</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,10 +2540,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566953</v>
+        <v>122567016</v>
       </c>
       <c r="B20" t="n">
-        <v>98347</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2538,47 +2552,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488429</v>
+        <v>488360</v>
       </c>
       <c r="R20" t="n">
-        <v>6786896</v>
+        <v>6786913</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2637,10 +2642,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567316</v>
+        <v>122566997</v>
       </c>
       <c r="B21" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2649,43 +2654,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488900</v>
+        <v>488731</v>
       </c>
       <c r="R21" t="n">
-        <v>6786628</v>
+        <v>6786733</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,10 +2744,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567299</v>
+        <v>122567022</v>
       </c>
       <c r="B22" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2756,43 +2756,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488786</v>
+        <v>488137</v>
       </c>
       <c r="R22" t="n">
-        <v>6786723</v>
+        <v>6787026</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2851,10 +2846,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567327</v>
+        <v>122566959</v>
       </c>
       <c r="B23" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2863,43 +2858,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488442</v>
+        <v>488317</v>
       </c>
       <c r="R23" t="n">
-        <v>6786881</v>
+        <v>6786858</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2958,10 +2948,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566904</v>
+        <v>122566902</v>
       </c>
       <c r="B24" t="n">
-        <v>90960</v>
+        <v>90964</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2998,10 +2988,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488552</v>
+        <v>488397</v>
       </c>
       <c r="R24" t="n">
-        <v>6786834</v>
+        <v>6786809</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3060,10 +3050,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566969</v>
+        <v>122566909</v>
       </c>
       <c r="B25" t="n">
-        <v>78762</v>
+        <v>91389</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3072,25 +3062,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3100,10 +3090,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488452</v>
+        <v>488882</v>
       </c>
       <c r="R25" t="n">
-        <v>6786772</v>
+        <v>6786607</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3162,10 +3152,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567023</v>
+        <v>122566907</v>
       </c>
       <c r="B26" t="n">
-        <v>78762</v>
+        <v>57494</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3178,34 +3168,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488135</v>
+        <v>488852</v>
       </c>
       <c r="R26" t="n">
-        <v>6787033</v>
+        <v>6786673</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3264,7 +3259,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122567308</v>
+        <v>122567306</v>
       </c>
       <c r="B27" t="n">
         <v>8441</v>
@@ -3300,7 +3295,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3309,10 +3304,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488669</v>
+        <v>488556</v>
       </c>
       <c r="R27" t="n">
-        <v>6786761</v>
+        <v>6786835</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3371,10 +3366,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567304</v>
+        <v>122566901</v>
       </c>
       <c r="B28" t="n">
-        <v>8441</v>
+        <v>57631</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3383,43 +3378,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488591</v>
+        <v>488142</v>
       </c>
       <c r="R28" t="n">
-        <v>6786769</v>
+        <v>6787017</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3478,10 +3468,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567305</v>
+        <v>122566998</v>
       </c>
       <c r="B29" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3490,43 +3480,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488519</v>
+        <v>488700</v>
       </c>
       <c r="R29" t="n">
-        <v>6786844</v>
+        <v>6786744</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3585,10 +3570,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567311</v>
+        <v>122566972</v>
       </c>
       <c r="B30" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3597,43 +3582,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488332</v>
+        <v>488465</v>
       </c>
       <c r="R30" t="n">
-        <v>6786824</v>
+        <v>6786729</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3692,10 +3672,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122566896</v>
+        <v>122566965</v>
       </c>
       <c r="B31" t="n">
-        <v>90940</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3708,21 +3688,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3732,10 +3712,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488882</v>
+        <v>488378</v>
       </c>
       <c r="R31" t="n">
-        <v>6786607</v>
+        <v>6786805</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3794,10 +3774,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122566902</v>
+        <v>122566995</v>
       </c>
       <c r="B32" t="n">
-        <v>90960</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3810,21 +3790,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3834,10 +3814,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488397</v>
+        <v>488833</v>
       </c>
       <c r="R32" t="n">
-        <v>6786809</v>
+        <v>6786674</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3896,10 +3876,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122566908</v>
+        <v>122566999</v>
       </c>
       <c r="B33" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3912,43 +3892,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488892</v>
+        <v>488686</v>
       </c>
       <c r="R33" t="n">
-        <v>6786620</v>
+        <v>6786738</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4007,10 +3978,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122566974</v>
+        <v>122566964</v>
       </c>
       <c r="B34" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4047,10 +4018,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488486</v>
+        <v>488351</v>
       </c>
       <c r="R34" t="n">
-        <v>6786718</v>
+        <v>6786831</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4109,10 +4080,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122567020</v>
+        <v>122566905</v>
       </c>
       <c r="B35" t="n">
-        <v>78762</v>
+        <v>57494</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4125,34 +4096,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488185</v>
+        <v>488294</v>
       </c>
       <c r="R35" t="n">
-        <v>6787005</v>
+        <v>6786826</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4211,10 +4187,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122567030</v>
+        <v>122566987</v>
       </c>
       <c r="B36" t="n">
-        <v>78407</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4227,21 +4203,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4251,10 +4227,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488769</v>
+        <v>488735</v>
       </c>
       <c r="R36" t="n">
-        <v>6786552</v>
+        <v>6786569</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4313,10 +4289,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122566899</v>
+        <v>122567007</v>
       </c>
       <c r="B37" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4329,21 +4305,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4353,10 +4329,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488482</v>
+        <v>488530</v>
       </c>
       <c r="R37" t="n">
-        <v>6786720</v>
+        <v>6786847</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4415,7 +4391,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567294</v>
+        <v>122567292</v>
       </c>
       <c r="B38" t="n">
         <v>8441</v>
@@ -4460,10 +4436,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488801</v>
+        <v>488533</v>
       </c>
       <c r="R38" t="n">
-        <v>6786563</v>
+        <v>6786690</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4522,10 +4498,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122566907</v>
+        <v>122567327</v>
       </c>
       <c r="B39" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4534,31 +4510,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4567,10 +4543,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488852</v>
+        <v>488442</v>
       </c>
       <c r="R39" t="n">
-        <v>6786673</v>
+        <v>6786881</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4629,7 +4605,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122567321</v>
+        <v>122567317</v>
       </c>
       <c r="B40" t="n">
         <v>8441</v>
@@ -4674,10 +4650,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488817</v>
+        <v>488892</v>
       </c>
       <c r="R40" t="n">
-        <v>6786693</v>
+        <v>6786620</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4736,10 +4712,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567326</v>
+        <v>122566980</v>
       </c>
       <c r="B41" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4748,43 +4724,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488545</v>
+        <v>488590</v>
       </c>
       <c r="R41" t="n">
-        <v>6786849</v>
+        <v>6786665</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4843,10 +4814,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122566998</v>
+        <v>122566956</v>
       </c>
       <c r="B42" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4883,10 +4854,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488700</v>
+        <v>488309</v>
       </c>
       <c r="R42" t="n">
-        <v>6786744</v>
+        <v>6786859</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4945,10 +4916,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567016</v>
+        <v>122566961</v>
       </c>
       <c r="B43" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4985,10 +4956,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488360</v>
+        <v>488327</v>
       </c>
       <c r="R43" t="n">
-        <v>6786913</v>
+        <v>6786847</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5047,10 +5018,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122566954</v>
+        <v>122566978</v>
       </c>
       <c r="B44" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5087,10 +5058,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488416</v>
+        <v>488583</v>
       </c>
       <c r="R44" t="n">
-        <v>6786896</v>
+        <v>6786679</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5149,10 +5120,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122566990</v>
+        <v>122567009</v>
       </c>
       <c r="B45" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5189,10 +5160,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488840</v>
+        <v>488465</v>
       </c>
       <c r="R45" t="n">
-        <v>6786622</v>
+        <v>6786880</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5251,10 +5222,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122566898</v>
+        <v>122567015</v>
       </c>
       <c r="B46" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5267,21 +5238,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5291,10 +5262,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488296</v>
+        <v>488366</v>
       </c>
       <c r="R46" t="n">
-        <v>6786844</v>
+        <v>6786907</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5353,10 +5324,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122566958</v>
+        <v>122566957</v>
       </c>
       <c r="B47" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5393,10 +5364,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488301</v>
+        <v>488300</v>
       </c>
       <c r="R47" t="n">
-        <v>6786839</v>
+        <v>6786820</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5455,10 +5426,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122566889</v>
+        <v>122567298</v>
       </c>
       <c r="B48" t="n">
-        <v>79380</v>
+        <v>8441</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5467,38 +5438,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488296</v>
+        <v>488789</v>
       </c>
       <c r="R48" t="n">
-        <v>6786844</v>
+        <v>6786702</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5557,10 +5533,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122566991</v>
+        <v>122567307</v>
       </c>
       <c r="B49" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5569,38 +5545,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488918</v>
+        <v>488535</v>
       </c>
       <c r="R49" t="n">
-        <v>6786607</v>
+        <v>6786843</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5659,10 +5640,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122567300</v>
+        <v>122566912</v>
       </c>
       <c r="B50" t="n">
-        <v>8441</v>
+        <v>91235</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5671,43 +5652,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488768</v>
+        <v>488895</v>
       </c>
       <c r="R50" t="n">
-        <v>6786742</v>
+        <v>6786588</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5766,10 +5742,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567298</v>
+        <v>122566908</v>
       </c>
       <c r="B51" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5778,31 +5754,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5811,10 +5791,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488789</v>
+        <v>488892</v>
       </c>
       <c r="R51" t="n">
-        <v>6786702</v>
+        <v>6786620</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5873,10 +5853,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567028</v>
+        <v>122567027</v>
       </c>
       <c r="B52" t="n">
-        <v>78407</v>
+        <v>78411</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5913,10 +5893,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488611</v>
+        <v>488618</v>
       </c>
       <c r="R52" t="n">
-        <v>6786649</v>
+        <v>6786631</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5975,10 +5955,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122566891</v>
+        <v>122567004</v>
       </c>
       <c r="B53" t="n">
-        <v>79380</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5991,21 +5971,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6015,10 +5995,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488616</v>
+        <v>488475</v>
       </c>
       <c r="R53" t="n">
-        <v>6786648</v>
+        <v>6786864</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6077,10 +6057,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567004</v>
+        <v>122566889</v>
       </c>
       <c r="B54" t="n">
-        <v>78762</v>
+        <v>79384</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6093,21 +6073,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6117,10 +6097,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488475</v>
+        <v>488296</v>
       </c>
       <c r="R54" t="n">
-        <v>6786864</v>
+        <v>6786844</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6179,10 +6159,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122567019</v>
+        <v>122567290</v>
       </c>
       <c r="B55" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6191,38 +6171,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488297</v>
+        <v>488345</v>
       </c>
       <c r="R55" t="n">
-        <v>6786946</v>
+        <v>6786796</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6281,10 +6266,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122567029</v>
+        <v>122567297</v>
       </c>
       <c r="B56" t="n">
-        <v>78407</v>
+        <v>8441</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6293,38 +6278,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488664</v>
+        <v>488804</v>
       </c>
       <c r="R56" t="n">
-        <v>6786615</v>
+        <v>6786700</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6383,10 +6373,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122566912</v>
+        <v>122567325</v>
       </c>
       <c r="B57" t="n">
-        <v>91231</v>
+        <v>8441</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6395,38 +6385,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488895</v>
+        <v>488576</v>
       </c>
       <c r="R57" t="n">
-        <v>6786588</v>
+        <v>6786782</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6485,7 +6480,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122567320</v>
+        <v>122567318</v>
       </c>
       <c r="B58" t="n">
         <v>8441</v>
@@ -6530,10 +6525,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488833</v>
+        <v>488883</v>
       </c>
       <c r="R58" t="n">
-        <v>6786674</v>
+        <v>6786645</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6592,10 +6587,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122567295</v>
+        <v>122566971</v>
       </c>
       <c r="B59" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6604,43 +6599,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488850</v>
+        <v>488461</v>
       </c>
       <c r="R59" t="n">
-        <v>6786668</v>
+        <v>6786736</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6699,10 +6689,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122567307</v>
+        <v>122567008</v>
       </c>
       <c r="B60" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6711,43 +6701,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488535</v>
+        <v>488495</v>
       </c>
       <c r="R60" t="n">
-        <v>6786843</v>
+        <v>6786888</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6806,10 +6791,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122567313</v>
+        <v>122566967</v>
       </c>
       <c r="B61" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6818,43 +6803,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488616</v>
+        <v>488387</v>
       </c>
       <c r="R61" t="n">
-        <v>6786649</v>
+        <v>6786773</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6913,10 +6893,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122566972</v>
+        <v>122566962</v>
       </c>
       <c r="B62" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6953,10 +6933,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488465</v>
+        <v>488324</v>
       </c>
       <c r="R62" t="n">
-        <v>6786729</v>
+        <v>6786843</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7015,10 +6995,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122567007</v>
+        <v>122567012</v>
       </c>
       <c r="B63" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7055,10 +7035,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488530</v>
+        <v>488420</v>
       </c>
       <c r="R63" t="n">
-        <v>6786847</v>
+        <v>6786898</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7117,10 +7097,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122567014</v>
+        <v>122567003</v>
       </c>
       <c r="B64" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7157,10 +7137,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488383</v>
+        <v>488550</v>
       </c>
       <c r="R64" t="n">
-        <v>6786912</v>
+        <v>6786822</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7219,10 +7199,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122566985</v>
+        <v>122566904</v>
       </c>
       <c r="B65" t="n">
-        <v>78762</v>
+        <v>90964</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7235,21 +7215,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7259,10 +7239,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488698</v>
+        <v>488552</v>
       </c>
       <c r="R65" t="n">
-        <v>6786584</v>
+        <v>6786834</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7321,10 +7301,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122566999</v>
+        <v>122566969</v>
       </c>
       <c r="B66" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7361,10 +7341,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488686</v>
+        <v>488452</v>
       </c>
       <c r="R66" t="n">
-        <v>6786738</v>
+        <v>6786772</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7423,10 +7403,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122567317</v>
+        <v>122567000</v>
       </c>
       <c r="B67" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7435,43 +7415,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488892</v>
+        <v>488678</v>
       </c>
       <c r="R67" t="n">
-        <v>6786620</v>
+        <v>6786753</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7530,10 +7505,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122566952</v>
+        <v>122567006</v>
       </c>
       <c r="B68" t="n">
-        <v>80719</v>
+        <v>78766</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7546,21 +7521,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7570,10 +7545,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488363</v>
+        <v>488556</v>
       </c>
       <c r="R68" t="n">
-        <v>6786907</v>
+        <v>6786835</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7632,10 +7607,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122566984</v>
+        <v>122567026</v>
       </c>
       <c r="B69" t="n">
-        <v>78762</v>
+        <v>78411</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7648,21 +7623,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7672,10 +7647,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488699</v>
+        <v>488539</v>
       </c>
       <c r="R69" t="n">
-        <v>6786596</v>
+        <v>6786689</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7734,10 +7709,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122566980</v>
+        <v>122566892</v>
       </c>
       <c r="B70" t="n">
-        <v>78762</v>
+        <v>79384</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7750,21 +7725,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7774,10 +7749,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488590</v>
+        <v>488699</v>
       </c>
       <c r="R70" t="n">
-        <v>6786665</v>
+        <v>6786599</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7836,10 +7811,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122567022</v>
+        <v>122567304</v>
       </c>
       <c r="B71" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7848,38 +7823,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488137</v>
+        <v>488591</v>
       </c>
       <c r="R71" t="n">
-        <v>6787026</v>
+        <v>6786769</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7938,10 +7918,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122566894</v>
+        <v>122567311</v>
       </c>
       <c r="B72" t="n">
-        <v>79380</v>
+        <v>8441</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7950,38 +7930,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488182</v>
+        <v>488332</v>
       </c>
       <c r="R72" t="n">
-        <v>6787001</v>
+        <v>6786824</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8040,7 +8025,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122567291</v>
+        <v>122567316</v>
       </c>
       <c r="B73" t="n">
         <v>8441</v>
@@ -8076,7 +8061,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8085,10 +8070,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488440</v>
+        <v>488900</v>
       </c>
       <c r="R73" t="n">
-        <v>6786759</v>
+        <v>6786628</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8147,10 +8132,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122566996</v>
+        <v>122567029</v>
       </c>
       <c r="B74" t="n">
-        <v>78762</v>
+        <v>78411</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8163,21 +8148,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8187,10 +8172,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488757</v>
+        <v>488664</v>
       </c>
       <c r="R74" t="n">
-        <v>6786723</v>
+        <v>6786615</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8249,10 +8234,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122567008</v>
+        <v>122566973</v>
       </c>
       <c r="B75" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8289,10 +8274,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488495</v>
+        <v>488482</v>
       </c>
       <c r="R75" t="n">
-        <v>6786888</v>
+        <v>6786720</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8351,10 +8336,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122567301</v>
+        <v>122566990</v>
       </c>
       <c r="B76" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8363,43 +8348,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488718</v>
+        <v>488840</v>
       </c>
       <c r="R76" t="n">
-        <v>6786752</v>
+        <v>6786622</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8458,10 +8438,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122567324</v>
+        <v>122566968</v>
       </c>
       <c r="B77" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8470,43 +8450,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488638</v>
+        <v>488431</v>
       </c>
       <c r="R77" t="n">
-        <v>6786764</v>
+        <v>6786772</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8565,10 +8540,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122566897</v>
+        <v>122566963</v>
       </c>
       <c r="B78" t="n">
-        <v>90940</v>
+        <v>78766</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8581,21 +8556,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8605,10 +8580,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488892</v>
+        <v>488341</v>
       </c>
       <c r="R78" t="n">
-        <v>6786591</v>
+        <v>6786832</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8667,10 +8642,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122566978</v>
+        <v>122567310</v>
       </c>
       <c r="B79" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8679,38 +8654,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488583</v>
+        <v>488294</v>
       </c>
       <c r="R79" t="n">
-        <v>6786679</v>
+        <v>6786825</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8769,10 +8749,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122566957</v>
+        <v>122567313</v>
       </c>
       <c r="B80" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8781,38 +8761,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488300</v>
+        <v>488616</v>
       </c>
       <c r="R80" t="n">
-        <v>6786820</v>
+        <v>6786649</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8871,10 +8856,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122567027</v>
+        <v>122567314</v>
       </c>
       <c r="B81" t="n">
-        <v>78407</v>
+        <v>8441</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8883,38 +8868,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488618</v>
+        <v>488747</v>
       </c>
       <c r="R81" t="n">
-        <v>6786631</v>
+        <v>6786566</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8973,7 +8963,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122567309</v>
+        <v>122567319</v>
       </c>
       <c r="B82" t="n">
         <v>8441</v>
@@ -9018,10 +9008,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488707</v>
+        <v>488869</v>
       </c>
       <c r="R82" t="n">
-        <v>6786747</v>
+        <v>6786685</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9080,7 +9070,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122567318</v>
+        <v>122567321</v>
       </c>
       <c r="B83" t="n">
         <v>8441</v>
@@ -9125,10 +9115,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488883</v>
+        <v>488817</v>
       </c>
       <c r="R83" t="n">
-        <v>6786645</v>
+        <v>6786693</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9187,10 +9177,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122566911</v>
+        <v>122566986</v>
       </c>
       <c r="B84" t="n">
-        <v>91231</v>
+        <v>78766</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9203,21 +9193,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9227,10 +9217,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488882</v>
+        <v>488714</v>
       </c>
       <c r="R84" t="n">
-        <v>6786609</v>
+        <v>6786574</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9289,10 +9279,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122566962</v>
+        <v>122566970</v>
       </c>
       <c r="B85" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9329,10 +9319,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488324</v>
+        <v>488469</v>
       </c>
       <c r="R85" t="n">
-        <v>6786843</v>
+        <v>6786751</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9391,10 +9381,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122566956</v>
+        <v>122567296</v>
       </c>
       <c r="B86" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9403,38 +9393,43 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488309</v>
+        <v>488834</v>
       </c>
       <c r="R86" t="n">
-        <v>6786859</v>
+        <v>6786685</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9493,10 +9488,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122567012</v>
+        <v>122567291</v>
       </c>
       <c r="B87" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9505,38 +9500,43 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488420</v>
+        <v>488440</v>
       </c>
       <c r="R87" t="n">
-        <v>6786898</v>
+        <v>6786759</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9595,10 +9595,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122566893</v>
+        <v>122567322</v>
       </c>
       <c r="B88" t="n">
-        <v>79380</v>
+        <v>8441</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9607,38 +9607,43 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488693</v>
+        <v>488700</v>
       </c>
       <c r="R88" t="n">
-        <v>6786741</v>
+        <v>6786746</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9697,10 +9702,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122567319</v>
+        <v>122566994</v>
       </c>
       <c r="B89" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9709,43 +9714,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488869</v>
+        <v>488883</v>
       </c>
       <c r="R89" t="n">
-        <v>6786685</v>
+        <v>6786645</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9804,10 +9804,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122566903</v>
+        <v>122567312</v>
       </c>
       <c r="B90" t="n">
-        <v>90960</v>
+        <v>8441</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9816,38 +9816,43 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488770</v>
+        <v>488341</v>
       </c>
       <c r="R90" t="n">
-        <v>6786732</v>
+        <v>6786832</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9906,10 +9911,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122567026</v>
+        <v>122567299</v>
       </c>
       <c r="B91" t="n">
-        <v>78407</v>
+        <v>8441</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9918,38 +9923,43 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488539</v>
+        <v>488786</v>
       </c>
       <c r="R91" t="n">
-        <v>6786689</v>
+        <v>6786723</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10008,10 +10018,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122566987</v>
+        <v>122567295</v>
       </c>
       <c r="B92" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10020,38 +10030,43 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488735</v>
+        <v>488850</v>
       </c>
       <c r="R92" t="n">
-        <v>6786569</v>
+        <v>6786668</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10110,10 +10125,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122566982</v>
+        <v>122566899</v>
       </c>
       <c r="B93" t="n">
-        <v>78762</v>
+        <v>57631</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10126,21 +10141,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10150,10 +10165,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488600</v>
+        <v>488482</v>
       </c>
       <c r="R93" t="n">
-        <v>6786662</v>
+        <v>6786720</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10212,10 +10227,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122567006</v>
+        <v>122566898</v>
       </c>
       <c r="B94" t="n">
-        <v>78762</v>
+        <v>57631</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10228,21 +10243,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10252,10 +10267,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488556</v>
+        <v>488296</v>
       </c>
       <c r="R94" t="n">
-        <v>6786835</v>
+        <v>6786844</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10314,10 +10329,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122566901</v>
+        <v>122567023</v>
       </c>
       <c r="B95" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10330,21 +10345,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10354,10 +10369,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>488142</v>
+        <v>488135</v>
       </c>
       <c r="R95" t="n">
-        <v>6787017</v>
+        <v>6787033</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10416,10 +10431,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122567296</v>
+        <v>122566982</v>
       </c>
       <c r="B96" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10428,43 +10443,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>488834</v>
+        <v>488600</v>
       </c>
       <c r="R96" t="n">
-        <v>6786685</v>
+        <v>6786662</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10523,10 +10533,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122567325</v>
+        <v>122567001</v>
       </c>
       <c r="B97" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10535,43 +10545,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>488576</v>
+        <v>488583</v>
       </c>
       <c r="R97" t="n">
-        <v>6786782</v>
+        <v>6786774</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10630,10 +10635,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122567025</v>
+        <v>122567030</v>
       </c>
       <c r="B98" t="n">
-        <v>78407</v>
+        <v>78411</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10670,10 +10675,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>488378</v>
+        <v>488769</v>
       </c>
       <c r="R98" t="n">
-        <v>6786805</v>
+        <v>6786552</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10732,10 +10737,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122566983</v>
+        <v>122566897</v>
       </c>
       <c r="B99" t="n">
-        <v>78762</v>
+        <v>90944</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10748,21 +10753,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10772,10 +10777,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>488609</v>
+        <v>488892</v>
       </c>
       <c r="R99" t="n">
-        <v>6786648</v>
+        <v>6786591</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10834,10 +10839,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122566965</v>
+        <v>122566952</v>
       </c>
       <c r="B100" t="n">
-        <v>78762</v>
+        <v>80723</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10850,21 +10855,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10874,10 +10879,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>488378</v>
+        <v>488363</v>
       </c>
       <c r="R100" t="n">
-        <v>6786805</v>
+        <v>6786907</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10936,10 +10941,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122566961</v>
+        <v>122566966</v>
       </c>
       <c r="B101" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10976,10 +10981,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>488327</v>
+        <v>488390</v>
       </c>
       <c r="R101" t="n">
-        <v>6786847</v>
+        <v>6786813</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11038,10 +11043,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122566970</v>
+        <v>122567013</v>
       </c>
       <c r="B102" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11078,10 +11083,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>488469</v>
+        <v>488389</v>
       </c>
       <c r="R102" t="n">
-        <v>6786751</v>
+        <v>6786901</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11140,10 +11145,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122567000</v>
+        <v>122567020</v>
       </c>
       <c r="B103" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11180,10 +11185,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>488678</v>
+        <v>488185</v>
       </c>
       <c r="R103" t="n">
-        <v>6786753</v>
+        <v>6787005</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11242,10 +11247,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122566995</v>
+        <v>122567303</v>
       </c>
       <c r="B104" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11254,38 +11259,43 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488833</v>
+        <v>488600</v>
       </c>
       <c r="R104" t="n">
-        <v>6786674</v>
+        <v>6786772</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11344,10 +11354,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122567001</v>
+        <v>122567305</v>
       </c>
       <c r="B105" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11356,38 +11366,43 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488583</v>
+        <v>488519</v>
       </c>
       <c r="R105" t="n">
-        <v>6786774</v>
+        <v>6786844</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11446,7 +11461,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122567292</v>
+        <v>122567320</v>
       </c>
       <c r="B106" t="n">
         <v>8441</v>
@@ -11482,7 +11497,7 @@
       <c r="I106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -11491,10 +11506,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488533</v>
+        <v>488833</v>
       </c>
       <c r="R106" t="n">
-        <v>6786690</v>
+        <v>6786674</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11553,7 +11568,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122567310</v>
+        <v>122567315</v>
       </c>
       <c r="B107" t="n">
         <v>8441</v>
@@ -11598,10 +11613,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488294</v>
+        <v>488773</v>
       </c>
       <c r="R107" t="n">
-        <v>6786825</v>
+        <v>6786561</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11660,10 +11675,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122567297</v>
+        <v>122567024</v>
       </c>
       <c r="B108" t="n">
-        <v>8441</v>
+        <v>91196</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11672,43 +11687,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>65</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>488804</v>
+        <v>488663</v>
       </c>
       <c r="R108" t="n">
-        <v>6786700</v>
+        <v>6786615</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11767,10 +11777,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122567293</v>
+        <v>122566984</v>
       </c>
       <c r="B109" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11779,43 +11789,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488790</v>
+        <v>488699</v>
       </c>
       <c r="R109" t="n">
-        <v>6786547</v>
+        <v>6786596</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11874,10 +11879,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122566909</v>
+        <v>122567014</v>
       </c>
       <c r="B110" t="n">
-        <v>91385</v>
+        <v>78766</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11886,25 +11891,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11914,10 +11919,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>488882</v>
+        <v>488383</v>
       </c>
       <c r="R110" t="n">
-        <v>6786607</v>
+        <v>6786912</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11976,10 +11981,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122567009</v>
+        <v>122567005</v>
       </c>
       <c r="B111" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12016,10 +12021,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>488465</v>
+        <v>488415</v>
       </c>
       <c r="R111" t="n">
-        <v>6786880</v>
+        <v>6786889</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12078,10 +12083,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122567015</v>
+        <v>122567025</v>
       </c>
       <c r="B112" t="n">
-        <v>78762</v>
+        <v>78411</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12094,21 +12099,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12118,10 +12123,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>488366</v>
+        <v>488378</v>
       </c>
       <c r="R112" t="n">
-        <v>6786907</v>
+        <v>6786805</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12180,10 +12185,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122566963</v>
+        <v>122566988</v>
       </c>
       <c r="B113" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12220,10 +12225,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488341</v>
+        <v>488803</v>
       </c>
       <c r="R113" t="n">
-        <v>6786832</v>
+        <v>6786562</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12282,10 +12287,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122567024</v>
+        <v>122567010</v>
       </c>
       <c r="B114" t="n">
-        <v>91192</v>
+        <v>78766</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12294,25 +12299,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12322,10 +12327,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488663</v>
+        <v>488442</v>
       </c>
       <c r="R114" t="n">
-        <v>6786615</v>
+        <v>6786881</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12384,10 +12389,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122566986</v>
+        <v>122566991</v>
       </c>
       <c r="B115" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12424,10 +12429,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>488714</v>
+        <v>488918</v>
       </c>
       <c r="R115" t="n">
-        <v>6786574</v>
+        <v>6786607</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12486,10 +12491,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122567010</v>
+        <v>122566985</v>
       </c>
       <c r="B116" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12526,10 +12531,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>488442</v>
+        <v>488698</v>
       </c>
       <c r="R116" t="n">
-        <v>6786881</v>
+        <v>6786584</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12588,10 +12593,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122566973</v>
+        <v>122567032</v>
       </c>
       <c r="B117" t="n">
-        <v>78762</v>
+        <v>5173</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12600,38 +12605,43 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>488482</v>
+        <v>488901</v>
       </c>
       <c r="R117" t="n">
-        <v>6786720</v>
+        <v>6786589</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12690,10 +12700,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122566968</v>
+        <v>122566891</v>
       </c>
       <c r="B118" t="n">
-        <v>78762</v>
+        <v>79384</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12706,21 +12716,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12730,10 +12740,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>488431</v>
+        <v>488616</v>
       </c>
       <c r="R118" t="n">
-        <v>6786772</v>
+        <v>6786648</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12792,7 +12802,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122567290</v>
+        <v>122567293</v>
       </c>
       <c r="B119" t="n">
         <v>8441</v>
@@ -12837,10 +12847,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>488345</v>
+        <v>488790</v>
       </c>
       <c r="R119" t="n">
-        <v>6786796</v>
+        <v>6786547</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12899,7 +12909,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122567322</v>
+        <v>122567301</v>
       </c>
       <c r="B120" t="n">
         <v>8441</v>
@@ -12935,7 +12945,7 @@
       <c r="I120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -12944,10 +12954,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>488700</v>
+        <v>488718</v>
       </c>
       <c r="R120" t="n">
-        <v>6786746</v>
+        <v>6786752</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13006,7 +13016,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122567314</v>
+        <v>122567324</v>
       </c>
       <c r="B121" t="n">
         <v>8441</v>
@@ -13051,10 +13061,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488747</v>
+        <v>488638</v>
       </c>
       <c r="R121" t="n">
-        <v>6786566</v>
+        <v>6786764</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13113,7 +13123,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122567312</v>
+        <v>122567326</v>
       </c>
       <c r="B122" t="n">
         <v>8441</v>
@@ -13158,10 +13168,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488341</v>
+        <v>488545</v>
       </c>
       <c r="R122" t="n">
-        <v>6786832</v>
+        <v>6786849</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13220,7 +13230,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122567306</v>
+        <v>122567309</v>
       </c>
       <c r="B123" t="n">
         <v>8441</v>
@@ -13256,7 +13266,7 @@
       <c r="I123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -13265,10 +13275,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>488556</v>
+        <v>488707</v>
       </c>
       <c r="R123" t="n">
-        <v>6786835</v>
+        <v>6786747</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13327,7 +13337,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122567303</v>
+        <v>122567323</v>
       </c>
       <c r="B124" t="n">
         <v>8441</v>
@@ -13363,7 +13373,7 @@
       <c r="I124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -13372,10 +13382,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>488600</v>
+        <v>488686</v>
       </c>
       <c r="R124" t="n">
-        <v>6786772</v>
+        <v>6786745</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13434,10 +13444,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122567323</v>
+        <v>122566979</v>
       </c>
       <c r="B125" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13446,43 +13456,38 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>488686</v>
+        <v>488583</v>
       </c>
       <c r="R125" t="n">
-        <v>6786745</v>
+        <v>6786676</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13541,10 +13546,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122566905</v>
+        <v>122566903</v>
       </c>
       <c r="B126" t="n">
-        <v>57494</v>
+        <v>90964</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13557,39 +13562,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>488294</v>
+        <v>488770</v>
       </c>
       <c r="R126" t="n">
-        <v>6786826</v>
+        <v>6786732</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13648,10 +13648,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122566971</v>
+        <v>122566894</v>
       </c>
       <c r="B127" t="n">
-        <v>78762</v>
+        <v>79384</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13664,21 +13664,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13688,10 +13688,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>488461</v>
+        <v>488182</v>
       </c>
       <c r="R127" t="n">
-        <v>6786736</v>
+        <v>6787001</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13750,10 +13750,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122567017</v>
+        <v>122566893</v>
       </c>
       <c r="B128" t="n">
-        <v>78762</v>
+        <v>79384</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13766,21 +13766,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13790,10 +13790,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>488353</v>
+        <v>488693</v>
       </c>
       <c r="R128" t="n">
-        <v>6786911</v>
+        <v>6786741</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13852,10 +13852,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122566960</v>
+        <v>122567011</v>
       </c>
       <c r="B129" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13892,10 +13892,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>488322</v>
+        <v>488427</v>
       </c>
       <c r="R129" t="n">
-        <v>6786853</v>
+        <v>6786888</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13954,10 +13954,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122567018</v>
+        <v>122567002</v>
       </c>
       <c r="B130" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13994,10 +13994,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>488345</v>
+        <v>488569</v>
       </c>
       <c r="R130" t="n">
-        <v>6786910</v>
+        <v>6786787</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14056,10 +14056,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122566890</v>
+        <v>122566981</v>
       </c>
       <c r="B131" t="n">
-        <v>79380</v>
+        <v>78766</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14072,21 +14072,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14096,10 +14096,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>488572</v>
+        <v>488599</v>
       </c>
       <c r="R131" t="n">
-        <v>6786674</v>
+        <v>6786673</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14158,10 +14158,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122567002</v>
+        <v>122566974</v>
       </c>
       <c r="B132" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14198,10 +14198,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>488569</v>
+        <v>488486</v>
       </c>
       <c r="R132" t="n">
-        <v>6786787</v>
+        <v>6786718</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>

--- a/artfynd/A 61338-2024 artfynd.xlsx
+++ b/artfynd/A 61338-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567289</v>
+        <v>122567292</v>
       </c>
       <c r="B2" t="n">
         <v>8441</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488322</v>
+        <v>488533</v>
       </c>
       <c r="R2" t="n">
-        <v>6786810</v>
+        <v>6786690</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122566953</v>
+        <v>122567307</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>8441</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,35 +794,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488429</v>
+        <v>488535</v>
       </c>
       <c r="R3" t="n">
-        <v>6786896</v>
+        <v>6786843</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567028</v>
+        <v>122567322</v>
       </c>
       <c r="B4" t="n">
-        <v>78411</v>
+        <v>8441</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,38 +901,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488611</v>
+        <v>488700</v>
       </c>
       <c r="R4" t="n">
-        <v>6786649</v>
+        <v>6786746</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122566996</v>
+        <v>122567020</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1035,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488757</v>
+        <v>488185</v>
       </c>
       <c r="R5" t="n">
-        <v>6786723</v>
+        <v>6787005</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566983</v>
+        <v>122566971</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1137,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488609</v>
+        <v>488461</v>
       </c>
       <c r="R6" t="n">
-        <v>6786648</v>
+        <v>6786736</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567018</v>
+        <v>122566894</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1239,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488345</v>
+        <v>488182</v>
       </c>
       <c r="R7" t="n">
-        <v>6786910</v>
+        <v>6787001</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566958</v>
+        <v>122566904</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>90964</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488301</v>
+        <v>488552</v>
       </c>
       <c r="R8" t="n">
-        <v>6786839</v>
+        <v>6786834</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566896</v>
+        <v>122567030</v>
       </c>
       <c r="B9" t="n">
-        <v>90944</v>
+        <v>78411</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488882</v>
+        <v>488769</v>
       </c>
       <c r="R9" t="n">
-        <v>6786607</v>
+        <v>6786552</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566911</v>
+        <v>122566912</v>
       </c>
       <c r="B10" t="n">
         <v>91235</v>
@@ -1545,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488882</v>
+        <v>488895</v>
       </c>
       <c r="R10" t="n">
-        <v>6786609</v>
+        <v>6786588</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566890</v>
+        <v>122566953</v>
       </c>
       <c r="B11" t="n">
-        <v>79384</v>
+        <v>98355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,38 +1620,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488572</v>
+        <v>488429</v>
       </c>
       <c r="R11" t="n">
-        <v>6786674</v>
+        <v>6786896</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1719,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566954</v>
+        <v>122567002</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1749,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488416</v>
+        <v>488569</v>
       </c>
       <c r="R12" t="n">
-        <v>6786896</v>
+        <v>6786787</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,7 +1923,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566976</v>
+        <v>122566956</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -1953,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488515</v>
+        <v>488309</v>
       </c>
       <c r="R14" t="n">
-        <v>6786685</v>
+        <v>6786859</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2015,7 +2025,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567017</v>
+        <v>122567000</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2055,10 +2065,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488353</v>
+        <v>488678</v>
       </c>
       <c r="R15" t="n">
-        <v>6786911</v>
+        <v>6786753</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,10 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567019</v>
+        <v>122567317</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,38 +2139,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488297</v>
+        <v>488892</v>
       </c>
       <c r="R16" t="n">
-        <v>6786946</v>
+        <v>6786620</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,10 +2234,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122567308</v>
+        <v>122567010</v>
       </c>
       <c r="B17" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,43 +2246,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488669</v>
+        <v>488442</v>
       </c>
       <c r="R17" t="n">
-        <v>6786761</v>
+        <v>6786881</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2326,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567300</v>
+        <v>122567022</v>
       </c>
       <c r="B18" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,43 +2348,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488768</v>
+        <v>488137</v>
       </c>
       <c r="R18" t="n">
-        <v>6786742</v>
+        <v>6787026</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2433,7 +2438,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122567294</v>
+        <v>122567296</v>
       </c>
       <c r="B19" t="n">
         <v>8441</v>
@@ -2478,10 +2483,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488801</v>
+        <v>488834</v>
       </c>
       <c r="R19" t="n">
-        <v>6786563</v>
+        <v>6786685</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,10 +2545,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122567016</v>
+        <v>122567316</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,38 +2557,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488360</v>
+        <v>488900</v>
       </c>
       <c r="R20" t="n">
-        <v>6786913</v>
+        <v>6786628</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,7 +2652,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566997</v>
+        <v>122567017</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -2682,10 +2692,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488731</v>
+        <v>488353</v>
       </c>
       <c r="R21" t="n">
-        <v>6786733</v>
+        <v>6786911</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,7 +2754,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567022</v>
+        <v>122566965</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -2784,10 +2794,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488137</v>
+        <v>488378</v>
       </c>
       <c r="R22" t="n">
-        <v>6787026</v>
+        <v>6786805</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,7 +2856,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566959</v>
+        <v>122567008</v>
       </c>
       <c r="B23" t="n">
         <v>78766</v>
@@ -2886,10 +2896,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488317</v>
+        <v>488495</v>
       </c>
       <c r="R23" t="n">
-        <v>6786858</v>
+        <v>6786888</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2948,10 +2958,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566902</v>
+        <v>122566977</v>
       </c>
       <c r="B24" t="n">
-        <v>90964</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2964,21 +2974,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2988,10 +2998,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488397</v>
+        <v>488515</v>
       </c>
       <c r="R24" t="n">
-        <v>6786809</v>
+        <v>6786685</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3050,10 +3060,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566909</v>
+        <v>122566893</v>
       </c>
       <c r="B25" t="n">
-        <v>91389</v>
+        <v>79384</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3062,25 +3072,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3090,10 +3100,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488882</v>
+        <v>488693</v>
       </c>
       <c r="R25" t="n">
-        <v>6786607</v>
+        <v>6786741</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3152,10 +3162,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566907</v>
+        <v>122567016</v>
       </c>
       <c r="B26" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3168,39 +3178,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488852</v>
+        <v>488360</v>
       </c>
       <c r="R26" t="n">
-        <v>6786673</v>
+        <v>6786913</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3259,10 +3264,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122567306</v>
+        <v>122566961</v>
       </c>
       <c r="B27" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3271,43 +3276,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488556</v>
+        <v>488327</v>
       </c>
       <c r="R27" t="n">
-        <v>6786835</v>
+        <v>6786847</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3366,10 +3366,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122566901</v>
+        <v>122566982</v>
       </c>
       <c r="B28" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3382,21 +3382,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3406,10 +3406,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488142</v>
+        <v>488600</v>
       </c>
       <c r="R28" t="n">
-        <v>6787017</v>
+        <v>6786662</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3468,10 +3468,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122566998</v>
+        <v>122567312</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3480,38 +3480,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488700</v>
+        <v>488341</v>
       </c>
       <c r="R29" t="n">
-        <v>6786744</v>
+        <v>6786832</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3570,10 +3575,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122566972</v>
+        <v>122567306</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3582,38 +3587,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488465</v>
+        <v>488556</v>
       </c>
       <c r="R30" t="n">
-        <v>6786729</v>
+        <v>6786835</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3672,7 +3682,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122566965</v>
+        <v>122567011</v>
       </c>
       <c r="B31" t="n">
         <v>78766</v>
@@ -3712,10 +3722,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488378</v>
+        <v>488427</v>
       </c>
       <c r="R31" t="n">
-        <v>6786805</v>
+        <v>6786888</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3774,7 +3784,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122566995</v>
+        <v>122567007</v>
       </c>
       <c r="B32" t="n">
         <v>78766</v>
@@ -3814,10 +3824,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488833</v>
+        <v>488530</v>
       </c>
       <c r="R32" t="n">
-        <v>6786674</v>
+        <v>6786847</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3876,10 +3886,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122566999</v>
+        <v>122567325</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3888,38 +3898,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488686</v>
+        <v>488576</v>
       </c>
       <c r="R33" t="n">
-        <v>6786738</v>
+        <v>6786782</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3978,7 +3993,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122566964</v>
+        <v>122566974</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -4018,10 +4033,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488351</v>
+        <v>488486</v>
       </c>
       <c r="R34" t="n">
-        <v>6786831</v>
+        <v>6786718</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4080,10 +4095,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122566905</v>
+        <v>122567006</v>
       </c>
       <c r="B35" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4096,39 +4111,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488294</v>
+        <v>488556</v>
       </c>
       <c r="R35" t="n">
-        <v>6786826</v>
+        <v>6786835</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4187,7 +4197,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122566987</v>
+        <v>122566959</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -4227,10 +4237,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488735</v>
+        <v>488317</v>
       </c>
       <c r="R36" t="n">
-        <v>6786569</v>
+        <v>6786858</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4289,7 +4299,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122567007</v>
+        <v>122567001</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4329,10 +4339,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488530</v>
+        <v>488583</v>
       </c>
       <c r="R37" t="n">
-        <v>6786847</v>
+        <v>6786774</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4391,10 +4401,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567292</v>
+        <v>122566969</v>
       </c>
       <c r="B38" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4403,43 +4413,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488533</v>
+        <v>488452</v>
       </c>
       <c r="R38" t="n">
-        <v>6786690</v>
+        <v>6786772</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4498,10 +4503,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122567327</v>
+        <v>122566980</v>
       </c>
       <c r="B39" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4510,43 +4515,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488442</v>
+        <v>488590</v>
       </c>
       <c r="R39" t="n">
-        <v>6786881</v>
+        <v>6786665</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4605,10 +4605,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122567317</v>
+        <v>122566998</v>
       </c>
       <c r="B40" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4617,43 +4617,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488892</v>
+        <v>488700</v>
       </c>
       <c r="R40" t="n">
-        <v>6786620</v>
+        <v>6786744</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4712,7 +4707,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122566980</v>
+        <v>122566981</v>
       </c>
       <c r="B41" t="n">
         <v>78766</v>
@@ -4752,10 +4747,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488590</v>
+        <v>488599</v>
       </c>
       <c r="R41" t="n">
-        <v>6786665</v>
+        <v>6786673</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4814,7 +4809,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122566956</v>
+        <v>122567014</v>
       </c>
       <c r="B42" t="n">
         <v>78766</v>
@@ -4854,10 +4849,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488309</v>
+        <v>488383</v>
       </c>
       <c r="R42" t="n">
-        <v>6786859</v>
+        <v>6786912</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4916,7 +4911,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122566961</v>
+        <v>122567003</v>
       </c>
       <c r="B43" t="n">
         <v>78766</v>
@@ -4956,10 +4951,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488327</v>
+        <v>488550</v>
       </c>
       <c r="R43" t="n">
-        <v>6786847</v>
+        <v>6786822</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5018,10 +5013,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122566978</v>
+        <v>122566909</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>91389</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5030,25 +5025,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5058,10 +5053,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488583</v>
+        <v>488882</v>
       </c>
       <c r="R44" t="n">
-        <v>6786679</v>
+        <v>6786607</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5120,10 +5115,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122567009</v>
+        <v>122567315</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5132,38 +5127,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488465</v>
+        <v>488773</v>
       </c>
       <c r="R45" t="n">
-        <v>6786880</v>
+        <v>6786561</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5222,10 +5222,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122567015</v>
+        <v>122567311</v>
       </c>
       <c r="B46" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5234,38 +5234,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488366</v>
+        <v>488332</v>
       </c>
       <c r="R46" t="n">
-        <v>6786907</v>
+        <v>6786824</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5324,10 +5329,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122566957</v>
+        <v>122567026</v>
       </c>
       <c r="B47" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5340,21 +5345,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5364,10 +5369,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488300</v>
+        <v>488539</v>
       </c>
       <c r="R47" t="n">
-        <v>6786820</v>
+        <v>6786689</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5426,10 +5431,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122567298</v>
+        <v>122567032</v>
       </c>
       <c r="B48" t="n">
-        <v>8441</v>
+        <v>5173</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5442,27 +5447,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5471,10 +5476,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488789</v>
+        <v>488901</v>
       </c>
       <c r="R48" t="n">
-        <v>6786702</v>
+        <v>6786589</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5533,7 +5538,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567307</v>
+        <v>122567326</v>
       </c>
       <c r="B49" t="n">
         <v>8441</v>
@@ -5569,7 +5574,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5578,10 +5583,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488535</v>
+        <v>488545</v>
       </c>
       <c r="R49" t="n">
-        <v>6786843</v>
+        <v>6786849</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5640,10 +5645,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122566912</v>
+        <v>122567015</v>
       </c>
       <c r="B50" t="n">
-        <v>91235</v>
+        <v>78766</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5656,21 +5661,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5680,10 +5685,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488895</v>
+        <v>488366</v>
       </c>
       <c r="R50" t="n">
-        <v>6786588</v>
+        <v>6786907</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5742,10 +5747,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122566908</v>
+        <v>122566963</v>
       </c>
       <c r="B51" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5758,43 +5763,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488892</v>
+        <v>488341</v>
       </c>
       <c r="R51" t="n">
-        <v>6786620</v>
+        <v>6786832</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5853,10 +5849,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567027</v>
+        <v>122566890</v>
       </c>
       <c r="B52" t="n">
-        <v>78411</v>
+        <v>79384</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5869,21 +5865,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5893,10 +5889,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488618</v>
+        <v>488572</v>
       </c>
       <c r="R52" t="n">
-        <v>6786631</v>
+        <v>6786674</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5955,7 +5951,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567004</v>
+        <v>122566991</v>
       </c>
       <c r="B53" t="n">
         <v>78766</v>
@@ -5995,10 +5991,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488475</v>
+        <v>488918</v>
       </c>
       <c r="R53" t="n">
-        <v>6786864</v>
+        <v>6786607</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6057,10 +6053,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122566889</v>
+        <v>122566986</v>
       </c>
       <c r="B54" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6073,21 +6069,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6097,10 +6093,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488296</v>
+        <v>488714</v>
       </c>
       <c r="R54" t="n">
-        <v>6786844</v>
+        <v>6786574</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6159,10 +6155,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122567290</v>
+        <v>122566967</v>
       </c>
       <c r="B55" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6171,43 +6167,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488345</v>
+        <v>488387</v>
       </c>
       <c r="R55" t="n">
-        <v>6786796</v>
+        <v>6786773</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6266,10 +6257,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122567297</v>
+        <v>122567025</v>
       </c>
       <c r="B56" t="n">
-        <v>8441</v>
+        <v>78411</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6278,43 +6269,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488804</v>
+        <v>488378</v>
       </c>
       <c r="R56" t="n">
-        <v>6786700</v>
+        <v>6786805</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6373,10 +6359,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567325</v>
+        <v>122567027</v>
       </c>
       <c r="B57" t="n">
-        <v>8441</v>
+        <v>78411</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6385,43 +6371,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488576</v>
+        <v>488618</v>
       </c>
       <c r="R57" t="n">
-        <v>6786782</v>
+        <v>6786631</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6480,10 +6461,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122567318</v>
+        <v>122566978</v>
       </c>
       <c r="B58" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6492,43 +6473,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488883</v>
+        <v>488583</v>
       </c>
       <c r="R58" t="n">
-        <v>6786645</v>
+        <v>6786679</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6587,7 +6563,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122566971</v>
+        <v>122567018</v>
       </c>
       <c r="B59" t="n">
         <v>78766</v>
@@ -6627,10 +6603,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488461</v>
+        <v>488345</v>
       </c>
       <c r="R59" t="n">
-        <v>6786736</v>
+        <v>6786910</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6689,7 +6665,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122567008</v>
+        <v>122566983</v>
       </c>
       <c r="B60" t="n">
         <v>78766</v>
@@ -6729,10 +6705,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488495</v>
+        <v>488609</v>
       </c>
       <c r="R60" t="n">
-        <v>6786888</v>
+        <v>6786648</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6791,10 +6767,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122566967</v>
+        <v>122566889</v>
       </c>
       <c r="B61" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6807,21 +6783,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6831,10 +6807,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488387</v>
+        <v>488296</v>
       </c>
       <c r="R61" t="n">
-        <v>6786773</v>
+        <v>6786844</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6893,10 +6869,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122566962</v>
+        <v>122566908</v>
       </c>
       <c r="B62" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6909,34 +6885,43 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488324</v>
+        <v>488892</v>
       </c>
       <c r="R62" t="n">
-        <v>6786843</v>
+        <v>6786620</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6995,10 +6980,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122567012</v>
+        <v>122567297</v>
       </c>
       <c r="B63" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7007,38 +6992,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488420</v>
+        <v>488804</v>
       </c>
       <c r="R63" t="n">
-        <v>6786898</v>
+        <v>6786700</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7097,10 +7087,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122567003</v>
+        <v>122567309</v>
       </c>
       <c r="B64" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7109,38 +7099,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488550</v>
+        <v>488707</v>
       </c>
       <c r="R64" t="n">
-        <v>6786822</v>
+        <v>6786747</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7199,10 +7194,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122566904</v>
+        <v>122567289</v>
       </c>
       <c r="B65" t="n">
-        <v>90964</v>
+        <v>8441</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7211,38 +7206,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488552</v>
+        <v>488322</v>
       </c>
       <c r="R65" t="n">
-        <v>6786834</v>
+        <v>6786810</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7301,10 +7301,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122566969</v>
+        <v>122567291</v>
       </c>
       <c r="B66" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7313,38 +7313,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488452</v>
+        <v>488440</v>
       </c>
       <c r="R66" t="n">
-        <v>6786772</v>
+        <v>6786759</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7403,10 +7408,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122567000</v>
+        <v>122567327</v>
       </c>
       <c r="B67" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7415,38 +7420,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488678</v>
+        <v>488442</v>
       </c>
       <c r="R67" t="n">
-        <v>6786753</v>
+        <v>6786881</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7505,10 +7515,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122567006</v>
+        <v>122567323</v>
       </c>
       <c r="B68" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7517,38 +7527,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488556</v>
+        <v>488686</v>
       </c>
       <c r="R68" t="n">
-        <v>6786835</v>
+        <v>6786745</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7607,10 +7622,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122567026</v>
+        <v>122567318</v>
       </c>
       <c r="B69" t="n">
-        <v>78411</v>
+        <v>8441</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7619,38 +7634,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488539</v>
+        <v>488883</v>
       </c>
       <c r="R69" t="n">
-        <v>6786689</v>
+        <v>6786645</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7709,10 +7729,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122566892</v>
+        <v>122566979</v>
       </c>
       <c r="B70" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7725,21 +7745,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7749,10 +7769,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488699</v>
+        <v>488583</v>
       </c>
       <c r="R70" t="n">
-        <v>6786599</v>
+        <v>6786676</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7811,7 +7831,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122567304</v>
+        <v>122567319</v>
       </c>
       <c r="B71" t="n">
         <v>8441</v>
@@ -7847,7 +7867,7 @@
       <c r="I71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -7856,10 +7876,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488591</v>
+        <v>488869</v>
       </c>
       <c r="R71" t="n">
-        <v>6786769</v>
+        <v>6786685</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7918,7 +7938,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122567311</v>
+        <v>122567310</v>
       </c>
       <c r="B72" t="n">
         <v>8441</v>
@@ -7963,10 +7983,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488332</v>
+        <v>488294</v>
       </c>
       <c r="R72" t="n">
-        <v>6786824</v>
+        <v>6786825</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8025,10 +8045,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122567316</v>
+        <v>122566990</v>
       </c>
       <c r="B73" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8037,43 +8057,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488900</v>
+        <v>488840</v>
       </c>
       <c r="R73" t="n">
-        <v>6786628</v>
+        <v>6786622</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8132,10 +8147,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122567029</v>
+        <v>122566954</v>
       </c>
       <c r="B74" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8148,21 +8163,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8172,10 +8187,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488664</v>
+        <v>488416</v>
       </c>
       <c r="R74" t="n">
-        <v>6786615</v>
+        <v>6786896</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8234,7 +8249,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122566973</v>
+        <v>122567005</v>
       </c>
       <c r="B75" t="n">
         <v>78766</v>
@@ -8274,10 +8289,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488482</v>
+        <v>488415</v>
       </c>
       <c r="R75" t="n">
-        <v>6786720</v>
+        <v>6786889</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8336,10 +8351,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122566990</v>
+        <v>122566952</v>
       </c>
       <c r="B76" t="n">
-        <v>78766</v>
+        <v>80723</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8352,21 +8367,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8376,10 +8391,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488840</v>
+        <v>488363</v>
       </c>
       <c r="R76" t="n">
-        <v>6786622</v>
+        <v>6786907</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8438,10 +8453,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122566968</v>
+        <v>122566903</v>
       </c>
       <c r="B77" t="n">
-        <v>78766</v>
+        <v>90964</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8454,21 +8469,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8478,10 +8493,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488431</v>
+        <v>488770</v>
       </c>
       <c r="R77" t="n">
-        <v>6786772</v>
+        <v>6786732</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8540,7 +8555,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122566963</v>
+        <v>122566962</v>
       </c>
       <c r="B78" t="n">
         <v>78766</v>
@@ -8580,10 +8595,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488341</v>
+        <v>488324</v>
       </c>
       <c r="R78" t="n">
-        <v>6786832</v>
+        <v>6786843</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8642,7 +8657,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122567310</v>
+        <v>122567298</v>
       </c>
       <c r="B79" t="n">
         <v>8441</v>
@@ -8678,7 +8693,7 @@
       <c r="I79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8687,10 +8702,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488294</v>
+        <v>488789</v>
       </c>
       <c r="R79" t="n">
-        <v>6786825</v>
+        <v>6786702</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8749,10 +8764,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122567313</v>
+        <v>122567012</v>
       </c>
       <c r="B80" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8761,43 +8776,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488616</v>
+        <v>488420</v>
       </c>
       <c r="R80" t="n">
-        <v>6786649</v>
+        <v>6786898</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8856,10 +8866,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122567314</v>
+        <v>122566995</v>
       </c>
       <c r="B81" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8868,43 +8878,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488747</v>
+        <v>488833</v>
       </c>
       <c r="R81" t="n">
-        <v>6786566</v>
+        <v>6786674</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8963,10 +8968,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122567319</v>
+        <v>122567024</v>
       </c>
       <c r="B82" t="n">
-        <v>8441</v>
+        <v>91196</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8975,43 +8980,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>65</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488869</v>
+        <v>488663</v>
       </c>
       <c r="R82" t="n">
-        <v>6786685</v>
+        <v>6786615</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9070,10 +9070,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122567321</v>
+        <v>122566911</v>
       </c>
       <c r="B83" t="n">
-        <v>8441</v>
+        <v>91235</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9082,43 +9082,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>658</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488817</v>
+        <v>488882</v>
       </c>
       <c r="R83" t="n">
-        <v>6786693</v>
+        <v>6786609</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9177,10 +9172,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122566986</v>
+        <v>122567304</v>
       </c>
       <c r="B84" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9189,38 +9184,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488714</v>
+        <v>488591</v>
       </c>
       <c r="R84" t="n">
-        <v>6786574</v>
+        <v>6786769</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9279,10 +9279,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122566970</v>
+        <v>122567305</v>
       </c>
       <c r="B85" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9291,38 +9291,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488469</v>
+        <v>488519</v>
       </c>
       <c r="R85" t="n">
-        <v>6786751</v>
+        <v>6786844</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9381,10 +9386,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122567296</v>
+        <v>122567009</v>
       </c>
       <c r="B86" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9393,43 +9398,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488834</v>
+        <v>488465</v>
       </c>
       <c r="R86" t="n">
-        <v>6786685</v>
+        <v>6786880</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9488,10 +9488,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122567291</v>
+        <v>122566972</v>
       </c>
       <c r="B87" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9500,43 +9500,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488440</v>
+        <v>488465</v>
       </c>
       <c r="R87" t="n">
-        <v>6786759</v>
+        <v>6786729</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9595,10 +9590,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122567322</v>
+        <v>122566988</v>
       </c>
       <c r="B88" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9607,43 +9602,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488700</v>
+        <v>488803</v>
       </c>
       <c r="R88" t="n">
-        <v>6786746</v>
+        <v>6786562</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9702,7 +9692,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122566994</v>
+        <v>122566957</v>
       </c>
       <c r="B89" t="n">
         <v>78766</v>
@@ -9742,10 +9732,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488883</v>
+        <v>488300</v>
       </c>
       <c r="R89" t="n">
-        <v>6786645</v>
+        <v>6786820</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9804,10 +9794,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122567312</v>
+        <v>122567004</v>
       </c>
       <c r="B90" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9816,43 +9806,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488341</v>
+        <v>488475</v>
       </c>
       <c r="R90" t="n">
-        <v>6786832</v>
+        <v>6786864</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9911,10 +9896,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122567299</v>
+        <v>122566973</v>
       </c>
       <c r="B91" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9923,43 +9908,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488786</v>
+        <v>488482</v>
       </c>
       <c r="R91" t="n">
-        <v>6786723</v>
+        <v>6786720</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10018,10 +9998,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122567295</v>
+        <v>122566999</v>
       </c>
       <c r="B92" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10030,43 +10010,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488850</v>
+        <v>488686</v>
       </c>
       <c r="R92" t="n">
-        <v>6786668</v>
+        <v>6786738</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10125,10 +10100,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122566899</v>
+        <v>122567013</v>
       </c>
       <c r="B93" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10141,21 +10116,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10165,10 +10140,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488482</v>
+        <v>488389</v>
       </c>
       <c r="R93" t="n">
-        <v>6786720</v>
+        <v>6786901</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10227,10 +10202,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122566898</v>
+        <v>122566997</v>
       </c>
       <c r="B94" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10243,21 +10218,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10267,10 +10242,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488296</v>
+        <v>488731</v>
       </c>
       <c r="R94" t="n">
-        <v>6786844</v>
+        <v>6786733</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10329,10 +10304,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122567023</v>
+        <v>122566901</v>
       </c>
       <c r="B95" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10345,21 +10320,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10369,10 +10344,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>488135</v>
+        <v>488142</v>
       </c>
       <c r="R95" t="n">
-        <v>6787033</v>
+        <v>6787017</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10431,10 +10406,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122566982</v>
+        <v>122567314</v>
       </c>
       <c r="B96" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10443,38 +10418,43 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>488600</v>
+        <v>488747</v>
       </c>
       <c r="R96" t="n">
-        <v>6786662</v>
+        <v>6786566</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10533,10 +10513,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122567001</v>
+        <v>122567300</v>
       </c>
       <c r="B97" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10545,38 +10525,43 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>488583</v>
+        <v>488768</v>
       </c>
       <c r="R97" t="n">
-        <v>6786774</v>
+        <v>6786742</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10635,10 +10620,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122567030</v>
+        <v>122567301</v>
       </c>
       <c r="B98" t="n">
-        <v>78411</v>
+        <v>8441</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10647,38 +10632,43 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>488769</v>
+        <v>488718</v>
       </c>
       <c r="R98" t="n">
-        <v>6786552</v>
+        <v>6786752</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10737,10 +10727,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122566897</v>
+        <v>122567320</v>
       </c>
       <c r="B99" t="n">
-        <v>90944</v>
+        <v>8441</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10749,38 +10739,43 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>488892</v>
+        <v>488833</v>
       </c>
       <c r="R99" t="n">
-        <v>6786591</v>
+        <v>6786674</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10839,10 +10834,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122566952</v>
+        <v>122566996</v>
       </c>
       <c r="B100" t="n">
-        <v>80723</v>
+        <v>78766</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10855,21 +10850,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10879,10 +10874,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>488363</v>
+        <v>488757</v>
       </c>
       <c r="R100" t="n">
-        <v>6786907</v>
+        <v>6786723</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10941,10 +10936,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122566966</v>
+        <v>122566897</v>
       </c>
       <c r="B101" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10957,21 +10952,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10981,10 +10976,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>488390</v>
+        <v>488892</v>
       </c>
       <c r="R101" t="n">
-        <v>6786813</v>
+        <v>6786591</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11043,10 +11038,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122567013</v>
+        <v>122567299</v>
       </c>
       <c r="B102" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11055,38 +11050,43 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>488389</v>
+        <v>488786</v>
       </c>
       <c r="R102" t="n">
-        <v>6786901</v>
+        <v>6786723</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11145,10 +11145,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122567020</v>
+        <v>122566902</v>
       </c>
       <c r="B103" t="n">
-        <v>78766</v>
+        <v>90964</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11161,21 +11161,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>488185</v>
+        <v>488397</v>
       </c>
       <c r="R103" t="n">
-        <v>6787005</v>
+        <v>6786809</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11247,10 +11247,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122567303</v>
+        <v>122566970</v>
       </c>
       <c r="B104" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11259,43 +11259,38 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488600</v>
+        <v>488469</v>
       </c>
       <c r="R104" t="n">
-        <v>6786772</v>
+        <v>6786751</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11354,10 +11349,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122567305</v>
+        <v>122566958</v>
       </c>
       <c r="B105" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11366,43 +11361,38 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488519</v>
+        <v>488301</v>
       </c>
       <c r="R105" t="n">
-        <v>6786844</v>
+        <v>6786839</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11461,10 +11451,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122567320</v>
+        <v>122566899</v>
       </c>
       <c r="B106" t="n">
-        <v>8441</v>
+        <v>57631</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11473,43 +11463,38 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488833</v>
+        <v>488482</v>
       </c>
       <c r="R106" t="n">
-        <v>6786674</v>
+        <v>6786720</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11568,10 +11553,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122567315</v>
+        <v>122566898</v>
       </c>
       <c r="B107" t="n">
-        <v>8441</v>
+        <v>57631</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11580,43 +11565,38 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488773</v>
+        <v>488296</v>
       </c>
       <c r="R107" t="n">
-        <v>6786561</v>
+        <v>6786844</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11675,10 +11655,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122567024</v>
+        <v>122567313</v>
       </c>
       <c r="B108" t="n">
-        <v>91196</v>
+        <v>8441</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11687,38 +11667,43 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>65</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>488663</v>
+        <v>488616</v>
       </c>
       <c r="R108" t="n">
-        <v>6786615</v>
+        <v>6786649</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11777,10 +11762,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122566984</v>
+        <v>122566905</v>
       </c>
       <c r="B109" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11793,34 +11778,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488699</v>
+        <v>488294</v>
       </c>
       <c r="R109" t="n">
-        <v>6786596</v>
+        <v>6786826</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11879,10 +11869,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122567014</v>
+        <v>122566892</v>
       </c>
       <c r="B110" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11895,21 +11885,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11919,10 +11909,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>488383</v>
+        <v>488699</v>
       </c>
       <c r="R110" t="n">
-        <v>6786912</v>
+        <v>6786599</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11981,7 +11971,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122567005</v>
+        <v>122566984</v>
       </c>
       <c r="B111" t="n">
         <v>78766</v>
@@ -12021,10 +12011,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>488415</v>
+        <v>488699</v>
       </c>
       <c r="R111" t="n">
-        <v>6786889</v>
+        <v>6786596</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12083,10 +12073,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122567025</v>
+        <v>122566994</v>
       </c>
       <c r="B112" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12099,21 +12089,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12123,10 +12113,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>488378</v>
+        <v>488883</v>
       </c>
       <c r="R112" t="n">
-        <v>6786805</v>
+        <v>6786645</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12185,7 +12175,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122566988</v>
+        <v>122566968</v>
       </c>
       <c r="B113" t="n">
         <v>78766</v>
@@ -12225,10 +12215,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488803</v>
+        <v>488431</v>
       </c>
       <c r="R113" t="n">
-        <v>6786562</v>
+        <v>6786772</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12287,10 +12277,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122567010</v>
+        <v>122567290</v>
       </c>
       <c r="B114" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12299,38 +12289,43 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488442</v>
+        <v>488345</v>
       </c>
       <c r="R114" t="n">
-        <v>6786881</v>
+        <v>6786796</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12389,10 +12384,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122566991</v>
+        <v>122567308</v>
       </c>
       <c r="B115" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12401,38 +12396,43 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>488918</v>
+        <v>488669</v>
       </c>
       <c r="R115" t="n">
-        <v>6786607</v>
+        <v>6786761</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12491,10 +12491,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122566985</v>
+        <v>122567293</v>
       </c>
       <c r="B116" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12503,38 +12503,43 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>488698</v>
+        <v>488790</v>
       </c>
       <c r="R116" t="n">
-        <v>6786584</v>
+        <v>6786547</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12593,10 +12598,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122567032</v>
+        <v>122567324</v>
       </c>
       <c r="B117" t="n">
-        <v>5173</v>
+        <v>8441</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12609,21 +12614,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12638,10 +12643,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>488901</v>
+        <v>488638</v>
       </c>
       <c r="R117" t="n">
-        <v>6786589</v>
+        <v>6786764</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12700,10 +12705,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122566891</v>
+        <v>122566966</v>
       </c>
       <c r="B118" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12716,21 +12721,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12740,10 +12745,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>488616</v>
+        <v>488390</v>
       </c>
       <c r="R118" t="n">
-        <v>6786648</v>
+        <v>6786813</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12802,10 +12807,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122567293</v>
+        <v>122566964</v>
       </c>
       <c r="B119" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12814,43 +12819,38 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>488790</v>
+        <v>488351</v>
       </c>
       <c r="R119" t="n">
-        <v>6786547</v>
+        <v>6786831</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12909,10 +12909,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122567301</v>
+        <v>122567019</v>
       </c>
       <c r="B120" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12921,43 +12921,38 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>488718</v>
+        <v>488297</v>
       </c>
       <c r="R120" t="n">
-        <v>6786752</v>
+        <v>6786946</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13016,10 +13011,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122567324</v>
+        <v>122567029</v>
       </c>
       <c r="B121" t="n">
-        <v>8441</v>
+        <v>78411</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13028,43 +13023,38 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488638</v>
+        <v>488664</v>
       </c>
       <c r="R121" t="n">
-        <v>6786764</v>
+        <v>6786615</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13123,10 +13113,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122567326</v>
+        <v>122566907</v>
       </c>
       <c r="B122" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13135,31 +13125,31 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -13168,10 +13158,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488545</v>
+        <v>488852</v>
       </c>
       <c r="R122" t="n">
-        <v>6786849</v>
+        <v>6786673</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13230,10 +13220,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122567309</v>
+        <v>122566987</v>
       </c>
       <c r="B123" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13242,43 +13232,38 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>488707</v>
+        <v>488735</v>
       </c>
       <c r="R123" t="n">
-        <v>6786747</v>
+        <v>6786569</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13337,10 +13322,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122567323</v>
+        <v>122566985</v>
       </c>
       <c r="B124" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13349,43 +13334,38 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>488686</v>
+        <v>488698</v>
       </c>
       <c r="R124" t="n">
-        <v>6786745</v>
+        <v>6786584</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13444,10 +13424,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122566979</v>
+        <v>122567321</v>
       </c>
       <c r="B125" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13456,38 +13436,43 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>488583</v>
+        <v>488817</v>
       </c>
       <c r="R125" t="n">
-        <v>6786676</v>
+        <v>6786693</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13546,10 +13531,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122566903</v>
+        <v>122567023</v>
       </c>
       <c r="B126" t="n">
-        <v>90964</v>
+        <v>78766</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13562,21 +13547,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13586,10 +13571,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>488770</v>
+        <v>488135</v>
       </c>
       <c r="R126" t="n">
-        <v>6786732</v>
+        <v>6787033</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13648,7 +13633,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122566894</v>
+        <v>122566891</v>
       </c>
       <c r="B127" t="n">
         <v>79384</v>
@@ -13688,10 +13673,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>488182</v>
+        <v>488616</v>
       </c>
       <c r="R127" t="n">
-        <v>6787001</v>
+        <v>6786648</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13750,10 +13735,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122566893</v>
+        <v>122566896</v>
       </c>
       <c r="B128" t="n">
-        <v>79384</v>
+        <v>90944</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13766,21 +13751,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13790,10 +13775,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>488693</v>
+        <v>488882</v>
       </c>
       <c r="R128" t="n">
-        <v>6786741</v>
+        <v>6786607</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13852,10 +13837,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122567011</v>
+        <v>122567295</v>
       </c>
       <c r="B129" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13864,38 +13849,43 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>488427</v>
+        <v>488850</v>
       </c>
       <c r="R129" t="n">
-        <v>6786888</v>
+        <v>6786668</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13954,10 +13944,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122567002</v>
+        <v>122567294</v>
       </c>
       <c r="B130" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13966,38 +13956,43 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>488569</v>
+        <v>488801</v>
       </c>
       <c r="R130" t="n">
-        <v>6786787</v>
+        <v>6786563</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14056,10 +14051,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122566981</v>
+        <v>122567303</v>
       </c>
       <c r="B131" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14068,38 +14063,43 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>488599</v>
+        <v>488600</v>
       </c>
       <c r="R131" t="n">
-        <v>6786673</v>
+        <v>6786772</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14158,10 +14158,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122566974</v>
+        <v>122567028</v>
       </c>
       <c r="B132" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14174,21 +14174,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14198,10 +14198,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>488486</v>
+        <v>488611</v>
       </c>
       <c r="R132" t="n">
-        <v>6786718</v>
+        <v>6786649</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>

--- a/artfynd/A 61338-2024 artfynd.xlsx
+++ b/artfynd/A 61338-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567292</v>
+        <v>122566964</v>
       </c>
       <c r="B2" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488533</v>
+        <v>488351</v>
       </c>
       <c r="R2" t="n">
-        <v>6786690</v>
+        <v>6786831</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567307</v>
+        <v>122567316</v>
       </c>
       <c r="B3" t="n">
         <v>8441</v>
@@ -818,7 +813,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -827,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488535</v>
+        <v>488900</v>
       </c>
       <c r="R3" t="n">
-        <v>6786843</v>
+        <v>6786628</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567322</v>
+        <v>122567306</v>
       </c>
       <c r="B4" t="n">
         <v>8441</v>
@@ -925,7 +920,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -934,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488700</v>
+        <v>488556</v>
       </c>
       <c r="R4" t="n">
-        <v>6786746</v>
+        <v>6786835</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567020</v>
+        <v>122566953</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,38 +1003,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488185</v>
+        <v>488429</v>
       </c>
       <c r="R5" t="n">
-        <v>6787005</v>
+        <v>6786896</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566971</v>
+        <v>122567327</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,38 +1114,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488461</v>
+        <v>488442</v>
       </c>
       <c r="R6" t="n">
-        <v>6786736</v>
+        <v>6786881</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566894</v>
+        <v>122567024</v>
       </c>
       <c r="B7" t="n">
-        <v>79384</v>
+        <v>91196</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1221,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488182</v>
+        <v>488663</v>
       </c>
       <c r="R7" t="n">
-        <v>6787001</v>
+        <v>6786615</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566904</v>
+        <v>122566970</v>
       </c>
       <c r="B8" t="n">
-        <v>90964</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488552</v>
+        <v>488469</v>
       </c>
       <c r="R8" t="n">
-        <v>6786834</v>
+        <v>6786751</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122567030</v>
+        <v>122566996</v>
       </c>
       <c r="B9" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1429,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488769</v>
+        <v>488757</v>
       </c>
       <c r="R9" t="n">
-        <v>6786552</v>
+        <v>6786723</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566912</v>
+        <v>122567032</v>
       </c>
       <c r="B10" t="n">
-        <v>91235</v>
+        <v>5173</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,38 +1527,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488895</v>
+        <v>488901</v>
       </c>
       <c r="R10" t="n">
-        <v>6786588</v>
+        <v>6786589</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566953</v>
+        <v>122566890</v>
       </c>
       <c r="B11" t="n">
-        <v>98355</v>
+        <v>79384</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,47 +1634,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488429</v>
+        <v>488572</v>
       </c>
       <c r="R11" t="n">
-        <v>6786896</v>
+        <v>6786674</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,7 +1724,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567002</v>
+        <v>122567006</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1759,10 +1764,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488569</v>
+        <v>488556</v>
       </c>
       <c r="R12" t="n">
-        <v>6786787</v>
+        <v>6786835</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,7 +1826,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566960</v>
+        <v>122566995</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1861,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488322</v>
+        <v>488833</v>
       </c>
       <c r="R13" t="n">
-        <v>6786853</v>
+        <v>6786674</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,7 +1928,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566956</v>
+        <v>122566963</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -1963,10 +1968,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488309</v>
+        <v>488341</v>
       </c>
       <c r="R14" t="n">
-        <v>6786859</v>
+        <v>6786832</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,10 +2030,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567000</v>
+        <v>122567319</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,38 +2042,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488678</v>
+        <v>488869</v>
       </c>
       <c r="R15" t="n">
-        <v>6786753</v>
+        <v>6786685</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,7 +2137,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567317</v>
+        <v>122567309</v>
       </c>
       <c r="B16" t="n">
         <v>8441</v>
@@ -2172,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488892</v>
+        <v>488707</v>
       </c>
       <c r="R16" t="n">
-        <v>6786620</v>
+        <v>6786747</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,10 +2244,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122567010</v>
+        <v>122567326</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,38 +2256,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488442</v>
+        <v>488545</v>
       </c>
       <c r="R17" t="n">
-        <v>6786881</v>
+        <v>6786849</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,7 +2351,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567022</v>
+        <v>122566980</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2376,10 +2391,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488137</v>
+        <v>488590</v>
       </c>
       <c r="R18" t="n">
-        <v>6787026</v>
+        <v>6786665</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,10 +2453,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122567296</v>
+        <v>122566979</v>
       </c>
       <c r="B19" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,43 +2465,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488834</v>
+        <v>488583</v>
       </c>
       <c r="R19" t="n">
-        <v>6786685</v>
+        <v>6786676</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2545,10 +2555,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122567316</v>
+        <v>122566959</v>
       </c>
       <c r="B20" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2557,43 +2567,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488900</v>
+        <v>488317</v>
       </c>
       <c r="R20" t="n">
-        <v>6786628</v>
+        <v>6786858</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2652,7 +2657,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567017</v>
+        <v>122566954</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -2692,10 +2697,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488353</v>
+        <v>488416</v>
       </c>
       <c r="R21" t="n">
-        <v>6786911</v>
+        <v>6786896</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2754,7 +2759,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566965</v>
+        <v>122566971</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -2794,10 +2799,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488378</v>
+        <v>488461</v>
       </c>
       <c r="R22" t="n">
-        <v>6786805</v>
+        <v>6786736</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2856,7 +2861,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567008</v>
+        <v>122566986</v>
       </c>
       <c r="B23" t="n">
         <v>78766</v>
@@ -2896,10 +2901,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488495</v>
+        <v>488714</v>
       </c>
       <c r="R23" t="n">
-        <v>6786888</v>
+        <v>6786574</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2958,7 +2963,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566977</v>
+        <v>122567003</v>
       </c>
       <c r="B24" t="n">
         <v>78766</v>
@@ -2998,10 +3003,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488515</v>
+        <v>488550</v>
       </c>
       <c r="R24" t="n">
-        <v>6786685</v>
+        <v>6786822</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3060,10 +3065,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566893</v>
+        <v>122567290</v>
       </c>
       <c r="B25" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3072,38 +3077,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488693</v>
+        <v>488345</v>
       </c>
       <c r="R25" t="n">
-        <v>6786741</v>
+        <v>6786796</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3162,10 +3172,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567016</v>
+        <v>122567324</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3174,38 +3184,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488360</v>
+        <v>488638</v>
       </c>
       <c r="R26" t="n">
-        <v>6786913</v>
+        <v>6786764</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3264,10 +3279,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566961</v>
+        <v>122566912</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>91235</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3280,21 +3295,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3304,10 +3319,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488327</v>
+        <v>488895</v>
       </c>
       <c r="R27" t="n">
-        <v>6786847</v>
+        <v>6786588</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3366,10 +3381,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122566982</v>
+        <v>122567296</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3378,38 +3393,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488600</v>
+        <v>488834</v>
       </c>
       <c r="R28" t="n">
-        <v>6786662</v>
+        <v>6786685</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3575,10 +3595,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567306</v>
+        <v>122567020</v>
       </c>
       <c r="B30" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3587,43 +3607,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488556</v>
+        <v>488185</v>
       </c>
       <c r="R30" t="n">
-        <v>6786835</v>
+        <v>6787005</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3682,7 +3697,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567011</v>
+        <v>122567010</v>
       </c>
       <c r="B31" t="n">
         <v>78766</v>
@@ -3722,10 +3737,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488427</v>
+        <v>488442</v>
       </c>
       <c r="R31" t="n">
-        <v>6786888</v>
+        <v>6786881</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3784,10 +3799,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122567007</v>
+        <v>122566903</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>90964</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3800,21 +3815,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3824,10 +3839,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488530</v>
+        <v>488770</v>
       </c>
       <c r="R32" t="n">
-        <v>6786847</v>
+        <v>6786732</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3886,10 +3901,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122567325</v>
+        <v>122566984</v>
       </c>
       <c r="B33" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3898,43 +3913,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488576</v>
+        <v>488699</v>
       </c>
       <c r="R33" t="n">
-        <v>6786782</v>
+        <v>6786596</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3993,7 +4003,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122566974</v>
+        <v>122567007</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -4033,10 +4043,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488486</v>
+        <v>488530</v>
       </c>
       <c r="R34" t="n">
-        <v>6786718</v>
+        <v>6786847</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4095,10 +4105,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122567006</v>
+        <v>122567314</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4107,38 +4117,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488556</v>
+        <v>488747</v>
       </c>
       <c r="R35" t="n">
-        <v>6786835</v>
+        <v>6786566</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4197,10 +4212,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122566959</v>
+        <v>122567313</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4209,38 +4224,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488317</v>
+        <v>488616</v>
       </c>
       <c r="R36" t="n">
-        <v>6786858</v>
+        <v>6786649</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4299,10 +4319,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122567001</v>
+        <v>122567293</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4311,38 +4331,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488583</v>
+        <v>488790</v>
       </c>
       <c r="R37" t="n">
-        <v>6786774</v>
+        <v>6786547</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4401,10 +4426,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122566969</v>
+        <v>122567295</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4413,38 +4438,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488452</v>
+        <v>488850</v>
       </c>
       <c r="R38" t="n">
-        <v>6786772</v>
+        <v>6786668</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4503,7 +4533,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122566980</v>
+        <v>122567002</v>
       </c>
       <c r="B39" t="n">
         <v>78766</v>
@@ -4543,10 +4573,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488590</v>
+        <v>488569</v>
       </c>
       <c r="R39" t="n">
-        <v>6786665</v>
+        <v>6786787</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4605,7 +4635,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122566998</v>
+        <v>122566991</v>
       </c>
       <c r="B40" t="n">
         <v>78766</v>
@@ -4645,10 +4675,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488700</v>
+        <v>488918</v>
       </c>
       <c r="R40" t="n">
-        <v>6786744</v>
+        <v>6786607</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4707,7 +4737,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122566981</v>
+        <v>122566982</v>
       </c>
       <c r="B41" t="n">
         <v>78766</v>
@@ -4747,10 +4777,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488599</v>
+        <v>488600</v>
       </c>
       <c r="R41" t="n">
-        <v>6786673</v>
+        <v>6786662</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4809,7 +4839,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567014</v>
+        <v>122566962</v>
       </c>
       <c r="B42" t="n">
         <v>78766</v>
@@ -4849,10 +4879,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488383</v>
+        <v>488324</v>
       </c>
       <c r="R42" t="n">
-        <v>6786912</v>
+        <v>6786843</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4911,10 +4941,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567003</v>
+        <v>122566899</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4927,21 +4957,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4951,10 +4981,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488550</v>
+        <v>488482</v>
       </c>
       <c r="R43" t="n">
-        <v>6786822</v>
+        <v>6786720</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5013,10 +5043,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122566909</v>
+        <v>122567304</v>
       </c>
       <c r="B44" t="n">
-        <v>91389</v>
+        <v>8441</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5025,38 +5055,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488882</v>
+        <v>488591</v>
       </c>
       <c r="R44" t="n">
-        <v>6786607</v>
+        <v>6786769</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5222,10 +5257,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122567311</v>
+        <v>122567027</v>
       </c>
       <c r="B46" t="n">
-        <v>8441</v>
+        <v>78411</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5234,43 +5269,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488332</v>
+        <v>488618</v>
       </c>
       <c r="R46" t="n">
-        <v>6786824</v>
+        <v>6786631</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5329,10 +5359,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122567026</v>
+        <v>122567016</v>
       </c>
       <c r="B47" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5345,21 +5375,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5369,10 +5399,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488539</v>
+        <v>488360</v>
       </c>
       <c r="R47" t="n">
-        <v>6786689</v>
+        <v>6786913</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5431,10 +5461,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122567032</v>
+        <v>122566976</v>
       </c>
       <c r="B48" t="n">
-        <v>5173</v>
+        <v>78766</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5443,43 +5473,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488901</v>
+        <v>488515</v>
       </c>
       <c r="R48" t="n">
-        <v>6786589</v>
+        <v>6786685</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5538,10 +5563,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567326</v>
+        <v>122566897</v>
       </c>
       <c r="B49" t="n">
-        <v>8441</v>
+        <v>90944</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5550,43 +5575,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488545</v>
+        <v>488892</v>
       </c>
       <c r="R49" t="n">
-        <v>6786849</v>
+        <v>6786591</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5645,10 +5665,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122567015</v>
+        <v>122567323</v>
       </c>
       <c r="B50" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5657,38 +5677,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488366</v>
+        <v>488686</v>
       </c>
       <c r="R50" t="n">
-        <v>6786907</v>
+        <v>6786745</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5747,7 +5772,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122566963</v>
+        <v>122567017</v>
       </c>
       <c r="B51" t="n">
         <v>78766</v>
@@ -5787,10 +5812,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488341</v>
+        <v>488353</v>
       </c>
       <c r="R51" t="n">
-        <v>6786832</v>
+        <v>6786911</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5849,10 +5874,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122566890</v>
+        <v>122566972</v>
       </c>
       <c r="B52" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5865,21 +5890,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5889,10 +5914,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488572</v>
+        <v>488465</v>
       </c>
       <c r="R52" t="n">
-        <v>6786674</v>
+        <v>6786729</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5951,10 +5976,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122566991</v>
+        <v>122566891</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5967,21 +5992,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5991,10 +6016,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488918</v>
+        <v>488616</v>
       </c>
       <c r="R53" t="n">
-        <v>6786607</v>
+        <v>6786648</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6053,10 +6078,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122566986</v>
+        <v>122566907</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6069,34 +6094,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488714</v>
+        <v>488852</v>
       </c>
       <c r="R54" t="n">
-        <v>6786574</v>
+        <v>6786673</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6155,10 +6185,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122566967</v>
+        <v>122567325</v>
       </c>
       <c r="B55" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6167,38 +6197,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488387</v>
+        <v>488576</v>
       </c>
       <c r="R55" t="n">
-        <v>6786773</v>
+        <v>6786782</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6257,10 +6292,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122567025</v>
+        <v>122567289</v>
       </c>
       <c r="B56" t="n">
-        <v>78411</v>
+        <v>8441</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6269,38 +6304,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488378</v>
+        <v>488322</v>
       </c>
       <c r="R56" t="n">
-        <v>6786805</v>
+        <v>6786810</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6359,10 +6399,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567027</v>
+        <v>122567318</v>
       </c>
       <c r="B57" t="n">
-        <v>78411</v>
+        <v>8441</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6371,38 +6411,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488618</v>
+        <v>488883</v>
       </c>
       <c r="R57" t="n">
-        <v>6786631</v>
+        <v>6786645</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6461,7 +6506,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122566978</v>
+        <v>122566998</v>
       </c>
       <c r="B58" t="n">
         <v>78766</v>
@@ -6501,10 +6546,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488583</v>
+        <v>488700</v>
       </c>
       <c r="R58" t="n">
-        <v>6786679</v>
+        <v>6786744</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6563,7 +6608,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122567018</v>
+        <v>122566956</v>
       </c>
       <c r="B59" t="n">
         <v>78766</v>
@@ -6603,10 +6648,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488345</v>
+        <v>488309</v>
       </c>
       <c r="R59" t="n">
-        <v>6786910</v>
+        <v>6786859</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6665,10 +6710,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122566983</v>
+        <v>122567321</v>
       </c>
       <c r="B60" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6677,38 +6722,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488609</v>
+        <v>488817</v>
       </c>
       <c r="R60" t="n">
-        <v>6786648</v>
+        <v>6786693</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6767,10 +6817,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122566889</v>
+        <v>122567292</v>
       </c>
       <c r="B61" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6779,38 +6829,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488296</v>
+        <v>488533</v>
       </c>
       <c r="R61" t="n">
-        <v>6786844</v>
+        <v>6786690</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6869,10 +6924,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122566908</v>
+        <v>122567311</v>
       </c>
       <c r="B62" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6881,35 +6936,31 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6918,10 +6969,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488892</v>
+        <v>488332</v>
       </c>
       <c r="R62" t="n">
-        <v>6786620</v>
+        <v>6786824</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6980,10 +7031,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122567297</v>
+        <v>122566987</v>
       </c>
       <c r="B63" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6992,43 +7043,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488804</v>
+        <v>488735</v>
       </c>
       <c r="R63" t="n">
-        <v>6786700</v>
+        <v>6786569</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7087,10 +7133,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122567309</v>
+        <v>122567009</v>
       </c>
       <c r="B64" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7099,43 +7145,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488707</v>
+        <v>488465</v>
       </c>
       <c r="R64" t="n">
-        <v>6786747</v>
+        <v>6786880</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7194,10 +7235,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122567289</v>
+        <v>122566961</v>
       </c>
       <c r="B65" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7206,43 +7247,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488322</v>
+        <v>488327</v>
       </c>
       <c r="R65" t="n">
-        <v>6786810</v>
+        <v>6786847</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7301,10 +7337,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122567291</v>
+        <v>122567014</v>
       </c>
       <c r="B66" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7313,43 +7349,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488440</v>
+        <v>488383</v>
       </c>
       <c r="R66" t="n">
-        <v>6786759</v>
+        <v>6786912</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7408,10 +7439,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122567327</v>
+        <v>122567008</v>
       </c>
       <c r="B67" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7420,43 +7451,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488442</v>
+        <v>488495</v>
       </c>
       <c r="R67" t="n">
-        <v>6786881</v>
+        <v>6786888</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7515,10 +7541,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122567323</v>
+        <v>122567000</v>
       </c>
       <c r="B68" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7527,43 +7553,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488686</v>
+        <v>488678</v>
       </c>
       <c r="R68" t="n">
-        <v>6786745</v>
+        <v>6786753</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7622,10 +7643,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122567318</v>
+        <v>122566908</v>
       </c>
       <c r="B69" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7634,31 +7655,35 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -7667,10 +7692,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488883</v>
+        <v>488892</v>
       </c>
       <c r="R69" t="n">
-        <v>6786645</v>
+        <v>6786620</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7729,10 +7754,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122566979</v>
+        <v>122566904</v>
       </c>
       <c r="B70" t="n">
-        <v>78766</v>
+        <v>90964</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7745,21 +7770,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7769,10 +7794,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488583</v>
+        <v>488552</v>
       </c>
       <c r="R70" t="n">
-        <v>6786676</v>
+        <v>6786834</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7831,7 +7856,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122567319</v>
+        <v>122567308</v>
       </c>
       <c r="B71" t="n">
         <v>8441</v>
@@ -7876,10 +7901,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488869</v>
+        <v>488669</v>
       </c>
       <c r="R71" t="n">
-        <v>6786685</v>
+        <v>6786761</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7938,7 +7963,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122567310</v>
+        <v>122567320</v>
       </c>
       <c r="B72" t="n">
         <v>8441</v>
@@ -7983,10 +8008,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488294</v>
+        <v>488833</v>
       </c>
       <c r="R72" t="n">
-        <v>6786825</v>
+        <v>6786674</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8045,7 +8070,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122566990</v>
+        <v>122567013</v>
       </c>
       <c r="B73" t="n">
         <v>78766</v>
@@ -8085,10 +8110,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488840</v>
+        <v>488389</v>
       </c>
       <c r="R73" t="n">
-        <v>6786622</v>
+        <v>6786901</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8147,10 +8172,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122566954</v>
+        <v>122567291</v>
       </c>
       <c r="B74" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8159,38 +8184,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488416</v>
+        <v>488440</v>
       </c>
       <c r="R74" t="n">
-        <v>6786896</v>
+        <v>6786759</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8249,10 +8279,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122567005</v>
+        <v>122567307</v>
       </c>
       <c r="B75" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8261,38 +8291,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488415</v>
+        <v>488535</v>
       </c>
       <c r="R75" t="n">
-        <v>6786889</v>
+        <v>6786843</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8453,10 +8488,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122566903</v>
+        <v>122567028</v>
       </c>
       <c r="B77" t="n">
-        <v>90964</v>
+        <v>78411</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8469,21 +8504,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8493,10 +8528,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488770</v>
+        <v>488611</v>
       </c>
       <c r="R77" t="n">
-        <v>6786732</v>
+        <v>6786649</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8555,7 +8590,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122566962</v>
+        <v>122567012</v>
       </c>
       <c r="B78" t="n">
         <v>78766</v>
@@ -8595,10 +8630,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488324</v>
+        <v>488420</v>
       </c>
       <c r="R78" t="n">
-        <v>6786843</v>
+        <v>6786898</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8657,10 +8692,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122567298</v>
+        <v>122566997</v>
       </c>
       <c r="B79" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8669,43 +8704,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488789</v>
+        <v>488731</v>
       </c>
       <c r="R79" t="n">
-        <v>6786702</v>
+        <v>6786733</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8764,7 +8794,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122567012</v>
+        <v>122567022</v>
       </c>
       <c r="B80" t="n">
         <v>78766</v>
@@ -8804,10 +8834,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488420</v>
+        <v>488137</v>
       </c>
       <c r="R80" t="n">
-        <v>6786898</v>
+        <v>6787026</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8866,10 +8896,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122566995</v>
+        <v>122567300</v>
       </c>
       <c r="B81" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8878,38 +8908,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488833</v>
+        <v>488768</v>
       </c>
       <c r="R81" t="n">
-        <v>6786674</v>
+        <v>6786742</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8968,10 +9003,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122567024</v>
+        <v>122567299</v>
       </c>
       <c r="B82" t="n">
-        <v>91196</v>
+        <v>8441</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8980,38 +9015,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>65</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488663</v>
+        <v>488786</v>
       </c>
       <c r="R82" t="n">
-        <v>6786615</v>
+        <v>6786723</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9070,10 +9110,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122566911</v>
+        <v>122567297</v>
       </c>
       <c r="B83" t="n">
-        <v>91235</v>
+        <v>8441</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9082,38 +9122,43 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>658</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488882</v>
+        <v>488804</v>
       </c>
       <c r="R83" t="n">
-        <v>6786609</v>
+        <v>6786700</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9172,7 +9217,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122567304</v>
+        <v>122567322</v>
       </c>
       <c r="B84" t="n">
         <v>8441</v>
@@ -9208,7 +9253,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9217,10 +9262,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488591</v>
+        <v>488700</v>
       </c>
       <c r="R84" t="n">
-        <v>6786769</v>
+        <v>6786746</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9279,10 +9324,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122567305</v>
+        <v>122566905</v>
       </c>
       <c r="B85" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9291,31 +9336,31 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9324,10 +9369,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488519</v>
+        <v>488294</v>
       </c>
       <c r="R85" t="n">
-        <v>6786844</v>
+        <v>6786826</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9386,10 +9431,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122567009</v>
+        <v>122566901</v>
       </c>
       <c r="B86" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9402,21 +9447,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9426,10 +9471,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488465</v>
+        <v>488142</v>
       </c>
       <c r="R86" t="n">
-        <v>6786880</v>
+        <v>6787017</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9488,7 +9533,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122566972</v>
+        <v>122566974</v>
       </c>
       <c r="B87" t="n">
         <v>78766</v>
@@ -9528,10 +9573,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488465</v>
+        <v>488486</v>
       </c>
       <c r="R87" t="n">
-        <v>6786729</v>
+        <v>6786718</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9590,7 +9635,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122566988</v>
+        <v>122566994</v>
       </c>
       <c r="B88" t="n">
         <v>78766</v>
@@ -9630,10 +9675,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488803</v>
+        <v>488883</v>
       </c>
       <c r="R88" t="n">
-        <v>6786562</v>
+        <v>6786645</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9692,7 +9737,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122566957</v>
+        <v>122566983</v>
       </c>
       <c r="B89" t="n">
         <v>78766</v>
@@ -9732,10 +9777,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488300</v>
+        <v>488609</v>
       </c>
       <c r="R89" t="n">
-        <v>6786820</v>
+        <v>6786648</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9794,10 +9839,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122567004</v>
+        <v>122567029</v>
       </c>
       <c r="B90" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9810,21 +9855,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9834,10 +9879,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488475</v>
+        <v>488664</v>
       </c>
       <c r="R90" t="n">
-        <v>6786864</v>
+        <v>6786615</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9896,10 +9941,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122566973</v>
+        <v>122566894</v>
       </c>
       <c r="B91" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9912,21 +9957,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9936,10 +9981,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488482</v>
+        <v>488182</v>
       </c>
       <c r="R91" t="n">
-        <v>6786720</v>
+        <v>6787001</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9998,7 +10043,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122566999</v>
+        <v>122567019</v>
       </c>
       <c r="B92" t="n">
         <v>78766</v>
@@ -10038,10 +10083,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488686</v>
+        <v>488297</v>
       </c>
       <c r="R92" t="n">
-        <v>6786738</v>
+        <v>6786946</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10100,10 +10145,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122567013</v>
+        <v>122567305</v>
       </c>
       <c r="B93" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10112,38 +10157,43 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488389</v>
+        <v>488519</v>
       </c>
       <c r="R93" t="n">
-        <v>6786901</v>
+        <v>6786844</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10202,7 +10252,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122566997</v>
+        <v>122567001</v>
       </c>
       <c r="B94" t="n">
         <v>78766</v>
@@ -10242,10 +10292,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488731</v>
+        <v>488583</v>
       </c>
       <c r="R94" t="n">
-        <v>6786733</v>
+        <v>6786774</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10304,10 +10354,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122566901</v>
+        <v>122566902</v>
       </c>
       <c r="B95" t="n">
-        <v>57631</v>
+        <v>90964</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10320,21 +10370,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10344,10 +10394,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>488142</v>
+        <v>488397</v>
       </c>
       <c r="R95" t="n">
-        <v>6787017</v>
+        <v>6786809</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10406,10 +10456,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122567314</v>
+        <v>122566968</v>
       </c>
       <c r="B96" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10418,43 +10468,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>488747</v>
+        <v>488431</v>
       </c>
       <c r="R96" t="n">
-        <v>6786566</v>
+        <v>6786772</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10513,10 +10558,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122567300</v>
+        <v>122566911</v>
       </c>
       <c r="B97" t="n">
-        <v>8441</v>
+        <v>91235</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10525,43 +10570,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>658</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>488768</v>
+        <v>488882</v>
       </c>
       <c r="R97" t="n">
-        <v>6786742</v>
+        <v>6786609</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10620,7 +10660,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122567301</v>
+        <v>122567298</v>
       </c>
       <c r="B98" t="n">
         <v>8441</v>
@@ -10665,10 +10705,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>488718</v>
+        <v>488789</v>
       </c>
       <c r="R98" t="n">
-        <v>6786752</v>
+        <v>6786702</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10727,7 +10767,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122567320</v>
+        <v>122567303</v>
       </c>
       <c r="B99" t="n">
         <v>8441</v>
@@ -10763,7 +10803,7 @@
       <c r="I99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -10772,10 +10812,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>488833</v>
+        <v>488600</v>
       </c>
       <c r="R99" t="n">
-        <v>6786674</v>
+        <v>6786772</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10834,7 +10874,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122566996</v>
+        <v>122566988</v>
       </c>
       <c r="B100" t="n">
         <v>78766</v>
@@ -10874,10 +10914,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>488757</v>
+        <v>488803</v>
       </c>
       <c r="R100" t="n">
-        <v>6786723</v>
+        <v>6786562</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10936,10 +10976,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122566897</v>
+        <v>122566978</v>
       </c>
       <c r="B101" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10952,21 +10992,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10976,10 +11016,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>488892</v>
+        <v>488583</v>
       </c>
       <c r="R101" t="n">
-        <v>6786591</v>
+        <v>6786679</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11038,10 +11078,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122567299</v>
+        <v>122566973</v>
       </c>
       <c r="B102" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11050,43 +11090,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>488786</v>
+        <v>488482</v>
       </c>
       <c r="R102" t="n">
-        <v>6786723</v>
+        <v>6786720</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11145,10 +11180,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122566902</v>
+        <v>122566999</v>
       </c>
       <c r="B103" t="n">
-        <v>90964</v>
+        <v>78766</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11161,21 +11196,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11185,10 +11220,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>488397</v>
+        <v>488686</v>
       </c>
       <c r="R103" t="n">
-        <v>6786809</v>
+        <v>6786738</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11247,7 +11282,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122566970</v>
+        <v>122566990</v>
       </c>
       <c r="B104" t="n">
         <v>78766</v>
@@ -11287,10 +11322,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488469</v>
+        <v>488840</v>
       </c>
       <c r="R104" t="n">
-        <v>6786751</v>
+        <v>6786622</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11349,7 +11384,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122566958</v>
+        <v>122566957</v>
       </c>
       <c r="B105" t="n">
         <v>78766</v>
@@ -11389,10 +11424,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488301</v>
+        <v>488300</v>
       </c>
       <c r="R105" t="n">
-        <v>6786839</v>
+        <v>6786820</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11451,10 +11486,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122566899</v>
+        <v>122567004</v>
       </c>
       <c r="B106" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11467,21 +11502,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11491,10 +11526,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488482</v>
+        <v>488475</v>
       </c>
       <c r="R106" t="n">
-        <v>6786720</v>
+        <v>6786864</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11553,10 +11588,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122566898</v>
+        <v>122567023</v>
       </c>
       <c r="B107" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11569,21 +11604,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11593,10 +11628,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488296</v>
+        <v>488135</v>
       </c>
       <c r="R107" t="n">
-        <v>6786844</v>
+        <v>6787033</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11655,10 +11690,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122567313</v>
+        <v>122566967</v>
       </c>
       <c r="B108" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11667,43 +11702,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>488616</v>
+        <v>488387</v>
       </c>
       <c r="R108" t="n">
-        <v>6786649</v>
+        <v>6786773</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11762,10 +11792,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122566905</v>
+        <v>122567018</v>
       </c>
       <c r="B109" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11778,39 +11808,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488294</v>
+        <v>488345</v>
       </c>
       <c r="R109" t="n">
-        <v>6786826</v>
+        <v>6786910</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11869,10 +11894,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122566892</v>
+        <v>122567026</v>
       </c>
       <c r="B110" t="n">
-        <v>79384</v>
+        <v>78411</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11885,21 +11910,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11909,10 +11934,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>488699</v>
+        <v>488539</v>
       </c>
       <c r="R110" t="n">
-        <v>6786599</v>
+        <v>6786689</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11971,7 +11996,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122566984</v>
+        <v>122566965</v>
       </c>
       <c r="B111" t="n">
         <v>78766</v>
@@ -12011,10 +12036,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>488699</v>
+        <v>488378</v>
       </c>
       <c r="R111" t="n">
-        <v>6786596</v>
+        <v>6786805</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12073,7 +12098,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122566994</v>
+        <v>122566985</v>
       </c>
       <c r="B112" t="n">
         <v>78766</v>
@@ -12113,10 +12138,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>488883</v>
+        <v>488698</v>
       </c>
       <c r="R112" t="n">
-        <v>6786645</v>
+        <v>6786584</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12175,7 +12200,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122566968</v>
+        <v>122567015</v>
       </c>
       <c r="B113" t="n">
         <v>78766</v>
@@ -12215,10 +12240,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488431</v>
+        <v>488366</v>
       </c>
       <c r="R113" t="n">
-        <v>6786772</v>
+        <v>6786907</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12277,7 +12302,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122567290</v>
+        <v>122567294</v>
       </c>
       <c r="B114" t="n">
         <v>8441</v>
@@ -12322,10 +12347,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488345</v>
+        <v>488801</v>
       </c>
       <c r="R114" t="n">
-        <v>6786796</v>
+        <v>6786563</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12384,10 +12409,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122567308</v>
+        <v>122566898</v>
       </c>
       <c r="B115" t="n">
-        <v>8441</v>
+        <v>57631</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12396,43 +12421,38 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>488669</v>
+        <v>488296</v>
       </c>
       <c r="R115" t="n">
-        <v>6786761</v>
+        <v>6786844</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12491,7 +12511,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122567293</v>
+        <v>122567301</v>
       </c>
       <c r="B116" t="n">
         <v>8441</v>
@@ -12536,10 +12556,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>488790</v>
+        <v>488718</v>
       </c>
       <c r="R116" t="n">
-        <v>6786547</v>
+        <v>6786752</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12598,10 +12618,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122567324</v>
+        <v>122566981</v>
       </c>
       <c r="B117" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12610,43 +12630,38 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>488638</v>
+        <v>488599</v>
       </c>
       <c r="R117" t="n">
-        <v>6786764</v>
+        <v>6786673</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12705,7 +12720,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122566966</v>
+        <v>122567005</v>
       </c>
       <c r="B118" t="n">
         <v>78766</v>
@@ -12745,10 +12760,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>488390</v>
+        <v>488415</v>
       </c>
       <c r="R118" t="n">
-        <v>6786813</v>
+        <v>6786889</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12807,7 +12822,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122566964</v>
+        <v>122566969</v>
       </c>
       <c r="B119" t="n">
         <v>78766</v>
@@ -12847,10 +12862,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>488351</v>
+        <v>488452</v>
       </c>
       <c r="R119" t="n">
-        <v>6786831</v>
+        <v>6786772</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12909,10 +12924,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122567019</v>
+        <v>122567025</v>
       </c>
       <c r="B120" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12925,21 +12940,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12949,10 +12964,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>488297</v>
+        <v>488378</v>
       </c>
       <c r="R120" t="n">
-        <v>6786946</v>
+        <v>6786805</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13011,7 +13026,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122567029</v>
+        <v>122567030</v>
       </c>
       <c r="B121" t="n">
         <v>78411</v>
@@ -13051,10 +13066,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488664</v>
+        <v>488769</v>
       </c>
       <c r="R121" t="n">
-        <v>6786615</v>
+        <v>6786552</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13113,10 +13128,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122566907</v>
+        <v>122566892</v>
       </c>
       <c r="B122" t="n">
-        <v>57494</v>
+        <v>79384</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13129,39 +13144,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488852</v>
+        <v>488699</v>
       </c>
       <c r="R122" t="n">
-        <v>6786673</v>
+        <v>6786599</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13220,10 +13230,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122566987</v>
+        <v>122566893</v>
       </c>
       <c r="B123" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13236,21 +13246,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13260,10 +13270,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>488735</v>
+        <v>488693</v>
       </c>
       <c r="R123" t="n">
-        <v>6786569</v>
+        <v>6786741</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13322,10 +13332,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122566985</v>
+        <v>122566889</v>
       </c>
       <c r="B124" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13338,21 +13348,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13362,10 +13372,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>488698</v>
+        <v>488296</v>
       </c>
       <c r="R124" t="n">
-        <v>6786584</v>
+        <v>6786844</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13424,10 +13434,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122567321</v>
+        <v>122566909</v>
       </c>
       <c r="B125" t="n">
-        <v>8441</v>
+        <v>91389</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13436,43 +13446,38 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>106545</v>
+        <v>1209</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>488817</v>
+        <v>488882</v>
       </c>
       <c r="R125" t="n">
-        <v>6786693</v>
+        <v>6786607</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13531,10 +13536,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122567023</v>
+        <v>122566896</v>
       </c>
       <c r="B126" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13547,21 +13552,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13571,10 +13576,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>488135</v>
+        <v>488882</v>
       </c>
       <c r="R126" t="n">
-        <v>6787033</v>
+        <v>6786607</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13633,10 +13638,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122566891</v>
+        <v>122567310</v>
       </c>
       <c r="B127" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13645,38 +13650,43 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>488616</v>
+        <v>488294</v>
       </c>
       <c r="R127" t="n">
-        <v>6786648</v>
+        <v>6786825</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13735,10 +13745,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122566896</v>
+        <v>122567317</v>
       </c>
       <c r="B128" t="n">
-        <v>90944</v>
+        <v>8441</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13747,38 +13757,43 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>488882</v>
+        <v>488892</v>
       </c>
       <c r="R128" t="n">
-        <v>6786607</v>
+        <v>6786620</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13837,10 +13852,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122567295</v>
+        <v>122567011</v>
       </c>
       <c r="B129" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13849,43 +13864,38 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>488850</v>
+        <v>488427</v>
       </c>
       <c r="R129" t="n">
-        <v>6786668</v>
+        <v>6786888</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13944,10 +13954,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122567294</v>
+        <v>122566958</v>
       </c>
       <c r="B130" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13956,43 +13966,38 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>488801</v>
+        <v>488301</v>
       </c>
       <c r="R130" t="n">
-        <v>6786563</v>
+        <v>6786839</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14051,10 +14056,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122567303</v>
+        <v>122566960</v>
       </c>
       <c r="B131" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14063,43 +14068,38 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>488600</v>
+        <v>488322</v>
       </c>
       <c r="R131" t="n">
-        <v>6786772</v>
+        <v>6786853</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14158,10 +14158,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122567028</v>
+        <v>122566966</v>
       </c>
       <c r="B132" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14174,21 +14174,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14198,10 +14198,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>488611</v>
+        <v>488390</v>
       </c>
       <c r="R132" t="n">
-        <v>6786649</v>
+        <v>6786813</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>

--- a/artfynd/A 61338-2024 artfynd.xlsx
+++ b/artfynd/A 61338-2024 artfynd.xlsx
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567024</v>
+        <v>122566970</v>
       </c>
       <c r="B7" t="n">
-        <v>91196</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,25 +1221,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488663</v>
+        <v>488469</v>
       </c>
       <c r="R7" t="n">
-        <v>6786615</v>
+        <v>6786751</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566970</v>
+        <v>122566996</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488469</v>
+        <v>488757</v>
       </c>
       <c r="R8" t="n">
-        <v>6786751</v>
+        <v>6786723</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566996</v>
+        <v>122567032</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>5173</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,38 +1425,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488757</v>
+        <v>488901</v>
       </c>
       <c r="R9" t="n">
-        <v>6786723</v>
+        <v>6786589</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122567032</v>
+        <v>122567024</v>
       </c>
       <c r="B10" t="n">
-        <v>5173</v>
+        <v>91196</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,43 +1532,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>65</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488901</v>
+        <v>488663</v>
       </c>
       <c r="R10" t="n">
-        <v>6786589</v>
+        <v>6786615</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1724,10 +1724,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567006</v>
+        <v>122567326</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,38 +1736,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488556</v>
+        <v>488545</v>
       </c>
       <c r="R12" t="n">
-        <v>6786835</v>
+        <v>6786849</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,7 +1831,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566995</v>
+        <v>122567006</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1866,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488833</v>
+        <v>488556</v>
       </c>
       <c r="R13" t="n">
-        <v>6786674</v>
+        <v>6786835</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,7 +1933,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566963</v>
+        <v>122566995</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -1968,10 +1973,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488341</v>
+        <v>488833</v>
       </c>
       <c r="R14" t="n">
-        <v>6786832</v>
+        <v>6786674</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,10 +2035,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567319</v>
+        <v>122566963</v>
       </c>
       <c r="B15" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,43 +2047,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488869</v>
+        <v>488341</v>
       </c>
       <c r="R15" t="n">
-        <v>6786685</v>
+        <v>6786832</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567309</v>
+        <v>122567319</v>
       </c>
       <c r="B16" t="n">
         <v>8441</v>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488707</v>
+        <v>488869</v>
       </c>
       <c r="R16" t="n">
-        <v>6786747</v>
+        <v>6786685</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,7 +2244,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122567326</v>
+        <v>122567309</v>
       </c>
       <c r="B17" t="n">
         <v>8441</v>
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488545</v>
+        <v>488707</v>
       </c>
       <c r="R17" t="n">
-        <v>6786849</v>
+        <v>6786747</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3279,10 +3279,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566912</v>
+        <v>122567020</v>
       </c>
       <c r="B27" t="n">
-        <v>91235</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3295,21 +3295,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488895</v>
+        <v>488185</v>
       </c>
       <c r="R27" t="n">
-        <v>6786588</v>
+        <v>6787005</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3381,10 +3381,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567296</v>
+        <v>122567010</v>
       </c>
       <c r="B28" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3393,43 +3393,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488834</v>
+        <v>488442</v>
       </c>
       <c r="R28" t="n">
-        <v>6786685</v>
+        <v>6786881</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3488,7 +3483,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567312</v>
+        <v>122567296</v>
       </c>
       <c r="B29" t="n">
         <v>8441</v>
@@ -3524,7 +3519,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3533,10 +3528,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488341</v>
+        <v>488834</v>
       </c>
       <c r="R29" t="n">
-        <v>6786832</v>
+        <v>6786685</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3595,10 +3590,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567020</v>
+        <v>122567312</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3607,38 +3602,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488185</v>
+        <v>488341</v>
       </c>
       <c r="R30" t="n">
-        <v>6787005</v>
+        <v>6786832</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3697,10 +3697,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567010</v>
+        <v>122566912</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>91235</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3713,21 +3713,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3737,10 +3737,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488442</v>
+        <v>488895</v>
       </c>
       <c r="R31" t="n">
-        <v>6786881</v>
+        <v>6786588</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4426,10 +4426,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567295</v>
+        <v>122566899</v>
       </c>
       <c r="B38" t="n">
-        <v>8441</v>
+        <v>57631</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4438,43 +4438,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488850</v>
+        <v>488482</v>
       </c>
       <c r="R38" t="n">
-        <v>6786668</v>
+        <v>6786720</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4533,10 +4528,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122567002</v>
+        <v>122567304</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4545,38 +4540,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488569</v>
+        <v>488591</v>
       </c>
       <c r="R39" t="n">
-        <v>6786787</v>
+        <v>6786769</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4635,10 +4635,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122566991</v>
+        <v>122567315</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4647,38 +4647,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488918</v>
+        <v>488773</v>
       </c>
       <c r="R40" t="n">
-        <v>6786607</v>
+        <v>6786561</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4737,10 +4742,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122566982</v>
+        <v>122567295</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4749,38 +4754,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488600</v>
+        <v>488850</v>
       </c>
       <c r="R41" t="n">
-        <v>6786662</v>
+        <v>6786668</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4839,7 +4849,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122566962</v>
+        <v>122567002</v>
       </c>
       <c r="B42" t="n">
         <v>78766</v>
@@ -4879,10 +4889,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488324</v>
+        <v>488569</v>
       </c>
       <c r="R42" t="n">
-        <v>6786843</v>
+        <v>6786787</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4941,10 +4951,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122566899</v>
+        <v>122566991</v>
       </c>
       <c r="B43" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4957,21 +4967,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4981,10 +4991,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488482</v>
+        <v>488918</v>
       </c>
       <c r="R43" t="n">
-        <v>6786720</v>
+        <v>6786607</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5043,10 +5053,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122567304</v>
+        <v>122566982</v>
       </c>
       <c r="B44" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5055,43 +5065,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488591</v>
+        <v>488600</v>
       </c>
       <c r="R44" t="n">
-        <v>6786769</v>
+        <v>6786662</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5150,10 +5155,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122567315</v>
+        <v>122566962</v>
       </c>
       <c r="B45" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5162,43 +5167,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488773</v>
+        <v>488324</v>
       </c>
       <c r="R45" t="n">
-        <v>6786561</v>
+        <v>6786843</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6292,10 +6292,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122567289</v>
+        <v>122566998</v>
       </c>
       <c r="B56" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6304,43 +6304,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488322</v>
+        <v>488700</v>
       </c>
       <c r="R56" t="n">
-        <v>6786810</v>
+        <v>6786744</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6399,10 +6394,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567318</v>
+        <v>122566956</v>
       </c>
       <c r="B57" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6411,43 +6406,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488883</v>
+        <v>488309</v>
       </c>
       <c r="R57" t="n">
-        <v>6786645</v>
+        <v>6786859</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6506,10 +6496,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122566998</v>
+        <v>122567289</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6518,38 +6508,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488700</v>
+        <v>488322</v>
       </c>
       <c r="R58" t="n">
-        <v>6786744</v>
+        <v>6786810</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6608,10 +6603,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122566956</v>
+        <v>122567318</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6620,38 +6615,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488309</v>
+        <v>488883</v>
       </c>
       <c r="R59" t="n">
-        <v>6786859</v>
+        <v>6786645</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7541,10 +7541,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122567000</v>
+        <v>122566904</v>
       </c>
       <c r="B68" t="n">
-        <v>78766</v>
+        <v>90964</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7557,21 +7557,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7581,10 +7581,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488678</v>
+        <v>488552</v>
       </c>
       <c r="R68" t="n">
-        <v>6786753</v>
+        <v>6786834</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7643,10 +7643,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122566908</v>
+        <v>122567000</v>
       </c>
       <c r="B69" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7659,43 +7659,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488892</v>
+        <v>488678</v>
       </c>
       <c r="R69" t="n">
-        <v>6786620</v>
+        <v>6786753</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7754,10 +7745,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122566904</v>
+        <v>122566908</v>
       </c>
       <c r="B70" t="n">
-        <v>90964</v>
+        <v>57494</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7770,34 +7761,43 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488552</v>
+        <v>488892</v>
       </c>
       <c r="R70" t="n">
-        <v>6786834</v>
+        <v>6786620</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8590,7 +8590,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122567012</v>
+        <v>122566997</v>
       </c>
       <c r="B78" t="n">
         <v>78766</v>
@@ -8630,10 +8630,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488420</v>
+        <v>488731</v>
       </c>
       <c r="R78" t="n">
-        <v>6786898</v>
+        <v>6786733</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8692,7 +8692,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122566997</v>
+        <v>122567022</v>
       </c>
       <c r="B79" t="n">
         <v>78766</v>
@@ -8732,10 +8732,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488731</v>
+        <v>488137</v>
       </c>
       <c r="R79" t="n">
-        <v>6786733</v>
+        <v>6787026</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8794,10 +8794,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122567022</v>
+        <v>122566901</v>
       </c>
       <c r="B80" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8810,21 +8810,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8834,10 +8834,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488137</v>
+        <v>488142</v>
       </c>
       <c r="R80" t="n">
-        <v>6787026</v>
+        <v>6787017</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8896,10 +8896,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122567300</v>
+        <v>122567012</v>
       </c>
       <c r="B81" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8908,43 +8908,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488768</v>
+        <v>488420</v>
       </c>
       <c r="R81" t="n">
-        <v>6786742</v>
+        <v>6786898</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9003,10 +8998,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122567299</v>
+        <v>122566905</v>
       </c>
       <c r="B82" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9015,31 +9010,31 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9048,10 +9043,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488786</v>
+        <v>488294</v>
       </c>
       <c r="R82" t="n">
-        <v>6786723</v>
+        <v>6786826</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9110,7 +9105,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122567297</v>
+        <v>122567300</v>
       </c>
       <c r="B83" t="n">
         <v>8441</v>
@@ -9155,10 +9150,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488804</v>
+        <v>488768</v>
       </c>
       <c r="R83" t="n">
-        <v>6786700</v>
+        <v>6786742</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9217,7 +9212,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122567322</v>
+        <v>122567299</v>
       </c>
       <c r="B84" t="n">
         <v>8441</v>
@@ -9253,7 +9248,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9262,10 +9257,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488700</v>
+        <v>488786</v>
       </c>
       <c r="R84" t="n">
-        <v>6786746</v>
+        <v>6786723</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9324,10 +9319,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122566905</v>
+        <v>122567297</v>
       </c>
       <c r="B85" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9336,31 +9331,31 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9369,10 +9364,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488294</v>
+        <v>488804</v>
       </c>
       <c r="R85" t="n">
-        <v>6786826</v>
+        <v>6786700</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9431,10 +9426,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122566901</v>
+        <v>122567322</v>
       </c>
       <c r="B86" t="n">
-        <v>57631</v>
+        <v>8441</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9443,38 +9438,43 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488142</v>
+        <v>488700</v>
       </c>
       <c r="R86" t="n">
-        <v>6787017</v>
+        <v>6786746</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9533,10 +9533,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122566974</v>
+        <v>122567029</v>
       </c>
       <c r="B87" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9549,21 +9549,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9573,10 +9573,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488486</v>
+        <v>488664</v>
       </c>
       <c r="R87" t="n">
-        <v>6786718</v>
+        <v>6786615</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9635,7 +9635,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122566994</v>
+        <v>122566974</v>
       </c>
       <c r="B88" t="n">
         <v>78766</v>
@@ -9675,10 +9675,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488883</v>
+        <v>488486</v>
       </c>
       <c r="R88" t="n">
-        <v>6786645</v>
+        <v>6786718</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9839,10 +9839,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122567029</v>
+        <v>122566894</v>
       </c>
       <c r="B90" t="n">
-        <v>78411</v>
+        <v>79384</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9855,21 +9855,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9879,10 +9879,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488664</v>
+        <v>488182</v>
       </c>
       <c r="R90" t="n">
-        <v>6786615</v>
+        <v>6787001</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9941,10 +9941,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122566894</v>
+        <v>122567019</v>
       </c>
       <c r="B91" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9957,21 +9957,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9981,10 +9981,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488182</v>
+        <v>488297</v>
       </c>
       <c r="R91" t="n">
-        <v>6787001</v>
+        <v>6786946</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10043,10 +10043,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122567019</v>
+        <v>122567305</v>
       </c>
       <c r="B92" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10055,38 +10055,43 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488297</v>
+        <v>488519</v>
       </c>
       <c r="R92" t="n">
-        <v>6786946</v>
+        <v>6786844</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10145,10 +10150,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122567305</v>
+        <v>122566994</v>
       </c>
       <c r="B93" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10157,43 +10162,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488519</v>
+        <v>488883</v>
       </c>
       <c r="R93" t="n">
-        <v>6786844</v>
+        <v>6786645</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10660,10 +10660,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122567298</v>
+        <v>122566988</v>
       </c>
       <c r="B98" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10672,43 +10672,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>488789</v>
+        <v>488803</v>
       </c>
       <c r="R98" t="n">
-        <v>6786702</v>
+        <v>6786562</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10767,10 +10762,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122567303</v>
+        <v>122566978</v>
       </c>
       <c r="B99" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10779,43 +10774,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>488600</v>
+        <v>488583</v>
       </c>
       <c r="R99" t="n">
-        <v>6786772</v>
+        <v>6786679</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10874,7 +10864,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122566988</v>
+        <v>122566973</v>
       </c>
       <c r="B100" t="n">
         <v>78766</v>
@@ -10914,10 +10904,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>488803</v>
+        <v>488482</v>
       </c>
       <c r="R100" t="n">
-        <v>6786562</v>
+        <v>6786720</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10976,7 +10966,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122566978</v>
+        <v>122566999</v>
       </c>
       <c r="B101" t="n">
         <v>78766</v>
@@ -11016,10 +11006,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>488583</v>
+        <v>488686</v>
       </c>
       <c r="R101" t="n">
-        <v>6786679</v>
+        <v>6786738</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11078,7 +11068,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122566973</v>
+        <v>122566990</v>
       </c>
       <c r="B102" t="n">
         <v>78766</v>
@@ -11118,10 +11108,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>488482</v>
+        <v>488840</v>
       </c>
       <c r="R102" t="n">
-        <v>6786720</v>
+        <v>6786622</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11180,7 +11170,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122566999</v>
+        <v>122566957</v>
       </c>
       <c r="B103" t="n">
         <v>78766</v>
@@ -11220,10 +11210,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>488686</v>
+        <v>488300</v>
       </c>
       <c r="R103" t="n">
-        <v>6786738</v>
+        <v>6786820</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11282,7 +11272,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122566990</v>
+        <v>122567004</v>
       </c>
       <c r="B104" t="n">
         <v>78766</v>
@@ -11322,10 +11312,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488840</v>
+        <v>488475</v>
       </c>
       <c r="R104" t="n">
-        <v>6786622</v>
+        <v>6786864</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11384,7 +11374,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122566957</v>
+        <v>122567023</v>
       </c>
       <c r="B105" t="n">
         <v>78766</v>
@@ -11424,10 +11414,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488300</v>
+        <v>488135</v>
       </c>
       <c r="R105" t="n">
-        <v>6786820</v>
+        <v>6787033</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11486,7 +11476,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122567004</v>
+        <v>122566967</v>
       </c>
       <c r="B106" t="n">
         <v>78766</v>
@@ -11526,10 +11516,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488475</v>
+        <v>488387</v>
       </c>
       <c r="R106" t="n">
-        <v>6786864</v>
+        <v>6786773</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11588,10 +11578,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122567023</v>
+        <v>122567298</v>
       </c>
       <c r="B107" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11600,38 +11590,43 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488135</v>
+        <v>488789</v>
       </c>
       <c r="R107" t="n">
-        <v>6787033</v>
+        <v>6786702</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11690,10 +11685,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122566967</v>
+        <v>122567303</v>
       </c>
       <c r="B108" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11702,38 +11697,43 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>488387</v>
+        <v>488600</v>
       </c>
       <c r="R108" t="n">
-        <v>6786773</v>
+        <v>6786772</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11792,10 +11792,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122567018</v>
+        <v>122567026</v>
       </c>
       <c r="B109" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11808,21 +11808,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11832,10 +11832,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488345</v>
+        <v>488539</v>
       </c>
       <c r="R109" t="n">
-        <v>6786910</v>
+        <v>6786689</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11894,10 +11894,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122567026</v>
+        <v>122566965</v>
       </c>
       <c r="B110" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11910,21 +11910,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11934,10 +11934,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>488539</v>
+        <v>488378</v>
       </c>
       <c r="R110" t="n">
-        <v>6786689</v>
+        <v>6786805</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11996,7 +11996,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122566965</v>
+        <v>122567015</v>
       </c>
       <c r="B111" t="n">
         <v>78766</v>
@@ -12036,10 +12036,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>488378</v>
+        <v>488366</v>
       </c>
       <c r="R111" t="n">
-        <v>6786805</v>
+        <v>6786907</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12098,7 +12098,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122566985</v>
+        <v>122567018</v>
       </c>
       <c r="B112" t="n">
         <v>78766</v>
@@ -12138,10 +12138,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>488698</v>
+        <v>488345</v>
       </c>
       <c r="R112" t="n">
-        <v>6786584</v>
+        <v>6786910</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12200,10 +12200,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122567015</v>
+        <v>122567294</v>
       </c>
       <c r="B113" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12212,38 +12212,43 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488366</v>
+        <v>488801</v>
       </c>
       <c r="R113" t="n">
-        <v>6786907</v>
+        <v>6786563</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12302,10 +12307,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122567294</v>
+        <v>122566985</v>
       </c>
       <c r="B114" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12314,43 +12319,38 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488801</v>
+        <v>488698</v>
       </c>
       <c r="R114" t="n">
-        <v>6786563</v>
+        <v>6786584</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>

--- a/artfynd/A 61338-2024 artfynd.xlsx
+++ b/artfynd/A 61338-2024 artfynd.xlsx
@@ -1724,10 +1724,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567326</v>
+        <v>122567006</v>
       </c>
       <c r="B12" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,43 +1736,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488545</v>
+        <v>488556</v>
       </c>
       <c r="R12" t="n">
-        <v>6786849</v>
+        <v>6786835</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,7 +1826,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567006</v>
+        <v>122566995</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1871,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488556</v>
+        <v>488833</v>
       </c>
       <c r="R13" t="n">
-        <v>6786835</v>
+        <v>6786674</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1933,7 +1928,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566995</v>
+        <v>122566963</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -1973,10 +1968,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488833</v>
+        <v>488341</v>
       </c>
       <c r="R14" t="n">
-        <v>6786674</v>
+        <v>6786832</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2035,10 +2030,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566963</v>
+        <v>122567319</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2047,38 +2042,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488341</v>
+        <v>488869</v>
       </c>
       <c r="R15" t="n">
-        <v>6786832</v>
+        <v>6786685</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567319</v>
+        <v>122567309</v>
       </c>
       <c r="B16" t="n">
         <v>8441</v>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488869</v>
+        <v>488707</v>
       </c>
       <c r="R16" t="n">
-        <v>6786685</v>
+        <v>6786747</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,7 +2244,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122567309</v>
+        <v>122567326</v>
       </c>
       <c r="B17" t="n">
         <v>8441</v>
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488707</v>
+        <v>488545</v>
       </c>
       <c r="R17" t="n">
-        <v>6786747</v>
+        <v>6786849</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3279,10 +3279,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122567020</v>
+        <v>122566912</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>91235</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3295,21 +3295,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488185</v>
+        <v>488895</v>
       </c>
       <c r="R27" t="n">
-        <v>6787005</v>
+        <v>6786588</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3381,10 +3381,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567010</v>
+        <v>122567296</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3393,38 +3393,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488442</v>
+        <v>488834</v>
       </c>
       <c r="R28" t="n">
-        <v>6786881</v>
+        <v>6786685</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3483,7 +3488,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567296</v>
+        <v>122567312</v>
       </c>
       <c r="B29" t="n">
         <v>8441</v>
@@ -3519,7 +3524,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3528,10 +3533,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488834</v>
+        <v>488341</v>
       </c>
       <c r="R29" t="n">
-        <v>6786685</v>
+        <v>6786832</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3590,10 +3595,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567312</v>
+        <v>122567020</v>
       </c>
       <c r="B30" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3602,43 +3607,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488341</v>
+        <v>488185</v>
       </c>
       <c r="R30" t="n">
-        <v>6786832</v>
+        <v>6787005</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3697,10 +3697,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122566912</v>
+        <v>122567010</v>
       </c>
       <c r="B31" t="n">
-        <v>91235</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3713,21 +3713,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3737,10 +3737,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488895</v>
+        <v>488442</v>
       </c>
       <c r="R31" t="n">
-        <v>6786588</v>
+        <v>6786881</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4426,10 +4426,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122566899</v>
+        <v>122567295</v>
       </c>
       <c r="B38" t="n">
-        <v>57631</v>
+        <v>8441</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4438,38 +4438,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488482</v>
+        <v>488850</v>
       </c>
       <c r="R38" t="n">
-        <v>6786720</v>
+        <v>6786668</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4528,10 +4533,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122567304</v>
+        <v>122567002</v>
       </c>
       <c r="B39" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4540,43 +4545,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488591</v>
+        <v>488569</v>
       </c>
       <c r="R39" t="n">
-        <v>6786769</v>
+        <v>6786787</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4635,10 +4635,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122567315</v>
+        <v>122566991</v>
       </c>
       <c r="B40" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4647,43 +4647,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488773</v>
+        <v>488918</v>
       </c>
       <c r="R40" t="n">
-        <v>6786561</v>
+        <v>6786607</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4742,10 +4737,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567295</v>
+        <v>122566982</v>
       </c>
       <c r="B41" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4754,43 +4749,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488850</v>
+        <v>488600</v>
       </c>
       <c r="R41" t="n">
-        <v>6786668</v>
+        <v>6786662</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4849,7 +4839,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567002</v>
+        <v>122566962</v>
       </c>
       <c r="B42" t="n">
         <v>78766</v>
@@ -4889,10 +4879,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488569</v>
+        <v>488324</v>
       </c>
       <c r="R42" t="n">
-        <v>6786787</v>
+        <v>6786843</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4951,10 +4941,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122566991</v>
+        <v>122566899</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4967,21 +4957,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4991,10 +4981,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488918</v>
+        <v>488482</v>
       </c>
       <c r="R43" t="n">
-        <v>6786607</v>
+        <v>6786720</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5053,10 +5043,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122566982</v>
+        <v>122567304</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5065,38 +5055,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488600</v>
+        <v>488591</v>
       </c>
       <c r="R44" t="n">
-        <v>6786662</v>
+        <v>6786769</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5155,10 +5150,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122566962</v>
+        <v>122567315</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5167,38 +5162,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488324</v>
+        <v>488773</v>
       </c>
       <c r="R45" t="n">
-        <v>6786843</v>
+        <v>6786561</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5976,10 +5976,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122566891</v>
+        <v>122567325</v>
       </c>
       <c r="B53" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5988,38 +5988,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488616</v>
+        <v>488576</v>
       </c>
       <c r="R53" t="n">
-        <v>6786648</v>
+        <v>6786782</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6078,10 +6083,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122566907</v>
+        <v>122566891</v>
       </c>
       <c r="B54" t="n">
-        <v>57494</v>
+        <v>79384</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6094,39 +6099,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488852</v>
+        <v>488616</v>
       </c>
       <c r="R54" t="n">
-        <v>6786673</v>
+        <v>6786648</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6185,10 +6185,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122567325</v>
+        <v>122566907</v>
       </c>
       <c r="B55" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6197,31 +6197,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488576</v>
+        <v>488852</v>
       </c>
       <c r="R55" t="n">
-        <v>6786782</v>
+        <v>6786673</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -10660,10 +10660,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122566988</v>
+        <v>122567298</v>
       </c>
       <c r="B98" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10672,38 +10672,43 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>488803</v>
+        <v>488789</v>
       </c>
       <c r="R98" t="n">
-        <v>6786562</v>
+        <v>6786702</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10762,10 +10767,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122566978</v>
+        <v>122567303</v>
       </c>
       <c r="B99" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10774,38 +10779,43 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>488583</v>
+        <v>488600</v>
       </c>
       <c r="R99" t="n">
-        <v>6786679</v>
+        <v>6786772</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10864,7 +10874,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122566973</v>
+        <v>122566988</v>
       </c>
       <c r="B100" t="n">
         <v>78766</v>
@@ -10904,10 +10914,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>488482</v>
+        <v>488803</v>
       </c>
       <c r="R100" t="n">
-        <v>6786720</v>
+        <v>6786562</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10966,7 +10976,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122566999</v>
+        <v>122566978</v>
       </c>
       <c r="B101" t="n">
         <v>78766</v>
@@ -11006,10 +11016,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>488686</v>
+        <v>488583</v>
       </c>
       <c r="R101" t="n">
-        <v>6786738</v>
+        <v>6786679</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11068,7 +11078,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122566990</v>
+        <v>122566973</v>
       </c>
       <c r="B102" t="n">
         <v>78766</v>
@@ -11108,10 +11118,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>488840</v>
+        <v>488482</v>
       </c>
       <c r="R102" t="n">
-        <v>6786622</v>
+        <v>6786720</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11170,7 +11180,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122566957</v>
+        <v>122566999</v>
       </c>
       <c r="B103" t="n">
         <v>78766</v>
@@ -11210,10 +11220,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>488300</v>
+        <v>488686</v>
       </c>
       <c r="R103" t="n">
-        <v>6786820</v>
+        <v>6786738</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11272,7 +11282,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122567004</v>
+        <v>122566990</v>
       </c>
       <c r="B104" t="n">
         <v>78766</v>
@@ -11312,10 +11322,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488475</v>
+        <v>488840</v>
       </c>
       <c r="R104" t="n">
-        <v>6786864</v>
+        <v>6786622</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11374,7 +11384,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122567023</v>
+        <v>122566957</v>
       </c>
       <c r="B105" t="n">
         <v>78766</v>
@@ -11414,10 +11424,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488135</v>
+        <v>488300</v>
       </c>
       <c r="R105" t="n">
-        <v>6787033</v>
+        <v>6786820</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11476,7 +11486,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122566967</v>
+        <v>122567004</v>
       </c>
       <c r="B106" t="n">
         <v>78766</v>
@@ -11516,10 +11526,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488387</v>
+        <v>488475</v>
       </c>
       <c r="R106" t="n">
-        <v>6786773</v>
+        <v>6786864</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11578,10 +11588,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122567298</v>
+        <v>122567023</v>
       </c>
       <c r="B107" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11590,43 +11600,38 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488789</v>
+        <v>488135</v>
       </c>
       <c r="R107" t="n">
-        <v>6786702</v>
+        <v>6787033</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11685,10 +11690,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122567303</v>
+        <v>122566967</v>
       </c>
       <c r="B108" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11697,43 +11702,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>488600</v>
+        <v>488387</v>
       </c>
       <c r="R108" t="n">
-        <v>6786772</v>
+        <v>6786773</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>

--- a/artfynd/A 61338-2024 artfynd.xlsx
+++ b/artfynd/A 61338-2024 artfynd.xlsx
@@ -4426,10 +4426,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567295</v>
+        <v>122566899</v>
       </c>
       <c r="B38" t="n">
-        <v>8441</v>
+        <v>57631</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4438,43 +4438,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488850</v>
+        <v>488482</v>
       </c>
       <c r="R38" t="n">
-        <v>6786668</v>
+        <v>6786720</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4533,10 +4528,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122567002</v>
+        <v>122567304</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4545,38 +4540,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488569</v>
+        <v>488591</v>
       </c>
       <c r="R39" t="n">
-        <v>6786787</v>
+        <v>6786769</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4635,10 +4635,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122566991</v>
+        <v>122567315</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4647,38 +4647,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488918</v>
+        <v>488773</v>
       </c>
       <c r="R40" t="n">
-        <v>6786607</v>
+        <v>6786561</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4737,10 +4742,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122566982</v>
+        <v>122567295</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4749,38 +4754,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488600</v>
+        <v>488850</v>
       </c>
       <c r="R41" t="n">
-        <v>6786662</v>
+        <v>6786668</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4839,7 +4849,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122566962</v>
+        <v>122567002</v>
       </c>
       <c r="B42" t="n">
         <v>78766</v>
@@ -4879,10 +4889,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488324</v>
+        <v>488569</v>
       </c>
       <c r="R42" t="n">
-        <v>6786843</v>
+        <v>6786787</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4941,10 +4951,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122566899</v>
+        <v>122566991</v>
       </c>
       <c r="B43" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4957,21 +4967,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4981,10 +4991,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488482</v>
+        <v>488918</v>
       </c>
       <c r="R43" t="n">
-        <v>6786720</v>
+        <v>6786607</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5043,10 +5053,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122567304</v>
+        <v>122566982</v>
       </c>
       <c r="B44" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5055,43 +5065,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488591</v>
+        <v>488600</v>
       </c>
       <c r="R44" t="n">
-        <v>6786769</v>
+        <v>6786662</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5150,10 +5155,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122567315</v>
+        <v>122566962</v>
       </c>
       <c r="B45" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5162,43 +5167,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488773</v>
+        <v>488324</v>
       </c>
       <c r="R45" t="n">
-        <v>6786561</v>
+        <v>6786843</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5772,10 +5772,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567017</v>
+        <v>122566907</v>
       </c>
       <c r="B51" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5788,34 +5788,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488353</v>
+        <v>488852</v>
       </c>
       <c r="R51" t="n">
-        <v>6786911</v>
+        <v>6786673</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5874,7 +5879,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122566972</v>
+        <v>122567017</v>
       </c>
       <c r="B52" t="n">
         <v>78766</v>
@@ -5914,10 +5919,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488465</v>
+        <v>488353</v>
       </c>
       <c r="R52" t="n">
-        <v>6786729</v>
+        <v>6786911</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5976,10 +5981,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567325</v>
+        <v>122566972</v>
       </c>
       <c r="B53" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5988,43 +5993,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488576</v>
+        <v>488465</v>
       </c>
       <c r="R53" t="n">
-        <v>6786782</v>
+        <v>6786729</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6185,10 +6185,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122566907</v>
+        <v>122567325</v>
       </c>
       <c r="B55" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6197,31 +6197,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488852</v>
+        <v>488576</v>
       </c>
       <c r="R55" t="n">
-        <v>6786673</v>
+        <v>6786782</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6292,10 +6292,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122566998</v>
+        <v>122567289</v>
       </c>
       <c r="B56" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6304,38 +6304,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488700</v>
+        <v>488322</v>
       </c>
       <c r="R56" t="n">
-        <v>6786744</v>
+        <v>6786810</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6394,10 +6399,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122566956</v>
+        <v>122567318</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6406,38 +6411,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488309</v>
+        <v>488883</v>
       </c>
       <c r="R57" t="n">
-        <v>6786859</v>
+        <v>6786645</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6496,10 +6506,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122567289</v>
+        <v>122566998</v>
       </c>
       <c r="B58" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6508,43 +6518,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488322</v>
+        <v>488700</v>
       </c>
       <c r="R58" t="n">
-        <v>6786810</v>
+        <v>6786744</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6603,10 +6608,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122567318</v>
+        <v>122566956</v>
       </c>
       <c r="B59" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6615,43 +6620,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488883</v>
+        <v>488309</v>
       </c>
       <c r="R59" t="n">
-        <v>6786645</v>
+        <v>6786859</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8172,10 +8172,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122567291</v>
+        <v>122566952</v>
       </c>
       <c r="B74" t="n">
-        <v>8441</v>
+        <v>80723</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8184,43 +8184,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>1049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488440</v>
+        <v>488363</v>
       </c>
       <c r="R74" t="n">
-        <v>6786759</v>
+        <v>6786907</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8279,7 +8274,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122567307</v>
+        <v>122567291</v>
       </c>
       <c r="B75" t="n">
         <v>8441</v>
@@ -8324,10 +8319,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488535</v>
+        <v>488440</v>
       </c>
       <c r="R75" t="n">
-        <v>6786843</v>
+        <v>6786759</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8386,10 +8381,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122566952</v>
+        <v>122567307</v>
       </c>
       <c r="B76" t="n">
-        <v>80723</v>
+        <v>8441</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8398,38 +8393,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1049</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488363</v>
+        <v>488535</v>
       </c>
       <c r="R76" t="n">
-        <v>6786907</v>
+        <v>6786843</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10660,10 +10660,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122567298</v>
+        <v>122566988</v>
       </c>
       <c r="B98" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10672,43 +10672,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>488789</v>
+        <v>488803</v>
       </c>
       <c r="R98" t="n">
-        <v>6786702</v>
+        <v>6786562</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10767,10 +10762,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122567303</v>
+        <v>122566978</v>
       </c>
       <c r="B99" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10779,43 +10774,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>488600</v>
+        <v>488583</v>
       </c>
       <c r="R99" t="n">
-        <v>6786772</v>
+        <v>6786679</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10874,7 +10864,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122566988</v>
+        <v>122566973</v>
       </c>
       <c r="B100" t="n">
         <v>78766</v>
@@ -10914,10 +10904,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>488803</v>
+        <v>488482</v>
       </c>
       <c r="R100" t="n">
-        <v>6786562</v>
+        <v>6786720</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10976,7 +10966,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122566978</v>
+        <v>122566999</v>
       </c>
       <c r="B101" t="n">
         <v>78766</v>
@@ -11016,10 +11006,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>488583</v>
+        <v>488686</v>
       </c>
       <c r="R101" t="n">
-        <v>6786679</v>
+        <v>6786738</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11078,7 +11068,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122566973</v>
+        <v>122566990</v>
       </c>
       <c r="B102" t="n">
         <v>78766</v>
@@ -11118,10 +11108,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>488482</v>
+        <v>488840</v>
       </c>
       <c r="R102" t="n">
-        <v>6786720</v>
+        <v>6786622</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11180,7 +11170,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122566999</v>
+        <v>122566957</v>
       </c>
       <c r="B103" t="n">
         <v>78766</v>
@@ -11220,10 +11210,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>488686</v>
+        <v>488300</v>
       </c>
       <c r="R103" t="n">
-        <v>6786738</v>
+        <v>6786820</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11282,7 +11272,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122566990</v>
+        <v>122567004</v>
       </c>
       <c r="B104" t="n">
         <v>78766</v>
@@ -11322,10 +11312,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488840</v>
+        <v>488475</v>
       </c>
       <c r="R104" t="n">
-        <v>6786622</v>
+        <v>6786864</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11384,7 +11374,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122566957</v>
+        <v>122567023</v>
       </c>
       <c r="B105" t="n">
         <v>78766</v>
@@ -11424,10 +11414,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488300</v>
+        <v>488135</v>
       </c>
       <c r="R105" t="n">
-        <v>6786820</v>
+        <v>6787033</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11486,7 +11476,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122567004</v>
+        <v>122566967</v>
       </c>
       <c r="B106" t="n">
         <v>78766</v>
@@ -11526,10 +11516,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488475</v>
+        <v>488387</v>
       </c>
       <c r="R106" t="n">
-        <v>6786864</v>
+        <v>6786773</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11588,10 +11578,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122567023</v>
+        <v>122567298</v>
       </c>
       <c r="B107" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11600,38 +11590,43 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488135</v>
+        <v>488789</v>
       </c>
       <c r="R107" t="n">
-        <v>6787033</v>
+        <v>6786702</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11690,10 +11685,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122566967</v>
+        <v>122567303</v>
       </c>
       <c r="B108" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11702,38 +11697,43 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>488387</v>
+        <v>488600</v>
       </c>
       <c r="R108" t="n">
-        <v>6786773</v>
+        <v>6786772</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11792,10 +11792,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122567026</v>
+        <v>122567018</v>
       </c>
       <c r="B109" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11808,21 +11808,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11832,10 +11832,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488539</v>
+        <v>488345</v>
       </c>
       <c r="R109" t="n">
-        <v>6786689</v>
+        <v>6786910</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11894,10 +11894,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122566965</v>
+        <v>122567026</v>
       </c>
       <c r="B110" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11910,21 +11910,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11934,10 +11934,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>488378</v>
+        <v>488539</v>
       </c>
       <c r="R110" t="n">
-        <v>6786805</v>
+        <v>6786689</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11996,7 +11996,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122567015</v>
+        <v>122566965</v>
       </c>
       <c r="B111" t="n">
         <v>78766</v>
@@ -12036,10 +12036,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>488366</v>
+        <v>488378</v>
       </c>
       <c r="R111" t="n">
-        <v>6786907</v>
+        <v>6786805</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12098,7 +12098,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122567018</v>
+        <v>122566985</v>
       </c>
       <c r="B112" t="n">
         <v>78766</v>
@@ -12138,10 +12138,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>488345</v>
+        <v>488698</v>
       </c>
       <c r="R112" t="n">
-        <v>6786910</v>
+        <v>6786584</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12200,10 +12200,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122567294</v>
+        <v>122567015</v>
       </c>
       <c r="B113" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12212,43 +12212,38 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488801</v>
+        <v>488366</v>
       </c>
       <c r="R113" t="n">
-        <v>6786563</v>
+        <v>6786907</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12307,10 +12302,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122566985</v>
+        <v>122567294</v>
       </c>
       <c r="B114" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12319,38 +12314,43 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488698</v>
+        <v>488801</v>
       </c>
       <c r="R114" t="n">
-        <v>6786584</v>
+        <v>6786563</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>

--- a/artfynd/A 61338-2024 artfynd.xlsx
+++ b/artfynd/A 61338-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122566964</v>
+        <v>122567301</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488351</v>
+        <v>488718</v>
       </c>
       <c r="R2" t="n">
-        <v>6786831</v>
+        <v>6786752</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567316</v>
+        <v>122567299</v>
       </c>
       <c r="B3" t="n">
         <v>8441</v>
@@ -813,7 +818,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488900</v>
+        <v>488786</v>
       </c>
       <c r="R3" t="n">
-        <v>6786628</v>
+        <v>6786723</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567306</v>
+        <v>122567017</v>
       </c>
       <c r="B4" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,43 +901,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488556</v>
+        <v>488353</v>
       </c>
       <c r="R4" t="n">
-        <v>6786835</v>
+        <v>6786911</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122566953</v>
+        <v>122566984</v>
       </c>
       <c r="B5" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,47 +1003,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488429</v>
+        <v>488699</v>
       </c>
       <c r="R5" t="n">
-        <v>6786896</v>
+        <v>6786596</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567327</v>
+        <v>122567000</v>
       </c>
       <c r="B6" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,43 +1105,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488442</v>
+        <v>488678</v>
       </c>
       <c r="R6" t="n">
-        <v>6786881</v>
+        <v>6786753</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566970</v>
+        <v>122566956</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1249,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488469</v>
+        <v>488309</v>
       </c>
       <c r="R7" t="n">
-        <v>6786751</v>
+        <v>6786859</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566996</v>
+        <v>122567314</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,38 +1309,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488757</v>
+        <v>488747</v>
       </c>
       <c r="R8" t="n">
-        <v>6786723</v>
+        <v>6786566</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122567032</v>
+        <v>122566911</v>
       </c>
       <c r="B9" t="n">
-        <v>5173</v>
+        <v>91235</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,43 +1416,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488901</v>
+        <v>488882</v>
       </c>
       <c r="R9" t="n">
-        <v>6786589</v>
+        <v>6786609</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122567024</v>
+        <v>122566973</v>
       </c>
       <c r="B10" t="n">
-        <v>91196</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,25 +1518,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1560,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488663</v>
+        <v>488482</v>
       </c>
       <c r="R10" t="n">
-        <v>6786615</v>
+        <v>6786720</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566890</v>
+        <v>122566980</v>
       </c>
       <c r="B11" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1638,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1662,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488572</v>
+        <v>488590</v>
       </c>
       <c r="R11" t="n">
-        <v>6786674</v>
+        <v>6786665</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1710,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567006</v>
+        <v>122566957</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1764,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488556</v>
+        <v>488300</v>
       </c>
       <c r="R12" t="n">
-        <v>6786835</v>
+        <v>6786820</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,7 +1812,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566995</v>
+        <v>122566983</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1866,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488833</v>
+        <v>488609</v>
       </c>
       <c r="R13" t="n">
-        <v>6786674</v>
+        <v>6786648</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566963</v>
+        <v>122567030</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1944,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1968,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488341</v>
+        <v>488769</v>
       </c>
       <c r="R14" t="n">
-        <v>6786832</v>
+        <v>6786552</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567319</v>
+        <v>122566908</v>
       </c>
       <c r="B15" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,31 +2028,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2075,10 +2065,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488869</v>
+        <v>488892</v>
       </c>
       <c r="R15" t="n">
-        <v>6786685</v>
+        <v>6786620</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,10 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567309</v>
+        <v>122566958</v>
       </c>
       <c r="B16" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2149,43 +2139,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488707</v>
+        <v>488301</v>
       </c>
       <c r="R16" t="n">
-        <v>6786747</v>
+        <v>6786839</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,10 +2229,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122567326</v>
+        <v>122566995</v>
       </c>
       <c r="B17" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2256,43 +2241,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488545</v>
+        <v>488833</v>
       </c>
       <c r="R17" t="n">
-        <v>6786849</v>
+        <v>6786674</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,7 +2331,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566980</v>
+        <v>122566971</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2391,10 +2371,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488590</v>
+        <v>488461</v>
       </c>
       <c r="R18" t="n">
-        <v>6786665</v>
+        <v>6786736</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,7 +2433,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566979</v>
+        <v>122566986</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2493,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488583</v>
+        <v>488714</v>
       </c>
       <c r="R19" t="n">
-        <v>6786676</v>
+        <v>6786574</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2555,7 +2535,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566959</v>
+        <v>122566967</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -2595,10 +2575,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488317</v>
+        <v>488387</v>
       </c>
       <c r="R20" t="n">
-        <v>6786858</v>
+        <v>6786773</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2657,10 +2637,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566954</v>
+        <v>122567295</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2669,38 +2649,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488416</v>
+        <v>488850</v>
       </c>
       <c r="R21" t="n">
-        <v>6786896</v>
+        <v>6786668</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2759,10 +2744,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566971</v>
+        <v>122566890</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2775,21 +2760,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2799,10 +2784,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488461</v>
+        <v>488572</v>
       </c>
       <c r="R22" t="n">
-        <v>6786736</v>
+        <v>6786674</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2861,10 +2846,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566986</v>
+        <v>122567297</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2873,38 +2858,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488714</v>
+        <v>488804</v>
       </c>
       <c r="R23" t="n">
-        <v>6786574</v>
+        <v>6786700</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2963,10 +2953,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567003</v>
+        <v>122567292</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2975,38 +2965,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ljothed, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488550</v>
+        <v>488533</v>
       </c>
       <c r="R24" t="n">
-        <v>6786822</v>
+        <v>6786690</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3065,10 +3060,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122567290</v>
+        <v>122567009</v>
       </c>
       <c r="B25" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3077,43 +3072,38 @@
       <